--- a/exports/xlsx/organization-series-registry.xlsx
+++ b/exports/xlsx/organization-series-registry.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organizations" sheetId="1" r:id="R20fa1824b14b46f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series" sheetId="2" r:id="R05d447bfc21c45ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Registry" sheetId="3" r:id="R1562ff774747439f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External ID Mapping" sheetId="4" r:id="R622324e95d874d70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidates" sheetId="5" r:id="R1f93e3450d3d494d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="6" r:id="R009903ff004d4d5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organizations" sheetId="1" r:id="R5b1190adcd144830"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series" sheetId="2" r:id="Rc4feb7f212ae44e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Registry" sheetId="3" r:id="R90d85e1e511344c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External ID Mapping" sheetId="4" r:id="R7bc47783a0244882"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidates" sheetId="5" r:id="Re5a0a0947123480b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="6" r:id="Rc01bad8c81a640f5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -39,7 +39,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF1F4E78"/>
+        <x:fgColor rgb="FF243447"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -50,7 +50,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="22">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -87,74 +87,11 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
-    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
-<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
-  <xfpb:bag type="Checkbox"/>
-  <xfpb:bag type="XFControls">
-    <xfpb:bagId k="CellControl">0</xfpb:bagId>
-  </xfpb:bag>
-  <xfpb:bag type="XFComplement">
-    <xfpb:bagId k="XFControls">1</xfpb:bagId>
-  </xfpb:bag>
-  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
-    <xfpb:a k="MappedFeaturePropertyBags">
-      <xfpb:bagId>2</xfpb:bagId>
-    </xfpb:a>
-  </xfpb:bag>
-</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -352,16 +289,16 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="42" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="48" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -372,153 +309,1239 @@
         <x:v>Kind</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>Name JA</x:v>
+        <x:v>日本語</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>Name ZH</x:v>
+        <x:v>简体中文</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>Name EN</x:v>
+        <x:v>English</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
-        <x:v>Parent Organization</x:v>
+        <x:v>日文别名</x:v>
       </x:c>
       <x:c r="G1" s="6" t="str">
+        <x:v>Parent</x:v>
+      </x:c>
+      <x:c r="H1" s="6" t="str">
         <x:v>Status</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="str">
-        <x:v>Official Website</x:v>
-      </x:c>
       <x:c r="I1" s="6" t="str">
+        <x:v>Official URL</x:v>
+      </x:c>
+      <x:c r="J1" s="6" t="str">
         <x:v>External IDs</x:v>
-      </x:c>
-      <x:c r="J1" s="6" t="str">
-        <x:v>First Published</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="14" t="str">
-        <x:v>maker_000001</x:v>
+        <x:v>label_000001</x:v>
       </x:c>
       <x:c r="B2" s="14" t="str">
-        <x:v>maker</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C2" s="14" t="str">
-        <x:v>アイデアポケット</x:v>
+        <x:v>MOODYZ DIVA</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str"/>
       <x:c r="E2" s="14" t="str"/>
       <x:c r="F2" s="14" t="str"/>
-      <x:c r="G2" s="14" t="str"/>
-      <x:c r="H2" s="14" t="str"/>
-      <x:c r="I2" s="14" t="str"/>
+      <x:c r="G2" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H2" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I2" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5048</x:v>
+      </x:c>
       <x:c r="J2" s="14" t="str">
-        <x:v>0.3.0</x:v>
+        <x:v>moodyz.label:5048</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="14" t="str">
-        <x:v>maker_000002</x:v>
+        <x:v>label_000002</x:v>
       </x:c>
       <x:c r="B3" s="14" t="str">
-        <x:v>maker</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C3" s="14" t="str">
-        <x:v>MOODYZ</x:v>
+        <x:v>みんなのキカタン</x:v>
       </x:c>
       <x:c r="D3" s="14" t="str"/>
       <x:c r="E3" s="14" t="str"/>
       <x:c r="F3" s="14" t="str"/>
-      <x:c r="G3" s="14" t="str"/>
-      <x:c r="H3" s="14" t="str"/>
-      <x:c r="I3" s="14" t="str"/>
+      <x:c r="G3" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I3" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/12798</x:v>
+      </x:c>
       <x:c r="J3" s="14" t="str">
-        <x:v>0.3.0</x:v>
+        <x:v>moodyz.label:12798</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="14" t="str">
-        <x:v>maker_000003</x:v>
+        <x:v>label_000003</x:v>
       </x:c>
       <x:c r="B4" s="14" t="str">
-        <x:v>maker</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C4" s="14" t="str">
-        <x:v>エスワン</x:v>
-      </x:c>
-      <x:c r="D4" s="14" t="str"/>
+        <x:v>死夜悪</x:v>
+      </x:c>
+      <x:c r="D4" s="14" t="str">
+        <x:v>死夜恶</x:v>
+      </x:c>
       <x:c r="E4" s="14" t="str"/>
       <x:c r="F4" s="14" t="str"/>
-      <x:c r="G4" s="14" t="str"/>
-      <x:c r="H4" s="14" t="str"/>
-      <x:c r="I4" s="14" t="str"/>
+      <x:c r="G4" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H4" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I4" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/2754</x:v>
+      </x:c>
       <x:c r="J4" s="14" t="str">
-        <x:v>0.3.0</x:v>
+        <x:v>attackers.label:2754</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14" t="str">
-        <x:v>label_000001</x:v>
+        <x:v>label_000004</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
-        <x:v>MOODYZ DIVA</x:v>
+        <x:v>龍縛</x:v>
       </x:c>
       <x:c r="D5" s="14" t="str">
-        <x:v>MOODYZ DIVA</x:v>
-      </x:c>
-      <x:c r="E5" s="14" t="str">
-        <x:v>MOODYZ DIVA</x:v>
-      </x:c>
-      <x:c r="F5" s="14" t="str">
-        <x:v>maker_000002</x:v>
-      </x:c>
+        <x:v>龙缚</x:v>
+      </x:c>
+      <x:c r="E5" s="14" t="str"/>
+      <x:c r="F5" s="14" t="str"/>
       <x:c r="G5" s="14" t="str">
-        <x:v>unknown</x:v>
+        <x:v>maker_000004</x:v>
       </x:c>
       <x:c r="H5" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5048</x:v>
+        <x:v>unknown</x:v>
       </x:c>
       <x:c r="I5" s="14" t="str">
-        <x:v>moodyz.label:5048</x:v>
+        <x:v>https://attackers.net/works/list/label/2751</x:v>
       </x:c>
       <x:c r="J5" s="14" t="str">
-        <x:v>0.4.0</x:v>
+        <x:v>attackers.label:2751</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="14" t="str">
-        <x:v>label_000002</x:v>
+        <x:v>label_000005</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C6" s="14" t="str">
-        <x:v>みんなのキカタン</x:v>
+        <x:v>大人のドラマ</x:v>
       </x:c>
       <x:c r="D6" s="14" t="str">
-        <x:v>大家的企画单体</x:v>
+        <x:v>成人剧情</x:v>
       </x:c>
       <x:c r="E6" s="14" t="str">
-        <x:v>Minna no Kikatan</x:v>
-      </x:c>
-      <x:c r="F6" s="14" t="str">
+        <x:v>Adult Drama</x:v>
+      </x:c>
+      <x:c r="F6" s="14" t="str"/>
+      <x:c r="G6" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H6" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I6" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/9455</x:v>
+      </x:c>
+      <x:c r="J6" s="14" t="str">
+        <x:v>attackers.label:9455</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="14" t="str">
+        <x:v>label_000006</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="str">
+        <x:v>淫魔</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="str">
+        <x:v>淫魔</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="str"/>
+      <x:c r="F7" s="14" t="str"/>
+      <x:c r="G7" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H7" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I7" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/2737</x:v>
+      </x:c>
+      <x:c r="J7" s="14" t="str">
+        <x:v>attackers.label:2737</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="14" t="str">
+        <x:v>label_000007</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="str">
+        <x:v>Attackers</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="str">
+        <x:v>Attackers</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="str">
+        <x:v>Attackers</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="str"/>
+      <x:c r="G8" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H8" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I8" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/2739</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="str">
+        <x:v>attackers.label:2739</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="14" t="str">
+        <x:v>label_000008</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="str">
+        <x:v>蛇縛</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="str">
+        <x:v>蛇缚</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="str"/>
+      <x:c r="F9" s="14" t="str"/>
+      <x:c r="G9" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H9" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I9" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/2749</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="str">
+        <x:v>attackers.label:2749</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="14" t="str">
+        <x:v>label_000009</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="str">
+        <x:v>アタッカーズ・アンソロジー</x:v>
+      </x:c>
+      <x:c r="D10" s="14" t="str">
+        <x:v>ATTACKERS Anthology</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="str">
+        <x:v>ATTACKERS Anthology</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="str"/>
+      <x:c r="G10" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H10" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I10" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/2735</x:v>
+      </x:c>
+      <x:c r="J10" s="14" t="str">
+        <x:v>attackers.label:2735</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="14" t="str">
+        <x:v>label_000010</x:v>
+      </x:c>
+      <x:c r="B11" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="str">
+        <x:v>SUPER SPECIAL</x:v>
+      </x:c>
+      <x:c r="D11" s="14" t="str">
+        <x:v>SUPER SPECIAL</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="str">
+        <x:v>SUPER SPECIAL</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="str"/>
+      <x:c r="G11" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H11" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I11" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/2756</x:v>
+      </x:c>
+      <x:c r="J11" s="14" t="str">
+        <x:v>attackers.label:2756</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="14" t="str">
+        <x:v>label_000011</x:v>
+      </x:c>
+      <x:c r="B12" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="str">
+        <x:v>誘女</x:v>
+      </x:c>
+      <x:c r="D12" s="14" t="str">
+        <x:v>诱女</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="str"/>
+      <x:c r="F12" s="14" t="str"/>
+      <x:c r="G12" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H12" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I12" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/12605</x:v>
+      </x:c>
+      <x:c r="J12" s="14" t="str">
+        <x:v>attackers.label:12605</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="14" t="str">
+        <x:v>label_000012</x:v>
+      </x:c>
+      <x:c r="B13" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="str">
+        <x:v>アタッカーズVR</x:v>
+      </x:c>
+      <x:c r="D13" s="14" t="str">
+        <x:v>ATTACKERS VR</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="str">
+        <x:v>ATTACKERS VR</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="str">
+        <x:v>ATTACKERS VR</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H13" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I13" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/81348</x:v>
+      </x:c>
+      <x:c r="J13" s="14" t="str">
+        <x:v>attackers.label:81348</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="14" t="str">
+        <x:v>label_000013</x:v>
+      </x:c>
+      <x:c r="B14" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="str">
+        <x:v>アタックゾーン</x:v>
+      </x:c>
+      <x:c r="D14" s="14" t="str">
+        <x:v>Attack Zone</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="str">
+        <x:v>Attack Zone</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="str">
+        <x:v>ATTACK ZONE</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H14" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I14" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/5245</x:v>
+      </x:c>
+      <x:c r="J14" s="14" t="str">
+        <x:v>attackers.label:5245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="14" t="str">
+        <x:v>label_000014</x:v>
+      </x:c>
+      <x:c r="B15" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="str">
+        <x:v>春のパンツまつり</x:v>
+      </x:c>
+      <x:c r="D15" s="14" t="str">
+        <x:v>春季内裤祭</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="str">
+        <x:v>Spring Panties Festival</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="str"/>
+      <x:c r="G15" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H15" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I15" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/85265</x:v>
+      </x:c>
+      <x:c r="J15" s="14" t="str">
+        <x:v>attackers.label:85265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="14" t="str">
+        <x:v>label_000015</x:v>
+      </x:c>
+      <x:c r="B16" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="str">
+        <x:v>AVOPEN</x:v>
+      </x:c>
+      <x:c r="D16" s="14" t="str">
+        <x:v>AVOPEN</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="str">
+        <x:v>AVOPEN</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="str"/>
+      <x:c r="G16" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H16" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I16" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/9483</x:v>
+      </x:c>
+      <x:c r="J16" s="14" t="str">
+        <x:v>attackers.label:9483</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="14" t="str">
+        <x:v>label_000016</x:v>
+      </x:c>
+      <x:c r="B17" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="str">
+        <x:v>AVグランプリ</x:v>
+      </x:c>
+      <x:c r="D17" s="14" t="str">
+        <x:v>AV大奖赛</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="str">
+        <x:v>AV Grand Prix</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="str">
+        <x:v>AV Grand Prix</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H17" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I17" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/10077</x:v>
+      </x:c>
+      <x:c r="J17" s="14" t="str">
+        <x:v>attackers.label:10077</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="14" t="str">
+        <x:v>label_000017</x:v>
+      </x:c>
+      <x:c r="B18" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="str">
+        <x:v>おっぱい祭り</x:v>
+      </x:c>
+      <x:c r="D18" s="14" t="str">
+        <x:v>Oppai祭</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="str">
+        <x:v>Oppai Festival</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="str"/>
+      <x:c r="G18" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H18" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I18" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/10142</x:v>
+      </x:c>
+      <x:c r="J18" s="14" t="str">
+        <x:v>attackers.label:10142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="14" t="str">
+        <x:v>label_000018</x:v>
+      </x:c>
+      <x:c r="B19" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="str">
+        <x:v>秋のシコシコ強化月間</x:v>
+      </x:c>
+      <x:c r="D19" s="14" t="str">
+        <x:v>秋季强化月</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="str"/>
+      <x:c r="F19" s="14" t="str"/>
+      <x:c r="G19" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H19" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I19" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/10144</x:v>
+      </x:c>
+      <x:c r="J19" s="14" t="str">
+        <x:v>attackers.label:10144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="14" t="str">
+        <x:v>label_000019</x:v>
+      </x:c>
+      <x:c r="B20" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="str">
+        <x:v>背徳ビチョビチョ！NTR大放出</x:v>
+      </x:c>
+      <x:c r="D20" s="14" t="str">
+        <x:v>背德湿透！NTR大放送</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="str"/>
+      <x:c r="F20" s="14" t="str"/>
+      <x:c r="G20" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H20" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I20" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/10151</x:v>
+      </x:c>
+      <x:c r="J20" s="14" t="str">
+        <x:v>attackers.label:10151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="14" t="str">
+        <x:v>label_000020</x:v>
+      </x:c>
+      <x:c r="B21" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="str">
+        <x:v>Madonna</x:v>
+      </x:c>
+      <x:c r="D21" s="14" t="str">
+        <x:v>Madonna</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="str">
+        <x:v>Madonna</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="str"/>
+      <x:c r="G21" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H21" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I21" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/3669</x:v>
+      </x:c>
+      <x:c r="J21" s="14" t="str">
+        <x:v>madonna.label:3669</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="14" t="str">
+        <x:v>label_000021</x:v>
+      </x:c>
+      <x:c r="B22" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="str">
+        <x:v>MONROE</x:v>
+      </x:c>
+      <x:c r="D22" s="14" t="str">
+        <x:v>MONROE</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="str">
+        <x:v>MONROE</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="str"/>
+      <x:c r="G22" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H22" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I22" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/12490</x:v>
+      </x:c>
+      <x:c r="J22" s="14" t="str">
+        <x:v>madonna.label:12490</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="14" t="str">
+        <x:v>label_000022</x:v>
+      </x:c>
+      <x:c r="B23" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="str">
+        <x:v>Obasan</x:v>
+      </x:c>
+      <x:c r="D23" s="14" t="str">
+        <x:v>Obasan</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="str">
+        <x:v>Obasan</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="str"/>
+      <x:c r="G23" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H23" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I23" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/9387</x:v>
+      </x:c>
+      <x:c r="J23" s="14" t="str">
+        <x:v>madonna.label:9387</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="14" t="str">
+        <x:v>label_000023</x:v>
+      </x:c>
+      <x:c r="B24" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="str">
+        <x:v>MadonnaVR</x:v>
+      </x:c>
+      <x:c r="D24" s="14" t="str">
+        <x:v>Madonna VR</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="str">
+        <x:v>Madonna VR</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="str">
+        <x:v>Madonna VR</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H24" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I24" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/9789</x:v>
+      </x:c>
+      <x:c r="J24" s="14" t="str">
+        <x:v>madonna.label:9789</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="14" t="str">
+        <x:v>label_000024</x:v>
+      </x:c>
+      <x:c r="B25" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="str">
+        <x:v>Fitch</x:v>
+      </x:c>
+      <x:c r="D25" s="14" t="str">
+        <x:v>Fitch</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="str">
+        <x:v>Fitch</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="str"/>
+      <x:c r="G25" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H25" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I25" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/7354</x:v>
+      </x:c>
+      <x:c r="J25" s="14" t="str">
+        <x:v>madonna.label:7354</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="14" t="str">
+        <x:v>label_000025</x:v>
+      </x:c>
+      <x:c r="B26" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="str">
+        <x:v>熟れコミ</x:v>
+      </x:c>
+      <x:c r="D26" s="14" t="str">
+        <x:v>熟れコミ</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="str"/>
+      <x:c r="F26" s="14" t="str"/>
+      <x:c r="G26" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H26" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I26" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/9419</x:v>
+      </x:c>
+      <x:c r="J26" s="14" t="str">
+        <x:v>madonna.label:9419</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="14" t="str">
+        <x:v>label_000026</x:v>
+      </x:c>
+      <x:c r="B27" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="str">
+        <x:v>ACHIJO(アチージョ)</x:v>
+      </x:c>
+      <x:c r="D27" s="14" t="str">
+        <x:v>ACHIJO(アチージョ)</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="str">
+        <x:v>ACHIJO</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="str">
+        <x:v>ACHIJO</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H27" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I27" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/12603</x:v>
+      </x:c>
+      <x:c r="J27" s="14" t="str">
+        <x:v>madonna.label:12603</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="14" t="str">
+        <x:v>label_000027</x:v>
+      </x:c>
+      <x:c r="B28" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="str">
+        <x:v>MADOOOON!!!!</x:v>
+      </x:c>
+      <x:c r="D28" s="14" t="str">
+        <x:v>MADOOOON!!!!</x:v>
+      </x:c>
+      <x:c r="E28" s="14" t="str">
+        <x:v>MADOOOON!!!!</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="str"/>
+      <x:c r="G28" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H28" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I28" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/12502</x:v>
+      </x:c>
+      <x:c r="J28" s="14" t="str">
+        <x:v>madonna.label:12502</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="14" t="str">
+        <x:v>label_000028</x:v>
+      </x:c>
+      <x:c r="B29" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="str">
+        <x:v>Re:Madonna/AIリマスター</x:v>
+      </x:c>
+      <x:c r="D29" s="14" t="str">
+        <x:v>Re:Madonna/AI重制</x:v>
+      </x:c>
+      <x:c r="E29" s="14" t="str">
+        <x:v>Re:Madonna/AI Remaster</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="str"/>
+      <x:c r="G29" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H29" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I29" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/10130</x:v>
+      </x:c>
+      <x:c r="J29" s="14" t="str">
+        <x:v>madonna.label:10130</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="14" t="str">
+        <x:v>label_000029</x:v>
+      </x:c>
+      <x:c r="B30" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C30" s="14" t="str">
+        <x:v>Fitch　BEST</x:v>
+      </x:c>
+      <x:c r="D30" s="14" t="str">
+        <x:v>Fitch BEST</x:v>
+      </x:c>
+      <x:c r="E30" s="14" t="str">
+        <x:v>Fitch BEST</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="str">
+        <x:v>Fitch BEST</x:v>
+      </x:c>
+      <x:c r="G30" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H30" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I30" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/7993</x:v>
+      </x:c>
+      <x:c r="J30" s="14" t="str">
+        <x:v>madonna.label:7993</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="14" t="str">
+        <x:v>label_000030</x:v>
+      </x:c>
+      <x:c r="B31" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C31" s="14" t="str">
+        <x:v>性録ch</x:v>
+      </x:c>
+      <x:c r="D31" s="14" t="str">
+        <x:v>性录ch</x:v>
+      </x:c>
+      <x:c r="E31" s="14" t="str"/>
+      <x:c r="F31" s="14" t="str"/>
+      <x:c r="G31" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H31" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I31" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/10159</x:v>
+      </x:c>
+      <x:c r="J31" s="14" t="str">
+        <x:v>madonna.label:10159</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="14" t="str">
+        <x:v>label_000031</x:v>
+      </x:c>
+      <x:c r="B32" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C32" s="14" t="str">
+        <x:v>※スマホ推奨タテ動画※マドーンショート</x:v>
+      </x:c>
+      <x:c r="D32" s="14" t="str">
+        <x:v>※推荐手机观看竖屏视频※Madonna Short</x:v>
+      </x:c>
+      <x:c r="E32" s="14" t="str">
+        <x:v>Mobile Recommended Vertical Video: Madonna Short</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="str">
+        <x:v>マドーンショート</x:v>
+      </x:c>
+      <x:c r="G32" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H32" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I32" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/10119</x:v>
+      </x:c>
+      <x:c r="J32" s="14" t="str">
+        <x:v>madonna.label:10119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="14" t="str">
+        <x:v>label_000032</x:v>
+      </x:c>
+      <x:c r="B33" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C33" s="14" t="str">
+        <x:v>春のパンツまつり</x:v>
+      </x:c>
+      <x:c r="D33" s="14" t="str">
+        <x:v>春季内裤祭</x:v>
+      </x:c>
+      <x:c r="E33" s="14" t="str">
+        <x:v>Spring Panties Festival</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="str"/>
+      <x:c r="G33" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H33" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I33" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/85265</x:v>
+      </x:c>
+      <x:c r="J33" s="14" t="str">
+        <x:v>madonna.label:85265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="14" t="str">
+        <x:v>label_000033</x:v>
+      </x:c>
+      <x:c r="B34" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C34" s="14" t="str">
+        <x:v>AVOPEN</x:v>
+      </x:c>
+      <x:c r="D34" s="14" t="str">
+        <x:v>AVOPEN</x:v>
+      </x:c>
+      <x:c r="E34" s="14" t="str">
+        <x:v>AVOPEN</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="str"/>
+      <x:c r="G34" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H34" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I34" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/9483</x:v>
+      </x:c>
+      <x:c r="J34" s="14" t="str">
+        <x:v>madonna.label:9483</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="14" t="str">
+        <x:v>label_000034</x:v>
+      </x:c>
+      <x:c r="B35" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C35" s="14" t="str">
+        <x:v>おっぱい祭り</x:v>
+      </x:c>
+      <x:c r="D35" s="14" t="str">
+        <x:v>Oppai祭</x:v>
+      </x:c>
+      <x:c r="E35" s="14" t="str">
+        <x:v>Oppai Festival</x:v>
+      </x:c>
+      <x:c r="F35" s="14" t="str"/>
+      <x:c r="G35" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H35" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I35" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/10142</x:v>
+      </x:c>
+      <x:c r="J35" s="14" t="str">
+        <x:v>madonna.label:10142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="14" t="str">
+        <x:v>label_000035</x:v>
+      </x:c>
+      <x:c r="B36" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C36" s="14" t="str">
+        <x:v>AVグランプリ</x:v>
+      </x:c>
+      <x:c r="D36" s="14" t="str">
+        <x:v>AV大奖赛</x:v>
+      </x:c>
+      <x:c r="E36" s="14" t="str">
+        <x:v>AV Grand Prix</x:v>
+      </x:c>
+      <x:c r="F36" s="14" t="str">
+        <x:v>AV Grand Prix</x:v>
+      </x:c>
+      <x:c r="G36" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H36" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I36" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/10077</x:v>
+      </x:c>
+      <x:c r="J36" s="14" t="str">
+        <x:v>madonna.label:10077</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="14" t="str">
+        <x:v>label_000036</x:v>
+      </x:c>
+      <x:c r="B37" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C37" s="14" t="str">
+        <x:v>背徳ビチョビチョ！NTR大放出</x:v>
+      </x:c>
+      <x:c r="D37" s="14" t="str">
+        <x:v>背德湿透！NTR大放送</x:v>
+      </x:c>
+      <x:c r="E37" s="14" t="str"/>
+      <x:c r="F37" s="14" t="str"/>
+      <x:c r="G37" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H37" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I37" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/10151</x:v>
+      </x:c>
+      <x:c r="J37" s="14" t="str">
+        <x:v>madonna.label:10151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="14" t="str">
+        <x:v>label_000037</x:v>
+      </x:c>
+      <x:c r="B38" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C38" s="14" t="str">
+        <x:v>bizarre　amaturs</x:v>
+      </x:c>
+      <x:c r="D38" s="14" t="str">
+        <x:v>bizarre amaturs</x:v>
+      </x:c>
+      <x:c r="E38" s="14" t="str">
+        <x:v>bizarre amaturs</x:v>
+      </x:c>
+      <x:c r="F38" s="14" t="str">
+        <x:v>bizarre amaturs</x:v>
+      </x:c>
+      <x:c r="G38" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H38" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I38" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/3125</x:v>
+      </x:c>
+      <x:c r="J38" s="14" t="str">
+        <x:v>madonna.label:3125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="14" t="str">
+        <x:v>maker_000001</x:v>
+      </x:c>
+      <x:c r="B39" s="14" t="str">
+        <x:v>maker</x:v>
+      </x:c>
+      <x:c r="C39" s="14" t="str">
+        <x:v>アイデアポケット</x:v>
+      </x:c>
+      <x:c r="D39" s="14" t="str"/>
+      <x:c r="E39" s="14" t="str"/>
+      <x:c r="F39" s="14" t="str"/>
+      <x:c r="G39" s="14" t="str"/>
+      <x:c r="H39" s="14" t="str"/>
+      <x:c r="I39" s="14" t="str"/>
+      <x:c r="J39" s="14" t="str"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="14" t="str">
         <x:v>maker_000002</x:v>
       </x:c>
-      <x:c r="G6" s="14" t="str">
-        <x:v>unknown</x:v>
-      </x:c>
-      <x:c r="H6" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/12798</x:v>
-      </x:c>
-      <x:c r="I6" s="14" t="str">
-        <x:v>moodyz.label:12798</x:v>
-      </x:c>
-      <x:c r="J6" s="14" t="str">
-        <x:v>0.4.0</x:v>
-      </x:c>
+      <x:c r="B40" s="14" t="str">
+        <x:v>maker</x:v>
+      </x:c>
+      <x:c r="C40" s="14" t="str">
+        <x:v>MOODYZ</x:v>
+      </x:c>
+      <x:c r="D40" s="14" t="str"/>
+      <x:c r="E40" s="14" t="str"/>
+      <x:c r="F40" s="14" t="str"/>
+      <x:c r="G40" s="14" t="str"/>
+      <x:c r="H40" s="14" t="str"/>
+      <x:c r="I40" s="14" t="str"/>
+      <x:c r="J40" s="14" t="str"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="14" t="str">
+        <x:v>maker_000003</x:v>
+      </x:c>
+      <x:c r="B41" s="14" t="str">
+        <x:v>maker</x:v>
+      </x:c>
+      <x:c r="C41" s="14" t="str">
+        <x:v>エスワン</x:v>
+      </x:c>
+      <x:c r="D41" s="14" t="str"/>
+      <x:c r="E41" s="14" t="str"/>
+      <x:c r="F41" s="14" t="str"/>
+      <x:c r="G41" s="14" t="str"/>
+      <x:c r="H41" s="14" t="str"/>
+      <x:c r="I41" s="14" t="str"/>
+      <x:c r="J41" s="14" t="str"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="B42" s="14" t="str">
+        <x:v>maker</x:v>
+      </x:c>
+      <x:c r="C42" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="D42" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="E42" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="F42" s="14" t="str">
+        <x:v>アタッカーズ</x:v>
+      </x:c>
+      <x:c r="G42" s="14" t="str"/>
+      <x:c r="H42" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I42" s="14" t="str">
+        <x:v>https://attackers.net/</x:v>
+      </x:c>
+      <x:c r="J42" s="14" t="str"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="B43" s="14" t="str">
+        <x:v>maker</x:v>
+      </x:c>
+      <x:c r="C43" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="D43" s="14" t="str">
+        <x:v>Madonna</x:v>
+      </x:c>
+      <x:c r="E43" s="14" t="str">
+        <x:v>Madonna</x:v>
+      </x:c>
+      <x:c r="F43" s="14" t="str">
+        <x:v>Madonna</x:v>
+      </x:c>
+      <x:c r="G43" s="14" t="str"/>
+      <x:c r="H43" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I43" s="14" t="str">
+        <x:v>https://madonna-av.com/</x:v>
+      </x:c>
+      <x:c r="J43" s="14" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -529,16 +1552,16 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="36" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="44" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="44" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="50" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -546,31 +1569,31 @@
         <x:v>ID</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>Name JA</x:v>
+        <x:v>日本語</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>Name ZH</x:v>
+        <x:v>简体中文</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>Name EN</x:v>
+        <x:v>English</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
         <x:v>Maker ID</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
+        <x:v>Maker</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
         <x:v>Label ID</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="str">
+      <x:c r="H1" s="6" t="str">
         <x:v>Status</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="str">
-        <x:v>Official Website</x:v>
-      </x:c>
       <x:c r="I1" s="6" t="str">
+        <x:v>Official URL</x:v>
+      </x:c>
+      <x:c r="J1" s="6" t="str">
         <x:v>External IDs</x:v>
-      </x:c>
-      <x:c r="J1" s="6" t="str">
-        <x:v>First Published</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -589,18 +1612,18 @@
       <x:c r="E2" s="14" t="str">
         <x:v>maker_000003</x:v>
       </x:c>
-      <x:c r="F2" s="14" t="str"/>
-      <x:c r="G2" s="14" t="str">
-        <x:v>unknown</x:v>
-      </x:c>
+      <x:c r="F2" s="14" t="str">
+        <x:v>エスワン</x:v>
+      </x:c>
+      <x:c r="G2" s="14" t="str"/>
       <x:c r="H2" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I2" s="14" t="str">
         <x:v>https://s1s1s1.com/works/list/series/414</x:v>
       </x:c>
-      <x:c r="I2" s="14" t="str">
+      <x:c r="J2" s="14" t="str">
         <x:v>s1.series:414</x:v>
-      </x:c>
-      <x:c r="J2" s="14" t="str">
-        <x:v>0.4.0</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -619,18 +1642,18 @@
       <x:c r="E3" s="14" t="str">
         <x:v>maker_000002</x:v>
       </x:c>
-      <x:c r="F3" s="14" t="str"/>
-      <x:c r="G3" s="14" t="str">
-        <x:v>unknown</x:v>
-      </x:c>
+      <x:c r="F3" s="14" t="str">
+        <x:v>MOODYZ</x:v>
+      </x:c>
+      <x:c r="G3" s="14" t="str"/>
       <x:c r="H3" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I3" s="14" t="str">
         <x:v>https://moodyz.com/works/list/series/5427</x:v>
       </x:c>
-      <x:c r="I3" s="14" t="str">
+      <x:c r="J3" s="14" t="str">
         <x:v>moodyz.series:5427</x:v>
-      </x:c>
-      <x:c r="J3" s="14" t="str">
-        <x:v>0.4.0</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -649,18 +1672,18 @@
       <x:c r="E4" s="14" t="str">
         <x:v>maker_000001</x:v>
       </x:c>
-      <x:c r="F4" s="14" t="str"/>
-      <x:c r="G4" s="14" t="str">
-        <x:v>unknown</x:v>
-      </x:c>
+      <x:c r="F4" s="14" t="str">
+        <x:v>アイデアポケット</x:v>
+      </x:c>
+      <x:c r="G4" s="14" t="str"/>
       <x:c r="H4" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I4" s="14" t="str">
         <x:v>https://ideapocket.com/works/list/series/863</x:v>
       </x:c>
-      <x:c r="I4" s="14" t="str">
+      <x:c r="J4" s="14" t="str">
         <x:v>ideapocket.series:863</x:v>
-      </x:c>
-      <x:c r="J4" s="14" t="str">
-        <x:v>0.4.0</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -679,18 +1702,18 @@
       <x:c r="E5" s="14" t="str">
         <x:v>maker_000001</x:v>
       </x:c>
-      <x:c r="F5" s="14" t="str"/>
-      <x:c r="G5" s="14" t="str">
-        <x:v>unknown</x:v>
-      </x:c>
+      <x:c r="F5" s="14" t="str">
+        <x:v>アイデアポケット</x:v>
+      </x:c>
+      <x:c r="G5" s="14" t="str"/>
       <x:c r="H5" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I5" s="14" t="str">
         <x:v>https://ideapocket.com/works/list/series/1011</x:v>
       </x:c>
-      <x:c r="I5" s="14" t="str">
+      <x:c r="J5" s="14" t="str">
         <x:v>ideapocket.series:1011</x:v>
-      </x:c>
-      <x:c r="J5" s="14" t="str">
-        <x:v>0.4.0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -702,16 +1725,16 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="44" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="56" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="60" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="54" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="70" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -719,31 +1742,31 @@
         <x:v>Source ID</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>Name</x:v>
+        <x:v>名称</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>Type</x:v>
+        <x:v>类型</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
         <x:v>Base URL</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>Entity Types</x:v>
+        <x:v>可枚举实体</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
-        <x:v>Access</x:v>
+        <x:v>访问状态</x:v>
       </x:c>
       <x:c r="G1" s="6" t="str">
-        <x:v>Last Checked</x:v>
+        <x:v>最后检查</x:v>
       </x:c>
       <x:c r="H1" s="6" t="str">
-        <x:v>Complete Traversal</x:v>
+        <x:v>完整遍历</x:v>
       </x:c>
       <x:c r="I1" s="6" t="str">
-        <x:v>Coverage</x:v>
+        <x:v>覆盖统计</x:v>
       </x:c>
       <x:c r="J1" s="6" t="str">
-        <x:v>Known Limitations</x:v>
+        <x:v>已知限制</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -768,11 +1791,11 @@
       <x:c r="G2" s="14" t="str">
         <x:v>2026-09-04</x:v>
       </x:c>
-      <x:c r="H2" s="20" t="b">
-        <x:v>0</x:v>
+      <x:c r="H2" s="14" t="str">
+        <x:v>no</x:v>
       </x:c>
       <x:c r="I2" s="14" t="str">
-        <x:v>series: discovered=2, reviewed=2, published=2, conflicts=0, unrecognized=0</x:v>
+        <x:v>series: 2/2 published</x:v>
       </x:c>
       <x:c r="J2" s="14" t="str">
         <x:v>本批次只验证高复用 Series 样本，没有遍历整个 Series 索引和所有分页。</x:v>
@@ -800,11 +1823,11 @@
       <x:c r="G3" s="14" t="str">
         <x:v>2026-09-04</x:v>
       </x:c>
-      <x:c r="H3" s="20" t="b">
-        <x:v>0</x:v>
+      <x:c r="H3" s="14" t="str">
+        <x:v>no</x:v>
       </x:c>
       <x:c r="I3" s="14" t="str">
-        <x:v>label: discovered=2, reviewed=2, published=2, conflicts=0, unrecognized=0; series: discovered=1, reviewed=1, published=1, conflicts=0, unrecognized=0</x:v>
+        <x:v>label: 2/2 published; series: 1/1 published</x:v>
       </x:c>
       <x:c r="J3" s="14" t="str">
         <x:v>尚未完整枚举全部 Label 和 Series，因此不能声明 MOODYZ 当前公开目录已覆盖。</x:v>
@@ -832,11 +1855,11 @@
       <x:c r="G4" s="14" t="str">
         <x:v>2026-09-04</x:v>
       </x:c>
-      <x:c r="H4" s="20" t="b">
-        <x:v>0</x:v>
+      <x:c r="H4" s="14" t="str">
+        <x:v>no</x:v>
       </x:c>
       <x:c r="I4" s="14" t="str">
-        <x:v>series: discovered=1, reviewed=1, published=1, conflicts=0, unrecognized=0</x:v>
+        <x:v>series: 1/1 published</x:v>
       </x:c>
       <x:c r="J4" s="14" t="str">
         <x:v>新人NO.1STYLE 页面本身存在多页作品，但本批次目标是确认 Series 实体，不等价于完整枚举 S1 全部 Series。</x:v>
@@ -864,14 +1887,78 @@
       <x:c r="G5" s="14" t="str">
         <x:v>2026-09-04</x:v>
       </x:c>
-      <x:c r="H5" s="20" t="b">
-        <x:v>1</x:v>
+      <x:c r="H5" s="14" t="str">
+        <x:v>yes</x:v>
       </x:c>
       <x:c r="I5" s="14" t="str">
-        <x:v>company: discovered=1, reviewed=1, published=0, conflicts=0, unrecognized=0</x:v>
+        <x:v>company: 0/1 published</x:v>
       </x:c>
       <x:c r="J5" s="14" t="str">
         <x:v>Localogue 当前正式 OrganizationKind 尚未把 company 作为一等消费类型，因此先进入 Staging，不伪装成 Maker。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="14" t="str">
+        <x:v>source_attackers_official</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="str">
+        <x:v>ATTACKERS 官方 Maker / Label 目录</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="str">
+        <x:v>https://attackers.net/</x:v>
+      </x:c>
+      <x:c r="E6" s="14" t="str">
+        <x:v>maker; label</x:v>
+      </x:c>
+      <x:c r="F6" s="14" t="str">
+        <x:v>reachable</x:v>
+      </x:c>
+      <x:c r="G6" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="H6" s="14" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="I6" s="14" t="str">
+        <x:v>maker: 1/1 published; label: 17/17 published</x:v>
+      </x:c>
+      <x:c r="J6" s="14" t="str">
+        <x:v>completeTraversal=true 仅表示 2026-09-04 时点官方 /works/label 当前可见索引已全部遍历；不代表历史已删除 Label、Series、Work 或集团/法律公司关系已完整覆盖。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="14" t="str">
+        <x:v>source_madonna_official</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="str">
+        <x:v>Madonna 官方 Maker / Label 目录</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="str">
+        <x:v>official</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="str">
+        <x:v>https://madonna-av.com/</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="str">
+        <x:v>maker; label</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="str">
+        <x:v>reachable</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="H7" s="14" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="I7" s="14" t="str">
+        <x:v>maker: 1/1 published; label: 18/18 published</x:v>
+      </x:c>
+      <x:c r="J7" s="14" t="str">
+        <x:v>completeTraversal=true 仅表示 2026-09-04 时点官方 /works/label 当前可见索引已全部遍历；不代表历史已删除 Label、Series、Work 或集团/法律公司关系已完整覆盖。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -884,12 +1971,12 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="48" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="54" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -909,10 +1996,10 @@
         <x:v>Status</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
+        <x:v>Reviewed</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
         <x:v>Source URL</x:v>
-      </x:c>
-      <x:c r="G1" s="6" t="str">
-        <x:v>Reviewed At</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -932,10 +2019,10 @@
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F2" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G2" s="14" t="str">
         <x:v>https://ideapocket.com/works/list/series/1011</x:v>
-      </x:c>
-      <x:c r="G2" s="14" t="str">
-        <x:v>2026-09-04</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -955,10 +2042,10 @@
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F3" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G3" s="14" t="str">
         <x:v>https://ideapocket.com/works/list/series/863</x:v>
-      </x:c>
-      <x:c r="G3" s="14" t="str">
-        <x:v>2026-09-04</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -978,10 +2065,10 @@
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F4" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G4" s="14" t="str">
         <x:v>https://moodyz.com/works/list/label/12798</x:v>
-      </x:c>
-      <x:c r="G4" s="14" t="str">
-        <x:v>2026-09-04</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1001,10 +2088,10 @@
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F5" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G5" s="14" t="str">
         <x:v>https://moodyz.com/works/list/label/5048</x:v>
-      </x:c>
-      <x:c r="G5" s="14" t="str">
-        <x:v>2026-09-04</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1024,10 +2111,10 @@
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F6" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G6" s="14" t="str">
         <x:v>https://moodyz.com/works/list/series/5427</x:v>
-      </x:c>
-      <x:c r="G6" s="14" t="str">
-        <x:v>2026-09-04</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1047,10 +2134,815 @@
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F7" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="str">
         <x:v>https://s1s1s1.com/works/list/series/414</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="str">
-        <x:v>2026-09-04</x:v>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="str">
+        <x:v>2754</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="str">
+        <x:v>label_000003</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/2754</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="str">
+        <x:v>2751</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="str">
+        <x:v>label_000004</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/2751</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="str">
+        <x:v>9455</x:v>
+      </x:c>
+      <x:c r="D10" s="14" t="str">
+        <x:v>label_000005</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/9455</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="B11" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="str">
+        <x:v>2737</x:v>
+      </x:c>
+      <x:c r="D11" s="14" t="str">
+        <x:v>label_000006</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/2737</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="B12" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="str">
+        <x:v>2739</x:v>
+      </x:c>
+      <x:c r="D12" s="14" t="str">
+        <x:v>label_000007</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/2739</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="B13" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="str">
+        <x:v>2749</x:v>
+      </x:c>
+      <x:c r="D13" s="14" t="str">
+        <x:v>label_000008</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/2749</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="B14" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="str">
+        <x:v>2735</x:v>
+      </x:c>
+      <x:c r="D14" s="14" t="str">
+        <x:v>label_000009</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/2735</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="B15" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="str">
+        <x:v>2756</x:v>
+      </x:c>
+      <x:c r="D15" s="14" t="str">
+        <x:v>label_000010</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/2756</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="B16" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="str">
+        <x:v>12605</x:v>
+      </x:c>
+      <x:c r="D16" s="14" t="str">
+        <x:v>label_000011</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/12605</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="B17" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="str">
+        <x:v>81348</x:v>
+      </x:c>
+      <x:c r="D17" s="14" t="str">
+        <x:v>label_000012</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/81348</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="B18" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="str">
+        <x:v>5245</x:v>
+      </x:c>
+      <x:c r="D18" s="14" t="str">
+        <x:v>label_000013</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/5245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="B19" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="str">
+        <x:v>85265</x:v>
+      </x:c>
+      <x:c r="D19" s="14" t="str">
+        <x:v>label_000014</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/85265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="B20" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="str">
+        <x:v>9483</x:v>
+      </x:c>
+      <x:c r="D20" s="14" t="str">
+        <x:v>label_000015</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/9483</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="B21" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="str">
+        <x:v>10077</x:v>
+      </x:c>
+      <x:c r="D21" s="14" t="str">
+        <x:v>label_000016</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/10077</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="B22" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="str">
+        <x:v>10142</x:v>
+      </x:c>
+      <x:c r="D22" s="14" t="str">
+        <x:v>label_000017</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/10142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="B23" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="str">
+        <x:v>10144</x:v>
+      </x:c>
+      <x:c r="D23" s="14" t="str">
+        <x:v>label_000018</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/10144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="B24" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="str">
+        <x:v>10151</x:v>
+      </x:c>
+      <x:c r="D24" s="14" t="str">
+        <x:v>label_000019</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/10151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="B25" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="str">
+        <x:v>3669</x:v>
+      </x:c>
+      <x:c r="D25" s="14" t="str">
+        <x:v>label_000020</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/3669</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="B26" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="str">
+        <x:v>12490</x:v>
+      </x:c>
+      <x:c r="D26" s="14" t="str">
+        <x:v>label_000021</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/12490</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="B27" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="str">
+        <x:v>9387</x:v>
+      </x:c>
+      <x:c r="D27" s="14" t="str">
+        <x:v>label_000022</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/9387</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="B28" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="str">
+        <x:v>9789</x:v>
+      </x:c>
+      <x:c r="D28" s="14" t="str">
+        <x:v>label_000023</x:v>
+      </x:c>
+      <x:c r="E28" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G28" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/9789</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="B29" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="str">
+        <x:v>7354</x:v>
+      </x:c>
+      <x:c r="D29" s="14" t="str">
+        <x:v>label_000024</x:v>
+      </x:c>
+      <x:c r="E29" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G29" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/7354</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="B30" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C30" s="14" t="str">
+        <x:v>9419</x:v>
+      </x:c>
+      <x:c r="D30" s="14" t="str">
+        <x:v>label_000025</x:v>
+      </x:c>
+      <x:c r="E30" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G30" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/9419</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="B31" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C31" s="14" t="str">
+        <x:v>12603</x:v>
+      </x:c>
+      <x:c r="D31" s="14" t="str">
+        <x:v>label_000026</x:v>
+      </x:c>
+      <x:c r="E31" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G31" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/12603</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="B32" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C32" s="14" t="str">
+        <x:v>12502</x:v>
+      </x:c>
+      <x:c r="D32" s="14" t="str">
+        <x:v>label_000027</x:v>
+      </x:c>
+      <x:c r="E32" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G32" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/12502</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="B33" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C33" s="14" t="str">
+        <x:v>10130</x:v>
+      </x:c>
+      <x:c r="D33" s="14" t="str">
+        <x:v>label_000028</x:v>
+      </x:c>
+      <x:c r="E33" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G33" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/10130</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="B34" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C34" s="14" t="str">
+        <x:v>7993</x:v>
+      </x:c>
+      <x:c r="D34" s="14" t="str">
+        <x:v>label_000029</x:v>
+      </x:c>
+      <x:c r="E34" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G34" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/7993</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="B35" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C35" s="14" t="str">
+        <x:v>10159</x:v>
+      </x:c>
+      <x:c r="D35" s="14" t="str">
+        <x:v>label_000030</x:v>
+      </x:c>
+      <x:c r="E35" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F35" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G35" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/10159</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="B36" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C36" s="14" t="str">
+        <x:v>10119</x:v>
+      </x:c>
+      <x:c r="D36" s="14" t="str">
+        <x:v>label_000031</x:v>
+      </x:c>
+      <x:c r="E36" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F36" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G36" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/10119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="B37" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C37" s="14" t="str">
+        <x:v>85265</x:v>
+      </x:c>
+      <x:c r="D37" s="14" t="str">
+        <x:v>label_000032</x:v>
+      </x:c>
+      <x:c r="E37" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F37" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G37" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/85265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="B38" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C38" s="14" t="str">
+        <x:v>9483</x:v>
+      </x:c>
+      <x:c r="D38" s="14" t="str">
+        <x:v>label_000033</x:v>
+      </x:c>
+      <x:c r="E38" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F38" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G38" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/9483</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="B39" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C39" s="14" t="str">
+        <x:v>10142</x:v>
+      </x:c>
+      <x:c r="D39" s="14" t="str">
+        <x:v>label_000034</x:v>
+      </x:c>
+      <x:c r="E39" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F39" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G39" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/10142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="B40" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C40" s="14" t="str">
+        <x:v>10077</x:v>
+      </x:c>
+      <x:c r="D40" s="14" t="str">
+        <x:v>label_000035</x:v>
+      </x:c>
+      <x:c r="E40" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F40" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G40" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/10077</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="B41" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C41" s="14" t="str">
+        <x:v>10151</x:v>
+      </x:c>
+      <x:c r="D41" s="14" t="str">
+        <x:v>label_000036</x:v>
+      </x:c>
+      <x:c r="E41" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F41" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G41" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/10151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="B42" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C42" s="14" t="str">
+        <x:v>3125</x:v>
+      </x:c>
+      <x:c r="D42" s="14" t="str">
+        <x:v>label_000037</x:v>
+      </x:c>
+      <x:c r="E42" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F42" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G42" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/3125</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1062,16 +2954,12 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="60" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="42" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="60" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="40" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="70" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1082,28 +2970,16 @@
         <x:v>Kind</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>Name JA</x:v>
+        <x:v>日本語</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>Name ZH</x:v>
+        <x:v>Status</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>Name EN</x:v>
+        <x:v>未发布原因</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
-        <x:v>Status</x:v>
-      </x:c>
-      <x:c r="G1" s="6" t="str">
-        <x:v>Reason Not Published</x:v>
-      </x:c>
-      <x:c r="H1" s="6" t="str">
-        <x:v>Official Website</x:v>
-      </x:c>
-      <x:c r="I1" s="6" t="str">
-        <x:v>Founded</x:v>
-      </x:c>
-      <x:c r="J1" s="6" t="str">
-        <x:v>Sources</x:v>
+        <x:v>Official URL</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -1117,25 +2993,13 @@
         <x:v>株式会社WILL</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
-        <x:v>WILL株式会社</x:v>
+        <x:v>reviewed-candidate</x:v>
       </x:c>
       <x:c r="E2" s="14" t="str">
-        <x:v>WILL Co., Ltd.</x:v>
+        <x:v>Localogue 当前正式 Shared Pack OrganizationKind 尚未把 company 作为一等类型；本仓库先保留正确语义，不把法律公司伪装成 maker。</x:v>
       </x:c>
       <x:c r="F2" s="14" t="str">
-        <x:v>reviewed-candidate</x:v>
-      </x:c>
-      <x:c r="G2" s="14" t="str">
-        <x:v>Localogue 当前正式 Shared Pack OrganizationKind 尚未把 company 作为一等类型；本仓库先保留正确语义，不把法律公司伪装成 maker。</x:v>
-      </x:c>
-      <x:c r="H2" s="14" t="str">
         <x:v>https://will-hp.jp/</x:v>
-      </x:c>
-      <x:c r="I2" s="14" t="str">
-        <x:v>2016-07-13</x:v>
-      </x:c>
-      <x:c r="J2" s="14" t="str">
-        <x:v>https://will-hp.jp/company/index.html</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1147,15 +3011,15 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="48" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="40" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="54" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1163,40 +3027,1136 @@
         <x:v>Result</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>Source ID</x:v>
+        <x:v>Reason</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
         <x:v>Provider</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>Entity Type</x:v>
+        <x:v>Type</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
         <x:v>External ID</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
-        <x:v>Name JA</x:v>
+        <x:v>日本語</x:v>
       </x:c>
       <x:c r="G1" s="6" t="str">
         <x:v>Community ID</x:v>
       </x:c>
       <x:c r="H1" s="6" t="str">
-        <x:v>Match Method</x:v>
+        <x:v>Candidates</x:v>
       </x:c>
       <x:c r="I1" s="6" t="str">
         <x:v>Source URL</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="14"/>
-      <x:c r="B2" s="14"/>
-      <x:c r="C2" s="14"/>
-      <x:c r="D2" s="14"/>
-      <x:c r="E2" s="14"/>
-      <x:c r="F2" s="14"/>
-      <x:c r="G2" s="14"/>
-      <x:c r="H2" s="14"/>
-      <x:c r="I2" s="14"/>
+      <x:c r="A2" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B2" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C2" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D2" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E2" s="14" t="str">
+        <x:v>5048</x:v>
+      </x:c>
+      <x:c r="F2" s="14" t="str">
+        <x:v>MOODYZ DIVA</x:v>
+      </x:c>
+      <x:c r="G2" s="14" t="str">
+        <x:v>label_000001</x:v>
+      </x:c>
+      <x:c r="H2" s="14" t="str"/>
+      <x:c r="I2" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5048</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B3" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C3" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="str">
+        <x:v>12798</x:v>
+      </x:c>
+      <x:c r="F3" s="14" t="str">
+        <x:v>みんなのキカタン</x:v>
+      </x:c>
+      <x:c r="G3" s="14" t="str">
+        <x:v>label_000002</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="str"/>
+      <x:c r="I3" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/12798</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B4" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C4" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="D4" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="E4" s="14" t="str">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="F4" s="14" t="str">
+        <x:v>新人NO.1STYLE</x:v>
+      </x:c>
+      <x:c r="G4" s="14" t="str">
+        <x:v>series_000001</x:v>
+      </x:c>
+      <x:c r="H4" s="14" t="str"/>
+      <x:c r="I4" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/414</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B5" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C5" s="14" t="str">
+        <x:v>moodyz.series</x:v>
+      </x:c>
+      <x:c r="D5" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="E5" s="14" t="str">
+        <x:v>5427</x:v>
+      </x:c>
+      <x:c r="F5" s="14" t="str">
+        <x:v>カラミざかり</x:v>
+      </x:c>
+      <x:c r="G5" s="14" t="str">
+        <x:v>series_000002</x:v>
+      </x:c>
+      <x:c r="H5" s="14" t="str"/>
+      <x:c r="I5" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/5427</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="str">
+        <x:v>ideapocket.series</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="E6" s="14" t="str">
+        <x:v>863</x:v>
+      </x:c>
+      <x:c r="F6" s="14" t="str">
+        <x:v>死ぬほど大嫌いな上司とまさかの相部屋に</x:v>
+      </x:c>
+      <x:c r="G6" s="14" t="str">
+        <x:v>series_000003</x:v>
+      </x:c>
+      <x:c r="H6" s="14" t="str"/>
+      <x:c r="I6" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/series/863</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="str">
+        <x:v>ideapocket.series</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="str">
+        <x:v>1011</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="str">
+        <x:v>うちの妻を犯して下さい</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="str">
+        <x:v>series_000004</x:v>
+      </x:c>
+      <x:c r="H7" s="14" t="str"/>
+      <x:c r="I7" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/series/1011</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="str">
+        <x:v>2754</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="str">
+        <x:v>死夜悪</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="str">
+        <x:v>label_000003</x:v>
+      </x:c>
+      <x:c r="H8" s="14" t="str"/>
+      <x:c r="I8" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/2754</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="str">
+        <x:v>2751</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="str">
+        <x:v>龍縛</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="str">
+        <x:v>label_000004</x:v>
+      </x:c>
+      <x:c r="H9" s="14" t="str"/>
+      <x:c r="I9" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/2751</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="D10" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="str">
+        <x:v>9455</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="str">
+        <x:v>大人のドラマ</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="str">
+        <x:v>label_000005</x:v>
+      </x:c>
+      <x:c r="H10" s="14" t="str"/>
+      <x:c r="I10" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/9455</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B11" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="D11" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="str">
+        <x:v>2737</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="str">
+        <x:v>淫魔</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="str">
+        <x:v>label_000006</x:v>
+      </x:c>
+      <x:c r="H11" s="14" t="str"/>
+      <x:c r="I11" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/2737</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B12" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="D12" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="str">
+        <x:v>2739</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="str">
+        <x:v>Attackers</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="str">
+        <x:v>label_000007</x:v>
+      </x:c>
+      <x:c r="H12" s="14" t="str"/>
+      <x:c r="I12" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/2739</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B13" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="D13" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="str">
+        <x:v>2749</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="str">
+        <x:v>蛇縛</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="str">
+        <x:v>label_000008</x:v>
+      </x:c>
+      <x:c r="H13" s="14" t="str"/>
+      <x:c r="I13" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/2749</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B14" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="D14" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="str">
+        <x:v>2735</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="str">
+        <x:v>アタッカーズ・アンソロジー</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="str">
+        <x:v>label_000009</x:v>
+      </x:c>
+      <x:c r="H14" s="14" t="str"/>
+      <x:c r="I14" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/2735</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B15" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="D15" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="str">
+        <x:v>2756</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="str">
+        <x:v>SUPER SPECIAL</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="str">
+        <x:v>label_000010</x:v>
+      </x:c>
+      <x:c r="H15" s="14" t="str"/>
+      <x:c r="I15" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/2756</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B16" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="D16" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="str">
+        <x:v>12605</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="str">
+        <x:v>誘女</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="str">
+        <x:v>label_000011</x:v>
+      </x:c>
+      <x:c r="H16" s="14" t="str"/>
+      <x:c r="I16" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/12605</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B17" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="D17" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="str">
+        <x:v>81348</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="str">
+        <x:v>アタッカーズVR</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="str">
+        <x:v>label_000012</x:v>
+      </x:c>
+      <x:c r="H17" s="14" t="str"/>
+      <x:c r="I17" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/81348</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B18" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="D18" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="str">
+        <x:v>5245</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="str">
+        <x:v>アタックゾーン</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="str">
+        <x:v>label_000013</x:v>
+      </x:c>
+      <x:c r="H18" s="14" t="str"/>
+      <x:c r="I18" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/5245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B19" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="D19" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="str">
+        <x:v>85265</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="str">
+        <x:v>春のパンツまつり</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="str">
+        <x:v>label_000014</x:v>
+      </x:c>
+      <x:c r="H19" s="14" t="str"/>
+      <x:c r="I19" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/85265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B20" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="D20" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="str">
+        <x:v>9483</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="str">
+        <x:v>AVOPEN</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="str">
+        <x:v>label_000015</x:v>
+      </x:c>
+      <x:c r="H20" s="14" t="str"/>
+      <x:c r="I20" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/9483</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B21" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="D21" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="str">
+        <x:v>10077</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="str">
+        <x:v>AVグランプリ</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="str">
+        <x:v>label_000016</x:v>
+      </x:c>
+      <x:c r="H21" s="14" t="str"/>
+      <x:c r="I21" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/10077</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B22" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="D22" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="str">
+        <x:v>10142</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="str">
+        <x:v>おっぱい祭り</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="str">
+        <x:v>label_000017</x:v>
+      </x:c>
+      <x:c r="H22" s="14" t="str"/>
+      <x:c r="I22" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/10142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B23" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="D23" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="str">
+        <x:v>10144</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="str">
+        <x:v>秋のシコシコ強化月間</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="str">
+        <x:v>label_000018</x:v>
+      </x:c>
+      <x:c r="H23" s="14" t="str"/>
+      <x:c r="I23" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/10144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B24" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="str">
+        <x:v>attackers.label</x:v>
+      </x:c>
+      <x:c r="D24" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="str">
+        <x:v>10151</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="str">
+        <x:v>背徳ビチョビチョ！NTR大放出</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="str">
+        <x:v>label_000019</x:v>
+      </x:c>
+      <x:c r="H24" s="14" t="str"/>
+      <x:c r="I24" s="14" t="str">
+        <x:v>https://attackers.net/works/list/label/10151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B25" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="D25" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="str">
+        <x:v>3669</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="str">
+        <x:v>Madonna</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="str">
+        <x:v>label_000020</x:v>
+      </x:c>
+      <x:c r="H25" s="14" t="str"/>
+      <x:c r="I25" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/3669</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B26" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="D26" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="str">
+        <x:v>12490</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="str">
+        <x:v>MONROE</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="str">
+        <x:v>label_000021</x:v>
+      </x:c>
+      <x:c r="H26" s="14" t="str"/>
+      <x:c r="I26" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/12490</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B27" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="D27" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="str">
+        <x:v>9387</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="str">
+        <x:v>Obasan</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="str">
+        <x:v>label_000022</x:v>
+      </x:c>
+      <x:c r="H27" s="14" t="str"/>
+      <x:c r="I27" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/9387</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B28" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="D28" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E28" s="14" t="str">
+        <x:v>9789</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="str">
+        <x:v>MadonnaVR</x:v>
+      </x:c>
+      <x:c r="G28" s="14" t="str">
+        <x:v>label_000023</x:v>
+      </x:c>
+      <x:c r="H28" s="14" t="str"/>
+      <x:c r="I28" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/9789</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B29" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="D29" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E29" s="14" t="str">
+        <x:v>7354</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="str">
+        <x:v>Fitch</x:v>
+      </x:c>
+      <x:c r="G29" s="14" t="str">
+        <x:v>label_000024</x:v>
+      </x:c>
+      <x:c r="H29" s="14" t="str"/>
+      <x:c r="I29" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/7354</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B30" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C30" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="D30" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E30" s="14" t="str">
+        <x:v>9419</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="str">
+        <x:v>熟れコミ</x:v>
+      </x:c>
+      <x:c r="G30" s="14" t="str">
+        <x:v>label_000025</x:v>
+      </x:c>
+      <x:c r="H30" s="14" t="str"/>
+      <x:c r="I30" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/9419</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B31" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C31" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="D31" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E31" s="14" t="str">
+        <x:v>12603</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="str">
+        <x:v>ACHIJO(アチージョ)</x:v>
+      </x:c>
+      <x:c r="G31" s="14" t="str">
+        <x:v>label_000026</x:v>
+      </x:c>
+      <x:c r="H31" s="14" t="str"/>
+      <x:c r="I31" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/12603</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B32" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C32" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="D32" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E32" s="14" t="str">
+        <x:v>12502</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="str">
+        <x:v>MADOOOON!!!!</x:v>
+      </x:c>
+      <x:c r="G32" s="14" t="str">
+        <x:v>label_000027</x:v>
+      </x:c>
+      <x:c r="H32" s="14" t="str"/>
+      <x:c r="I32" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/12502</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B33" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C33" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="D33" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E33" s="14" t="str">
+        <x:v>10130</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="str">
+        <x:v>Re:Madonna/AIリマスター</x:v>
+      </x:c>
+      <x:c r="G33" s="14" t="str">
+        <x:v>label_000028</x:v>
+      </x:c>
+      <x:c r="H33" s="14" t="str"/>
+      <x:c r="I33" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/10130</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B34" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C34" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="D34" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E34" s="14" t="str">
+        <x:v>7993</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="str">
+        <x:v>Fitch　BEST</x:v>
+      </x:c>
+      <x:c r="G34" s="14" t="str">
+        <x:v>label_000029</x:v>
+      </x:c>
+      <x:c r="H34" s="14" t="str"/>
+      <x:c r="I34" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/7993</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B35" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C35" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="D35" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E35" s="14" t="str">
+        <x:v>10159</x:v>
+      </x:c>
+      <x:c r="F35" s="14" t="str">
+        <x:v>性録ch</x:v>
+      </x:c>
+      <x:c r="G35" s="14" t="str">
+        <x:v>label_000030</x:v>
+      </x:c>
+      <x:c r="H35" s="14" t="str"/>
+      <x:c r="I35" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/10159</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B36" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C36" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="D36" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E36" s="14" t="str">
+        <x:v>10119</x:v>
+      </x:c>
+      <x:c r="F36" s="14" t="str">
+        <x:v>※スマホ推奨タテ動画※マドーンショート</x:v>
+      </x:c>
+      <x:c r="G36" s="14" t="str">
+        <x:v>label_000031</x:v>
+      </x:c>
+      <x:c r="H36" s="14" t="str"/>
+      <x:c r="I36" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/10119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B37" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C37" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="D37" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E37" s="14" t="str">
+        <x:v>85265</x:v>
+      </x:c>
+      <x:c r="F37" s="14" t="str">
+        <x:v>春のパンツまつり</x:v>
+      </x:c>
+      <x:c r="G37" s="14" t="str">
+        <x:v>label_000032</x:v>
+      </x:c>
+      <x:c r="H37" s="14" t="str"/>
+      <x:c r="I37" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/85265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B38" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C38" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="D38" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E38" s="14" t="str">
+        <x:v>9483</x:v>
+      </x:c>
+      <x:c r="F38" s="14" t="str">
+        <x:v>AVOPEN</x:v>
+      </x:c>
+      <x:c r="G38" s="14" t="str">
+        <x:v>label_000033</x:v>
+      </x:c>
+      <x:c r="H38" s="14" t="str"/>
+      <x:c r="I38" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/9483</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B39" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C39" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="D39" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E39" s="14" t="str">
+        <x:v>10142</x:v>
+      </x:c>
+      <x:c r="F39" s="14" t="str">
+        <x:v>おっぱい祭り</x:v>
+      </x:c>
+      <x:c r="G39" s="14" t="str">
+        <x:v>label_000034</x:v>
+      </x:c>
+      <x:c r="H39" s="14" t="str"/>
+      <x:c r="I39" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/10142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B40" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C40" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="D40" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E40" s="14" t="str">
+        <x:v>10077</x:v>
+      </x:c>
+      <x:c r="F40" s="14" t="str">
+        <x:v>AVグランプリ</x:v>
+      </x:c>
+      <x:c r="G40" s="14" t="str">
+        <x:v>label_000035</x:v>
+      </x:c>
+      <x:c r="H40" s="14" t="str"/>
+      <x:c r="I40" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/10077</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B41" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C41" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="D41" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E41" s="14" t="str">
+        <x:v>10151</x:v>
+      </x:c>
+      <x:c r="F41" s="14" t="str">
+        <x:v>背徳ビチョビチョ！NTR大放出</x:v>
+      </x:c>
+      <x:c r="G41" s="14" t="str">
+        <x:v>label_000036</x:v>
+      </x:c>
+      <x:c r="H41" s="14" t="str"/>
+      <x:c r="I41" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/10151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B42" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C42" s="14" t="str">
+        <x:v>madonna.label</x:v>
+      </x:c>
+      <x:c r="D42" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E42" s="14" t="str">
+        <x:v>3125</x:v>
+      </x:c>
+      <x:c r="F42" s="14" t="str">
+        <x:v>bizarre　amaturs</x:v>
+      </x:c>
+      <x:c r="G42" s="14" t="str">
+        <x:v>label_000037</x:v>
+      </x:c>
+      <x:c r="H42" s="14" t="str"/>
+      <x:c r="I42" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/label/3125</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/exports/xlsx/organization-series-registry.xlsx
+++ b/exports/xlsx/organization-series-registry.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organizations" sheetId="1" r:id="R5b1190adcd144830"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series" sheetId="2" r:id="Rc4feb7f212ae44e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Registry" sheetId="3" r:id="R90d85e1e511344c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External ID Mapping" sheetId="4" r:id="R7bc47783a0244882"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidates" sheetId="5" r:id="Re5a0a0947123480b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="6" r:id="Rc01bad8c81a640f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organizations" sheetId="1" r:id="Ra6d2b7576cd8440f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series" sheetId="2" r:id="R5f15b0d030c84e0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Registry" sheetId="3" r:id="R8adec21e8c77418a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External ID Mapping" sheetId="4" r:id="R4d43d99bcdc04073"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidates" sheetId="5" r:id="R53377e02164a4b0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="6" r:id="R50081e7e53e14103"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -291,14 +291,14 @@
   <x:cols>
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="32" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="48" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="28" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="50" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -343,9 +343,15 @@
       <x:c r="C2" s="14" t="str">
         <x:v>MOODYZ DIVA</x:v>
       </x:c>
-      <x:c r="D2" s="14" t="str"/>
-      <x:c r="E2" s="14" t="str"/>
-      <x:c r="F2" s="14" t="str"/>
+      <x:c r="D2" s="14" t="str">
+        <x:v>MOODYZ DIVA</x:v>
+      </x:c>
+      <x:c r="E2" s="14" t="str">
+        <x:v>MOODYZ DIVA</x:v>
+      </x:c>
+      <x:c r="F2" s="14" t="str">
+        <x:v>MOODYZ　DIVA</x:v>
+      </x:c>
       <x:c r="G2" s="14" t="str">
         <x:v>maker_000002</x:v>
       </x:c>
@@ -369,8 +375,12 @@
       <x:c r="C3" s="14" t="str">
         <x:v>みんなのキカタン</x:v>
       </x:c>
-      <x:c r="D3" s="14" t="str"/>
-      <x:c r="E3" s="14" t="str"/>
+      <x:c r="D3" s="14" t="str">
+        <x:v>大家的企画单体</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="str">
+        <x:v>Minna no Kikatan</x:v>
+      </x:c>
       <x:c r="F3" s="14" t="str"/>
       <x:c r="G3" s="14" t="str">
         <x:v>maker_000002</x:v>
@@ -1435,113 +1445,1393 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="14" t="str">
-        <x:v>maker_000001</x:v>
+        <x:v>label_000038</x:v>
       </x:c>
       <x:c r="B39" s="14" t="str">
-        <x:v>maker</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C39" s="14" t="str">
-        <x:v>アイデアポケット</x:v>
-      </x:c>
-      <x:c r="D39" s="14" t="str"/>
-      <x:c r="E39" s="14" t="str"/>
-      <x:c r="F39" s="14" t="str"/>
-      <x:c r="G39" s="14" t="str"/>
-      <x:c r="H39" s="14" t="str"/>
-      <x:c r="I39" s="14" t="str"/>
-      <x:c r="J39" s="14" t="str"/>
+        <x:v>MOODYZ BEST</x:v>
+      </x:c>
+      <x:c r="D39" s="14" t="str">
+        <x:v>MOODYZ BEST</x:v>
+      </x:c>
+      <x:c r="E39" s="14" t="str">
+        <x:v>MOODYZ BEST</x:v>
+      </x:c>
+      <x:c r="F39" s="14" t="str">
+        <x:v>MOODYZ　BEST</x:v>
+      </x:c>
+      <x:c r="G39" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H39" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I39" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5047</x:v>
+      </x:c>
+      <x:c r="J39" s="14" t="str">
+        <x:v>moodyz.label:5047</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="14" t="str">
+        <x:v>label_000039</x:v>
+      </x:c>
+      <x:c r="B40" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C40" s="14" t="str">
+        <x:v>MOODYZ ACID</x:v>
+      </x:c>
+      <x:c r="D40" s="14" t="str">
+        <x:v>MOODYZ ACID</x:v>
+      </x:c>
+      <x:c r="E40" s="14" t="str">
+        <x:v>MOODYZ ACID</x:v>
+      </x:c>
+      <x:c r="F40" s="14" t="str">
+        <x:v>MOODYZ　ACID</x:v>
+      </x:c>
+      <x:c r="G40" s="14" t="str">
         <x:v>maker_000002</x:v>
       </x:c>
-      <x:c r="B40" s="14" t="str">
-        <x:v>maker</x:v>
-      </x:c>
-      <x:c r="C40" s="14" t="str">
-        <x:v>MOODYZ</x:v>
-      </x:c>
-      <x:c r="D40" s="14" t="str"/>
-      <x:c r="E40" s="14" t="str"/>
-      <x:c r="F40" s="14" t="str"/>
-      <x:c r="G40" s="14" t="str"/>
-      <x:c r="H40" s="14" t="str"/>
-      <x:c r="I40" s="14" t="str"/>
-      <x:c r="J40" s="14" t="str"/>
+      <x:c r="H40" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I40" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5046</x:v>
+      </x:c>
+      <x:c r="J40" s="14" t="str">
+        <x:v>moodyz.label:5046</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="14" t="str">
-        <x:v>maker_000003</x:v>
+        <x:v>label_000040</x:v>
       </x:c>
       <x:c r="B41" s="14" t="str">
-        <x:v>maker</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C41" s="14" t="str">
-        <x:v>エスワン</x:v>
-      </x:c>
-      <x:c r="D41" s="14" t="str"/>
-      <x:c r="E41" s="14" t="str"/>
-      <x:c r="F41" s="14" t="str"/>
-      <x:c r="G41" s="14" t="str"/>
-      <x:c r="H41" s="14" t="str"/>
-      <x:c r="I41" s="14" t="str"/>
-      <x:c r="J41" s="14" t="str"/>
+        <x:v>MOODYZ GATI</x:v>
+      </x:c>
+      <x:c r="D41" s="14" t="str">
+        <x:v>MOODYZ GATI</x:v>
+      </x:c>
+      <x:c r="E41" s="14" t="str">
+        <x:v>MOODYZ GATI</x:v>
+      </x:c>
+      <x:c r="F41" s="14" t="str">
+        <x:v>MOODYZ　GATI</x:v>
+      </x:c>
+      <x:c r="G41" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H41" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I41" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/6879</x:v>
+      </x:c>
+      <x:c r="J41" s="14" t="str">
+        <x:v>moodyz.label:6879</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="14" t="str">
-        <x:v>maker_000004</x:v>
+        <x:v>label_000041</x:v>
       </x:c>
       <x:c r="B42" s="14" t="str">
-        <x:v>maker</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C42" s="14" t="str">
-        <x:v>ATTACKERS</x:v>
+        <x:v>MOODYZ VR</x:v>
       </x:c>
       <x:c r="D42" s="14" t="str">
-        <x:v>ATTACKERS</x:v>
+        <x:v>MOODYZ VR</x:v>
       </x:c>
       <x:c r="E42" s="14" t="str">
-        <x:v>ATTACKERS</x:v>
-      </x:c>
-      <x:c r="F42" s="14" t="str">
-        <x:v>アタッカーズ</x:v>
-      </x:c>
-      <x:c r="G42" s="14" t="str"/>
+        <x:v>MOODYZ VR</x:v>
+      </x:c>
+      <x:c r="F42" s="14" t="str"/>
+      <x:c r="G42" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
       <x:c r="H42" s="14" t="str">
         <x:v>unknown</x:v>
       </x:c>
       <x:c r="I42" s="14" t="str">
-        <x:v>https://attackers.net/</x:v>
-      </x:c>
-      <x:c r="J42" s="14" t="str"/>
+        <x:v>https://moodyz.com/works/list/label/9782</x:v>
+      </x:c>
+      <x:c r="J42" s="14" t="str">
+        <x:v>moodyz.label:9782</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="14" t="str">
+        <x:v>label_000042</x:v>
+      </x:c>
+      <x:c r="B43" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C43" s="14" t="str">
+        <x:v>MOODYZ Fresh</x:v>
+      </x:c>
+      <x:c r="D43" s="14" t="str">
+        <x:v>MOODYZ Fresh</x:v>
+      </x:c>
+      <x:c r="E43" s="14" t="str">
+        <x:v>MOODYZ Fresh</x:v>
+      </x:c>
+      <x:c r="F43" s="14" t="str"/>
+      <x:c r="G43" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H43" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I43" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9732</x:v>
+      </x:c>
+      <x:c r="J43" s="14" t="str">
+        <x:v>moodyz.label:9732</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="14" t="str">
+        <x:v>label_000043</x:v>
+      </x:c>
+      <x:c r="B44" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C44" s="14" t="str">
+        <x:v>まんきつ</x:v>
+      </x:c>
+      <x:c r="D44" s="14" t="str"/>
+      <x:c r="E44" s="14" t="str"/>
+      <x:c r="F44" s="14" t="str"/>
+      <x:c r="G44" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H44" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I44" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9308</x:v>
+      </x:c>
+      <x:c r="J44" s="14" t="str">
+        <x:v>moodyz.label:9308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="14" t="str">
+        <x:v>label_000044</x:v>
+      </x:c>
+      <x:c r="B45" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C45" s="14" t="str">
+        <x:v>MOODYZ REAL</x:v>
+      </x:c>
+      <x:c r="D45" s="14" t="str">
+        <x:v>MOODYZ REAL</x:v>
+      </x:c>
+      <x:c r="E45" s="14" t="str">
+        <x:v>MOODYZ REAL</x:v>
+      </x:c>
+      <x:c r="F45" s="14" t="str">
+        <x:v>MOODYZ　REAL</x:v>
+      </x:c>
+      <x:c r="G45" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H45" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I45" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5090</x:v>
+      </x:c>
+      <x:c r="J45" s="14" t="str">
+        <x:v>moodyz.label:5090</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="14" t="str">
+        <x:v>label_000045</x:v>
+      </x:c>
+      <x:c r="B46" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C46" s="14" t="str">
+        <x:v>MOODYZ ISM</x:v>
+      </x:c>
+      <x:c r="D46" s="14" t="str">
+        <x:v>MOODYZ ISM</x:v>
+      </x:c>
+      <x:c r="E46" s="14" t="str">
+        <x:v>MOODYZ ISM</x:v>
+      </x:c>
+      <x:c r="F46" s="14" t="str">
+        <x:v>MOODYZ　ISM</x:v>
+      </x:c>
+      <x:c r="G46" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H46" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I46" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5049</x:v>
+      </x:c>
+      <x:c r="J46" s="14" t="str">
+        <x:v>moodyz.label:5049</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="14" t="str">
+        <x:v>label_000046</x:v>
+      </x:c>
+      <x:c r="B47" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C47" s="14" t="str">
+        <x:v>きれいなお姉さんは好きですか</x:v>
+      </x:c>
+      <x:c r="D47" s="14" t="str"/>
+      <x:c r="E47" s="14" t="str"/>
+      <x:c r="F47" s="14" t="str"/>
+      <x:c r="G47" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H47" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I47" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10107</x:v>
+      </x:c>
+      <x:c r="J47" s="14" t="str">
+        <x:v>moodyz.label:10107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="14" t="str">
+        <x:v>label_000047</x:v>
+      </x:c>
+      <x:c r="B48" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C48" s="14" t="str">
+        <x:v>MOODYZ ニュージーニアス</x:v>
+      </x:c>
+      <x:c r="D48" s="14" t="str"/>
+      <x:c r="E48" s="14" t="str">
+        <x:v>MOODYZ New Genius</x:v>
+      </x:c>
+      <x:c r="F48" s="14" t="str"/>
+      <x:c r="G48" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H48" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I48" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10131</x:v>
+      </x:c>
+      <x:c r="J48" s="14" t="str">
+        <x:v>moodyz.label:10131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="14" t="str">
+        <x:v>label_000048</x:v>
+      </x:c>
+      <x:c r="B49" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C49" s="14" t="str">
+        <x:v>MUTTURI</x:v>
+      </x:c>
+      <x:c r="D49" s="14" t="str">
+        <x:v>MUTTURI</x:v>
+      </x:c>
+      <x:c r="E49" s="14" t="str">
+        <x:v>MUTTURI</x:v>
+      </x:c>
+      <x:c r="F49" s="14" t="str"/>
+      <x:c r="G49" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H49" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I49" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9458</x:v>
+      </x:c>
+      <x:c r="J49" s="14" t="str">
+        <x:v>moodyz.label:9458</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="14" t="str">
+        <x:v>label_000049</x:v>
+      </x:c>
+      <x:c r="B50" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C50" s="14" t="str">
+        <x:v>MOODYZ VALUE</x:v>
+      </x:c>
+      <x:c r="D50" s="14" t="str">
+        <x:v>MOODYZ VALUE</x:v>
+      </x:c>
+      <x:c r="E50" s="14" t="str">
+        <x:v>MOODYZ VALUE</x:v>
+      </x:c>
+      <x:c r="F50" s="14" t="str">
+        <x:v>MOODYZ　VALUE</x:v>
+      </x:c>
+      <x:c r="G50" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H50" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I50" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5409</x:v>
+      </x:c>
+      <x:c r="J50" s="14" t="str">
+        <x:v>moodyz.label:5409</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="14" t="str">
+        <x:v>label_000050</x:v>
+      </x:c>
+      <x:c r="B51" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C51" s="14" t="str">
+        <x:v>ハメドリ</x:v>
+      </x:c>
+      <x:c r="D51" s="14" t="str"/>
+      <x:c r="E51" s="14" t="str"/>
+      <x:c r="F51" s="14" t="str"/>
+      <x:c r="G51" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H51" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I51" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10174</x:v>
+      </x:c>
+      <x:c r="J51" s="14" t="str">
+        <x:v>moodyz.label:10174</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="14" t="str">
+        <x:v>label_000051</x:v>
+      </x:c>
+      <x:c r="B52" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C52" s="14" t="str">
+        <x:v>MOODYZ ASS</x:v>
+      </x:c>
+      <x:c r="D52" s="14" t="str">
+        <x:v>MOODYZ ASS</x:v>
+      </x:c>
+      <x:c r="E52" s="14" t="str">
+        <x:v>MOODYZ ASS</x:v>
+      </x:c>
+      <x:c r="F52" s="14" t="str"/>
+      <x:c r="G52" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H52" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I52" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/8916</x:v>
+      </x:c>
+      <x:c r="J52" s="14" t="str">
+        <x:v>moodyz.label:8916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="14" t="str">
+        <x:v>label_000052</x:v>
+      </x:c>
+      <x:c r="B53" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C53" s="14" t="str">
+        <x:v>Q-EYE</x:v>
+      </x:c>
+      <x:c r="D53" s="14" t="str">
+        <x:v>Q-EYE</x:v>
+      </x:c>
+      <x:c r="E53" s="14" t="str">
+        <x:v>Q-EYE</x:v>
+      </x:c>
+      <x:c r="F53" s="14" t="str"/>
+      <x:c r="G53" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H53" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I53" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9397</x:v>
+      </x:c>
+      <x:c r="J53" s="14" t="str">
+        <x:v>moodyz.label:9397</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="14" t="str">
+        <x:v>label_000053</x:v>
+      </x:c>
+      <x:c r="B54" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C54" s="14" t="str">
+        <x:v>エロい！</x:v>
+      </x:c>
+      <x:c r="D54" s="14" t="str"/>
+      <x:c r="E54" s="14" t="str"/>
+      <x:c r="F54" s="14" t="str"/>
+      <x:c r="G54" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H54" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I54" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10106</x:v>
+      </x:c>
+      <x:c r="J54" s="14" t="str">
+        <x:v>moodyz.label:10106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="14" t="str">
+        <x:v>label_000054</x:v>
+      </x:c>
+      <x:c r="B55" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C55" s="14" t="str">
+        <x:v>寝取られ本舗</x:v>
+      </x:c>
+      <x:c r="D55" s="14" t="str"/>
+      <x:c r="E55" s="14" t="str"/>
+      <x:c r="F55" s="14" t="str"/>
+      <x:c r="G55" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H55" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I55" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9288</x:v>
+      </x:c>
+      <x:c r="J55" s="14" t="str">
+        <x:v>moodyz.label:9288</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="14" t="str">
+        <x:v>label_000055</x:v>
+      </x:c>
+      <x:c r="B56" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C56" s="14" t="str">
+        <x:v>MOODYZ ES</x:v>
+      </x:c>
+      <x:c r="D56" s="14" t="str">
+        <x:v>MOODYZ ES</x:v>
+      </x:c>
+      <x:c r="E56" s="14" t="str">
+        <x:v>MOODYZ ES</x:v>
+      </x:c>
+      <x:c r="F56" s="14" t="str"/>
+      <x:c r="G56" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H56" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I56" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/8917</x:v>
+      </x:c>
+      <x:c r="J56" s="14" t="str">
+        <x:v>moodyz.label:8917</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="14" t="str">
+        <x:v>label_000056</x:v>
+      </x:c>
+      <x:c r="B57" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C57" s="14" t="str">
+        <x:v>春のパンツまつり</x:v>
+      </x:c>
+      <x:c r="D57" s="14" t="str">
+        <x:v>春季内裤祭</x:v>
+      </x:c>
+      <x:c r="E57" s="14" t="str">
+        <x:v>Spring Panties Festival</x:v>
+      </x:c>
+      <x:c r="F57" s="14" t="str"/>
+      <x:c r="G57" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H57" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I57" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/85265</x:v>
+      </x:c>
+      <x:c r="J57" s="14" t="str">
+        <x:v>moodyz.label:85265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="14" t="str">
+        <x:v>label_000057</x:v>
+      </x:c>
+      <x:c r="B58" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C58" s="14" t="str">
+        <x:v>BD-MOODYZ DIVA</x:v>
+      </x:c>
+      <x:c r="D58" s="14" t="str">
+        <x:v>BD-MOODYZ DIVA</x:v>
+      </x:c>
+      <x:c r="E58" s="14" t="str">
+        <x:v>BD-MOODYZ DIVA</x:v>
+      </x:c>
+      <x:c r="F58" s="14" t="str"/>
+      <x:c r="G58" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H58" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I58" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/11471</x:v>
+      </x:c>
+      <x:c r="J58" s="14" t="str">
+        <x:v>moodyz.label:11471</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="14" t="str">
+        <x:v>label_000058</x:v>
+      </x:c>
+      <x:c r="B59" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C59" s="14" t="str">
+        <x:v>MOODYZ HARD</x:v>
+      </x:c>
+      <x:c r="D59" s="14" t="str">
+        <x:v>MOODYZ HARD</x:v>
+      </x:c>
+      <x:c r="E59" s="14" t="str">
+        <x:v>MOODYZ HARD</x:v>
+      </x:c>
+      <x:c r="F59" s="14" t="str"/>
+      <x:c r="G59" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H59" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I59" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10157</x:v>
+      </x:c>
+      <x:c r="J59" s="14" t="str">
+        <x:v>moodyz.label:10157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="14" t="str">
+        <x:v>label_000059</x:v>
+      </x:c>
+      <x:c r="B60" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C60" s="14" t="str">
+        <x:v>AVOPEN</x:v>
+      </x:c>
+      <x:c r="D60" s="14" t="str">
+        <x:v>AVOPEN</x:v>
+      </x:c>
+      <x:c r="E60" s="14" t="str">
+        <x:v>AVOPEN</x:v>
+      </x:c>
+      <x:c r="F60" s="14" t="str"/>
+      <x:c r="G60" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H60" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I60" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9483</x:v>
+      </x:c>
+      <x:c r="J60" s="14" t="str">
+        <x:v>moodyz.label:9483</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="14" t="str">
+        <x:v>label_000060</x:v>
+      </x:c>
+      <x:c r="B61" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C61" s="14" t="str">
+        <x:v>おっぱい祭り</x:v>
+      </x:c>
+      <x:c r="D61" s="14" t="str">
+        <x:v>Oppai祭</x:v>
+      </x:c>
+      <x:c r="E61" s="14" t="str">
+        <x:v>Oppai Festival</x:v>
+      </x:c>
+      <x:c r="F61" s="14" t="str"/>
+      <x:c r="G61" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H61" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I61" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10142</x:v>
+      </x:c>
+      <x:c r="J61" s="14" t="str">
+        <x:v>moodyz.label:10142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="14" t="str">
+        <x:v>label_000061</x:v>
+      </x:c>
+      <x:c r="B62" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C62" s="14" t="str">
+        <x:v>秋のシコシコ強化月間</x:v>
+      </x:c>
+      <x:c r="D62" s="14" t="str">
+        <x:v>秋季强化月</x:v>
+      </x:c>
+      <x:c r="E62" s="14" t="str"/>
+      <x:c r="F62" s="14" t="str"/>
+      <x:c r="G62" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H62" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I62" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10144</x:v>
+      </x:c>
+      <x:c r="J62" s="14" t="str">
+        <x:v>moodyz.label:10144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="14" t="str">
+        <x:v>label_000062</x:v>
+      </x:c>
+      <x:c r="B63" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C63" s="14" t="str">
+        <x:v>背徳ビチョビチョ！NTR大放出</x:v>
+      </x:c>
+      <x:c r="D63" s="14" t="str">
+        <x:v>背德湿透！NTR大放出</x:v>
+      </x:c>
+      <x:c r="E63" s="14" t="str"/>
+      <x:c r="F63" s="14" t="str"/>
+      <x:c r="G63" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H63" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I63" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10151</x:v>
+      </x:c>
+      <x:c r="J63" s="14" t="str">
+        <x:v>moodyz.label:10151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="14" t="str">
+        <x:v>label_000063</x:v>
+      </x:c>
+      <x:c r="B64" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C64" s="14" t="str">
+        <x:v>AVグランプリ</x:v>
+      </x:c>
+      <x:c r="D64" s="14" t="str">
+        <x:v>AV大奖赛</x:v>
+      </x:c>
+      <x:c r="E64" s="14" t="str">
+        <x:v>AV Grand Prix</x:v>
+      </x:c>
+      <x:c r="F64" s="14" t="str">
+        <x:v>AV Grand Prix</x:v>
+      </x:c>
+      <x:c r="G64" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H64" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I64" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10077</x:v>
+      </x:c>
+      <x:c r="J64" s="14" t="str">
+        <x:v>moodyz.label:10077</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="14" t="str">
+        <x:v>label_000064</x:v>
+      </x:c>
+      <x:c r="B65" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C65" s="14" t="str">
+        <x:v>MOODYZショート</x:v>
+      </x:c>
+      <x:c r="D65" s="14" t="str">
+        <x:v>MOODYZ短片</x:v>
+      </x:c>
+      <x:c r="E65" s="14" t="str">
+        <x:v>MOODYZ Short</x:v>
+      </x:c>
+      <x:c r="F65" s="14" t="str"/>
+      <x:c r="G65" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H65" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I65" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10172</x:v>
+      </x:c>
+      <x:c r="J65" s="14" t="str">
+        <x:v>moodyz.label:10172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="14" t="str">
+        <x:v>label_000065</x:v>
+      </x:c>
+      <x:c r="B66" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C66" s="14" t="str">
+        <x:v>ティッシュ</x:v>
+      </x:c>
+      <x:c r="D66" s="14" t="str"/>
+      <x:c r="E66" s="14" t="str"/>
+      <x:c r="F66" s="14" t="str"/>
+      <x:c r="G66" s="14" t="str">
+        <x:v>maker_000001</x:v>
+      </x:c>
+      <x:c r="H66" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I66" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/2771</x:v>
+      </x:c>
+      <x:c r="J66" s="14" t="str">
+        <x:v>ideapocket.label:2771</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="14" t="str">
+        <x:v>label_000066</x:v>
+      </x:c>
+      <x:c r="B67" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C67" s="14" t="str">
+        <x:v>アイデアポケットBEST</x:v>
+      </x:c>
+      <x:c r="D67" s="14" t="str">
+        <x:v>IDEAPOCKET BEST</x:v>
+      </x:c>
+      <x:c r="E67" s="14" t="str">
+        <x:v>IDEAPOCKET BEST</x:v>
+      </x:c>
+      <x:c r="F67" s="14" t="str"/>
+      <x:c r="G67" s="14" t="str">
+        <x:v>maker_000001</x:v>
+      </x:c>
+      <x:c r="H67" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I67" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/2769</x:v>
+      </x:c>
+      <x:c r="J67" s="14" t="str">
+        <x:v>ideapocket.label:2769</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="14" t="str">
+        <x:v>label_000067</x:v>
+      </x:c>
+      <x:c r="B68" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C68" s="14" t="str">
+        <x:v>IP-VR</x:v>
+      </x:c>
+      <x:c r="D68" s="14" t="str">
+        <x:v>IP-VR</x:v>
+      </x:c>
+      <x:c r="E68" s="14" t="str">
+        <x:v>IP-VR</x:v>
+      </x:c>
+      <x:c r="F68" s="14" t="str"/>
+      <x:c r="G68" s="14" t="str">
+        <x:v>maker_000001</x:v>
+      </x:c>
+      <x:c r="H68" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I68" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/9790</x:v>
+      </x:c>
+      <x:c r="J68" s="14" t="str">
+        <x:v>ideapocket.label:9790</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="14" t="str">
+        <x:v>label_000068</x:v>
+      </x:c>
+      <x:c r="B69" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C69" s="14" t="str">
+        <x:v>Supreme</x:v>
+      </x:c>
+      <x:c r="D69" s="14" t="str">
+        <x:v>Supreme</x:v>
+      </x:c>
+      <x:c r="E69" s="14" t="str">
+        <x:v>Supreme</x:v>
+      </x:c>
+      <x:c r="F69" s="14" t="str"/>
+      <x:c r="G69" s="14" t="str">
+        <x:v>maker_000001</x:v>
+      </x:c>
+      <x:c r="H69" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I69" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/2776</x:v>
+      </x:c>
+      <x:c r="J69" s="14" t="str">
+        <x:v>ideapocket.label:2776</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="14" t="str">
+        <x:v>label_000069</x:v>
+      </x:c>
+      <x:c r="B70" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C70" s="14" t="str">
+        <x:v>アイポケ逸材発掘プロジェクト</x:v>
+      </x:c>
+      <x:c r="D70" s="14" t="str"/>
+      <x:c r="E70" s="14" t="str"/>
+      <x:c r="F70" s="14" t="str"/>
+      <x:c r="G70" s="14" t="str">
+        <x:v>maker_000001</x:v>
+      </x:c>
+      <x:c r="H70" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I70" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/12442</x:v>
+      </x:c>
+      <x:c r="J70" s="14" t="str">
+        <x:v>ideapocket.label:12442</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="14" t="str">
+        <x:v>label_000070</x:v>
+      </x:c>
+      <x:c r="B71" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C71" s="14" t="str">
+        <x:v>HIGH-SCHOOL Pink</x:v>
+      </x:c>
+      <x:c r="D71" s="14" t="str">
+        <x:v>HIGH-SCHOOL Pink</x:v>
+      </x:c>
+      <x:c r="E71" s="14" t="str">
+        <x:v>HIGH-SCHOOL Pink</x:v>
+      </x:c>
+      <x:c r="F71" s="14" t="str">
+        <x:v>HIGH-SCHOOL　Pink</x:v>
+      </x:c>
+      <x:c r="G71" s="14" t="str">
+        <x:v>maker_000001</x:v>
+      </x:c>
+      <x:c r="H71" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I71" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/2767</x:v>
+      </x:c>
+      <x:c r="J71" s="14" t="str">
+        <x:v>ideapocket.label:2767</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="14" t="str">
+        <x:v>label_000071</x:v>
+      </x:c>
+      <x:c r="B72" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C72" s="14" t="str">
+        <x:v>ゆるポケ</x:v>
+      </x:c>
+      <x:c r="D72" s="14" t="str"/>
+      <x:c r="E72" s="14" t="str"/>
+      <x:c r="F72" s="14" t="str"/>
+      <x:c r="G72" s="14" t="str">
+        <x:v>maker_000001</x:v>
+      </x:c>
+      <x:c r="H72" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I72" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/12835</x:v>
+      </x:c>
+      <x:c r="J72" s="14" t="str">
+        <x:v>ideapocket.label:12835</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="14" t="str">
+        <x:v>label_000072</x:v>
+      </x:c>
+      <x:c r="B73" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C73" s="14" t="str">
+        <x:v>Angel</x:v>
+      </x:c>
+      <x:c r="D73" s="14" t="str">
+        <x:v>Angel</x:v>
+      </x:c>
+      <x:c r="E73" s="14" t="str">
+        <x:v>Angel</x:v>
+      </x:c>
+      <x:c r="F73" s="14" t="str"/>
+      <x:c r="G73" s="14" t="str">
+        <x:v>maker_000001</x:v>
+      </x:c>
+      <x:c r="H73" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I73" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/2758</x:v>
+      </x:c>
+      <x:c r="J73" s="14" t="str">
+        <x:v>ideapocket.label:2758</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="14" t="str">
+        <x:v>label_000073</x:v>
+      </x:c>
+      <x:c r="B74" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C74" s="14" t="str">
+        <x:v>SELECTED</x:v>
+      </x:c>
+      <x:c r="D74" s="14" t="str">
+        <x:v>SELECTED</x:v>
+      </x:c>
+      <x:c r="E74" s="14" t="str">
+        <x:v>SELECTED</x:v>
+      </x:c>
+      <x:c r="F74" s="14" t="str"/>
+      <x:c r="G74" s="14" t="str">
+        <x:v>maker_000001</x:v>
+      </x:c>
+      <x:c r="H74" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I74" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/10103</x:v>
+      </x:c>
+      <x:c r="J74" s="14" t="str">
+        <x:v>ideapocket.label:10103</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="14" t="str">
+        <x:v>label_000074</x:v>
+      </x:c>
+      <x:c r="B75" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C75" s="14" t="str">
+        <x:v>AVOPEN</x:v>
+      </x:c>
+      <x:c r="D75" s="14" t="str">
+        <x:v>AVOPEN</x:v>
+      </x:c>
+      <x:c r="E75" s="14" t="str">
+        <x:v>AVOPEN</x:v>
+      </x:c>
+      <x:c r="F75" s="14" t="str"/>
+      <x:c r="G75" s="14" t="str">
+        <x:v>maker_000001</x:v>
+      </x:c>
+      <x:c r="H75" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I75" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/9483</x:v>
+      </x:c>
+      <x:c r="J75" s="14" t="str">
+        <x:v>ideapocket.label:9483</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="14" t="str">
+        <x:v>label_000075</x:v>
+      </x:c>
+      <x:c r="B76" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C76" s="14" t="str">
+        <x:v>春のパンツまつり</x:v>
+      </x:c>
+      <x:c r="D76" s="14" t="str">
+        <x:v>春季内裤祭</x:v>
+      </x:c>
+      <x:c r="E76" s="14" t="str">
+        <x:v>Spring Panties Festival</x:v>
+      </x:c>
+      <x:c r="F76" s="14" t="str"/>
+      <x:c r="G76" s="14" t="str">
+        <x:v>maker_000001</x:v>
+      </x:c>
+      <x:c r="H76" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I76" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/85265</x:v>
+      </x:c>
+      <x:c r="J76" s="14" t="str">
+        <x:v>ideapocket.label:85265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="14" t="str">
+        <x:v>label_000076</x:v>
+      </x:c>
+      <x:c r="B77" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C77" s="14" t="str">
+        <x:v>AVグランプリ</x:v>
+      </x:c>
+      <x:c r="D77" s="14" t="str">
+        <x:v>AV大奖赛</x:v>
+      </x:c>
+      <x:c r="E77" s="14" t="str">
+        <x:v>AV Grand Prix</x:v>
+      </x:c>
+      <x:c r="F77" s="14" t="str">
+        <x:v>AV Grand Prix</x:v>
+      </x:c>
+      <x:c r="G77" s="14" t="str">
+        <x:v>maker_000001</x:v>
+      </x:c>
+      <x:c r="H77" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I77" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/10077</x:v>
+      </x:c>
+      <x:c r="J77" s="14" t="str">
+        <x:v>ideapocket.label:10077</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="14" t="str">
+        <x:v>label_000077</x:v>
+      </x:c>
+      <x:c r="B78" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C78" s="14" t="str">
+        <x:v>おっぱい祭り</x:v>
+      </x:c>
+      <x:c r="D78" s="14" t="str">
+        <x:v>Oppai祭</x:v>
+      </x:c>
+      <x:c r="E78" s="14" t="str">
+        <x:v>Oppai Festival</x:v>
+      </x:c>
+      <x:c r="F78" s="14" t="str"/>
+      <x:c r="G78" s="14" t="str">
+        <x:v>maker_000001</x:v>
+      </x:c>
+      <x:c r="H78" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I78" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/10142</x:v>
+      </x:c>
+      <x:c r="J78" s="14" t="str">
+        <x:v>ideapocket.label:10142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="14" t="str">
+        <x:v>label_000078</x:v>
+      </x:c>
+      <x:c r="B79" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C79" s="14" t="str">
+        <x:v>背徳ビチョビチョ！NTR大放出</x:v>
+      </x:c>
+      <x:c r="D79" s="14" t="str">
+        <x:v>背德湿透！NTR大放出</x:v>
+      </x:c>
+      <x:c r="E79" s="14" t="str"/>
+      <x:c r="F79" s="14" t="str"/>
+      <x:c r="G79" s="14" t="str">
+        <x:v>maker_000001</x:v>
+      </x:c>
+      <x:c r="H79" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I79" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/10151</x:v>
+      </x:c>
+      <x:c r="J79" s="14" t="str">
+        <x:v>ideapocket.label:10151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="14" t="str">
+        <x:v>label_000079</x:v>
+      </x:c>
+      <x:c r="B80" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C80" s="14" t="str">
+        <x:v>Angel PREMIUM</x:v>
+      </x:c>
+      <x:c r="D80" s="14" t="str">
+        <x:v>Angel PREMIUM</x:v>
+      </x:c>
+      <x:c r="E80" s="14" t="str">
+        <x:v>Angel PREMIUM</x:v>
+      </x:c>
+      <x:c r="F80" s="14" t="str">
+        <x:v>Angel　PREMIUM</x:v>
+      </x:c>
+      <x:c r="G80" s="14" t="str">
+        <x:v>maker_000001</x:v>
+      </x:c>
+      <x:c r="H80" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I80" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/2760</x:v>
+      </x:c>
+      <x:c r="J80" s="14" t="str">
+        <x:v>ideapocket.label:2760</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="14" t="str">
+        <x:v>label_000080</x:v>
+      </x:c>
+      <x:c r="B81" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C81" s="14" t="str">
+        <x:v>秋のシコシコ強化月間</x:v>
+      </x:c>
+      <x:c r="D81" s="14" t="str">
+        <x:v>秋季强化月</x:v>
+      </x:c>
+      <x:c r="E81" s="14" t="str"/>
+      <x:c r="F81" s="14" t="str"/>
+      <x:c r="G81" s="14" t="str">
+        <x:v>maker_000001</x:v>
+      </x:c>
+      <x:c r="H81" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I81" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/10144</x:v>
+      </x:c>
+      <x:c r="J81" s="14" t="str">
+        <x:v>ideapocket.label:10144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="14" t="str">
+        <x:v>maker_000001</x:v>
+      </x:c>
+      <x:c r="B82" s="14" t="str">
+        <x:v>maker</x:v>
+      </x:c>
+      <x:c r="C82" s="14" t="str">
+        <x:v>アイデアポケット</x:v>
+      </x:c>
+      <x:c r="D82" s="14" t="str"/>
+      <x:c r="E82" s="14" t="str"/>
+      <x:c r="F82" s="14" t="str"/>
+      <x:c r="G82" s="14" t="str"/>
+      <x:c r="H82" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I82" s="14" t="str">
+        <x:v>https://ideapocket.com/</x:v>
+      </x:c>
+      <x:c r="J82" s="14" t="str"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="B83" s="14" t="str">
+        <x:v>maker</x:v>
+      </x:c>
+      <x:c r="C83" s="14" t="str">
+        <x:v>MOODYZ</x:v>
+      </x:c>
+      <x:c r="D83" s="14" t="str"/>
+      <x:c r="E83" s="14" t="str"/>
+      <x:c r="F83" s="14" t="str"/>
+      <x:c r="G83" s="14" t="str"/>
+      <x:c r="H83" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I83" s="14" t="str">
+        <x:v>https://moodyz.com/</x:v>
+      </x:c>
+      <x:c r="J83" s="14" t="str"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="14" t="str">
+        <x:v>maker_000003</x:v>
+      </x:c>
+      <x:c r="B84" s="14" t="str">
+        <x:v>maker</x:v>
+      </x:c>
+      <x:c r="C84" s="14" t="str">
+        <x:v>エスワン</x:v>
+      </x:c>
+      <x:c r="D84" s="14" t="str"/>
+      <x:c r="E84" s="14" t="str"/>
+      <x:c r="F84" s="14" t="str"/>
+      <x:c r="G84" s="14" t="str"/>
+      <x:c r="H84" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I84" s="14" t="str">
+        <x:v>https://s1s1s1.com/</x:v>
+      </x:c>
+      <x:c r="J84" s="14" t="str"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="B85" s="14" t="str">
+        <x:v>maker</x:v>
+      </x:c>
+      <x:c r="C85" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="D85" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="E85" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="F85" s="14" t="str">
+        <x:v>アタッカーズ</x:v>
+      </x:c>
+      <x:c r="G85" s="14" t="str"/>
+      <x:c r="H85" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I85" s="14" t="str">
+        <x:v>https://attackers.net/</x:v>
+      </x:c>
+      <x:c r="J85" s="14" t="str"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
-      <x:c r="B43" s="14" t="str">
+      <x:c r="B86" s="14" t="str">
         <x:v>maker</x:v>
       </x:c>
-      <x:c r="C43" s="14" t="str">
+      <x:c r="C86" s="14" t="str">
         <x:v>マドンナ</x:v>
       </x:c>
-      <x:c r="D43" s="14" t="str">
+      <x:c r="D86" s="14" t="str">
         <x:v>Madonna</x:v>
       </x:c>
-      <x:c r="E43" s="14" t="str">
+      <x:c r="E86" s="14" t="str">
         <x:v>Madonna</x:v>
       </x:c>
-      <x:c r="F43" s="14" t="str">
+      <x:c r="F86" s="14" t="str">
         <x:v>Madonna</x:v>
       </x:c>
-      <x:c r="G43" s="14" t="str"/>
-      <x:c r="H43" s="14" t="str">
-        <x:v>unknown</x:v>
-      </x:c>
-      <x:c r="I43" s="14" t="str">
+      <x:c r="G86" s="14" t="str"/>
+      <x:c r="H86" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I86" s="14" t="str">
         <x:v>https://madonna-av.com/</x:v>
       </x:c>
-      <x:c r="J43" s="14" t="str"/>
+      <x:c r="J86" s="14" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1561,7 +2851,7 @@
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="50" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="28" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1725,16 +3015,16 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="44" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="54" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="70" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="66" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="76" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1760,10 +3050,10 @@
         <x:v>最后检查</x:v>
       </x:c>
       <x:c r="H1" s="6" t="str">
-        <x:v>完整遍历</x:v>
+        <x:v>来源完整遍历</x:v>
       </x:c>
       <x:c r="I1" s="6" t="str">
-        <x:v>覆盖统计</x:v>
+        <x:v>实体类型覆盖</x:v>
       </x:c>
       <x:c r="J1" s="6" t="str">
         <x:v>已知限制</x:v>
@@ -1795,10 +3085,10 @@
         <x:v>no</x:v>
       </x:c>
       <x:c r="I2" s="14" t="str">
-        <x:v>series: 2/2 published</x:v>
+        <x:v>label: 16/16 published, complete=yes; series: 2/2 published, complete=no</x:v>
       </x:c>
       <x:c r="J2" s="14" t="str">
-        <x:v>本批次只验证高复用 Series 样本，没有遍历整个 Series 索引和所有分页。</x:v>
+        <x:v>IDEAPOCKET 当前官方 Label Index 已完整遍历；Series 仍未完整枚举，因此来源级 completeTraversal 继续为 false。历史已删除/隐藏 Label 与其他实体类型不在本批次完整性声明内。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1827,10 +3117,10 @@
         <x:v>no</x:v>
       </x:c>
       <x:c r="I3" s="14" t="str">
-        <x:v>label: 2/2 published; series: 1/1 published</x:v>
+        <x:v>label: 29/29 published, complete=yes; series: 1/1 published, complete=no</x:v>
       </x:c>
       <x:c r="J3" s="14" t="str">
-        <x:v>尚未完整枚举全部 Label 和 Series，因此不能声明 MOODYZ 当前公开目录已覆盖。</x:v>
+        <x:v>MOODYZ 当前官方 Label Index 已完整遍历；Series 仍未完整枚举，因此来源级 completeTraversal 继续为 false。历史已删除/隐藏 Label 与其他实体类型不在本批次完整性声明内。</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1859,7 +3149,7 @@
         <x:v>no</x:v>
       </x:c>
       <x:c r="I4" s="14" t="str">
-        <x:v>series: 1/1 published</x:v>
+        <x:v>series: 1/1 published, complete=no</x:v>
       </x:c>
       <x:c r="J4" s="14" t="str">
         <x:v>新人NO.1STYLE 页面本身存在多页作品，但本批次目标是确认 Series 实体，不等价于完整枚举 S1 全部 Series。</x:v>
@@ -1891,7 +3181,7 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="I5" s="14" t="str">
-        <x:v>company: 0/1 published</x:v>
+        <x:v>company: 0/1 published, complete=yes</x:v>
       </x:c>
       <x:c r="J5" s="14" t="str">
         <x:v>Localogue 当前正式 OrganizationKind 尚未把 company 作为一等消费类型，因此先进入 Staging，不伪装成 Maker。</x:v>
@@ -1923,7 +3213,7 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="I6" s="14" t="str">
-        <x:v>maker: 1/1 published; label: 17/17 published</x:v>
+        <x:v>maker: 1/1 published, complete=yes; label: 17/17 published, complete=yes</x:v>
       </x:c>
       <x:c r="J6" s="14" t="str">
         <x:v>completeTraversal=true 仅表示 2026-09-04 时点官方 /works/label 当前可见索引已全部遍历；不代表历史已删除 Label、Series、Work 或集团/法律公司关系已完整覆盖。</x:v>
@@ -1955,7 +3245,7 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="I7" s="14" t="str">
-        <x:v>maker: 1/1 published; label: 18/18 published</x:v>
+        <x:v>maker: 1/1 published, complete=yes; label: 18/18 published, complete=yes</x:v>
       </x:c>
       <x:c r="J7" s="14" t="str">
         <x:v>completeTraversal=true 仅表示 2026-09-04 时点官方 /works/label 当前可见索引已全部遍历；不代表历史已删除 Label、Series、Work 或集团/法律公司关系已完整覆盖。</x:v>
@@ -1976,7 +3266,7 @@
     <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="54" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="56" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -2943,6 +4233,995 @@
       </x:c>
       <x:c r="G42" s="14" t="str">
         <x:v>https://madonna-av.com/works/list/label/3125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B43" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C43" s="14" t="str">
+        <x:v>5047</x:v>
+      </x:c>
+      <x:c r="D43" s="14" t="str">
+        <x:v>label_000038</x:v>
+      </x:c>
+      <x:c r="E43" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F43" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G43" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5047</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B44" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C44" s="14" t="str">
+        <x:v>5046</x:v>
+      </x:c>
+      <x:c r="D44" s="14" t="str">
+        <x:v>label_000039</x:v>
+      </x:c>
+      <x:c r="E44" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F44" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G44" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5046</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B45" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C45" s="14" t="str">
+        <x:v>6879</x:v>
+      </x:c>
+      <x:c r="D45" s="14" t="str">
+        <x:v>label_000040</x:v>
+      </x:c>
+      <x:c r="E45" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F45" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G45" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/6879</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B46" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C46" s="14" t="str">
+        <x:v>9782</x:v>
+      </x:c>
+      <x:c r="D46" s="14" t="str">
+        <x:v>label_000041</x:v>
+      </x:c>
+      <x:c r="E46" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F46" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G46" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9782</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B47" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C47" s="14" t="str">
+        <x:v>9732</x:v>
+      </x:c>
+      <x:c r="D47" s="14" t="str">
+        <x:v>label_000042</x:v>
+      </x:c>
+      <x:c r="E47" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F47" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G47" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9732</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B48" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C48" s="14" t="str">
+        <x:v>9308</x:v>
+      </x:c>
+      <x:c r="D48" s="14" t="str">
+        <x:v>label_000043</x:v>
+      </x:c>
+      <x:c r="E48" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F48" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G48" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B49" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C49" s="14" t="str">
+        <x:v>5090</x:v>
+      </x:c>
+      <x:c r="D49" s="14" t="str">
+        <x:v>label_000044</x:v>
+      </x:c>
+      <x:c r="E49" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F49" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G49" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5090</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B50" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C50" s="14" t="str">
+        <x:v>5049</x:v>
+      </x:c>
+      <x:c r="D50" s="14" t="str">
+        <x:v>label_000045</x:v>
+      </x:c>
+      <x:c r="E50" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F50" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G50" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5049</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B51" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C51" s="14" t="str">
+        <x:v>10107</x:v>
+      </x:c>
+      <x:c r="D51" s="14" t="str">
+        <x:v>label_000046</x:v>
+      </x:c>
+      <x:c r="E51" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F51" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G51" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B52" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C52" s="14" t="str">
+        <x:v>10131</x:v>
+      </x:c>
+      <x:c r="D52" s="14" t="str">
+        <x:v>label_000047</x:v>
+      </x:c>
+      <x:c r="E52" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F52" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G52" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B53" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C53" s="14" t="str">
+        <x:v>9458</x:v>
+      </x:c>
+      <x:c r="D53" s="14" t="str">
+        <x:v>label_000048</x:v>
+      </x:c>
+      <x:c r="E53" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F53" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G53" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9458</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B54" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C54" s="14" t="str">
+        <x:v>5409</x:v>
+      </x:c>
+      <x:c r="D54" s="14" t="str">
+        <x:v>label_000049</x:v>
+      </x:c>
+      <x:c r="E54" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F54" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G54" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5409</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B55" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C55" s="14" t="str">
+        <x:v>10174</x:v>
+      </x:c>
+      <x:c r="D55" s="14" t="str">
+        <x:v>label_000050</x:v>
+      </x:c>
+      <x:c r="E55" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F55" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G55" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10174</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B56" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C56" s="14" t="str">
+        <x:v>8916</x:v>
+      </x:c>
+      <x:c r="D56" s="14" t="str">
+        <x:v>label_000051</x:v>
+      </x:c>
+      <x:c r="E56" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F56" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G56" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/8916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B57" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C57" s="14" t="str">
+        <x:v>9397</x:v>
+      </x:c>
+      <x:c r="D57" s="14" t="str">
+        <x:v>label_000052</x:v>
+      </x:c>
+      <x:c r="E57" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F57" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G57" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9397</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B58" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C58" s="14" t="str">
+        <x:v>10106</x:v>
+      </x:c>
+      <x:c r="D58" s="14" t="str">
+        <x:v>label_000053</x:v>
+      </x:c>
+      <x:c r="E58" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F58" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G58" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B59" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C59" s="14" t="str">
+        <x:v>9288</x:v>
+      </x:c>
+      <x:c r="D59" s="14" t="str">
+        <x:v>label_000054</x:v>
+      </x:c>
+      <x:c r="E59" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F59" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G59" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9288</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B60" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C60" s="14" t="str">
+        <x:v>8917</x:v>
+      </x:c>
+      <x:c r="D60" s="14" t="str">
+        <x:v>label_000055</x:v>
+      </x:c>
+      <x:c r="E60" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F60" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G60" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/8917</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B61" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C61" s="14" t="str">
+        <x:v>85265</x:v>
+      </x:c>
+      <x:c r="D61" s="14" t="str">
+        <x:v>label_000056</x:v>
+      </x:c>
+      <x:c r="E61" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F61" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G61" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/85265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B62" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C62" s="14" t="str">
+        <x:v>11471</x:v>
+      </x:c>
+      <x:c r="D62" s="14" t="str">
+        <x:v>label_000057</x:v>
+      </x:c>
+      <x:c r="E62" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F62" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G62" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/11471</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B63" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C63" s="14" t="str">
+        <x:v>10157</x:v>
+      </x:c>
+      <x:c r="D63" s="14" t="str">
+        <x:v>label_000058</x:v>
+      </x:c>
+      <x:c r="E63" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F63" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G63" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B64" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C64" s="14" t="str">
+        <x:v>9483</x:v>
+      </x:c>
+      <x:c r="D64" s="14" t="str">
+        <x:v>label_000059</x:v>
+      </x:c>
+      <x:c r="E64" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F64" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G64" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9483</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B65" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C65" s="14" t="str">
+        <x:v>10142</x:v>
+      </x:c>
+      <x:c r="D65" s="14" t="str">
+        <x:v>label_000060</x:v>
+      </x:c>
+      <x:c r="E65" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F65" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G65" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B66" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C66" s="14" t="str">
+        <x:v>10144</x:v>
+      </x:c>
+      <x:c r="D66" s="14" t="str">
+        <x:v>label_000061</x:v>
+      </x:c>
+      <x:c r="E66" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F66" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G66" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B67" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C67" s="14" t="str">
+        <x:v>10151</x:v>
+      </x:c>
+      <x:c r="D67" s="14" t="str">
+        <x:v>label_000062</x:v>
+      </x:c>
+      <x:c r="E67" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F67" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G67" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B68" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C68" s="14" t="str">
+        <x:v>10077</x:v>
+      </x:c>
+      <x:c r="D68" s="14" t="str">
+        <x:v>label_000063</x:v>
+      </x:c>
+      <x:c r="E68" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F68" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G68" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10077</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B69" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C69" s="14" t="str">
+        <x:v>10172</x:v>
+      </x:c>
+      <x:c r="D69" s="14" t="str">
+        <x:v>label_000064</x:v>
+      </x:c>
+      <x:c r="E69" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F69" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G69" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="B70" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C70" s="14" t="str">
+        <x:v>2771</x:v>
+      </x:c>
+      <x:c r="D70" s="14" t="str">
+        <x:v>label_000065</x:v>
+      </x:c>
+      <x:c r="E70" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F70" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G70" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/2771</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="B71" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C71" s="14" t="str">
+        <x:v>2769</x:v>
+      </x:c>
+      <x:c r="D71" s="14" t="str">
+        <x:v>label_000066</x:v>
+      </x:c>
+      <x:c r="E71" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F71" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G71" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/2769</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="B72" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C72" s="14" t="str">
+        <x:v>9790</x:v>
+      </x:c>
+      <x:c r="D72" s="14" t="str">
+        <x:v>label_000067</x:v>
+      </x:c>
+      <x:c r="E72" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F72" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G72" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/9790</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="B73" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C73" s="14" t="str">
+        <x:v>2776</x:v>
+      </x:c>
+      <x:c r="D73" s="14" t="str">
+        <x:v>label_000068</x:v>
+      </x:c>
+      <x:c r="E73" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F73" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G73" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/2776</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="B74" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C74" s="14" t="str">
+        <x:v>12442</x:v>
+      </x:c>
+      <x:c r="D74" s="14" t="str">
+        <x:v>label_000069</x:v>
+      </x:c>
+      <x:c r="E74" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F74" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G74" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/12442</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="B75" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C75" s="14" t="str">
+        <x:v>2767</x:v>
+      </x:c>
+      <x:c r="D75" s="14" t="str">
+        <x:v>label_000070</x:v>
+      </x:c>
+      <x:c r="E75" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F75" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G75" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/2767</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="B76" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C76" s="14" t="str">
+        <x:v>12835</x:v>
+      </x:c>
+      <x:c r="D76" s="14" t="str">
+        <x:v>label_000071</x:v>
+      </x:c>
+      <x:c r="E76" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F76" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G76" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/12835</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="B77" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C77" s="14" t="str">
+        <x:v>2758</x:v>
+      </x:c>
+      <x:c r="D77" s="14" t="str">
+        <x:v>label_000072</x:v>
+      </x:c>
+      <x:c r="E77" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F77" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G77" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/2758</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="B78" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C78" s="14" t="str">
+        <x:v>10103</x:v>
+      </x:c>
+      <x:c r="D78" s="14" t="str">
+        <x:v>label_000073</x:v>
+      </x:c>
+      <x:c r="E78" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F78" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G78" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/10103</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="B79" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C79" s="14" t="str">
+        <x:v>9483</x:v>
+      </x:c>
+      <x:c r="D79" s="14" t="str">
+        <x:v>label_000074</x:v>
+      </x:c>
+      <x:c r="E79" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F79" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G79" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/9483</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="B80" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C80" s="14" t="str">
+        <x:v>85265</x:v>
+      </x:c>
+      <x:c r="D80" s="14" t="str">
+        <x:v>label_000075</x:v>
+      </x:c>
+      <x:c r="E80" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F80" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G80" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/85265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="B81" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C81" s="14" t="str">
+        <x:v>10077</x:v>
+      </x:c>
+      <x:c r="D81" s="14" t="str">
+        <x:v>label_000076</x:v>
+      </x:c>
+      <x:c r="E81" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F81" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G81" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/10077</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="B82" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C82" s="14" t="str">
+        <x:v>10142</x:v>
+      </x:c>
+      <x:c r="D82" s="14" t="str">
+        <x:v>label_000077</x:v>
+      </x:c>
+      <x:c r="E82" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F82" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G82" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/10142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="B83" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C83" s="14" t="str">
+        <x:v>10151</x:v>
+      </x:c>
+      <x:c r="D83" s="14" t="str">
+        <x:v>label_000078</x:v>
+      </x:c>
+      <x:c r="E83" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F83" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G83" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/10151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="B84" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C84" s="14" t="str">
+        <x:v>2760</x:v>
+      </x:c>
+      <x:c r="D84" s="14" t="str">
+        <x:v>label_000079</x:v>
+      </x:c>
+      <x:c r="E84" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F84" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G84" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/2760</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="B85" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C85" s="14" t="str">
+        <x:v>10144</x:v>
+      </x:c>
+      <x:c r="D85" s="14" t="str">
+        <x:v>label_000080</x:v>
+      </x:c>
+      <x:c r="E85" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F85" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G85" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/10144</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2958,8 +5237,8 @@
     <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="70" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="48" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="72" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="50" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -3019,7 +5298,7 @@
     <x:col min="6" max="6" width="40" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="54" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="56" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -4158,6 +6437,1167 @@
         <x:v>https://madonna-av.com/works/list/label/3125</x:v>
       </x:c>
     </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B43" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C43" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D43" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E43" s="14" t="str">
+        <x:v>5047</x:v>
+      </x:c>
+      <x:c r="F43" s="14" t="str">
+        <x:v>MOODYZ BEST</x:v>
+      </x:c>
+      <x:c r="G43" s="14" t="str">
+        <x:v>label_000038</x:v>
+      </x:c>
+      <x:c r="H43" s="14" t="str"/>
+      <x:c r="I43" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5047</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B44" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C44" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D44" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E44" s="14" t="str">
+        <x:v>5046</x:v>
+      </x:c>
+      <x:c r="F44" s="14" t="str">
+        <x:v>MOODYZ ACID</x:v>
+      </x:c>
+      <x:c r="G44" s="14" t="str">
+        <x:v>label_000039</x:v>
+      </x:c>
+      <x:c r="H44" s="14" t="str"/>
+      <x:c r="I44" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5046</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B45" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C45" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D45" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E45" s="14" t="str">
+        <x:v>6879</x:v>
+      </x:c>
+      <x:c r="F45" s="14" t="str">
+        <x:v>MOODYZ GATI</x:v>
+      </x:c>
+      <x:c r="G45" s="14" t="str">
+        <x:v>label_000040</x:v>
+      </x:c>
+      <x:c r="H45" s="14" t="str"/>
+      <x:c r="I45" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/6879</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B46" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C46" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D46" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E46" s="14" t="str">
+        <x:v>9782</x:v>
+      </x:c>
+      <x:c r="F46" s="14" t="str">
+        <x:v>MOODYZ VR</x:v>
+      </x:c>
+      <x:c r="G46" s="14" t="str">
+        <x:v>label_000041</x:v>
+      </x:c>
+      <x:c r="H46" s="14" t="str"/>
+      <x:c r="I46" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9782</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B47" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C47" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D47" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E47" s="14" t="str">
+        <x:v>9732</x:v>
+      </x:c>
+      <x:c r="F47" s="14" t="str">
+        <x:v>MOODYZ Fresh</x:v>
+      </x:c>
+      <x:c r="G47" s="14" t="str">
+        <x:v>label_000042</x:v>
+      </x:c>
+      <x:c r="H47" s="14" t="str"/>
+      <x:c r="I47" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9732</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B48" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C48" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D48" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E48" s="14" t="str">
+        <x:v>9308</x:v>
+      </x:c>
+      <x:c r="F48" s="14" t="str">
+        <x:v>まんきつ</x:v>
+      </x:c>
+      <x:c r="G48" s="14" t="str">
+        <x:v>label_000043</x:v>
+      </x:c>
+      <x:c r="H48" s="14" t="str"/>
+      <x:c r="I48" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B49" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C49" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D49" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E49" s="14" t="str">
+        <x:v>5090</x:v>
+      </x:c>
+      <x:c r="F49" s="14" t="str">
+        <x:v>MOODYZ REAL</x:v>
+      </x:c>
+      <x:c r="G49" s="14" t="str">
+        <x:v>label_000044</x:v>
+      </x:c>
+      <x:c r="H49" s="14" t="str"/>
+      <x:c r="I49" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5090</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B50" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C50" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D50" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E50" s="14" t="str">
+        <x:v>5049</x:v>
+      </x:c>
+      <x:c r="F50" s="14" t="str">
+        <x:v>MOODYZ ISM</x:v>
+      </x:c>
+      <x:c r="G50" s="14" t="str">
+        <x:v>label_000045</x:v>
+      </x:c>
+      <x:c r="H50" s="14" t="str"/>
+      <x:c r="I50" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5049</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B51" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C51" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D51" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E51" s="14" t="str">
+        <x:v>10107</x:v>
+      </x:c>
+      <x:c r="F51" s="14" t="str">
+        <x:v>きれいなお姉さんは好きですか</x:v>
+      </x:c>
+      <x:c r="G51" s="14" t="str">
+        <x:v>label_000046</x:v>
+      </x:c>
+      <x:c r="H51" s="14" t="str"/>
+      <x:c r="I51" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B52" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C52" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D52" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E52" s="14" t="str">
+        <x:v>10131</x:v>
+      </x:c>
+      <x:c r="F52" s="14" t="str">
+        <x:v>MOODYZ ニュージーニアス</x:v>
+      </x:c>
+      <x:c r="G52" s="14" t="str">
+        <x:v>label_000047</x:v>
+      </x:c>
+      <x:c r="H52" s="14" t="str"/>
+      <x:c r="I52" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B53" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C53" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D53" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E53" s="14" t="str">
+        <x:v>9458</x:v>
+      </x:c>
+      <x:c r="F53" s="14" t="str">
+        <x:v>MUTTURI</x:v>
+      </x:c>
+      <x:c r="G53" s="14" t="str">
+        <x:v>label_000048</x:v>
+      </x:c>
+      <x:c r="H53" s="14" t="str"/>
+      <x:c r="I53" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9458</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B54" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C54" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D54" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E54" s="14" t="str">
+        <x:v>5409</x:v>
+      </x:c>
+      <x:c r="F54" s="14" t="str">
+        <x:v>MOODYZ VALUE</x:v>
+      </x:c>
+      <x:c r="G54" s="14" t="str">
+        <x:v>label_000049</x:v>
+      </x:c>
+      <x:c r="H54" s="14" t="str"/>
+      <x:c r="I54" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5409</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B55" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C55" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D55" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E55" s="14" t="str">
+        <x:v>10174</x:v>
+      </x:c>
+      <x:c r="F55" s="14" t="str">
+        <x:v>ハメドリ</x:v>
+      </x:c>
+      <x:c r="G55" s="14" t="str">
+        <x:v>label_000050</x:v>
+      </x:c>
+      <x:c r="H55" s="14" t="str"/>
+      <x:c r="I55" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10174</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B56" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C56" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D56" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E56" s="14" t="str">
+        <x:v>8916</x:v>
+      </x:c>
+      <x:c r="F56" s="14" t="str">
+        <x:v>MOODYZ ASS</x:v>
+      </x:c>
+      <x:c r="G56" s="14" t="str">
+        <x:v>label_000051</x:v>
+      </x:c>
+      <x:c r="H56" s="14" t="str"/>
+      <x:c r="I56" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/8916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B57" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C57" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D57" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E57" s="14" t="str">
+        <x:v>9397</x:v>
+      </x:c>
+      <x:c r="F57" s="14" t="str">
+        <x:v>Q-EYE</x:v>
+      </x:c>
+      <x:c r="G57" s="14" t="str">
+        <x:v>label_000052</x:v>
+      </x:c>
+      <x:c r="H57" s="14" t="str"/>
+      <x:c r="I57" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9397</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B58" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C58" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D58" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E58" s="14" t="str">
+        <x:v>10106</x:v>
+      </x:c>
+      <x:c r="F58" s="14" t="str">
+        <x:v>エロい！</x:v>
+      </x:c>
+      <x:c r="G58" s="14" t="str">
+        <x:v>label_000053</x:v>
+      </x:c>
+      <x:c r="H58" s="14" t="str"/>
+      <x:c r="I58" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B59" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C59" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D59" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E59" s="14" t="str">
+        <x:v>9288</x:v>
+      </x:c>
+      <x:c r="F59" s="14" t="str">
+        <x:v>寝取られ本舗</x:v>
+      </x:c>
+      <x:c r="G59" s="14" t="str">
+        <x:v>label_000054</x:v>
+      </x:c>
+      <x:c r="H59" s="14" t="str"/>
+      <x:c r="I59" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9288</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B60" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C60" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D60" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E60" s="14" t="str">
+        <x:v>8917</x:v>
+      </x:c>
+      <x:c r="F60" s="14" t="str">
+        <x:v>MOODYZ ES</x:v>
+      </x:c>
+      <x:c r="G60" s="14" t="str">
+        <x:v>label_000055</x:v>
+      </x:c>
+      <x:c r="H60" s="14" t="str"/>
+      <x:c r="I60" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/8917</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B61" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C61" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D61" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E61" s="14" t="str">
+        <x:v>85265</x:v>
+      </x:c>
+      <x:c r="F61" s="14" t="str">
+        <x:v>春のパンツまつり</x:v>
+      </x:c>
+      <x:c r="G61" s="14" t="str">
+        <x:v>label_000056</x:v>
+      </x:c>
+      <x:c r="H61" s="14" t="str"/>
+      <x:c r="I61" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/85265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B62" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C62" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D62" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E62" s="14" t="str">
+        <x:v>11471</x:v>
+      </x:c>
+      <x:c r="F62" s="14" t="str">
+        <x:v>BD-MOODYZ DIVA</x:v>
+      </x:c>
+      <x:c r="G62" s="14" t="str">
+        <x:v>label_000057</x:v>
+      </x:c>
+      <x:c r="H62" s="14" t="str"/>
+      <x:c r="I62" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/11471</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B63" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C63" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D63" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E63" s="14" t="str">
+        <x:v>10157</x:v>
+      </x:c>
+      <x:c r="F63" s="14" t="str">
+        <x:v>MOODYZ HARD</x:v>
+      </x:c>
+      <x:c r="G63" s="14" t="str">
+        <x:v>label_000058</x:v>
+      </x:c>
+      <x:c r="H63" s="14" t="str"/>
+      <x:c r="I63" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B64" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C64" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D64" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E64" s="14" t="str">
+        <x:v>9483</x:v>
+      </x:c>
+      <x:c r="F64" s="14" t="str">
+        <x:v>AVOPEN</x:v>
+      </x:c>
+      <x:c r="G64" s="14" t="str">
+        <x:v>label_000059</x:v>
+      </x:c>
+      <x:c r="H64" s="14" t="str"/>
+      <x:c r="I64" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9483</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B65" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C65" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D65" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E65" s="14" t="str">
+        <x:v>10142</x:v>
+      </x:c>
+      <x:c r="F65" s="14" t="str">
+        <x:v>おっぱい祭り</x:v>
+      </x:c>
+      <x:c r="G65" s="14" t="str">
+        <x:v>label_000060</x:v>
+      </x:c>
+      <x:c r="H65" s="14" t="str"/>
+      <x:c r="I65" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B66" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C66" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D66" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E66" s="14" t="str">
+        <x:v>10144</x:v>
+      </x:c>
+      <x:c r="F66" s="14" t="str">
+        <x:v>秋のシコシコ強化月間</x:v>
+      </x:c>
+      <x:c r="G66" s="14" t="str">
+        <x:v>label_000061</x:v>
+      </x:c>
+      <x:c r="H66" s="14" t="str"/>
+      <x:c r="I66" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B67" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C67" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D67" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E67" s="14" t="str">
+        <x:v>10151</x:v>
+      </x:c>
+      <x:c r="F67" s="14" t="str">
+        <x:v>背徳ビチョビチョ！NTR大放出</x:v>
+      </x:c>
+      <x:c r="G67" s="14" t="str">
+        <x:v>label_000062</x:v>
+      </x:c>
+      <x:c r="H67" s="14" t="str"/>
+      <x:c r="I67" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B68" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C68" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D68" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E68" s="14" t="str">
+        <x:v>10077</x:v>
+      </x:c>
+      <x:c r="F68" s="14" t="str">
+        <x:v>AVグランプリ</x:v>
+      </x:c>
+      <x:c r="G68" s="14" t="str">
+        <x:v>label_000063</x:v>
+      </x:c>
+      <x:c r="H68" s="14" t="str"/>
+      <x:c r="I68" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10077</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B69" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C69" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D69" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E69" s="14" t="str">
+        <x:v>10172</x:v>
+      </x:c>
+      <x:c r="F69" s="14" t="str">
+        <x:v>MOODYZショート</x:v>
+      </x:c>
+      <x:c r="G69" s="14" t="str">
+        <x:v>label_000064</x:v>
+      </x:c>
+      <x:c r="H69" s="14" t="str"/>
+      <x:c r="I69" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B70" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C70" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="D70" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E70" s="14" t="str">
+        <x:v>2771</x:v>
+      </x:c>
+      <x:c r="F70" s="14" t="str">
+        <x:v>ティッシュ</x:v>
+      </x:c>
+      <x:c r="G70" s="14" t="str">
+        <x:v>label_000065</x:v>
+      </x:c>
+      <x:c r="H70" s="14" t="str"/>
+      <x:c r="I70" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/2771</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B71" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C71" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="D71" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E71" s="14" t="str">
+        <x:v>2769</x:v>
+      </x:c>
+      <x:c r="F71" s="14" t="str">
+        <x:v>アイデアポケットBEST</x:v>
+      </x:c>
+      <x:c r="G71" s="14" t="str">
+        <x:v>label_000066</x:v>
+      </x:c>
+      <x:c r="H71" s="14" t="str"/>
+      <x:c r="I71" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/2769</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B72" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C72" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="D72" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E72" s="14" t="str">
+        <x:v>9790</x:v>
+      </x:c>
+      <x:c r="F72" s="14" t="str">
+        <x:v>IP-VR</x:v>
+      </x:c>
+      <x:c r="G72" s="14" t="str">
+        <x:v>label_000067</x:v>
+      </x:c>
+      <x:c r="H72" s="14" t="str"/>
+      <x:c r="I72" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/9790</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B73" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C73" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="D73" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E73" s="14" t="str">
+        <x:v>2776</x:v>
+      </x:c>
+      <x:c r="F73" s="14" t="str">
+        <x:v>Supreme</x:v>
+      </x:c>
+      <x:c r="G73" s="14" t="str">
+        <x:v>label_000068</x:v>
+      </x:c>
+      <x:c r="H73" s="14" t="str"/>
+      <x:c r="I73" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/2776</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B74" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C74" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="D74" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E74" s="14" t="str">
+        <x:v>12442</x:v>
+      </x:c>
+      <x:c r="F74" s="14" t="str">
+        <x:v>アイポケ逸材発掘プロジェクト</x:v>
+      </x:c>
+      <x:c r="G74" s="14" t="str">
+        <x:v>label_000069</x:v>
+      </x:c>
+      <x:c r="H74" s="14" t="str"/>
+      <x:c r="I74" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/12442</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B75" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C75" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="D75" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E75" s="14" t="str">
+        <x:v>2767</x:v>
+      </x:c>
+      <x:c r="F75" s="14" t="str">
+        <x:v>HIGH-SCHOOL Pink</x:v>
+      </x:c>
+      <x:c r="G75" s="14" t="str">
+        <x:v>label_000070</x:v>
+      </x:c>
+      <x:c r="H75" s="14" t="str"/>
+      <x:c r="I75" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/2767</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B76" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C76" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="D76" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E76" s="14" t="str">
+        <x:v>12835</x:v>
+      </x:c>
+      <x:c r="F76" s="14" t="str">
+        <x:v>ゆるポケ</x:v>
+      </x:c>
+      <x:c r="G76" s="14" t="str">
+        <x:v>label_000071</x:v>
+      </x:c>
+      <x:c r="H76" s="14" t="str"/>
+      <x:c r="I76" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/12835</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B77" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C77" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="D77" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E77" s="14" t="str">
+        <x:v>2758</x:v>
+      </x:c>
+      <x:c r="F77" s="14" t="str">
+        <x:v>Angel</x:v>
+      </x:c>
+      <x:c r="G77" s="14" t="str">
+        <x:v>label_000072</x:v>
+      </x:c>
+      <x:c r="H77" s="14" t="str"/>
+      <x:c r="I77" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/2758</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B78" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C78" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="D78" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E78" s="14" t="str">
+        <x:v>10103</x:v>
+      </x:c>
+      <x:c r="F78" s="14" t="str">
+        <x:v>SELECTED</x:v>
+      </x:c>
+      <x:c r="G78" s="14" t="str">
+        <x:v>label_000073</x:v>
+      </x:c>
+      <x:c r="H78" s="14" t="str"/>
+      <x:c r="I78" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/10103</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B79" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C79" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="D79" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E79" s="14" t="str">
+        <x:v>9483</x:v>
+      </x:c>
+      <x:c r="F79" s="14" t="str">
+        <x:v>AVOPEN</x:v>
+      </x:c>
+      <x:c r="G79" s="14" t="str">
+        <x:v>label_000074</x:v>
+      </x:c>
+      <x:c r="H79" s="14" t="str"/>
+      <x:c r="I79" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/9483</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B80" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C80" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="D80" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E80" s="14" t="str">
+        <x:v>85265</x:v>
+      </x:c>
+      <x:c r="F80" s="14" t="str">
+        <x:v>春のパンツまつり</x:v>
+      </x:c>
+      <x:c r="G80" s="14" t="str">
+        <x:v>label_000075</x:v>
+      </x:c>
+      <x:c r="H80" s="14" t="str"/>
+      <x:c r="I80" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/85265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B81" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C81" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="D81" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E81" s="14" t="str">
+        <x:v>10077</x:v>
+      </x:c>
+      <x:c r="F81" s="14" t="str">
+        <x:v>AVグランプリ</x:v>
+      </x:c>
+      <x:c r="G81" s="14" t="str">
+        <x:v>label_000076</x:v>
+      </x:c>
+      <x:c r="H81" s="14" t="str"/>
+      <x:c r="I81" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/10077</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B82" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C82" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="D82" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E82" s="14" t="str">
+        <x:v>10142</x:v>
+      </x:c>
+      <x:c r="F82" s="14" t="str">
+        <x:v>おっぱい祭り</x:v>
+      </x:c>
+      <x:c r="G82" s="14" t="str">
+        <x:v>label_000077</x:v>
+      </x:c>
+      <x:c r="H82" s="14" t="str"/>
+      <x:c r="I82" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/10142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B83" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C83" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="D83" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E83" s="14" t="str">
+        <x:v>10151</x:v>
+      </x:c>
+      <x:c r="F83" s="14" t="str">
+        <x:v>背徳ビチョビチョ！NTR大放出</x:v>
+      </x:c>
+      <x:c r="G83" s="14" t="str">
+        <x:v>label_000078</x:v>
+      </x:c>
+      <x:c r="H83" s="14" t="str"/>
+      <x:c r="I83" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/10151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B84" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C84" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="D84" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E84" s="14" t="str">
+        <x:v>2760</x:v>
+      </x:c>
+      <x:c r="F84" s="14" t="str">
+        <x:v>Angel PREMIUM</x:v>
+      </x:c>
+      <x:c r="G84" s="14" t="str">
+        <x:v>label_000079</x:v>
+      </x:c>
+      <x:c r="H84" s="14" t="str"/>
+      <x:c r="I84" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/2760</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B85" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C85" s="14" t="str">
+        <x:v>ideapocket.label</x:v>
+      </x:c>
+      <x:c r="D85" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E85" s="14" t="str">
+        <x:v>10144</x:v>
+      </x:c>
+      <x:c r="F85" s="14" t="str">
+        <x:v>秋のシコシコ強化月間</x:v>
+      </x:c>
+      <x:c r="G85" s="14" t="str">
+        <x:v>label_000080</x:v>
+      </x:c>
+      <x:c r="H85" s="14" t="str"/>
+      <x:c r="I85" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/label/10144</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/exports/xlsx/organization-series-registry.xlsx
+++ b/exports/xlsx/organization-series-registry.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organizations" sheetId="1" r:id="Ra6d2b7576cd8440f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series" sheetId="2" r:id="R5f15b0d030c84e0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Registry" sheetId="3" r:id="R8adec21e8c77418a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External ID Mapping" sheetId="4" r:id="R4d43d99bcdc04073"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidates" sheetId="5" r:id="R53377e02164a4b0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="6" r:id="R50081e7e53e14103"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organizations" sheetId="1" r:id="R402bda752bc146a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series" sheetId="2" r:id="R9c3a3dc39cb14519"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Registry" sheetId="3" r:id="R3b5d9f67d01d449a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External ID Mapping" sheetId="4" r:id="R25c7f3ffefb94747"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidates" sheetId="5" r:id="R19c77bb446bc42ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="6" r:id="R5ce4d898e9b14088"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -293,11 +293,11 @@
     <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="32" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="50" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="52" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -2713,35 +2713,45 @@
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="14" t="str">
-        <x:v>maker_000001</x:v>
+        <x:v>label_000081</x:v>
       </x:c>
       <x:c r="B82" s="14" t="str">
-        <x:v>maker</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C82" s="14" t="str">
-        <x:v>アイデアポケット</x:v>
-      </x:c>
-      <x:c r="D82" s="14" t="str"/>
-      <x:c r="E82" s="14" t="str"/>
-      <x:c r="F82" s="14" t="str"/>
-      <x:c r="G82" s="14" t="str"/>
+        <x:v>S1 NO.1 STYLE</x:v>
+      </x:c>
+      <x:c r="D82" s="14" t="str">
+        <x:v>S1 NO.1 STYLE</x:v>
+      </x:c>
+      <x:c r="E82" s="14" t="str">
+        <x:v>S1 NO.1 STYLE</x:v>
+      </x:c>
+      <x:c r="F82" s="14" t="str">
+        <x:v>S1　NO.1　STYLE</x:v>
+      </x:c>
+      <x:c r="G82" s="14" t="str">
+        <x:v>maker_000003</x:v>
+      </x:c>
       <x:c r="H82" s="14" t="str">
         <x:v>unknown</x:v>
       </x:c>
       <x:c r="I82" s="14" t="str">
-        <x:v>https://ideapocket.com/</x:v>
-      </x:c>
-      <x:c r="J82" s="14" t="str"/>
+        <x:v>https://s1s1s1.com/works/list/label/4355</x:v>
+      </x:c>
+      <x:c r="J82" s="14" t="str">
+        <x:v>s1.label:4355</x:v>
+      </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="14" t="str">
-        <x:v>maker_000002</x:v>
+        <x:v>maker_000001</x:v>
       </x:c>
       <x:c r="B83" s="14" t="str">
         <x:v>maker</x:v>
       </x:c>
       <x:c r="C83" s="14" t="str">
-        <x:v>MOODYZ</x:v>
+        <x:v>アイデアポケット</x:v>
       </x:c>
       <x:c r="D83" s="14" t="str"/>
       <x:c r="E83" s="14" t="str"/>
@@ -2751,19 +2761,19 @@
         <x:v>unknown</x:v>
       </x:c>
       <x:c r="I83" s="14" t="str">
-        <x:v>https://moodyz.com/</x:v>
+        <x:v>https://ideapocket.com/</x:v>
       </x:c>
       <x:c r="J83" s="14" t="str"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="14" t="str">
-        <x:v>maker_000003</x:v>
+        <x:v>maker_000002</x:v>
       </x:c>
       <x:c r="B84" s="14" t="str">
         <x:v>maker</x:v>
       </x:c>
       <x:c r="C84" s="14" t="str">
-        <x:v>エスワン</x:v>
+        <x:v>MOODYZ</x:v>
       </x:c>
       <x:c r="D84" s="14" t="str"/>
       <x:c r="E84" s="14" t="str"/>
@@ -2773,65 +2783,87 @@
         <x:v>unknown</x:v>
       </x:c>
       <x:c r="I84" s="14" t="str">
-        <x:v>https://s1s1s1.com/</x:v>
+        <x:v>https://moodyz.com/</x:v>
       </x:c>
       <x:c r="J84" s="14" t="str"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="14" t="str">
-        <x:v>maker_000004</x:v>
+        <x:v>maker_000003</x:v>
       </x:c>
       <x:c r="B85" s="14" t="str">
         <x:v>maker</x:v>
       </x:c>
       <x:c r="C85" s="14" t="str">
-        <x:v>ATTACKERS</x:v>
-      </x:c>
-      <x:c r="D85" s="14" t="str">
-        <x:v>ATTACKERS</x:v>
-      </x:c>
-      <x:c r="E85" s="14" t="str">
-        <x:v>ATTACKERS</x:v>
-      </x:c>
-      <x:c r="F85" s="14" t="str">
-        <x:v>アタッカーズ</x:v>
-      </x:c>
+        <x:v>エスワン</x:v>
+      </x:c>
+      <x:c r="D85" s="14" t="str"/>
+      <x:c r="E85" s="14" t="str"/>
+      <x:c r="F85" s="14" t="str"/>
       <x:c r="G85" s="14" t="str"/>
       <x:c r="H85" s="14" t="str">
         <x:v>unknown</x:v>
       </x:c>
       <x:c r="I85" s="14" t="str">
-        <x:v>https://attackers.net/</x:v>
+        <x:v>https://s1s1s1.com/</x:v>
       </x:c>
       <x:c r="J85" s="14" t="str"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000004</x:v>
       </x:c>
       <x:c r="B86" s="14" t="str">
         <x:v>maker</x:v>
       </x:c>
       <x:c r="C86" s="14" t="str">
-        <x:v>マドンナ</x:v>
+        <x:v>ATTACKERS</x:v>
       </x:c>
       <x:c r="D86" s="14" t="str">
-        <x:v>Madonna</x:v>
+        <x:v>ATTACKERS</x:v>
       </x:c>
       <x:c r="E86" s="14" t="str">
-        <x:v>Madonna</x:v>
+        <x:v>ATTACKERS</x:v>
       </x:c>
       <x:c r="F86" s="14" t="str">
-        <x:v>Madonna</x:v>
+        <x:v>アタッカーズ</x:v>
       </x:c>
       <x:c r="G86" s="14" t="str"/>
       <x:c r="H86" s="14" t="str">
         <x:v>unknown</x:v>
       </x:c>
       <x:c r="I86" s="14" t="str">
+        <x:v>https://attackers.net/</x:v>
+      </x:c>
+      <x:c r="J86" s="14" t="str"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="B87" s="14" t="str">
+        <x:v>maker</x:v>
+      </x:c>
+      <x:c r="C87" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="D87" s="14" t="str">
+        <x:v>Madonna</x:v>
+      </x:c>
+      <x:c r="E87" s="14" t="str">
+        <x:v>Madonna</x:v>
+      </x:c>
+      <x:c r="F87" s="14" t="str">
+        <x:v>Madonna</x:v>
+      </x:c>
+      <x:c r="G87" s="14" t="str"/>
+      <x:c r="H87" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I87" s="14" t="str">
         <x:v>https://madonna-av.com/</x:v>
       </x:c>
-      <x:c r="J86" s="14" t="str"/>
+      <x:c r="J87" s="14" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2843,14 +2875,14 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="38" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="44" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="42" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="50" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="54" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -3004,6 +3036,396 @@
       </x:c>
       <x:c r="J5" s="14" t="str">
         <x:v>ideapocket.series:1011</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="14" t="str">
+        <x:v>series_000005</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="str">
+        <x:v>おま●こ、くぱぁ</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="str">
+        <x:v>阴部，张开</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="str">
+        <x:v>Spread Open</x:v>
+      </x:c>
+      <x:c r="E6" s="14" t="str">
+        <x:v>maker_000003</x:v>
+      </x:c>
+      <x:c r="F6" s="14" t="str">
+        <x:v>エスワン</x:v>
+      </x:c>
+      <x:c r="G6" s="14" t="str"/>
+      <x:c r="H6" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I6" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/422</x:v>
+      </x:c>
+      <x:c r="J6" s="14" t="str">
+        <x:v>s1.series:422</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="14" t="str">
+        <x:v>series_000006</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="str">
+        <x:v>ラブキモメン</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="str">
+        <x:v>爱上恶心男</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="str">
+        <x:v>Love Creepy Men</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="str">
+        <x:v>maker_000003</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="str">
+        <x:v>エスワン</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="str"/>
+      <x:c r="H7" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I7" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/570</x:v>
+      </x:c>
+      <x:c r="J7" s="14" t="str">
+        <x:v>s1.series:570</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="14" t="str">
+        <x:v>series_000007</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="str">
+        <x:v>侵入者</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="str">
+        <x:v>入侵者</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="str">
+        <x:v>Intruder</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="str"/>
+      <x:c r="H8" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I8" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2402</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="str">
+        <x:v>attackers.series:2402</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="14" t="str">
+        <x:v>series_000008</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="str">
+        <x:v>あなたに愛されたくて。</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="str">
+        <x:v>渴望被你爱。</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="str">
+        <x:v>Wanting to Be Loved by You</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="str"/>
+      <x:c r="H9" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I9" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2269</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="str">
+        <x:v>attackers.series:2269</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="14" t="str">
+        <x:v>series_000009</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="str">
+        <x:v>あなた、許して…。</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="str">
+        <x:v>亲爱的，请原谅我……</x:v>
+      </x:c>
+      <x:c r="D10" s="14" t="str">
+        <x:v>Please Forgive Me...</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="str"/>
+      <x:c r="H10" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I10" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2270</x:v>
+      </x:c>
+      <x:c r="J10" s="14" t="str">
+        <x:v>attackers.series:2270</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="14" t="str">
+        <x:v>series_000010</x:v>
+      </x:c>
+      <x:c r="B11" s="14" t="str">
+        <x:v>脱獄者</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="str">
+        <x:v>越狱者</x:v>
+      </x:c>
+      <x:c r="D11" s="14" t="str">
+        <x:v>Escapee</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="str"/>
+      <x:c r="H11" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I11" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2293</x:v>
+      </x:c>
+      <x:c r="J11" s="14" t="str">
+        <x:v>attackers.series:2293</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="14" t="str">
+        <x:v>series_000011</x:v>
+      </x:c>
+      <x:c r="B12" s="14" t="str">
+        <x:v>奴隷島</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="str">
+        <x:v>奴隶岛</x:v>
+      </x:c>
+      <x:c r="D12" s="14" t="str">
+        <x:v>Slave Island</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="str"/>
+      <x:c r="H12" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I12" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2256</x:v>
+      </x:c>
+      <x:c r="J12" s="14" t="str">
+        <x:v>attackers.series:2256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="14" t="str">
+        <x:v>series_000012</x:v>
+      </x:c>
+      <x:c r="B13" s="14" t="str">
+        <x:v>犯される度に美しく</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="str">
+        <x:v>每次被侵犯都更加美丽</x:v>
+      </x:c>
+      <x:c r="D13" s="14" t="str">
+        <x:v>More Beautiful Each Time</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="str"/>
+      <x:c r="H13" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I13" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2274</x:v>
+      </x:c>
+      <x:c r="J13" s="14" t="str">
+        <x:v>attackers.series:2274</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="14" t="str">
+        <x:v>series_000013</x:v>
+      </x:c>
+      <x:c r="B14" s="14" t="str">
+        <x:v>団鬼六</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="str">
+        <x:v>团鬼六</x:v>
+      </x:c>
+      <x:c r="D14" s="14" t="str">
+        <x:v>Dan Oniroku</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="str"/>
+      <x:c r="H14" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I14" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2325</x:v>
+      </x:c>
+      <x:c r="J14" s="14" t="str">
+        <x:v>attackers.series:2325</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="14" t="str">
+        <x:v>series_000014</x:v>
+      </x:c>
+      <x:c r="B15" s="14" t="str">
+        <x:v>調教志願</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="str">
+        <x:v>自愿调教</x:v>
+      </x:c>
+      <x:c r="D15" s="14" t="str">
+        <x:v>Voluntary Training</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="str"/>
+      <x:c r="H15" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I15" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/5317</x:v>
+      </x:c>
+      <x:c r="J15" s="14" t="str">
+        <x:v>attackers.series:5317</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="14" t="str">
+        <x:v>series_000015</x:v>
+      </x:c>
+      <x:c r="B16" s="14" t="str">
+        <x:v>年下レズビアンに愛された私</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="str">
+        <x:v>被年下女同性恋者爱上的我</x:v>
+      </x:c>
+      <x:c r="D16" s="14" t="str">
+        <x:v>Loved by a Younger Lesbian</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="str"/>
+      <x:c r="H16" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I16" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1846</x:v>
+      </x:c>
+      <x:c r="J16" s="14" t="str">
+        <x:v>madonna.series:1846</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="14" t="str">
+        <x:v>series_000016</x:v>
+      </x:c>
+      <x:c r="B17" s="14" t="str">
+        <x:v>廃業寸前</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="str">
+        <x:v>濒临停业</x:v>
+      </x:c>
+      <x:c r="D17" s="14" t="str">
+        <x:v>On the Verge of Closing</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="str"/>
+      <x:c r="H17" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I17" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1891</x:v>
+      </x:c>
+      <x:c r="J17" s="14" t="str">
+        <x:v>madonna.series:1891</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="14" t="str">
+        <x:v>series_000017</x:v>
+      </x:c>
+      <x:c r="B18" s="14" t="str">
+        <x:v>夫の上司に飾られた　人妻ボディアクセサリー</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="str">
+        <x:v>被丈夫上司装饰的人妻身体饰品</x:v>
+      </x:c>
+      <x:c r="D18" s="14" t="str">
+        <x:v>Married Woman Body Accessory Adorned by Her Husband's Boss</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="str"/>
+      <x:c r="H18" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I18" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1749</x:v>
+      </x:c>
+      <x:c r="J18" s="14" t="str">
+        <x:v>madonna.series:1749</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3023,8 +3445,8 @@
     <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="66" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="76" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="70" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="80" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -3149,10 +3571,10 @@
         <x:v>no</x:v>
       </x:c>
       <x:c r="I4" s="14" t="str">
-        <x:v>series: 1/1 published, complete=no</x:v>
+        <x:v>label: 1/1 published, complete=no; series: 3/3 published, complete=no</x:v>
       </x:c>
       <x:c r="J4" s="14" t="str">
-        <x:v>新人NO.1STYLE 页面本身存在多页作品，但本批次目标是确认 Series 实体，不等价于完整枚举 S1 全部 Series。</x:v>
+        <x:v>S1 主 Label 4355 与 3 个 Series 已逐项核验，但官方索引在当前采集环境中未形成可证明的完整枚举快照，因此 Label 与 Series coverage 均保持 incomplete。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3201,7 +3623,7 @@
         <x:v>https://attackers.net/</x:v>
       </x:c>
       <x:c r="E6" s="14" t="str">
-        <x:v>maker; label</x:v>
+        <x:v>maker; label; series</x:v>
       </x:c>
       <x:c r="F6" s="14" t="str">
         <x:v>reachable</x:v>
@@ -3210,13 +3632,13 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="H6" s="14" t="str">
-        <x:v>yes</x:v>
+        <x:v>no</x:v>
       </x:c>
       <x:c r="I6" s="14" t="str">
-        <x:v>maker: 1/1 published, complete=yes; label: 17/17 published, complete=yes</x:v>
+        <x:v>maker: 1/1 published, complete=yes; label: 17/17 published, complete=yes; series: 8/8 published, complete=no</x:v>
       </x:c>
       <x:c r="J6" s="14" t="str">
-        <x:v>completeTraversal=true 仅表示 2026-09-04 时点官方 /works/label 当前可见索引已全部遍历；不代表历史已删除 Label、Series、Work 或集团/法律公司关系已完整覆盖。</x:v>
+        <x:v>ATTACKERS 当前 Maker/Label coverage 已完整；本批次新增 8 个官方 Series 样本，但尚未完整枚举 Series Index，因此来源级 completeTraversal 降为 false。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3233,7 +3655,7 @@
         <x:v>https://madonna-av.com/</x:v>
       </x:c>
       <x:c r="E7" s="14" t="str">
-        <x:v>maker; label</x:v>
+        <x:v>maker; label; series</x:v>
       </x:c>
       <x:c r="F7" s="14" t="str">
         <x:v>reachable</x:v>
@@ -3242,13 +3664,13 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="H7" s="14" t="str">
-        <x:v>yes</x:v>
+        <x:v>no</x:v>
       </x:c>
       <x:c r="I7" s="14" t="str">
-        <x:v>maker: 1/1 published, complete=yes; label: 18/18 published, complete=yes</x:v>
+        <x:v>maker: 1/1 published, complete=yes; label: 18/18 published, complete=yes; series: 3/3 published, complete=no</x:v>
       </x:c>
       <x:c r="J7" s="14" t="str">
-        <x:v>completeTraversal=true 仅表示 2026-09-04 时点官方 /works/label 当前可见索引已全部遍历；不代表历史已删除 Label、Series、Work 或集团/法律公司关系已完整覆盖。</x:v>
+        <x:v>Madonna 当前 Maker/Label coverage 已完整；本批次新增 3 个官方 Series 样本，但尚未完整枚举 Series Index，因此来源级 completeTraversal 降为 false。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3266,7 +3688,7 @@
     <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="56" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="58" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -3294,16 +3716,16 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="14" t="str">
-        <x:v>ideapocket.series</x:v>
+        <x:v>attackers.label</x:v>
       </x:c>
       <x:c r="B2" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C2" s="14" t="str">
-        <x:v>1011</x:v>
+        <x:v>10077</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
-        <x:v>series_000004</x:v>
+        <x:v>label_000016</x:v>
       </x:c>
       <x:c r="E2" s="14" t="str">
         <x:v>approved</x:v>
@@ -3312,21 +3734,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G2" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/series/1011</x:v>
+        <x:v>https://attackers.net/works/list/label/10077</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="14" t="str">
-        <x:v>ideapocket.series</x:v>
+        <x:v>attackers.label</x:v>
       </x:c>
       <x:c r="B3" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C3" s="14" t="str">
-        <x:v>863</x:v>
+        <x:v>10142</x:v>
       </x:c>
       <x:c r="D3" s="14" t="str">
-        <x:v>series_000003</x:v>
+        <x:v>label_000017</x:v>
       </x:c>
       <x:c r="E3" s="14" t="str">
         <x:v>approved</x:v>
@@ -3335,21 +3757,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G3" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/series/863</x:v>
+        <x:v>https://attackers.net/works/list/label/10142</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>attackers.label</x:v>
       </x:c>
       <x:c r="B4" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C4" s="14" t="str">
-        <x:v>12798</x:v>
+        <x:v>10144</x:v>
       </x:c>
       <x:c r="D4" s="14" t="str">
-        <x:v>label_000002</x:v>
+        <x:v>label_000018</x:v>
       </x:c>
       <x:c r="E4" s="14" t="str">
         <x:v>approved</x:v>
@@ -3358,21 +3780,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G4" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/12798</x:v>
+        <x:v>https://attackers.net/works/list/label/10144</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>attackers.label</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
-        <x:v>5048</x:v>
+        <x:v>10151</x:v>
       </x:c>
       <x:c r="D5" s="14" t="str">
-        <x:v>label_000001</x:v>
+        <x:v>label_000019</x:v>
       </x:c>
       <x:c r="E5" s="14" t="str">
         <x:v>approved</x:v>
@@ -3381,21 +3803,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G5" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5048</x:v>
+        <x:v>https://attackers.net/works/list/label/10151</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="14" t="str">
-        <x:v>moodyz.series</x:v>
+        <x:v>attackers.label</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C6" s="14" t="str">
-        <x:v>5427</x:v>
+        <x:v>12605</x:v>
       </x:c>
       <x:c r="D6" s="14" t="str">
-        <x:v>series_000002</x:v>
+        <x:v>label_000011</x:v>
       </x:c>
       <x:c r="E6" s="14" t="str">
         <x:v>approved</x:v>
@@ -3404,21 +3826,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G6" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/series/5427</x:v>
+        <x:v>https://attackers.net/works/list/label/12605</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="14" t="str">
-        <x:v>s1.series</x:v>
+        <x:v>attackers.label</x:v>
       </x:c>
       <x:c r="B7" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C7" s="14" t="str">
-        <x:v>414</x:v>
+        <x:v>2735</x:v>
       </x:c>
       <x:c r="D7" s="14" t="str">
-        <x:v>series_000001</x:v>
+        <x:v>label_000009</x:v>
       </x:c>
       <x:c r="E7" s="14" t="str">
         <x:v>approved</x:v>
@@ -3427,7 +3849,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G7" s="14" t="str">
-        <x:v>https://s1s1s1.com/works/list/series/414</x:v>
+        <x:v>https://attackers.net/works/list/label/2735</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -3438,10 +3860,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C8" s="14" t="str">
-        <x:v>2754</x:v>
+        <x:v>2737</x:v>
       </x:c>
       <x:c r="D8" s="14" t="str">
-        <x:v>label_000003</x:v>
+        <x:v>label_000006</x:v>
       </x:c>
       <x:c r="E8" s="14" t="str">
         <x:v>approved</x:v>
@@ -3450,7 +3872,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G8" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/2754</x:v>
+        <x:v>https://attackers.net/works/list/label/2737</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3461,10 +3883,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C9" s="14" t="str">
-        <x:v>2751</x:v>
+        <x:v>2739</x:v>
       </x:c>
       <x:c r="D9" s="14" t="str">
-        <x:v>label_000004</x:v>
+        <x:v>label_000007</x:v>
       </x:c>
       <x:c r="E9" s="14" t="str">
         <x:v>approved</x:v>
@@ -3473,7 +3895,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G9" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/2751</x:v>
+        <x:v>https://attackers.net/works/list/label/2739</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -3484,10 +3906,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C10" s="14" t="str">
-        <x:v>9455</x:v>
+        <x:v>2749</x:v>
       </x:c>
       <x:c r="D10" s="14" t="str">
-        <x:v>label_000005</x:v>
+        <x:v>label_000008</x:v>
       </x:c>
       <x:c r="E10" s="14" t="str">
         <x:v>approved</x:v>
@@ -3496,7 +3918,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G10" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/9455</x:v>
+        <x:v>https://attackers.net/works/list/label/2749</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -3507,10 +3929,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C11" s="14" t="str">
-        <x:v>2737</x:v>
+        <x:v>2751</x:v>
       </x:c>
       <x:c r="D11" s="14" t="str">
-        <x:v>label_000006</x:v>
+        <x:v>label_000004</x:v>
       </x:c>
       <x:c r="E11" s="14" t="str">
         <x:v>approved</x:v>
@@ -3519,7 +3941,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G11" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/2737</x:v>
+        <x:v>https://attackers.net/works/list/label/2751</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -3530,10 +3952,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C12" s="14" t="str">
-        <x:v>2739</x:v>
+        <x:v>2754</x:v>
       </x:c>
       <x:c r="D12" s="14" t="str">
-        <x:v>label_000007</x:v>
+        <x:v>label_000003</x:v>
       </x:c>
       <x:c r="E12" s="14" t="str">
         <x:v>approved</x:v>
@@ -3542,7 +3964,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G12" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/2739</x:v>
+        <x:v>https://attackers.net/works/list/label/2754</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -3553,10 +3975,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>2749</x:v>
+        <x:v>2756</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
-        <x:v>label_000008</x:v>
+        <x:v>label_000010</x:v>
       </x:c>
       <x:c r="E13" s="14" t="str">
         <x:v>approved</x:v>
@@ -3565,7 +3987,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G13" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/2749</x:v>
+        <x:v>https://attackers.net/works/list/label/2756</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -3576,10 +3998,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>2735</x:v>
+        <x:v>5245</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
-        <x:v>label_000009</x:v>
+        <x:v>label_000013</x:v>
       </x:c>
       <x:c r="E14" s="14" t="str">
         <x:v>approved</x:v>
@@ -3588,7 +4010,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G14" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/2735</x:v>
+        <x:v>https://attackers.net/works/list/label/5245</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -3599,10 +4021,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C15" s="14" t="str">
-        <x:v>2756</x:v>
+        <x:v>81348</x:v>
       </x:c>
       <x:c r="D15" s="14" t="str">
-        <x:v>label_000010</x:v>
+        <x:v>label_000012</x:v>
       </x:c>
       <x:c r="E15" s="14" t="str">
         <x:v>approved</x:v>
@@ -3611,7 +4033,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G15" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/2756</x:v>
+        <x:v>https://attackers.net/works/list/label/81348</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -3622,10 +4044,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C16" s="14" t="str">
-        <x:v>12605</x:v>
+        <x:v>85265</x:v>
       </x:c>
       <x:c r="D16" s="14" t="str">
-        <x:v>label_000011</x:v>
+        <x:v>label_000014</x:v>
       </x:c>
       <x:c r="E16" s="14" t="str">
         <x:v>approved</x:v>
@@ -3634,7 +4056,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G16" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/12605</x:v>
+        <x:v>https://attackers.net/works/list/label/85265</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -3645,10 +4067,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C17" s="14" t="str">
-        <x:v>81348</x:v>
+        <x:v>9455</x:v>
       </x:c>
       <x:c r="D17" s="14" t="str">
-        <x:v>label_000012</x:v>
+        <x:v>label_000005</x:v>
       </x:c>
       <x:c r="E17" s="14" t="str">
         <x:v>approved</x:v>
@@ -3657,7 +4079,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G17" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/81348</x:v>
+        <x:v>https://attackers.net/works/list/label/9455</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -3668,10 +4090,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C18" s="14" t="str">
-        <x:v>5245</x:v>
+        <x:v>9483</x:v>
       </x:c>
       <x:c r="D18" s="14" t="str">
-        <x:v>label_000013</x:v>
+        <x:v>label_000015</x:v>
       </x:c>
       <x:c r="E18" s="14" t="str">
         <x:v>approved</x:v>
@@ -3680,21 +4102,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G18" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/5245</x:v>
+        <x:v>https://attackers.net/works/list/label/9483</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="14" t="str">
-        <x:v>attackers.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B19" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C19" s="14" t="str">
-        <x:v>85265</x:v>
+        <x:v>2256</x:v>
       </x:c>
       <x:c r="D19" s="14" t="str">
-        <x:v>label_000014</x:v>
+        <x:v>series_000011</x:v>
       </x:c>
       <x:c r="E19" s="14" t="str">
         <x:v>approved</x:v>
@@ -3703,21 +4125,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G19" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/85265</x:v>
+        <x:v>https://attackers.net/works/list/series/2256</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="14" t="str">
-        <x:v>attackers.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B20" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
-        <x:v>9483</x:v>
+        <x:v>2269</x:v>
       </x:c>
       <x:c r="D20" s="14" t="str">
-        <x:v>label_000015</x:v>
+        <x:v>series_000008</x:v>
       </x:c>
       <x:c r="E20" s="14" t="str">
         <x:v>approved</x:v>
@@ -3726,21 +4148,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G20" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/9483</x:v>
+        <x:v>https://attackers.net/works/list/series/2269</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="14" t="str">
-        <x:v>attackers.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B21" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
-        <x:v>10077</x:v>
+        <x:v>2270</x:v>
       </x:c>
       <x:c r="D21" s="14" t="str">
-        <x:v>label_000016</x:v>
+        <x:v>series_000009</x:v>
       </x:c>
       <x:c r="E21" s="14" t="str">
         <x:v>approved</x:v>
@@ -3749,21 +4171,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G21" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/10077</x:v>
+        <x:v>https://attackers.net/works/list/series/2270</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="14" t="str">
-        <x:v>attackers.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B22" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
-        <x:v>10142</x:v>
+        <x:v>2274</x:v>
       </x:c>
       <x:c r="D22" s="14" t="str">
-        <x:v>label_000017</x:v>
+        <x:v>series_000012</x:v>
       </x:c>
       <x:c r="E22" s="14" t="str">
         <x:v>approved</x:v>
@@ -3772,21 +4194,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G22" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/10142</x:v>
+        <x:v>https://attackers.net/works/list/series/2274</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="14" t="str">
-        <x:v>attackers.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B23" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C23" s="14" t="str">
-        <x:v>10144</x:v>
+        <x:v>2293</x:v>
       </x:c>
       <x:c r="D23" s="14" t="str">
-        <x:v>label_000018</x:v>
+        <x:v>series_000010</x:v>
       </x:c>
       <x:c r="E23" s="14" t="str">
         <x:v>approved</x:v>
@@ -3795,21 +4217,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G23" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/10144</x:v>
+        <x:v>https://attackers.net/works/list/series/2293</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="14" t="str">
-        <x:v>attackers.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B24" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C24" s="14" t="str">
-        <x:v>10151</x:v>
+        <x:v>2325</x:v>
       </x:c>
       <x:c r="D24" s="14" t="str">
-        <x:v>label_000019</x:v>
+        <x:v>series_000013</x:v>
       </x:c>
       <x:c r="E24" s="14" t="str">
         <x:v>approved</x:v>
@@ -3818,21 +4240,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G24" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/10151</x:v>
+        <x:v>https://attackers.net/works/list/series/2325</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B25" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C25" s="14" t="str">
-        <x:v>3669</x:v>
+        <x:v>2402</x:v>
       </x:c>
       <x:c r="D25" s="14" t="str">
-        <x:v>label_000020</x:v>
+        <x:v>series_000007</x:v>
       </x:c>
       <x:c r="E25" s="14" t="str">
         <x:v>approved</x:v>
@@ -3841,21 +4263,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G25" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/3669</x:v>
+        <x:v>https://attackers.net/works/list/series/2402</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B26" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C26" s="14" t="str">
-        <x:v>12490</x:v>
+        <x:v>5317</x:v>
       </x:c>
       <x:c r="D26" s="14" t="str">
-        <x:v>label_000021</x:v>
+        <x:v>series_000014</x:v>
       </x:c>
       <x:c r="E26" s="14" t="str">
         <x:v>approved</x:v>
@@ -3864,21 +4286,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G26" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/12490</x:v>
+        <x:v>https://attackers.net/works/list/series/5317</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B27" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C27" s="14" t="str">
-        <x:v>9387</x:v>
+        <x:v>10077</x:v>
       </x:c>
       <x:c r="D27" s="14" t="str">
-        <x:v>label_000022</x:v>
+        <x:v>label_000076</x:v>
       </x:c>
       <x:c r="E27" s="14" t="str">
         <x:v>approved</x:v>
@@ -3887,21 +4309,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G27" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/9387</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10077</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B28" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C28" s="14" t="str">
-        <x:v>9789</x:v>
+        <x:v>10103</x:v>
       </x:c>
       <x:c r="D28" s="14" t="str">
-        <x:v>label_000023</x:v>
+        <x:v>label_000073</x:v>
       </x:c>
       <x:c r="E28" s="14" t="str">
         <x:v>approved</x:v>
@@ -3910,21 +4332,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G28" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/9789</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10103</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B29" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C29" s="14" t="str">
-        <x:v>7354</x:v>
+        <x:v>10142</x:v>
       </x:c>
       <x:c r="D29" s="14" t="str">
-        <x:v>label_000024</x:v>
+        <x:v>label_000077</x:v>
       </x:c>
       <x:c r="E29" s="14" t="str">
         <x:v>approved</x:v>
@@ -3933,21 +4355,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G29" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/7354</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10142</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B30" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C30" s="14" t="str">
-        <x:v>9419</x:v>
+        <x:v>10144</x:v>
       </x:c>
       <x:c r="D30" s="14" t="str">
-        <x:v>label_000025</x:v>
+        <x:v>label_000080</x:v>
       </x:c>
       <x:c r="E30" s="14" t="str">
         <x:v>approved</x:v>
@@ -3956,21 +4378,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G30" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/9419</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10144</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B31" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C31" s="14" t="str">
-        <x:v>12603</x:v>
+        <x:v>10151</x:v>
       </x:c>
       <x:c r="D31" s="14" t="str">
-        <x:v>label_000026</x:v>
+        <x:v>label_000078</x:v>
       </x:c>
       <x:c r="E31" s="14" t="str">
         <x:v>approved</x:v>
@@ -3979,21 +4401,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G31" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/12603</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10151</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B32" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C32" s="14" t="str">
-        <x:v>12502</x:v>
+        <x:v>12442</x:v>
       </x:c>
       <x:c r="D32" s="14" t="str">
-        <x:v>label_000027</x:v>
+        <x:v>label_000069</x:v>
       </x:c>
       <x:c r="E32" s="14" t="str">
         <x:v>approved</x:v>
@@ -4002,21 +4424,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G32" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/12502</x:v>
+        <x:v>https://ideapocket.com/works/list/label/12442</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B33" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C33" s="14" t="str">
-        <x:v>10130</x:v>
+        <x:v>12835</x:v>
       </x:c>
       <x:c r="D33" s="14" t="str">
-        <x:v>label_000028</x:v>
+        <x:v>label_000071</x:v>
       </x:c>
       <x:c r="E33" s="14" t="str">
         <x:v>approved</x:v>
@@ -4025,21 +4447,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G33" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10130</x:v>
+        <x:v>https://ideapocket.com/works/list/label/12835</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B34" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C34" s="14" t="str">
-        <x:v>7993</x:v>
+        <x:v>2758</x:v>
       </x:c>
       <x:c r="D34" s="14" t="str">
-        <x:v>label_000029</x:v>
+        <x:v>label_000072</x:v>
       </x:c>
       <x:c r="E34" s="14" t="str">
         <x:v>approved</x:v>
@@ -4048,21 +4470,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G34" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/7993</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2758</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B35" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C35" s="14" t="str">
-        <x:v>10159</x:v>
+        <x:v>2760</x:v>
       </x:c>
       <x:c r="D35" s="14" t="str">
-        <x:v>label_000030</x:v>
+        <x:v>label_000079</x:v>
       </x:c>
       <x:c r="E35" s="14" t="str">
         <x:v>approved</x:v>
@@ -4071,21 +4493,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G35" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10159</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2760</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B36" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C36" s="14" t="str">
-        <x:v>10119</x:v>
+        <x:v>2767</x:v>
       </x:c>
       <x:c r="D36" s="14" t="str">
-        <x:v>label_000031</x:v>
+        <x:v>label_000070</x:v>
       </x:c>
       <x:c r="E36" s="14" t="str">
         <x:v>approved</x:v>
@@ -4094,21 +4516,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G36" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10119</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2767</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B37" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C37" s="14" t="str">
-        <x:v>85265</x:v>
+        <x:v>2769</x:v>
       </x:c>
       <x:c r="D37" s="14" t="str">
-        <x:v>label_000032</x:v>
+        <x:v>label_000066</x:v>
       </x:c>
       <x:c r="E37" s="14" t="str">
         <x:v>approved</x:v>
@@ -4117,21 +4539,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G37" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/85265</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2769</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B38" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C38" s="14" t="str">
-        <x:v>9483</x:v>
+        <x:v>2771</x:v>
       </x:c>
       <x:c r="D38" s="14" t="str">
-        <x:v>label_000033</x:v>
+        <x:v>label_000065</x:v>
       </x:c>
       <x:c r="E38" s="14" t="str">
         <x:v>approved</x:v>
@@ -4140,21 +4562,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G38" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/9483</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2771</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B39" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C39" s="14" t="str">
-        <x:v>10142</x:v>
+        <x:v>2776</x:v>
       </x:c>
       <x:c r="D39" s="14" t="str">
-        <x:v>label_000034</x:v>
+        <x:v>label_000068</x:v>
       </x:c>
       <x:c r="E39" s="14" t="str">
         <x:v>approved</x:v>
@@ -4163,21 +4585,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G39" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10142</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2776</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B40" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C40" s="14" t="str">
-        <x:v>10077</x:v>
+        <x:v>85265</x:v>
       </x:c>
       <x:c r="D40" s="14" t="str">
-        <x:v>label_000035</x:v>
+        <x:v>label_000075</x:v>
       </x:c>
       <x:c r="E40" s="14" t="str">
         <x:v>approved</x:v>
@@ -4186,21 +4608,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G40" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10077</x:v>
+        <x:v>https://ideapocket.com/works/list/label/85265</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B41" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C41" s="14" t="str">
-        <x:v>10151</x:v>
+        <x:v>9483</x:v>
       </x:c>
       <x:c r="D41" s="14" t="str">
-        <x:v>label_000036</x:v>
+        <x:v>label_000074</x:v>
       </x:c>
       <x:c r="E41" s="14" t="str">
         <x:v>approved</x:v>
@@ -4209,21 +4631,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G41" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10151</x:v>
+        <x:v>https://ideapocket.com/works/list/label/9483</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B42" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C42" s="14" t="str">
-        <x:v>3125</x:v>
+        <x:v>9790</x:v>
       </x:c>
       <x:c r="D42" s="14" t="str">
-        <x:v>label_000037</x:v>
+        <x:v>label_000067</x:v>
       </x:c>
       <x:c r="E42" s="14" t="str">
         <x:v>approved</x:v>
@@ -4232,21 +4654,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G42" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/3125</x:v>
+        <x:v>https://ideapocket.com/works/list/label/9790</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>ideapocket.series</x:v>
       </x:c>
       <x:c r="B43" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C43" s="14" t="str">
-        <x:v>5047</x:v>
+        <x:v>1011</x:v>
       </x:c>
       <x:c r="D43" s="14" t="str">
-        <x:v>label_000038</x:v>
+        <x:v>series_000004</x:v>
       </x:c>
       <x:c r="E43" s="14" t="str">
         <x:v>approved</x:v>
@@ -4255,21 +4677,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G43" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5047</x:v>
+        <x:v>https://ideapocket.com/works/list/series/1011</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>ideapocket.series</x:v>
       </x:c>
       <x:c r="B44" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C44" s="14" t="str">
-        <x:v>5046</x:v>
+        <x:v>863</x:v>
       </x:c>
       <x:c r="D44" s="14" t="str">
-        <x:v>label_000039</x:v>
+        <x:v>series_000003</x:v>
       </x:c>
       <x:c r="E44" s="14" t="str">
         <x:v>approved</x:v>
@@ -4278,21 +4700,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G44" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5046</x:v>
+        <x:v>https://ideapocket.com/works/list/series/863</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B45" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C45" s="14" t="str">
-        <x:v>6879</x:v>
+        <x:v>10077</x:v>
       </x:c>
       <x:c r="D45" s="14" t="str">
-        <x:v>label_000040</x:v>
+        <x:v>label_000035</x:v>
       </x:c>
       <x:c r="E45" s="14" t="str">
         <x:v>approved</x:v>
@@ -4301,21 +4723,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G45" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/6879</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10077</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B46" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C46" s="14" t="str">
-        <x:v>9782</x:v>
+        <x:v>10119</x:v>
       </x:c>
       <x:c r="D46" s="14" t="str">
-        <x:v>label_000041</x:v>
+        <x:v>label_000031</x:v>
       </x:c>
       <x:c r="E46" s="14" t="str">
         <x:v>approved</x:v>
@@ -4324,21 +4746,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G46" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9782</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10119</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B47" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C47" s="14" t="str">
-        <x:v>9732</x:v>
+        <x:v>10130</x:v>
       </x:c>
       <x:c r="D47" s="14" t="str">
-        <x:v>label_000042</x:v>
+        <x:v>label_000028</x:v>
       </x:c>
       <x:c r="E47" s="14" t="str">
         <x:v>approved</x:v>
@@ -4347,21 +4769,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G47" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9732</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10130</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B48" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C48" s="14" t="str">
-        <x:v>9308</x:v>
+        <x:v>10142</x:v>
       </x:c>
       <x:c r="D48" s="14" t="str">
-        <x:v>label_000043</x:v>
+        <x:v>label_000034</x:v>
       </x:c>
       <x:c r="E48" s="14" t="str">
         <x:v>approved</x:v>
@@ -4370,21 +4792,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G48" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9308</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10142</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B49" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C49" s="14" t="str">
-        <x:v>5090</x:v>
+        <x:v>10151</x:v>
       </x:c>
       <x:c r="D49" s="14" t="str">
-        <x:v>label_000044</x:v>
+        <x:v>label_000036</x:v>
       </x:c>
       <x:c r="E49" s="14" t="str">
         <x:v>approved</x:v>
@@ -4393,21 +4815,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G49" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5090</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10151</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B50" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C50" s="14" t="str">
-        <x:v>5049</x:v>
+        <x:v>10159</x:v>
       </x:c>
       <x:c r="D50" s="14" t="str">
-        <x:v>label_000045</x:v>
+        <x:v>label_000030</x:v>
       </x:c>
       <x:c r="E50" s="14" t="str">
         <x:v>approved</x:v>
@@ -4416,21 +4838,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G50" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5049</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10159</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B51" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C51" s="14" t="str">
-        <x:v>10107</x:v>
+        <x:v>12490</x:v>
       </x:c>
       <x:c r="D51" s="14" t="str">
-        <x:v>label_000046</x:v>
+        <x:v>label_000021</x:v>
       </x:c>
       <x:c r="E51" s="14" t="str">
         <x:v>approved</x:v>
@@ -4439,21 +4861,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G51" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10107</x:v>
+        <x:v>https://madonna-av.com/works/list/label/12490</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B52" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C52" s="14" t="str">
-        <x:v>10131</x:v>
+        <x:v>12502</x:v>
       </x:c>
       <x:c r="D52" s="14" t="str">
-        <x:v>label_000047</x:v>
+        <x:v>label_000027</x:v>
       </x:c>
       <x:c r="E52" s="14" t="str">
         <x:v>approved</x:v>
@@ -4462,21 +4884,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G52" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10131</x:v>
+        <x:v>https://madonna-av.com/works/list/label/12502</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B53" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C53" s="14" t="str">
-        <x:v>9458</x:v>
+        <x:v>12603</x:v>
       </x:c>
       <x:c r="D53" s="14" t="str">
-        <x:v>label_000048</x:v>
+        <x:v>label_000026</x:v>
       </x:c>
       <x:c r="E53" s="14" t="str">
         <x:v>approved</x:v>
@@ -4485,21 +4907,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G53" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9458</x:v>
+        <x:v>https://madonna-av.com/works/list/label/12603</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B54" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C54" s="14" t="str">
-        <x:v>5409</x:v>
+        <x:v>3125</x:v>
       </x:c>
       <x:c r="D54" s="14" t="str">
-        <x:v>label_000049</x:v>
+        <x:v>label_000037</x:v>
       </x:c>
       <x:c r="E54" s="14" t="str">
         <x:v>approved</x:v>
@@ -4508,21 +4930,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G54" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5409</x:v>
+        <x:v>https://madonna-av.com/works/list/label/3125</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B55" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C55" s="14" t="str">
-        <x:v>10174</x:v>
+        <x:v>3669</x:v>
       </x:c>
       <x:c r="D55" s="14" t="str">
-        <x:v>label_000050</x:v>
+        <x:v>label_000020</x:v>
       </x:c>
       <x:c r="E55" s="14" t="str">
         <x:v>approved</x:v>
@@ -4531,21 +4953,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G55" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10174</x:v>
+        <x:v>https://madonna-av.com/works/list/label/3669</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B56" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C56" s="14" t="str">
-        <x:v>8916</x:v>
+        <x:v>7354</x:v>
       </x:c>
       <x:c r="D56" s="14" t="str">
-        <x:v>label_000051</x:v>
+        <x:v>label_000024</x:v>
       </x:c>
       <x:c r="E56" s="14" t="str">
         <x:v>approved</x:v>
@@ -4554,21 +4976,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G56" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/8916</x:v>
+        <x:v>https://madonna-av.com/works/list/label/7354</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B57" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C57" s="14" t="str">
-        <x:v>9397</x:v>
+        <x:v>7993</x:v>
       </x:c>
       <x:c r="D57" s="14" t="str">
-        <x:v>label_000052</x:v>
+        <x:v>label_000029</x:v>
       </x:c>
       <x:c r="E57" s="14" t="str">
         <x:v>approved</x:v>
@@ -4577,21 +4999,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G57" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9397</x:v>
+        <x:v>https://madonna-av.com/works/list/label/7993</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B58" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C58" s="14" t="str">
-        <x:v>10106</x:v>
+        <x:v>85265</x:v>
       </x:c>
       <x:c r="D58" s="14" t="str">
-        <x:v>label_000053</x:v>
+        <x:v>label_000032</x:v>
       </x:c>
       <x:c r="E58" s="14" t="str">
         <x:v>approved</x:v>
@@ -4600,21 +5022,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G58" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10106</x:v>
+        <x:v>https://madonna-av.com/works/list/label/85265</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B59" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C59" s="14" t="str">
-        <x:v>9288</x:v>
+        <x:v>9387</x:v>
       </x:c>
       <x:c r="D59" s="14" t="str">
-        <x:v>label_000054</x:v>
+        <x:v>label_000022</x:v>
       </x:c>
       <x:c r="E59" s="14" t="str">
         <x:v>approved</x:v>
@@ -4623,21 +5045,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G59" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9288</x:v>
+        <x:v>https://madonna-av.com/works/list/label/9387</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B60" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C60" s="14" t="str">
-        <x:v>8917</x:v>
+        <x:v>9419</x:v>
       </x:c>
       <x:c r="D60" s="14" t="str">
-        <x:v>label_000055</x:v>
+        <x:v>label_000025</x:v>
       </x:c>
       <x:c r="E60" s="14" t="str">
         <x:v>approved</x:v>
@@ -4646,21 +5068,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G60" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/8917</x:v>
+        <x:v>https://madonna-av.com/works/list/label/9419</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B61" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C61" s="14" t="str">
-        <x:v>85265</x:v>
+        <x:v>9483</x:v>
       </x:c>
       <x:c r="D61" s="14" t="str">
-        <x:v>label_000056</x:v>
+        <x:v>label_000033</x:v>
       </x:c>
       <x:c r="E61" s="14" t="str">
         <x:v>approved</x:v>
@@ -4669,21 +5091,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G61" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/85265</x:v>
+        <x:v>https://madonna-av.com/works/list/label/9483</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B62" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C62" s="14" t="str">
-        <x:v>11471</x:v>
+        <x:v>9789</x:v>
       </x:c>
       <x:c r="D62" s="14" t="str">
-        <x:v>label_000057</x:v>
+        <x:v>label_000023</x:v>
       </x:c>
       <x:c r="E62" s="14" t="str">
         <x:v>approved</x:v>
@@ -4692,21 +5114,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G62" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/11471</x:v>
+        <x:v>https://madonna-av.com/works/list/label/9789</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B63" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C63" s="14" t="str">
-        <x:v>10157</x:v>
+        <x:v>1749</x:v>
       </x:c>
       <x:c r="D63" s="14" t="str">
-        <x:v>label_000058</x:v>
+        <x:v>series_000017</x:v>
       </x:c>
       <x:c r="E63" s="14" t="str">
         <x:v>approved</x:v>
@@ -4715,21 +5137,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G63" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10157</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1749</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B64" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C64" s="14" t="str">
-        <x:v>9483</x:v>
+        <x:v>1846</x:v>
       </x:c>
       <x:c r="D64" s="14" t="str">
-        <x:v>label_000059</x:v>
+        <x:v>series_000015</x:v>
       </x:c>
       <x:c r="E64" s="14" t="str">
         <x:v>approved</x:v>
@@ -4738,21 +5160,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G64" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9483</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1846</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B65" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C65" s="14" t="str">
-        <x:v>10142</x:v>
+        <x:v>1891</x:v>
       </x:c>
       <x:c r="D65" s="14" t="str">
-        <x:v>label_000060</x:v>
+        <x:v>series_000016</x:v>
       </x:c>
       <x:c r="E65" s="14" t="str">
         <x:v>approved</x:v>
@@ -4761,7 +5183,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G65" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10142</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1891</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -4772,10 +5194,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C66" s="14" t="str">
-        <x:v>10144</x:v>
+        <x:v>10077</x:v>
       </x:c>
       <x:c r="D66" s="14" t="str">
-        <x:v>label_000061</x:v>
+        <x:v>label_000063</x:v>
       </x:c>
       <x:c r="E66" s="14" t="str">
         <x:v>approved</x:v>
@@ -4784,7 +5206,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G66" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10144</x:v>
+        <x:v>https://moodyz.com/works/list/label/10077</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -4795,10 +5217,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C67" s="14" t="str">
-        <x:v>10151</x:v>
+        <x:v>10106</x:v>
       </x:c>
       <x:c r="D67" s="14" t="str">
-        <x:v>label_000062</x:v>
+        <x:v>label_000053</x:v>
       </x:c>
       <x:c r="E67" s="14" t="str">
         <x:v>approved</x:v>
@@ -4807,7 +5229,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G67" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10151</x:v>
+        <x:v>https://moodyz.com/works/list/label/10106</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -4818,10 +5240,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C68" s="14" t="str">
-        <x:v>10077</x:v>
+        <x:v>10107</x:v>
       </x:c>
       <x:c r="D68" s="14" t="str">
-        <x:v>label_000063</x:v>
+        <x:v>label_000046</x:v>
       </x:c>
       <x:c r="E68" s="14" t="str">
         <x:v>approved</x:v>
@@ -4830,7 +5252,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G68" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10077</x:v>
+        <x:v>https://moodyz.com/works/list/label/10107</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -4841,10 +5263,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C69" s="14" t="str">
-        <x:v>10172</x:v>
+        <x:v>10131</x:v>
       </x:c>
       <x:c r="D69" s="14" t="str">
-        <x:v>label_000064</x:v>
+        <x:v>label_000047</x:v>
       </x:c>
       <x:c r="E69" s="14" t="str">
         <x:v>approved</x:v>
@@ -4853,21 +5275,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G69" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10172</x:v>
+        <x:v>https://moodyz.com/works/list/label/10131</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B70" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C70" s="14" t="str">
-        <x:v>2771</x:v>
+        <x:v>10142</x:v>
       </x:c>
       <x:c r="D70" s="14" t="str">
-        <x:v>label_000065</x:v>
+        <x:v>label_000060</x:v>
       </x:c>
       <x:c r="E70" s="14" t="str">
         <x:v>approved</x:v>
@@ -4876,21 +5298,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G70" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2771</x:v>
+        <x:v>https://moodyz.com/works/list/label/10142</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B71" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C71" s="14" t="str">
-        <x:v>2769</x:v>
+        <x:v>10144</x:v>
       </x:c>
       <x:c r="D71" s="14" t="str">
-        <x:v>label_000066</x:v>
+        <x:v>label_000061</x:v>
       </x:c>
       <x:c r="E71" s="14" t="str">
         <x:v>approved</x:v>
@@ -4899,21 +5321,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G71" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2769</x:v>
+        <x:v>https://moodyz.com/works/list/label/10144</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B72" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C72" s="14" t="str">
-        <x:v>9790</x:v>
+        <x:v>10151</x:v>
       </x:c>
       <x:c r="D72" s="14" t="str">
-        <x:v>label_000067</x:v>
+        <x:v>label_000062</x:v>
       </x:c>
       <x:c r="E72" s="14" t="str">
         <x:v>approved</x:v>
@@ -4922,21 +5344,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G72" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/9790</x:v>
+        <x:v>https://moodyz.com/works/list/label/10151</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B73" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C73" s="14" t="str">
-        <x:v>2776</x:v>
+        <x:v>10157</x:v>
       </x:c>
       <x:c r="D73" s="14" t="str">
-        <x:v>label_000068</x:v>
+        <x:v>label_000058</x:v>
       </x:c>
       <x:c r="E73" s="14" t="str">
         <x:v>approved</x:v>
@@ -4945,21 +5367,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G73" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2776</x:v>
+        <x:v>https://moodyz.com/works/list/label/10157</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B74" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C74" s="14" t="str">
-        <x:v>12442</x:v>
+        <x:v>10172</x:v>
       </x:c>
       <x:c r="D74" s="14" t="str">
-        <x:v>label_000069</x:v>
+        <x:v>label_000064</x:v>
       </x:c>
       <x:c r="E74" s="14" t="str">
         <x:v>approved</x:v>
@@ -4968,21 +5390,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G74" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/12442</x:v>
+        <x:v>https://moodyz.com/works/list/label/10172</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B75" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C75" s="14" t="str">
-        <x:v>2767</x:v>
+        <x:v>10174</x:v>
       </x:c>
       <x:c r="D75" s="14" t="str">
-        <x:v>label_000070</x:v>
+        <x:v>label_000050</x:v>
       </x:c>
       <x:c r="E75" s="14" t="str">
         <x:v>approved</x:v>
@@ -4991,21 +5413,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G75" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2767</x:v>
+        <x:v>https://moodyz.com/works/list/label/10174</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B76" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C76" s="14" t="str">
-        <x:v>12835</x:v>
+        <x:v>11471</x:v>
       </x:c>
       <x:c r="D76" s="14" t="str">
-        <x:v>label_000071</x:v>
+        <x:v>label_000057</x:v>
       </x:c>
       <x:c r="E76" s="14" t="str">
         <x:v>approved</x:v>
@@ -5014,21 +5436,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G76" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/12835</x:v>
+        <x:v>https://moodyz.com/works/list/label/11471</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B77" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C77" s="14" t="str">
-        <x:v>2758</x:v>
+        <x:v>12798</x:v>
       </x:c>
       <x:c r="D77" s="14" t="str">
-        <x:v>label_000072</x:v>
+        <x:v>label_000002</x:v>
       </x:c>
       <x:c r="E77" s="14" t="str">
         <x:v>approved</x:v>
@@ -5037,21 +5459,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G77" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2758</x:v>
+        <x:v>https://moodyz.com/works/list/label/12798</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B78" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C78" s="14" t="str">
-        <x:v>10103</x:v>
+        <x:v>5046</x:v>
       </x:c>
       <x:c r="D78" s="14" t="str">
-        <x:v>label_000073</x:v>
+        <x:v>label_000039</x:v>
       </x:c>
       <x:c r="E78" s="14" t="str">
         <x:v>approved</x:v>
@@ -5060,21 +5482,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G78" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10103</x:v>
+        <x:v>https://moodyz.com/works/list/label/5046</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B79" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C79" s="14" t="str">
-        <x:v>9483</x:v>
+        <x:v>5047</x:v>
       </x:c>
       <x:c r="D79" s="14" t="str">
-        <x:v>label_000074</x:v>
+        <x:v>label_000038</x:v>
       </x:c>
       <x:c r="E79" s="14" t="str">
         <x:v>approved</x:v>
@@ -5083,21 +5505,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G79" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/9483</x:v>
+        <x:v>https://moodyz.com/works/list/label/5047</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B80" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C80" s="14" t="str">
-        <x:v>85265</x:v>
+        <x:v>5048</x:v>
       </x:c>
       <x:c r="D80" s="14" t="str">
-        <x:v>label_000075</x:v>
+        <x:v>label_000001</x:v>
       </x:c>
       <x:c r="E80" s="14" t="str">
         <x:v>approved</x:v>
@@ -5106,21 +5528,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G80" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/85265</x:v>
+        <x:v>https://moodyz.com/works/list/label/5048</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B81" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C81" s="14" t="str">
-        <x:v>10077</x:v>
+        <x:v>5049</x:v>
       </x:c>
       <x:c r="D81" s="14" t="str">
-        <x:v>label_000076</x:v>
+        <x:v>label_000045</x:v>
       </x:c>
       <x:c r="E81" s="14" t="str">
         <x:v>approved</x:v>
@@ -5129,21 +5551,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G81" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10077</x:v>
+        <x:v>https://moodyz.com/works/list/label/5049</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B82" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C82" s="14" t="str">
-        <x:v>10142</x:v>
+        <x:v>5090</x:v>
       </x:c>
       <x:c r="D82" s="14" t="str">
-        <x:v>label_000077</x:v>
+        <x:v>label_000044</x:v>
       </x:c>
       <x:c r="E82" s="14" t="str">
         <x:v>approved</x:v>
@@ -5152,21 +5574,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G82" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10142</x:v>
+        <x:v>https://moodyz.com/works/list/label/5090</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B83" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C83" s="14" t="str">
-        <x:v>10151</x:v>
+        <x:v>5409</x:v>
       </x:c>
       <x:c r="D83" s="14" t="str">
-        <x:v>label_000078</x:v>
+        <x:v>label_000049</x:v>
       </x:c>
       <x:c r="E83" s="14" t="str">
         <x:v>approved</x:v>
@@ -5175,21 +5597,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G83" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10151</x:v>
+        <x:v>https://moodyz.com/works/list/label/5409</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B84" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C84" s="14" t="str">
-        <x:v>2760</x:v>
+        <x:v>6879</x:v>
       </x:c>
       <x:c r="D84" s="14" t="str">
-        <x:v>label_000079</x:v>
+        <x:v>label_000040</x:v>
       </x:c>
       <x:c r="E84" s="14" t="str">
         <x:v>approved</x:v>
@@ -5198,21 +5620,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G84" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2760</x:v>
+        <x:v>https://moodyz.com/works/list/label/6879</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B85" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C85" s="14" t="str">
-        <x:v>10144</x:v>
+        <x:v>85265</x:v>
       </x:c>
       <x:c r="D85" s="14" t="str">
-        <x:v>label_000080</x:v>
+        <x:v>label_000056</x:v>
       </x:c>
       <x:c r="E85" s="14" t="str">
         <x:v>approved</x:v>
@@ -5221,7 +5643,329 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G85" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10144</x:v>
+        <x:v>https://moodyz.com/works/list/label/85265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B86" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C86" s="14" t="str">
+        <x:v>8916</x:v>
+      </x:c>
+      <x:c r="D86" s="14" t="str">
+        <x:v>label_000051</x:v>
+      </x:c>
+      <x:c r="E86" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F86" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G86" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/8916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B87" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C87" s="14" t="str">
+        <x:v>8917</x:v>
+      </x:c>
+      <x:c r="D87" s="14" t="str">
+        <x:v>label_000055</x:v>
+      </x:c>
+      <x:c r="E87" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F87" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G87" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/8917</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B88" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C88" s="14" t="str">
+        <x:v>9288</x:v>
+      </x:c>
+      <x:c r="D88" s="14" t="str">
+        <x:v>label_000054</x:v>
+      </x:c>
+      <x:c r="E88" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F88" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G88" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9288</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B89" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C89" s="14" t="str">
+        <x:v>9308</x:v>
+      </x:c>
+      <x:c r="D89" s="14" t="str">
+        <x:v>label_000043</x:v>
+      </x:c>
+      <x:c r="E89" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F89" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G89" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B90" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C90" s="14" t="str">
+        <x:v>9397</x:v>
+      </x:c>
+      <x:c r="D90" s="14" t="str">
+        <x:v>label_000052</x:v>
+      </x:c>
+      <x:c r="E90" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F90" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G90" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9397</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B91" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C91" s="14" t="str">
+        <x:v>9458</x:v>
+      </x:c>
+      <x:c r="D91" s="14" t="str">
+        <x:v>label_000048</x:v>
+      </x:c>
+      <x:c r="E91" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F91" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G91" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9458</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B92" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C92" s="14" t="str">
+        <x:v>9483</x:v>
+      </x:c>
+      <x:c r="D92" s="14" t="str">
+        <x:v>label_000059</x:v>
+      </x:c>
+      <x:c r="E92" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F92" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G92" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9483</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B93" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C93" s="14" t="str">
+        <x:v>9732</x:v>
+      </x:c>
+      <x:c r="D93" s="14" t="str">
+        <x:v>label_000042</x:v>
+      </x:c>
+      <x:c r="E93" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F93" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G93" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9732</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B94" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C94" s="14" t="str">
+        <x:v>9782</x:v>
+      </x:c>
+      <x:c r="D94" s="14" t="str">
+        <x:v>label_000041</x:v>
+      </x:c>
+      <x:c r="E94" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F94" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G94" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9782</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="14" t="str">
+        <x:v>moodyz.series</x:v>
+      </x:c>
+      <x:c r="B95" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C95" s="14" t="str">
+        <x:v>5427</x:v>
+      </x:c>
+      <x:c r="D95" s="14" t="str">
+        <x:v>series_000002</x:v>
+      </x:c>
+      <x:c r="E95" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F95" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G95" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/5427</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="14" t="str">
+        <x:v>s1.label</x:v>
+      </x:c>
+      <x:c r="B96" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C96" s="14" t="str">
+        <x:v>4355</x:v>
+      </x:c>
+      <x:c r="D96" s="14" t="str">
+        <x:v>label_000081</x:v>
+      </x:c>
+      <x:c r="E96" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F96" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G96" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/label/4355</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="B97" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C97" s="14" t="str">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="D97" s="14" t="str">
+        <x:v>series_000001</x:v>
+      </x:c>
+      <x:c r="E97" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F97" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G97" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/414</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="B98" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C98" s="14" t="str">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="D98" s="14" t="str">
+        <x:v>series_000005</x:v>
+      </x:c>
+      <x:c r="E98" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F98" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G98" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/422</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="B99" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C99" s="14" t="str">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="D99" s="14" t="str">
+        <x:v>series_000006</x:v>
+      </x:c>
+      <x:c r="E99" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F99" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G99" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/570</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5295,10 +6039,10 @@
     <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="40" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="56" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="58" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -7598,6 +8342,384 @@
         <x:v>https://ideapocket.com/works/list/label/10144</x:v>
       </x:c>
     </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B86" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C86" s="14" t="str">
+        <x:v>s1.label</x:v>
+      </x:c>
+      <x:c r="D86" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E86" s="14" t="str">
+        <x:v>4355</x:v>
+      </x:c>
+      <x:c r="F86" s="14" t="str">
+        <x:v>S1 NO.1 STYLE</x:v>
+      </x:c>
+      <x:c r="G86" s="14" t="str">
+        <x:v>label_000081</x:v>
+      </x:c>
+      <x:c r="H86" s="14" t="str"/>
+      <x:c r="I86" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/label/4355</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B87" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C87" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="D87" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="E87" s="14" t="str">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="F87" s="14" t="str">
+        <x:v>おま●こ、くぱぁ</x:v>
+      </x:c>
+      <x:c r="G87" s="14" t="str">
+        <x:v>series_000005</x:v>
+      </x:c>
+      <x:c r="H87" s="14" t="str"/>
+      <x:c r="I87" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/422</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B88" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C88" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="D88" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="E88" s="14" t="str">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="F88" s="14" t="str">
+        <x:v>ラブキモメン</x:v>
+      </x:c>
+      <x:c r="G88" s="14" t="str">
+        <x:v>series_000006</x:v>
+      </x:c>
+      <x:c r="H88" s="14" t="str"/>
+      <x:c r="I88" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/570</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B89" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C89" s="14" t="str">
+        <x:v>attackers.series</x:v>
+      </x:c>
+      <x:c r="D89" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="E89" s="14" t="str">
+        <x:v>2402</x:v>
+      </x:c>
+      <x:c r="F89" s="14" t="str">
+        <x:v>侵入者</x:v>
+      </x:c>
+      <x:c r="G89" s="14" t="str">
+        <x:v>series_000007</x:v>
+      </x:c>
+      <x:c r="H89" s="14" t="str"/>
+      <x:c r="I89" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2402</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B90" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C90" s="14" t="str">
+        <x:v>attackers.series</x:v>
+      </x:c>
+      <x:c r="D90" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="E90" s="14" t="str">
+        <x:v>2269</x:v>
+      </x:c>
+      <x:c r="F90" s="14" t="str">
+        <x:v>あなたに愛されたくて。</x:v>
+      </x:c>
+      <x:c r="G90" s="14" t="str">
+        <x:v>series_000008</x:v>
+      </x:c>
+      <x:c r="H90" s="14" t="str"/>
+      <x:c r="I90" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2269</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B91" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C91" s="14" t="str">
+        <x:v>attackers.series</x:v>
+      </x:c>
+      <x:c r="D91" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="E91" s="14" t="str">
+        <x:v>2270</x:v>
+      </x:c>
+      <x:c r="F91" s="14" t="str">
+        <x:v>あなた、許して…。</x:v>
+      </x:c>
+      <x:c r="G91" s="14" t="str">
+        <x:v>series_000009</x:v>
+      </x:c>
+      <x:c r="H91" s="14" t="str"/>
+      <x:c r="I91" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2270</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B92" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C92" s="14" t="str">
+        <x:v>attackers.series</x:v>
+      </x:c>
+      <x:c r="D92" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="E92" s="14" t="str">
+        <x:v>2293</x:v>
+      </x:c>
+      <x:c r="F92" s="14" t="str">
+        <x:v>脱獄者</x:v>
+      </x:c>
+      <x:c r="G92" s="14" t="str">
+        <x:v>series_000010</x:v>
+      </x:c>
+      <x:c r="H92" s="14" t="str"/>
+      <x:c r="I92" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2293</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B93" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C93" s="14" t="str">
+        <x:v>attackers.series</x:v>
+      </x:c>
+      <x:c r="D93" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="E93" s="14" t="str">
+        <x:v>2256</x:v>
+      </x:c>
+      <x:c r="F93" s="14" t="str">
+        <x:v>奴隷島</x:v>
+      </x:c>
+      <x:c r="G93" s="14" t="str">
+        <x:v>series_000011</x:v>
+      </x:c>
+      <x:c r="H93" s="14" t="str"/>
+      <x:c r="I93" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B94" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C94" s="14" t="str">
+        <x:v>attackers.series</x:v>
+      </x:c>
+      <x:c r="D94" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="E94" s="14" t="str">
+        <x:v>2274</x:v>
+      </x:c>
+      <x:c r="F94" s="14" t="str">
+        <x:v>犯される度に美しく</x:v>
+      </x:c>
+      <x:c r="G94" s="14" t="str">
+        <x:v>series_000012</x:v>
+      </x:c>
+      <x:c r="H94" s="14" t="str"/>
+      <x:c r="I94" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2274</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B95" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C95" s="14" t="str">
+        <x:v>attackers.series</x:v>
+      </x:c>
+      <x:c r="D95" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="E95" s="14" t="str">
+        <x:v>2325</x:v>
+      </x:c>
+      <x:c r="F95" s="14" t="str">
+        <x:v>団鬼六</x:v>
+      </x:c>
+      <x:c r="G95" s="14" t="str">
+        <x:v>series_000013</x:v>
+      </x:c>
+      <x:c r="H95" s="14" t="str"/>
+      <x:c r="I95" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2325</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B96" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C96" s="14" t="str">
+        <x:v>attackers.series</x:v>
+      </x:c>
+      <x:c r="D96" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="E96" s="14" t="str">
+        <x:v>5317</x:v>
+      </x:c>
+      <x:c r="F96" s="14" t="str">
+        <x:v>調教志願</x:v>
+      </x:c>
+      <x:c r="G96" s="14" t="str">
+        <x:v>series_000014</x:v>
+      </x:c>
+      <x:c r="H96" s="14" t="str"/>
+      <x:c r="I96" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/5317</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B97" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C97" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="D97" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="E97" s="14" t="str">
+        <x:v>1846</x:v>
+      </x:c>
+      <x:c r="F97" s="14" t="str">
+        <x:v>年下レズビアンに愛された私</x:v>
+      </x:c>
+      <x:c r="G97" s="14" t="str">
+        <x:v>series_000015</x:v>
+      </x:c>
+      <x:c r="H97" s="14" t="str"/>
+      <x:c r="I97" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1846</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B98" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C98" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="D98" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="E98" s="14" t="str">
+        <x:v>1891</x:v>
+      </x:c>
+      <x:c r="F98" s="14" t="str">
+        <x:v>廃業寸前</x:v>
+      </x:c>
+      <x:c r="G98" s="14" t="str">
+        <x:v>series_000016</x:v>
+      </x:c>
+      <x:c r="H98" s="14" t="str"/>
+      <x:c r="I98" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1891</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B99" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C99" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="D99" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="E99" s="14" t="str">
+        <x:v>1749</x:v>
+      </x:c>
+      <x:c r="F99" s="14" t="str">
+        <x:v>夫の上司に飾られた　人妻ボディアクセサリー</x:v>
+      </x:c>
+      <x:c r="G99" s="14" t="str">
+        <x:v>series_000017</x:v>
+      </x:c>
+      <x:c r="H99" s="14" t="str"/>
+      <x:c r="I99" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1749</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/exports/xlsx/organization-series-registry.xlsx
+++ b/exports/xlsx/organization-series-registry.xlsx
@@ -2,12 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organizations" sheetId="1" r:id="R402bda752bc146a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series" sheetId="2" r:id="R9c3a3dc39cb14519"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Registry" sheetId="3" r:id="R3b5d9f67d01d449a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External ID Mapping" sheetId="4" r:id="R25c7f3ffefb94747"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidates" sheetId="5" r:id="R19c77bb446bc42ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="6" r:id="R5ce4d898e9b14088"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organizations" sheetId="1" r:id="Rd9f14d44a5474c3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series" sheetId="2" r:id="Recc42d6c82724ab4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Registry" sheetId="3" r:id="R7a84e57844ea40ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External ID Mapping" sheetId="4" r:id="R66b2e2bc90a641d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidates" sheetId="5" r:id="Re70d3ff4cc694522"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="6" r:id="R14db8a04de684f48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Index Snapshots" sheetId="7" r:id="R86249e00269f4b4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Index Candidates" sheetId="8" r:id="R70800396fd1e4f21"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3445,8 +3447,8 @@
     <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="70" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="80" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="78" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="84" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -3507,7 +3509,7 @@
         <x:v>no</x:v>
       </x:c>
       <x:c r="I2" s="14" t="str">
-        <x:v>label: 16/16 published, complete=yes; series: 2/2 published, complete=no</x:v>
+        <x:v>label: 16/16 published, unrecognized=0, complete=yes; series: 2/2 published, unrecognized=0, complete=no</x:v>
       </x:c>
       <x:c r="J2" s="14" t="str">
         <x:v>IDEAPOCKET 当前官方 Label Index 已完整遍历；Series 仍未完整枚举，因此来源级 completeTraversal 继续为 false。历史已删除/隐藏 Label 与其他实体类型不在本批次完整性声明内。</x:v>
@@ -3539,7 +3541,7 @@
         <x:v>no</x:v>
       </x:c>
       <x:c r="I3" s="14" t="str">
-        <x:v>label: 29/29 published, complete=yes; series: 1/1 published, complete=no</x:v>
+        <x:v>label: 29/29 published, unrecognized=0, complete=yes; series: 1/1 published, unrecognized=0, complete=no</x:v>
       </x:c>
       <x:c r="J3" s="14" t="str">
         <x:v>MOODYZ 当前官方 Label Index 已完整遍历；Series 仍未完整枚举，因此来源级 completeTraversal 继续为 false。历史已删除/隐藏 Label 与其他实体类型不在本批次完整性声明内。</x:v>
@@ -3571,7 +3573,7 @@
         <x:v>no</x:v>
       </x:c>
       <x:c r="I4" s="14" t="str">
-        <x:v>label: 1/1 published, complete=no; series: 3/3 published, complete=no</x:v>
+        <x:v>label: 1/1 published, unrecognized=0, complete=no; series: 3/3 published, unrecognized=0, complete=no</x:v>
       </x:c>
       <x:c r="J4" s="14" t="str">
         <x:v>S1 主 Label 4355 与 3 个 Series 已逐项核验，但官方索引在当前采集环境中未形成可证明的完整枚举快照，因此 Label 与 Series coverage 均保持 incomplete。</x:v>
@@ -3603,7 +3605,7 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="I5" s="14" t="str">
-        <x:v>company: 0/1 published, complete=yes</x:v>
+        <x:v>company: 0/1 published, unrecognized=0, complete=yes</x:v>
       </x:c>
       <x:c r="J5" s="14" t="str">
         <x:v>Localogue 当前正式 OrganizationKind 尚未把 company 作为一等消费类型，因此先进入 Staging，不伪装成 Maker。</x:v>
@@ -3635,10 +3637,10 @@
         <x:v>no</x:v>
       </x:c>
       <x:c r="I6" s="14" t="str">
-        <x:v>maker: 1/1 published, complete=yes; label: 17/17 published, complete=yes; series: 8/8 published, complete=no</x:v>
+        <x:v>maker: 1/1 published, unrecognized=0, complete=yes; label: 17/17 published, unrecognized=0, complete=yes; series: 8/17 published, unrecognized=9, complete=no</x:v>
       </x:c>
       <x:c r="J6" s="14" t="str">
-        <x:v>ATTACKERS 当前 Maker/Label coverage 已完整；本批次新增 8 个官方 Series 样本，但尚未完整枚举 Series Index，因此来源级 completeTraversal 降为 false。</x:v>
+        <x:v>ATTACKERS Maker/Label coverage 已完整；Series 已建立 partial index snapshot。当前联合发现 17 个 Series，其中 8 个已发布、9 个仍为待审核候选；快照不是完整遍历，因此 Series 与来源级 completeTraversal 继续为 false。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3667,10 +3669,10 @@
         <x:v>no</x:v>
       </x:c>
       <x:c r="I7" s="14" t="str">
-        <x:v>maker: 1/1 published, complete=yes; label: 18/18 published, complete=yes; series: 3/3 published, complete=no</x:v>
+        <x:v>maker: 1/1 published, unrecognized=0, complete=yes; label: 18/18 published, unrecognized=0, complete=yes; series: 3/13 published, unrecognized=10, complete=no</x:v>
       </x:c>
       <x:c r="J7" s="14" t="str">
-        <x:v>Madonna 当前 Maker/Label coverage 已完整；本批次新增 3 个官方 Series 样本，但尚未完整枚举 Series Index，因此来源级 completeTraversal 降为 false。</x:v>
+        <x:v>Madonna Maker/Label coverage 已完整；Series 已建立 partial index snapshot。当前联合发现 13 个 Series，其中 3 个已发布、10 个仍为待审核候选；快照不是完整遍历，因此 Series 与来源级 completeTraversal 继续为 false。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8723,4 +8725,676 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Snapshot ID</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>Source ID</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>Maker ID</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>Captured</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>Complete</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>Entries</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="14" t="str">
+        <x:v>attackers-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="B2" s="14" t="str">
+        <x:v>attackers.series</x:v>
+      </x:c>
+      <x:c r="C2" s="14" t="str">
+        <x:v>source_attackers_official</x:v>
+      </x:c>
+      <x:c r="D2" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="E2" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="F2" s="14" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="G2" s="14" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="B3" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C3" s="14" t="str">
+        <x:v>source_madonna_official</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="F3" s="14" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="G3" s="14" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="58" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Classification</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Reason</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>Snapshot ID</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>External ID</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>日本語</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>Maker ID</x:v>
+      </x:c>
+      <x:c r="H1" s="6" t="str">
+        <x:v>Community ID</x:v>
+      </x:c>
+      <x:c r="I1" s="6" t="str">
+        <x:v>Candidates</x:v>
+      </x:c>
+      <x:c r="J1" s="6" t="str">
+        <x:v>Source URL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="14" t="str">
+        <x:v>candidate-new</x:v>
+      </x:c>
+      <x:c r="B2" s="14" t="str">
+        <x:v>unmapped-official-series-id</x:v>
+      </x:c>
+      <x:c r="C2" s="14" t="str">
+        <x:v>attackers.series</x:v>
+      </x:c>
+      <x:c r="D2" s="14" t="str">
+        <x:v>attackers-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E2" s="14" t="str">
+        <x:v>2253</x:v>
+      </x:c>
+      <x:c r="F2" s="14" t="str">
+        <x:v>アナル奴隷白書</x:v>
+      </x:c>
+      <x:c r="G2" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H2" s="14" t="str"/>
+      <x:c r="I2" s="14" t="str"/>
+      <x:c r="J2" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2253</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="14" t="str">
+        <x:v>candidate-new</x:v>
+      </x:c>
+      <x:c r="B3" s="14" t="str">
+        <x:v>unmapped-official-series-id</x:v>
+      </x:c>
+      <x:c r="C3" s="14" t="str">
+        <x:v>attackers.series</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="str">
+        <x:v>attackers-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="str">
+        <x:v>2254</x:v>
+      </x:c>
+      <x:c r="F3" s="14" t="str">
+        <x:v>夫の目の前で犯されて</x:v>
+      </x:c>
+      <x:c r="G3" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="str"/>
+      <x:c r="I3" s="14" t="str"/>
+      <x:c r="J3" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2254</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="14" t="str">
+        <x:v>candidate-new</x:v>
+      </x:c>
+      <x:c r="B4" s="14" t="str">
+        <x:v>unmapped-official-series-id</x:v>
+      </x:c>
+      <x:c r="C4" s="14" t="str">
+        <x:v>attackers.series</x:v>
+      </x:c>
+      <x:c r="D4" s="14" t="str">
+        <x:v>attackers-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E4" s="14" t="str">
+        <x:v>2255</x:v>
+      </x:c>
+      <x:c r="F4" s="14" t="str">
+        <x:v>地獄の女神</x:v>
+      </x:c>
+      <x:c r="G4" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H4" s="14" t="str"/>
+      <x:c r="I4" s="14" t="str"/>
+      <x:c r="J4" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2255</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="14" t="str">
+        <x:v>candidate-new</x:v>
+      </x:c>
+      <x:c r="B5" s="14" t="str">
+        <x:v>unmapped-official-series-id</x:v>
+      </x:c>
+      <x:c r="C5" s="14" t="str">
+        <x:v>attackers.series</x:v>
+      </x:c>
+      <x:c r="D5" s="14" t="str">
+        <x:v>attackers-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E5" s="14" t="str">
+        <x:v>2257</x:v>
+      </x:c>
+      <x:c r="F5" s="14" t="str">
+        <x:v>絶対調教</x:v>
+      </x:c>
+      <x:c r="G5" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H5" s="14" t="str"/>
+      <x:c r="I5" s="14" t="str"/>
+      <x:c r="J5" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2257</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="14" t="str">
+        <x:v>candidate-new</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="str">
+        <x:v>unmapped-official-series-id</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="str">
+        <x:v>attackers.series</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="str">
+        <x:v>attackers-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E6" s="14" t="str">
+        <x:v>2258</x:v>
+      </x:c>
+      <x:c r="F6" s="14" t="str">
+        <x:v>淫乱奴隷の強制快楽</x:v>
+      </x:c>
+      <x:c r="G6" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H6" s="14" t="str"/>
+      <x:c r="I6" s="14" t="str"/>
+      <x:c r="J6" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2258</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="14" t="str">
+        <x:v>candidate-new</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="str">
+        <x:v>unmapped-official-series-id</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="str">
+        <x:v>attackers.series</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="str">
+        <x:v>attackers-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="str">
+        <x:v>2259</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="str">
+        <x:v>貞操帯の女</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H7" s="14" t="str"/>
+      <x:c r="I7" s="14" t="str"/>
+      <x:c r="J7" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2259</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="14" t="str">
+        <x:v>candidate-new</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="str">
+        <x:v>unmapped-official-series-id</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="str">
+        <x:v>attackers.series</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="str">
+        <x:v>attackers-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="str">
+        <x:v>2260</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="str">
+        <x:v>楠木女学院</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H8" s="14" t="str"/>
+      <x:c r="I8" s="14" t="str"/>
+      <x:c r="J8" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2260</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="14" t="str">
+        <x:v>candidate-new</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="str">
+        <x:v>unmapped-official-series-id</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="str">
+        <x:v>attackers.series</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="str">
+        <x:v>attackers-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="str">
+        <x:v>2261</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="str">
+        <x:v>鬼畜輪姦</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H9" s="14" t="str"/>
+      <x:c r="I9" s="14" t="str"/>
+      <x:c r="J9" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2261</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="14" t="str">
+        <x:v>candidate-new</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="str">
+        <x:v>unmapped-official-series-id</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="str">
+        <x:v>attackers.series</x:v>
+      </x:c>
+      <x:c r="D10" s="14" t="str">
+        <x:v>attackers-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="str">
+        <x:v>2263</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="str">
+        <x:v>女豹</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H10" s="14" t="str"/>
+      <x:c r="I10" s="14" t="str"/>
+      <x:c r="J10" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2263</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="14" t="str">
+        <x:v>candidate-new</x:v>
+      </x:c>
+      <x:c r="B11" s="14" t="str">
+        <x:v>unmapped-official-series-id</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="D11" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="str">
+        <x:v>1549</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="str">
+        <x:v>となりの奥さん</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H11" s="14" t="str"/>
+      <x:c r="I11" s="14" t="str"/>
+      <x:c r="J11" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="14" t="str">
+        <x:v>candidate-new</x:v>
+      </x:c>
+      <x:c r="B12" s="14" t="str">
+        <x:v>unmapped-official-series-id</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="D12" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="str">
+        <x:v>1550</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="str">
+        <x:v>美熟女と黒人</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H12" s="14" t="str"/>
+      <x:c r="I12" s="14" t="str"/>
+      <x:c r="J12" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1550</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="14" t="str">
+        <x:v>candidate-new</x:v>
+      </x:c>
+      <x:c r="B13" s="14" t="str">
+        <x:v>unmapped-official-series-id</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="D13" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="str">
+        <x:v>1551</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="str">
+        <x:v>愛する夫の目の前で・・・</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H13" s="14" t="str"/>
+      <x:c r="I13" s="14" t="str"/>
+      <x:c r="J13" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1551</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="14" t="str">
+        <x:v>candidate-new</x:v>
+      </x:c>
+      <x:c r="B14" s="14" t="str">
+        <x:v>unmapped-official-series-id</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="D14" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="str">
+        <x:v>1552</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="str">
+        <x:v>特選 友達の母</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H14" s="14" t="str"/>
+      <x:c r="I14" s="14" t="str"/>
+      <x:c r="J14" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1552</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="14" t="str">
+        <x:v>candidate-new</x:v>
+      </x:c>
+      <x:c r="B15" s="14" t="str">
+        <x:v>unmapped-official-series-id</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="D15" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="str">
+        <x:v>1553</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="str">
+        <x:v>僕のおばさん</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H15" s="14" t="str"/>
+      <x:c r="I15" s="14" t="str"/>
+      <x:c r="J15" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1553</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="14" t="str">
+        <x:v>candidate-new</x:v>
+      </x:c>
+      <x:c r="B16" s="14" t="str">
+        <x:v>unmapped-official-series-id</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="D16" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="str">
+        <x:v>1554</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="str">
+        <x:v>素人人妻ナンパ総集編4時間</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H16" s="14" t="str"/>
+      <x:c r="I16" s="14" t="str"/>
+      <x:c r="J16" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1554</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="14" t="str">
+        <x:v>candidate-new</x:v>
+      </x:c>
+      <x:c r="B17" s="14" t="str">
+        <x:v>unmapped-official-series-id</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="D17" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="str">
+        <x:v>1555</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="str">
+        <x:v>五十路熟女18人4時間</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H17" s="14" t="str"/>
+      <x:c r="I17" s="14" t="str"/>
+      <x:c r="J17" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1555</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="14" t="str">
+        <x:v>candidate-new</x:v>
+      </x:c>
+      <x:c r="B18" s="14" t="str">
+        <x:v>unmapped-official-series-id</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="D18" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="str">
+        <x:v>1556</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="str">
+        <x:v>団地妻20人4時間</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H18" s="14" t="str"/>
+      <x:c r="I18" s="14" t="str"/>
+      <x:c r="J18" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1556</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="14" t="str">
+        <x:v>candidate-new</x:v>
+      </x:c>
+      <x:c r="B19" s="14" t="str">
+        <x:v>unmapped-official-series-id</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="D19" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="str">
+        <x:v>1557</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="str">
+        <x:v>犯された熟女たち総集編4時間</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H19" s="14" t="str"/>
+      <x:c r="I19" s="14" t="str"/>
+      <x:c r="J19" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1557</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="14" t="str">
+        <x:v>candidate-new</x:v>
+      </x:c>
+      <x:c r="B20" s="14" t="str">
+        <x:v>unmapped-official-series-id</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="D20" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="str">
+        <x:v>1558</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="str">
+        <x:v>妖艶おんな愛戯</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H20" s="14" t="str"/>
+      <x:c r="I20" s="14" t="str"/>
+      <x:c r="J20" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1558</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/exports/xlsx/organization-series-registry.xlsx
+++ b/exports/xlsx/organization-series-registry.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organizations" sheetId="1" r:id="Rd9f14d44a5474c3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series" sheetId="2" r:id="Recc42d6c82724ab4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Registry" sheetId="3" r:id="R7a84e57844ea40ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External ID Mapping" sheetId="4" r:id="R66b2e2bc90a641d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidates" sheetId="5" r:id="Re70d3ff4cc694522"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="6" r:id="R14db8a04de684f48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Index Snapshots" sheetId="7" r:id="R86249e00269f4b4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Index Candidates" sheetId="8" r:id="R70800396fd1e4f21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organizations" sheetId="1" r:id="R99c11c025a1b4ef6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series" sheetId="2" r:id="R9e948d889be9401d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Registry" sheetId="3" r:id="R4de48abc726344f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External ID Mapping" sheetId="4" r:id="R99fba7629ccd40b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidates" sheetId="5" r:id="R2a23d413f5844b98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="6" r:id="R25195b39020a48a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Index Snapshots" sheetId="7" r:id="R61ad35e8c3214efa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Index Candidates" sheetId="8" r:id="Rc5bea03cb82e4d0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Candidate Reviews" sheetId="9" r:id="Rf4dff31bee8041d8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3430,6 +3431,576 @@
         <x:v>madonna.series:1749</x:v>
       </x:c>
     </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="14" t="str">
+        <x:v>series_000018</x:v>
+      </x:c>
+      <x:c r="B19" s="14" t="str">
+        <x:v>アナル奴隷白書</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="str">
+        <x:v>肛门奴隶白皮书</x:v>
+      </x:c>
+      <x:c r="D19" s="14" t="str">
+        <x:v>Anal Slave Report</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="str"/>
+      <x:c r="H19" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I19" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2253</x:v>
+      </x:c>
+      <x:c r="J19" s="14" t="str">
+        <x:v>attackers.series:2253</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="14" t="str">
+        <x:v>series_000019</x:v>
+      </x:c>
+      <x:c r="B20" s="14" t="str">
+        <x:v>夫の目の前で犯されて</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="str">
+        <x:v>在丈夫面前被侵犯</x:v>
+      </x:c>
+      <x:c r="D20" s="14" t="str">
+        <x:v>Violated Before Her Husband’s Eyes</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="str"/>
+      <x:c r="H20" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I20" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2254</x:v>
+      </x:c>
+      <x:c r="J20" s="14" t="str">
+        <x:v>attackers.series:2254</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="14" t="str">
+        <x:v>series_000020</x:v>
+      </x:c>
+      <x:c r="B21" s="14" t="str">
+        <x:v>地獄の女神</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="str">
+        <x:v>地狱女神</x:v>
+      </x:c>
+      <x:c r="D21" s="14" t="str">
+        <x:v>Goddess of Hell</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="str"/>
+      <x:c r="H21" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I21" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2255</x:v>
+      </x:c>
+      <x:c r="J21" s="14" t="str">
+        <x:v>attackers.series:2255</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="14" t="str">
+        <x:v>series_000021</x:v>
+      </x:c>
+      <x:c r="B22" s="14" t="str">
+        <x:v>絶対調教</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="str">
+        <x:v>绝对调教</x:v>
+      </x:c>
+      <x:c r="D22" s="14" t="str">
+        <x:v>Absolute Training</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="str"/>
+      <x:c r="H22" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I22" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2257</x:v>
+      </x:c>
+      <x:c r="J22" s="14" t="str">
+        <x:v>attackers.series:2257</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="14" t="str">
+        <x:v>series_000022</x:v>
+      </x:c>
+      <x:c r="B23" s="14" t="str">
+        <x:v>淫乱奴隷の強制快楽</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="str">
+        <x:v>淫乱奴隶的强制快感</x:v>
+      </x:c>
+      <x:c r="D23" s="14" t="str">
+        <x:v>Forced Pleasure of a Lewd Slave</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="str"/>
+      <x:c r="H23" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I23" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2258</x:v>
+      </x:c>
+      <x:c r="J23" s="14" t="str">
+        <x:v>attackers.series:2258</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="14" t="str">
+        <x:v>series_000023</x:v>
+      </x:c>
+      <x:c r="B24" s="14" t="str">
+        <x:v>貞操帯の女</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="str">
+        <x:v>贞操带之女</x:v>
+      </x:c>
+      <x:c r="D24" s="14" t="str">
+        <x:v>Woman in a Chastity Belt</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="str"/>
+      <x:c r="H24" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I24" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2259</x:v>
+      </x:c>
+      <x:c r="J24" s="14" t="str">
+        <x:v>attackers.series:2259</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="14" t="str">
+        <x:v>series_000024</x:v>
+      </x:c>
+      <x:c r="B25" s="14" t="str">
+        <x:v>楠木女学院</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="str">
+        <x:v>楠木女子学院</x:v>
+      </x:c>
+      <x:c r="D25" s="14" t="str">
+        <x:v>Kusunoki Girls’ Academy</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="str"/>
+      <x:c r="H25" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I25" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2260</x:v>
+      </x:c>
+      <x:c r="J25" s="14" t="str">
+        <x:v>attackers.series:2260</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="14" t="str">
+        <x:v>series_000025</x:v>
+      </x:c>
+      <x:c r="B26" s="14" t="str">
+        <x:v>鬼畜輪姦</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="str">
+        <x:v>残酷轮奸</x:v>
+      </x:c>
+      <x:c r="D26" s="14" t="str">
+        <x:v>Brutal Gang Assault</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="str"/>
+      <x:c r="H26" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I26" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2261</x:v>
+      </x:c>
+      <x:c r="J26" s="14" t="str">
+        <x:v>attackers.series:2261</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="14" t="str">
+        <x:v>series_000026</x:v>
+      </x:c>
+      <x:c r="B27" s="14" t="str">
+        <x:v>女豹</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="str">
+        <x:v>女豹</x:v>
+      </x:c>
+      <x:c r="D27" s="14" t="str">
+        <x:v>Leopard Woman</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="str"/>
+      <x:c r="H27" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I27" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2263</x:v>
+      </x:c>
+      <x:c r="J27" s="14" t="str">
+        <x:v>attackers.series:2263</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="14" t="str">
+        <x:v>series_000027</x:v>
+      </x:c>
+      <x:c r="B28" s="14" t="str">
+        <x:v>となりの奥さん</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="str">
+        <x:v>邻家的太太</x:v>
+      </x:c>
+      <x:c r="D28" s="14" t="str">
+        <x:v>The Wife Next Door</x:v>
+      </x:c>
+      <x:c r="E28" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="G28" s="14" t="str"/>
+      <x:c r="H28" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I28" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1549</x:v>
+      </x:c>
+      <x:c r="J28" s="14" t="str">
+        <x:v>madonna.series:1549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="14" t="str">
+        <x:v>series_000028</x:v>
+      </x:c>
+      <x:c r="B29" s="14" t="str">
+        <x:v>美熟女と黒人</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="str">
+        <x:v>美熟女与黑人</x:v>
+      </x:c>
+      <x:c r="D29" s="14" t="str">
+        <x:v>Beautiful Mature Woman and Black Man</x:v>
+      </x:c>
+      <x:c r="E29" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="G29" s="14" t="str"/>
+      <x:c r="H29" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I29" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1550</x:v>
+      </x:c>
+      <x:c r="J29" s="14" t="str">
+        <x:v>madonna.series:1550</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="14" t="str">
+        <x:v>series_000029</x:v>
+      </x:c>
+      <x:c r="B30" s="14" t="str">
+        <x:v>愛する夫の目の前で・・・</x:v>
+      </x:c>
+      <x:c r="C30" s="14" t="str">
+        <x:v>在深爱的丈夫面前……</x:v>
+      </x:c>
+      <x:c r="D30" s="14" t="str">
+        <x:v>Before Her Beloved Husband...</x:v>
+      </x:c>
+      <x:c r="E30" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="G30" s="14" t="str"/>
+      <x:c r="H30" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I30" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1551</x:v>
+      </x:c>
+      <x:c r="J30" s="14" t="str">
+        <x:v>madonna.series:1551</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="14" t="str">
+        <x:v>series_000030</x:v>
+      </x:c>
+      <x:c r="B31" s="14" t="str">
+        <x:v>特選 友達の母</x:v>
+      </x:c>
+      <x:c r="C31" s="14" t="str">
+        <x:v>特选 朋友的母亲</x:v>
+      </x:c>
+      <x:c r="D31" s="14" t="str">
+        <x:v>Special Selection: Friend’s Mother</x:v>
+      </x:c>
+      <x:c r="E31" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="G31" s="14" t="str"/>
+      <x:c r="H31" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I31" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1552</x:v>
+      </x:c>
+      <x:c r="J31" s="14" t="str">
+        <x:v>madonna.series:1552</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="14" t="str">
+        <x:v>series_000031</x:v>
+      </x:c>
+      <x:c r="B32" s="14" t="str">
+        <x:v>僕のおばさん</x:v>
+      </x:c>
+      <x:c r="C32" s="14" t="str">
+        <x:v>我的阿姨</x:v>
+      </x:c>
+      <x:c r="D32" s="14" t="str">
+        <x:v>My Aunt</x:v>
+      </x:c>
+      <x:c r="E32" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="G32" s="14" t="str"/>
+      <x:c r="H32" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I32" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1553</x:v>
+      </x:c>
+      <x:c r="J32" s="14" t="str">
+        <x:v>madonna.series:1553</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="14" t="str">
+        <x:v>series_000032</x:v>
+      </x:c>
+      <x:c r="B33" s="14" t="str">
+        <x:v>素人人妻ナンパ総集編4時間</x:v>
+      </x:c>
+      <x:c r="C33" s="14" t="str">
+        <x:v>素人妻搭讪总集篇4小时</x:v>
+      </x:c>
+      <x:c r="D33" s="14" t="str">
+        <x:v>Amateur Married Women Pickup Compilation, 4 Hours</x:v>
+      </x:c>
+      <x:c r="E33" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="G33" s="14" t="str"/>
+      <x:c r="H33" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I33" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1554</x:v>
+      </x:c>
+      <x:c r="J33" s="14" t="str">
+        <x:v>madonna.series:1554</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="14" t="str">
+        <x:v>series_000033</x:v>
+      </x:c>
+      <x:c r="B34" s="14" t="str">
+        <x:v>五十路熟女18人4時間</x:v>
+      </x:c>
+      <x:c r="C34" s="14" t="str">
+        <x:v>五十岁熟女18人4小时</x:v>
+      </x:c>
+      <x:c r="D34" s="14" t="str">
+        <x:v>18 Mature Women in Their 50s, 4 Hours</x:v>
+      </x:c>
+      <x:c r="E34" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="G34" s="14" t="str"/>
+      <x:c r="H34" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I34" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1555</x:v>
+      </x:c>
+      <x:c r="J34" s="14" t="str">
+        <x:v>madonna.series:1555</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="14" t="str">
+        <x:v>series_000034</x:v>
+      </x:c>
+      <x:c r="B35" s="14" t="str">
+        <x:v>団地妻20人4時間</x:v>
+      </x:c>
+      <x:c r="C35" s="14" t="str">
+        <x:v>住宅区人妻20人4小时</x:v>
+      </x:c>
+      <x:c r="D35" s="14" t="str">
+        <x:v>20 Apartment-Complex Wives, 4 Hours</x:v>
+      </x:c>
+      <x:c r="E35" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="F35" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="G35" s="14" t="str"/>
+      <x:c r="H35" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I35" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1556</x:v>
+      </x:c>
+      <x:c r="J35" s="14" t="str">
+        <x:v>madonna.series:1556</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="14" t="str">
+        <x:v>series_000035</x:v>
+      </x:c>
+      <x:c r="B36" s="14" t="str">
+        <x:v>犯された熟女たち総集編4時間</x:v>
+      </x:c>
+      <x:c r="C36" s="14" t="str">
+        <x:v>被侵犯熟女总集篇4小时</x:v>
+      </x:c>
+      <x:c r="D36" s="14" t="str">
+        <x:v>Assaulted Mature Women Compilation, 4 Hours</x:v>
+      </x:c>
+      <x:c r="E36" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="F36" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="G36" s="14" t="str"/>
+      <x:c r="H36" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I36" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1557</x:v>
+      </x:c>
+      <x:c r="J36" s="14" t="str">
+        <x:v>madonna.series:1557</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="14" t="str">
+        <x:v>series_000036</x:v>
+      </x:c>
+      <x:c r="B37" s="14" t="str">
+        <x:v>妖艶おんな愛戯</x:v>
+      </x:c>
+      <x:c r="C37" s="14" t="str">
+        <x:v>妖艳女人爱戏</x:v>
+      </x:c>
+      <x:c r="D37" s="14" t="str">
+        <x:v>Seductive Women’s Love Play</x:v>
+      </x:c>
+      <x:c r="E37" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="F37" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="G37" s="14" t="str"/>
+      <x:c r="H37" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="I37" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1558</x:v>
+      </x:c>
+      <x:c r="J37" s="14" t="str">
+        <x:v>madonna.series:1558</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3637,10 +4208,10 @@
         <x:v>no</x:v>
       </x:c>
       <x:c r="I6" s="14" t="str">
-        <x:v>maker: 1/1 published, unrecognized=0, complete=yes; label: 17/17 published, unrecognized=0, complete=yes; series: 8/17 published, unrecognized=9, complete=no</x:v>
+        <x:v>maker: 1/1 published, unrecognized=0, complete=yes; label: 17/17 published, unrecognized=0, complete=yes; series: 17/17 published, unrecognized=0, complete=no</x:v>
       </x:c>
       <x:c r="J6" s="14" t="str">
-        <x:v>ATTACKERS Maker/Label coverage 已完整；Series 已建立 partial index snapshot。当前联合发现 17 个 Series，其中 8 个已发布、9 个仍为待审核候选；快照不是完整遍历，因此 Series 与来源级 completeTraversal 继续为 false。</x:v>
+        <x:v>ATTACKERS 当前 partial Series Snapshot 联合发现 17 个 Series，已全部审核并发布；但 Snapshot 不是完整索引遍历，因此 Series 与来源级 completeTraversal 继续为 false。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3669,10 +4240,10 @@
         <x:v>no</x:v>
       </x:c>
       <x:c r="I7" s="14" t="str">
-        <x:v>maker: 1/1 published, unrecognized=0, complete=yes; label: 18/18 published, unrecognized=0, complete=yes; series: 3/13 published, unrecognized=10, complete=no</x:v>
+        <x:v>maker: 1/1 published, unrecognized=0, complete=yes; label: 18/18 published, unrecognized=0, complete=yes; series: 13/13 published, unrecognized=0, complete=no</x:v>
       </x:c>
       <x:c r="J7" s="14" t="str">
-        <x:v>Madonna Maker/Label coverage 已完整；Series 已建立 partial index snapshot。当前联合发现 13 个 Series，其中 3 个已发布、10 个仍为待审核候选；快照不是完整遍历，因此 Series 与来源级 completeTraversal 继续为 false。</x:v>
+        <x:v>Madonna 当前 partial Series Snapshot 联合发现 13 个 Series，已全部审核并发布；但 Snapshot 不是完整索引遍历，因此 Series 与来源级 completeTraversal 继续为 false。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4115,10 +4686,10 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C19" s="14" t="str">
-        <x:v>2256</x:v>
+        <x:v>2253</x:v>
       </x:c>
       <x:c r="D19" s="14" t="str">
-        <x:v>series_000011</x:v>
+        <x:v>series_000018</x:v>
       </x:c>
       <x:c r="E19" s="14" t="str">
         <x:v>approved</x:v>
@@ -4127,7 +4698,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G19" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2256</x:v>
+        <x:v>https://attackers.net/works/list/series/2253</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -4138,10 +4709,10 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
-        <x:v>2269</x:v>
+        <x:v>2254</x:v>
       </x:c>
       <x:c r="D20" s="14" t="str">
-        <x:v>series_000008</x:v>
+        <x:v>series_000019</x:v>
       </x:c>
       <x:c r="E20" s="14" t="str">
         <x:v>approved</x:v>
@@ -4150,7 +4721,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G20" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2269</x:v>
+        <x:v>https://attackers.net/works/list/series/2254</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -4161,10 +4732,10 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
-        <x:v>2270</x:v>
+        <x:v>2255</x:v>
       </x:c>
       <x:c r="D21" s="14" t="str">
-        <x:v>series_000009</x:v>
+        <x:v>series_000020</x:v>
       </x:c>
       <x:c r="E21" s="14" t="str">
         <x:v>approved</x:v>
@@ -4173,7 +4744,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G21" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2270</x:v>
+        <x:v>https://attackers.net/works/list/series/2255</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -4184,10 +4755,10 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
-        <x:v>2274</x:v>
+        <x:v>2256</x:v>
       </x:c>
       <x:c r="D22" s="14" t="str">
-        <x:v>series_000012</x:v>
+        <x:v>series_000011</x:v>
       </x:c>
       <x:c r="E22" s="14" t="str">
         <x:v>approved</x:v>
@@ -4196,7 +4767,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G22" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2274</x:v>
+        <x:v>https://attackers.net/works/list/series/2256</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -4207,10 +4778,10 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C23" s="14" t="str">
-        <x:v>2293</x:v>
+        <x:v>2257</x:v>
       </x:c>
       <x:c r="D23" s="14" t="str">
-        <x:v>series_000010</x:v>
+        <x:v>series_000021</x:v>
       </x:c>
       <x:c r="E23" s="14" t="str">
         <x:v>approved</x:v>
@@ -4219,7 +4790,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G23" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2293</x:v>
+        <x:v>https://attackers.net/works/list/series/2257</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -4230,10 +4801,10 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C24" s="14" t="str">
-        <x:v>2325</x:v>
+        <x:v>2258</x:v>
       </x:c>
       <x:c r="D24" s="14" t="str">
-        <x:v>series_000013</x:v>
+        <x:v>series_000022</x:v>
       </x:c>
       <x:c r="E24" s="14" t="str">
         <x:v>approved</x:v>
@@ -4242,7 +4813,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G24" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2325</x:v>
+        <x:v>https://attackers.net/works/list/series/2258</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -4253,10 +4824,10 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C25" s="14" t="str">
-        <x:v>2402</x:v>
+        <x:v>2259</x:v>
       </x:c>
       <x:c r="D25" s="14" t="str">
-        <x:v>series_000007</x:v>
+        <x:v>series_000023</x:v>
       </x:c>
       <x:c r="E25" s="14" t="str">
         <x:v>approved</x:v>
@@ -4265,7 +4836,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G25" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2402</x:v>
+        <x:v>https://attackers.net/works/list/series/2259</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -4276,10 +4847,10 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C26" s="14" t="str">
-        <x:v>5317</x:v>
+        <x:v>2260</x:v>
       </x:c>
       <x:c r="D26" s="14" t="str">
-        <x:v>series_000014</x:v>
+        <x:v>series_000024</x:v>
       </x:c>
       <x:c r="E26" s="14" t="str">
         <x:v>approved</x:v>
@@ -4288,21 +4859,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G26" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/5317</x:v>
+        <x:v>https://attackers.net/works/list/series/2260</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B27" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C27" s="14" t="str">
-        <x:v>10077</x:v>
+        <x:v>2261</x:v>
       </x:c>
       <x:c r="D27" s="14" t="str">
-        <x:v>label_000076</x:v>
+        <x:v>series_000025</x:v>
       </x:c>
       <x:c r="E27" s="14" t="str">
         <x:v>approved</x:v>
@@ -4311,21 +4882,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G27" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10077</x:v>
+        <x:v>https://attackers.net/works/list/series/2261</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B28" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C28" s="14" t="str">
-        <x:v>10103</x:v>
+        <x:v>2263</x:v>
       </x:c>
       <x:c r="D28" s="14" t="str">
-        <x:v>label_000073</x:v>
+        <x:v>series_000026</x:v>
       </x:c>
       <x:c r="E28" s="14" t="str">
         <x:v>approved</x:v>
@@ -4334,21 +4905,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G28" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10103</x:v>
+        <x:v>https://attackers.net/works/list/series/2263</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B29" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C29" s="14" t="str">
-        <x:v>10142</x:v>
+        <x:v>2269</x:v>
       </x:c>
       <x:c r="D29" s="14" t="str">
-        <x:v>label_000077</x:v>
+        <x:v>series_000008</x:v>
       </x:c>
       <x:c r="E29" s="14" t="str">
         <x:v>approved</x:v>
@@ -4357,21 +4928,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G29" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10142</x:v>
+        <x:v>https://attackers.net/works/list/series/2269</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B30" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C30" s="14" t="str">
-        <x:v>10144</x:v>
+        <x:v>2270</x:v>
       </x:c>
       <x:c r="D30" s="14" t="str">
-        <x:v>label_000080</x:v>
+        <x:v>series_000009</x:v>
       </x:c>
       <x:c r="E30" s="14" t="str">
         <x:v>approved</x:v>
@@ -4380,21 +4951,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G30" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10144</x:v>
+        <x:v>https://attackers.net/works/list/series/2270</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B31" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C31" s="14" t="str">
-        <x:v>10151</x:v>
+        <x:v>2274</x:v>
       </x:c>
       <x:c r="D31" s="14" t="str">
-        <x:v>label_000078</x:v>
+        <x:v>series_000012</x:v>
       </x:c>
       <x:c r="E31" s="14" t="str">
         <x:v>approved</x:v>
@@ -4403,21 +4974,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G31" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10151</x:v>
+        <x:v>https://attackers.net/works/list/series/2274</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B32" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C32" s="14" t="str">
-        <x:v>12442</x:v>
+        <x:v>2293</x:v>
       </x:c>
       <x:c r="D32" s="14" t="str">
-        <x:v>label_000069</x:v>
+        <x:v>series_000010</x:v>
       </x:c>
       <x:c r="E32" s="14" t="str">
         <x:v>approved</x:v>
@@ -4426,21 +4997,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G32" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/12442</x:v>
+        <x:v>https://attackers.net/works/list/series/2293</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B33" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C33" s="14" t="str">
-        <x:v>12835</x:v>
+        <x:v>2325</x:v>
       </x:c>
       <x:c r="D33" s="14" t="str">
-        <x:v>label_000071</x:v>
+        <x:v>series_000013</x:v>
       </x:c>
       <x:c r="E33" s="14" t="str">
         <x:v>approved</x:v>
@@ -4449,21 +5020,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G33" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/12835</x:v>
+        <x:v>https://attackers.net/works/list/series/2325</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B34" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C34" s="14" t="str">
-        <x:v>2758</x:v>
+        <x:v>2402</x:v>
       </x:c>
       <x:c r="D34" s="14" t="str">
-        <x:v>label_000072</x:v>
+        <x:v>series_000007</x:v>
       </x:c>
       <x:c r="E34" s="14" t="str">
         <x:v>approved</x:v>
@@ -4472,21 +5043,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G34" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2758</x:v>
+        <x:v>https://attackers.net/works/list/series/2402</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B35" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C35" s="14" t="str">
-        <x:v>2760</x:v>
+        <x:v>5317</x:v>
       </x:c>
       <x:c r="D35" s="14" t="str">
-        <x:v>label_000079</x:v>
+        <x:v>series_000014</x:v>
       </x:c>
       <x:c r="E35" s="14" t="str">
         <x:v>approved</x:v>
@@ -4495,7 +5066,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G35" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2760</x:v>
+        <x:v>https://attackers.net/works/list/series/5317</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -4506,10 +5077,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C36" s="14" t="str">
-        <x:v>2767</x:v>
+        <x:v>10077</x:v>
       </x:c>
       <x:c r="D36" s="14" t="str">
-        <x:v>label_000070</x:v>
+        <x:v>label_000076</x:v>
       </x:c>
       <x:c r="E36" s="14" t="str">
         <x:v>approved</x:v>
@@ -4518,7 +5089,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G36" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2767</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10077</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -4529,10 +5100,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C37" s="14" t="str">
-        <x:v>2769</x:v>
+        <x:v>10103</x:v>
       </x:c>
       <x:c r="D37" s="14" t="str">
-        <x:v>label_000066</x:v>
+        <x:v>label_000073</x:v>
       </x:c>
       <x:c r="E37" s="14" t="str">
         <x:v>approved</x:v>
@@ -4541,7 +5112,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G37" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2769</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10103</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -4552,10 +5123,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C38" s="14" t="str">
-        <x:v>2771</x:v>
+        <x:v>10142</x:v>
       </x:c>
       <x:c r="D38" s="14" t="str">
-        <x:v>label_000065</x:v>
+        <x:v>label_000077</x:v>
       </x:c>
       <x:c r="E38" s="14" t="str">
         <x:v>approved</x:v>
@@ -4564,7 +5135,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G38" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2771</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10142</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -4575,10 +5146,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C39" s="14" t="str">
-        <x:v>2776</x:v>
+        <x:v>10144</x:v>
       </x:c>
       <x:c r="D39" s="14" t="str">
-        <x:v>label_000068</x:v>
+        <x:v>label_000080</x:v>
       </x:c>
       <x:c r="E39" s="14" t="str">
         <x:v>approved</x:v>
@@ -4587,7 +5158,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G39" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2776</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10144</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -4598,10 +5169,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C40" s="14" t="str">
-        <x:v>85265</x:v>
+        <x:v>10151</x:v>
       </x:c>
       <x:c r="D40" s="14" t="str">
-        <x:v>label_000075</x:v>
+        <x:v>label_000078</x:v>
       </x:c>
       <x:c r="E40" s="14" t="str">
         <x:v>approved</x:v>
@@ -4610,7 +5181,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G40" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/85265</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10151</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -4621,10 +5192,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C41" s="14" t="str">
-        <x:v>9483</x:v>
+        <x:v>12442</x:v>
       </x:c>
       <x:c r="D41" s="14" t="str">
-        <x:v>label_000074</x:v>
+        <x:v>label_000069</x:v>
       </x:c>
       <x:c r="E41" s="14" t="str">
         <x:v>approved</x:v>
@@ -4633,7 +5204,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G41" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/9483</x:v>
+        <x:v>https://ideapocket.com/works/list/label/12442</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -4644,10 +5215,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C42" s="14" t="str">
-        <x:v>9790</x:v>
+        <x:v>12835</x:v>
       </x:c>
       <x:c r="D42" s="14" t="str">
-        <x:v>label_000067</x:v>
+        <x:v>label_000071</x:v>
       </x:c>
       <x:c r="E42" s="14" t="str">
         <x:v>approved</x:v>
@@ -4656,21 +5227,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G42" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/9790</x:v>
+        <x:v>https://ideapocket.com/works/list/label/12835</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="14" t="str">
-        <x:v>ideapocket.series</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B43" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C43" s="14" t="str">
-        <x:v>1011</x:v>
+        <x:v>2758</x:v>
       </x:c>
       <x:c r="D43" s="14" t="str">
-        <x:v>series_000004</x:v>
+        <x:v>label_000072</x:v>
       </x:c>
       <x:c r="E43" s="14" t="str">
         <x:v>approved</x:v>
@@ -4679,21 +5250,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G43" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/series/1011</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2758</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="14" t="str">
-        <x:v>ideapocket.series</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B44" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C44" s="14" t="str">
-        <x:v>863</x:v>
+        <x:v>2760</x:v>
       </x:c>
       <x:c r="D44" s="14" t="str">
-        <x:v>series_000003</x:v>
+        <x:v>label_000079</x:v>
       </x:c>
       <x:c r="E44" s="14" t="str">
         <x:v>approved</x:v>
@@ -4702,21 +5273,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G44" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/series/863</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2760</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B45" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C45" s="14" t="str">
-        <x:v>10077</x:v>
+        <x:v>2767</x:v>
       </x:c>
       <x:c r="D45" s="14" t="str">
-        <x:v>label_000035</x:v>
+        <x:v>label_000070</x:v>
       </x:c>
       <x:c r="E45" s="14" t="str">
         <x:v>approved</x:v>
@@ -4725,21 +5296,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G45" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10077</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2767</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B46" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C46" s="14" t="str">
-        <x:v>10119</x:v>
+        <x:v>2769</x:v>
       </x:c>
       <x:c r="D46" s="14" t="str">
-        <x:v>label_000031</x:v>
+        <x:v>label_000066</x:v>
       </x:c>
       <x:c r="E46" s="14" t="str">
         <x:v>approved</x:v>
@@ -4748,21 +5319,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G46" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10119</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2769</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B47" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C47" s="14" t="str">
-        <x:v>10130</x:v>
+        <x:v>2771</x:v>
       </x:c>
       <x:c r="D47" s="14" t="str">
-        <x:v>label_000028</x:v>
+        <x:v>label_000065</x:v>
       </x:c>
       <x:c r="E47" s="14" t="str">
         <x:v>approved</x:v>
@@ -4771,21 +5342,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G47" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10130</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2771</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B48" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C48" s="14" t="str">
-        <x:v>10142</x:v>
+        <x:v>2776</x:v>
       </x:c>
       <x:c r="D48" s="14" t="str">
-        <x:v>label_000034</x:v>
+        <x:v>label_000068</x:v>
       </x:c>
       <x:c r="E48" s="14" t="str">
         <x:v>approved</x:v>
@@ -4794,21 +5365,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G48" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10142</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2776</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B49" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C49" s="14" t="str">
-        <x:v>10151</x:v>
+        <x:v>85265</x:v>
       </x:c>
       <x:c r="D49" s="14" t="str">
-        <x:v>label_000036</x:v>
+        <x:v>label_000075</x:v>
       </x:c>
       <x:c r="E49" s="14" t="str">
         <x:v>approved</x:v>
@@ -4817,21 +5388,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G49" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10151</x:v>
+        <x:v>https://ideapocket.com/works/list/label/85265</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B50" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C50" s="14" t="str">
-        <x:v>10159</x:v>
+        <x:v>9483</x:v>
       </x:c>
       <x:c r="D50" s="14" t="str">
-        <x:v>label_000030</x:v>
+        <x:v>label_000074</x:v>
       </x:c>
       <x:c r="E50" s="14" t="str">
         <x:v>approved</x:v>
@@ -4840,21 +5411,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G50" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10159</x:v>
+        <x:v>https://ideapocket.com/works/list/label/9483</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B51" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C51" s="14" t="str">
-        <x:v>12490</x:v>
+        <x:v>9790</x:v>
       </x:c>
       <x:c r="D51" s="14" t="str">
-        <x:v>label_000021</x:v>
+        <x:v>label_000067</x:v>
       </x:c>
       <x:c r="E51" s="14" t="str">
         <x:v>approved</x:v>
@@ -4863,21 +5434,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G51" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/12490</x:v>
+        <x:v>https://ideapocket.com/works/list/label/9790</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.series</x:v>
       </x:c>
       <x:c r="B52" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C52" s="14" t="str">
-        <x:v>12502</x:v>
+        <x:v>1011</x:v>
       </x:c>
       <x:c r="D52" s="14" t="str">
-        <x:v>label_000027</x:v>
+        <x:v>series_000004</x:v>
       </x:c>
       <x:c r="E52" s="14" t="str">
         <x:v>approved</x:v>
@@ -4886,21 +5457,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G52" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/12502</x:v>
+        <x:v>https://ideapocket.com/works/list/series/1011</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.series</x:v>
       </x:c>
       <x:c r="B53" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C53" s="14" t="str">
-        <x:v>12603</x:v>
+        <x:v>863</x:v>
       </x:c>
       <x:c r="D53" s="14" t="str">
-        <x:v>label_000026</x:v>
+        <x:v>series_000003</x:v>
       </x:c>
       <x:c r="E53" s="14" t="str">
         <x:v>approved</x:v>
@@ -4909,7 +5480,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G53" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/12603</x:v>
+        <x:v>https://ideapocket.com/works/list/series/863</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -4920,10 +5491,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C54" s="14" t="str">
-        <x:v>3125</x:v>
+        <x:v>10077</x:v>
       </x:c>
       <x:c r="D54" s="14" t="str">
-        <x:v>label_000037</x:v>
+        <x:v>label_000035</x:v>
       </x:c>
       <x:c r="E54" s="14" t="str">
         <x:v>approved</x:v>
@@ -4932,7 +5503,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G54" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/3125</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10077</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -4943,10 +5514,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C55" s="14" t="str">
-        <x:v>3669</x:v>
+        <x:v>10119</x:v>
       </x:c>
       <x:c r="D55" s="14" t="str">
-        <x:v>label_000020</x:v>
+        <x:v>label_000031</x:v>
       </x:c>
       <x:c r="E55" s="14" t="str">
         <x:v>approved</x:v>
@@ -4955,7 +5526,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G55" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/3669</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10119</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -4966,10 +5537,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C56" s="14" t="str">
-        <x:v>7354</x:v>
+        <x:v>10130</x:v>
       </x:c>
       <x:c r="D56" s="14" t="str">
-        <x:v>label_000024</x:v>
+        <x:v>label_000028</x:v>
       </x:c>
       <x:c r="E56" s="14" t="str">
         <x:v>approved</x:v>
@@ -4978,7 +5549,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G56" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/7354</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10130</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -4989,10 +5560,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C57" s="14" t="str">
-        <x:v>7993</x:v>
+        <x:v>10142</x:v>
       </x:c>
       <x:c r="D57" s="14" t="str">
-        <x:v>label_000029</x:v>
+        <x:v>label_000034</x:v>
       </x:c>
       <x:c r="E57" s="14" t="str">
         <x:v>approved</x:v>
@@ -5001,7 +5572,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G57" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/7993</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10142</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -5012,10 +5583,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C58" s="14" t="str">
-        <x:v>85265</x:v>
+        <x:v>10151</x:v>
       </x:c>
       <x:c r="D58" s="14" t="str">
-        <x:v>label_000032</x:v>
+        <x:v>label_000036</x:v>
       </x:c>
       <x:c r="E58" s="14" t="str">
         <x:v>approved</x:v>
@@ -5024,7 +5595,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G58" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/85265</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10151</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -5035,10 +5606,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C59" s="14" t="str">
-        <x:v>9387</x:v>
+        <x:v>10159</x:v>
       </x:c>
       <x:c r="D59" s="14" t="str">
-        <x:v>label_000022</x:v>
+        <x:v>label_000030</x:v>
       </x:c>
       <x:c r="E59" s="14" t="str">
         <x:v>approved</x:v>
@@ -5047,7 +5618,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G59" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/9387</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10159</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -5058,10 +5629,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C60" s="14" t="str">
-        <x:v>9419</x:v>
+        <x:v>12490</x:v>
       </x:c>
       <x:c r="D60" s="14" t="str">
-        <x:v>label_000025</x:v>
+        <x:v>label_000021</x:v>
       </x:c>
       <x:c r="E60" s="14" t="str">
         <x:v>approved</x:v>
@@ -5070,7 +5641,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G60" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/9419</x:v>
+        <x:v>https://madonna-av.com/works/list/label/12490</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -5081,10 +5652,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C61" s="14" t="str">
-        <x:v>9483</x:v>
+        <x:v>12502</x:v>
       </x:c>
       <x:c r="D61" s="14" t="str">
-        <x:v>label_000033</x:v>
+        <x:v>label_000027</x:v>
       </x:c>
       <x:c r="E61" s="14" t="str">
         <x:v>approved</x:v>
@@ -5093,7 +5664,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G61" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/9483</x:v>
+        <x:v>https://madonna-av.com/works/list/label/12502</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -5104,10 +5675,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C62" s="14" t="str">
-        <x:v>9789</x:v>
+        <x:v>12603</x:v>
       </x:c>
       <x:c r="D62" s="14" t="str">
-        <x:v>label_000023</x:v>
+        <x:v>label_000026</x:v>
       </x:c>
       <x:c r="E62" s="14" t="str">
         <x:v>approved</x:v>
@@ -5116,21 +5687,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G62" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/9789</x:v>
+        <x:v>https://madonna-av.com/works/list/label/12603</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B63" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C63" s="14" t="str">
-        <x:v>1749</x:v>
+        <x:v>3125</x:v>
       </x:c>
       <x:c r="D63" s="14" t="str">
-        <x:v>series_000017</x:v>
+        <x:v>label_000037</x:v>
       </x:c>
       <x:c r="E63" s="14" t="str">
         <x:v>approved</x:v>
@@ -5139,21 +5710,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G63" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1749</x:v>
+        <x:v>https://madonna-av.com/works/list/label/3125</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B64" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C64" s="14" t="str">
-        <x:v>1846</x:v>
+        <x:v>3669</x:v>
       </x:c>
       <x:c r="D64" s="14" t="str">
-        <x:v>series_000015</x:v>
+        <x:v>label_000020</x:v>
       </x:c>
       <x:c r="E64" s="14" t="str">
         <x:v>approved</x:v>
@@ -5162,21 +5733,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G64" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1846</x:v>
+        <x:v>https://madonna-av.com/works/list/label/3669</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B65" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C65" s="14" t="str">
-        <x:v>1891</x:v>
+        <x:v>7354</x:v>
       </x:c>
       <x:c r="D65" s="14" t="str">
-        <x:v>series_000016</x:v>
+        <x:v>label_000024</x:v>
       </x:c>
       <x:c r="E65" s="14" t="str">
         <x:v>approved</x:v>
@@ -5185,21 +5756,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G65" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1891</x:v>
+        <x:v>https://madonna-av.com/works/list/label/7354</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B66" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C66" s="14" t="str">
-        <x:v>10077</x:v>
+        <x:v>7993</x:v>
       </x:c>
       <x:c r="D66" s="14" t="str">
-        <x:v>label_000063</x:v>
+        <x:v>label_000029</x:v>
       </x:c>
       <x:c r="E66" s="14" t="str">
         <x:v>approved</x:v>
@@ -5208,21 +5779,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G66" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10077</x:v>
+        <x:v>https://madonna-av.com/works/list/label/7993</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B67" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C67" s="14" t="str">
-        <x:v>10106</x:v>
+        <x:v>85265</x:v>
       </x:c>
       <x:c r="D67" s="14" t="str">
-        <x:v>label_000053</x:v>
+        <x:v>label_000032</x:v>
       </x:c>
       <x:c r="E67" s="14" t="str">
         <x:v>approved</x:v>
@@ -5231,21 +5802,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G67" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10106</x:v>
+        <x:v>https://madonna-av.com/works/list/label/85265</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B68" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C68" s="14" t="str">
-        <x:v>10107</x:v>
+        <x:v>9387</x:v>
       </x:c>
       <x:c r="D68" s="14" t="str">
-        <x:v>label_000046</x:v>
+        <x:v>label_000022</x:v>
       </x:c>
       <x:c r="E68" s="14" t="str">
         <x:v>approved</x:v>
@@ -5254,21 +5825,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G68" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10107</x:v>
+        <x:v>https://madonna-av.com/works/list/label/9387</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B69" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C69" s="14" t="str">
-        <x:v>10131</x:v>
+        <x:v>9419</x:v>
       </x:c>
       <x:c r="D69" s="14" t="str">
-        <x:v>label_000047</x:v>
+        <x:v>label_000025</x:v>
       </x:c>
       <x:c r="E69" s="14" t="str">
         <x:v>approved</x:v>
@@ -5277,21 +5848,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G69" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10131</x:v>
+        <x:v>https://madonna-av.com/works/list/label/9419</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B70" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C70" s="14" t="str">
-        <x:v>10142</x:v>
+        <x:v>9483</x:v>
       </x:c>
       <x:c r="D70" s="14" t="str">
-        <x:v>label_000060</x:v>
+        <x:v>label_000033</x:v>
       </x:c>
       <x:c r="E70" s="14" t="str">
         <x:v>approved</x:v>
@@ -5300,21 +5871,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G70" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10142</x:v>
+        <x:v>https://madonna-av.com/works/list/label/9483</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B71" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C71" s="14" t="str">
-        <x:v>10144</x:v>
+        <x:v>9789</x:v>
       </x:c>
       <x:c r="D71" s="14" t="str">
-        <x:v>label_000061</x:v>
+        <x:v>label_000023</x:v>
       </x:c>
       <x:c r="E71" s="14" t="str">
         <x:v>approved</x:v>
@@ -5323,21 +5894,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G71" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10144</x:v>
+        <x:v>https://madonna-av.com/works/list/label/9789</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B72" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C72" s="14" t="str">
-        <x:v>10151</x:v>
+        <x:v>1549</x:v>
       </x:c>
       <x:c r="D72" s="14" t="str">
-        <x:v>label_000062</x:v>
+        <x:v>series_000027</x:v>
       </x:c>
       <x:c r="E72" s="14" t="str">
         <x:v>approved</x:v>
@@ -5346,21 +5917,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G72" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10151</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1549</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B73" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C73" s="14" t="str">
-        <x:v>10157</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D73" s="14" t="str">
-        <x:v>label_000058</x:v>
+        <x:v>series_000028</x:v>
       </x:c>
       <x:c r="E73" s="14" t="str">
         <x:v>approved</x:v>
@@ -5369,21 +5940,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G73" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10157</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1550</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B74" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C74" s="14" t="str">
-        <x:v>10172</x:v>
+        <x:v>1551</x:v>
       </x:c>
       <x:c r="D74" s="14" t="str">
-        <x:v>label_000064</x:v>
+        <x:v>series_000029</x:v>
       </x:c>
       <x:c r="E74" s="14" t="str">
         <x:v>approved</x:v>
@@ -5392,21 +5963,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G74" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10172</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1551</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B75" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C75" s="14" t="str">
-        <x:v>10174</x:v>
+        <x:v>1552</x:v>
       </x:c>
       <x:c r="D75" s="14" t="str">
-        <x:v>label_000050</x:v>
+        <x:v>series_000030</x:v>
       </x:c>
       <x:c r="E75" s="14" t="str">
         <x:v>approved</x:v>
@@ -5415,21 +5986,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G75" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10174</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1552</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B76" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C76" s="14" t="str">
-        <x:v>11471</x:v>
+        <x:v>1553</x:v>
       </x:c>
       <x:c r="D76" s="14" t="str">
-        <x:v>label_000057</x:v>
+        <x:v>series_000031</x:v>
       </x:c>
       <x:c r="E76" s="14" t="str">
         <x:v>approved</x:v>
@@ -5438,21 +6009,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G76" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/11471</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1553</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B77" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C77" s="14" t="str">
-        <x:v>12798</x:v>
+        <x:v>1554</x:v>
       </x:c>
       <x:c r="D77" s="14" t="str">
-        <x:v>label_000002</x:v>
+        <x:v>series_000032</x:v>
       </x:c>
       <x:c r="E77" s="14" t="str">
         <x:v>approved</x:v>
@@ -5461,21 +6032,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G77" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/12798</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1554</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B78" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C78" s="14" t="str">
-        <x:v>5046</x:v>
+        <x:v>1555</x:v>
       </x:c>
       <x:c r="D78" s="14" t="str">
-        <x:v>label_000039</x:v>
+        <x:v>series_000033</x:v>
       </x:c>
       <x:c r="E78" s="14" t="str">
         <x:v>approved</x:v>
@@ -5484,21 +6055,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G78" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5046</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1555</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B79" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C79" s="14" t="str">
-        <x:v>5047</x:v>
+        <x:v>1556</x:v>
       </x:c>
       <x:c r="D79" s="14" t="str">
-        <x:v>label_000038</x:v>
+        <x:v>series_000034</x:v>
       </x:c>
       <x:c r="E79" s="14" t="str">
         <x:v>approved</x:v>
@@ -5507,21 +6078,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G79" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5047</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1556</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B80" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C80" s="14" t="str">
-        <x:v>5048</x:v>
+        <x:v>1557</x:v>
       </x:c>
       <x:c r="D80" s="14" t="str">
-        <x:v>label_000001</x:v>
+        <x:v>series_000035</x:v>
       </x:c>
       <x:c r="E80" s="14" t="str">
         <x:v>approved</x:v>
@@ -5530,21 +6101,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G80" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5048</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1557</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B81" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C81" s="14" t="str">
-        <x:v>5049</x:v>
+        <x:v>1558</x:v>
       </x:c>
       <x:c r="D81" s="14" t="str">
-        <x:v>label_000045</x:v>
+        <x:v>series_000036</x:v>
       </x:c>
       <x:c r="E81" s="14" t="str">
         <x:v>approved</x:v>
@@ -5553,21 +6124,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G81" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5049</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1558</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B82" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C82" s="14" t="str">
-        <x:v>5090</x:v>
+        <x:v>1749</x:v>
       </x:c>
       <x:c r="D82" s="14" t="str">
-        <x:v>label_000044</x:v>
+        <x:v>series_000017</x:v>
       </x:c>
       <x:c r="E82" s="14" t="str">
         <x:v>approved</x:v>
@@ -5576,21 +6147,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G82" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5090</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1749</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B83" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C83" s="14" t="str">
-        <x:v>5409</x:v>
+        <x:v>1846</x:v>
       </x:c>
       <x:c r="D83" s="14" t="str">
-        <x:v>label_000049</x:v>
+        <x:v>series_000015</x:v>
       </x:c>
       <x:c r="E83" s="14" t="str">
         <x:v>approved</x:v>
@@ -5599,21 +6170,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G83" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5409</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1846</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B84" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C84" s="14" t="str">
-        <x:v>6879</x:v>
+        <x:v>1891</x:v>
       </x:c>
       <x:c r="D84" s="14" t="str">
-        <x:v>label_000040</x:v>
+        <x:v>series_000016</x:v>
       </x:c>
       <x:c r="E84" s="14" t="str">
         <x:v>approved</x:v>
@@ -5622,7 +6193,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G84" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/6879</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1891</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -5633,10 +6204,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C85" s="14" t="str">
-        <x:v>85265</x:v>
+        <x:v>10077</x:v>
       </x:c>
       <x:c r="D85" s="14" t="str">
-        <x:v>label_000056</x:v>
+        <x:v>label_000063</x:v>
       </x:c>
       <x:c r="E85" s="14" t="str">
         <x:v>approved</x:v>
@@ -5645,7 +6216,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G85" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/85265</x:v>
+        <x:v>https://moodyz.com/works/list/label/10077</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -5656,10 +6227,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C86" s="14" t="str">
-        <x:v>8916</x:v>
+        <x:v>10106</x:v>
       </x:c>
       <x:c r="D86" s="14" t="str">
-        <x:v>label_000051</x:v>
+        <x:v>label_000053</x:v>
       </x:c>
       <x:c r="E86" s="14" t="str">
         <x:v>approved</x:v>
@@ -5668,7 +6239,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G86" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/8916</x:v>
+        <x:v>https://moodyz.com/works/list/label/10106</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -5679,10 +6250,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C87" s="14" t="str">
-        <x:v>8917</x:v>
+        <x:v>10107</x:v>
       </x:c>
       <x:c r="D87" s="14" t="str">
-        <x:v>label_000055</x:v>
+        <x:v>label_000046</x:v>
       </x:c>
       <x:c r="E87" s="14" t="str">
         <x:v>approved</x:v>
@@ -5691,7 +6262,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G87" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/8917</x:v>
+        <x:v>https://moodyz.com/works/list/label/10107</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -5702,10 +6273,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C88" s="14" t="str">
-        <x:v>9288</x:v>
+        <x:v>10131</x:v>
       </x:c>
       <x:c r="D88" s="14" t="str">
-        <x:v>label_000054</x:v>
+        <x:v>label_000047</x:v>
       </x:c>
       <x:c r="E88" s="14" t="str">
         <x:v>approved</x:v>
@@ -5714,7 +6285,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G88" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9288</x:v>
+        <x:v>https://moodyz.com/works/list/label/10131</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -5725,10 +6296,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C89" s="14" t="str">
-        <x:v>9308</x:v>
+        <x:v>10142</x:v>
       </x:c>
       <x:c r="D89" s="14" t="str">
-        <x:v>label_000043</x:v>
+        <x:v>label_000060</x:v>
       </x:c>
       <x:c r="E89" s="14" t="str">
         <x:v>approved</x:v>
@@ -5737,7 +6308,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G89" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9308</x:v>
+        <x:v>https://moodyz.com/works/list/label/10142</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -5748,10 +6319,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C90" s="14" t="str">
-        <x:v>9397</x:v>
+        <x:v>10144</x:v>
       </x:c>
       <x:c r="D90" s="14" t="str">
-        <x:v>label_000052</x:v>
+        <x:v>label_000061</x:v>
       </x:c>
       <x:c r="E90" s="14" t="str">
         <x:v>approved</x:v>
@@ -5760,7 +6331,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G90" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9397</x:v>
+        <x:v>https://moodyz.com/works/list/label/10144</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -5771,10 +6342,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C91" s="14" t="str">
-        <x:v>9458</x:v>
+        <x:v>10151</x:v>
       </x:c>
       <x:c r="D91" s="14" t="str">
-        <x:v>label_000048</x:v>
+        <x:v>label_000062</x:v>
       </x:c>
       <x:c r="E91" s="14" t="str">
         <x:v>approved</x:v>
@@ -5783,7 +6354,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G91" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9458</x:v>
+        <x:v>https://moodyz.com/works/list/label/10151</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -5794,10 +6365,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C92" s="14" t="str">
-        <x:v>9483</x:v>
+        <x:v>10157</x:v>
       </x:c>
       <x:c r="D92" s="14" t="str">
-        <x:v>label_000059</x:v>
+        <x:v>label_000058</x:v>
       </x:c>
       <x:c r="E92" s="14" t="str">
         <x:v>approved</x:v>
@@ -5806,7 +6377,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G92" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9483</x:v>
+        <x:v>https://moodyz.com/works/list/label/10157</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -5817,10 +6388,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C93" s="14" t="str">
-        <x:v>9732</x:v>
+        <x:v>10172</x:v>
       </x:c>
       <x:c r="D93" s="14" t="str">
-        <x:v>label_000042</x:v>
+        <x:v>label_000064</x:v>
       </x:c>
       <x:c r="E93" s="14" t="str">
         <x:v>approved</x:v>
@@ -5829,7 +6400,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G93" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9732</x:v>
+        <x:v>https://moodyz.com/works/list/label/10172</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -5840,10 +6411,10 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C94" s="14" t="str">
-        <x:v>9782</x:v>
+        <x:v>10174</x:v>
       </x:c>
       <x:c r="D94" s="14" t="str">
-        <x:v>label_000041</x:v>
+        <x:v>label_000050</x:v>
       </x:c>
       <x:c r="E94" s="14" t="str">
         <x:v>approved</x:v>
@@ -5852,21 +6423,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G94" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9782</x:v>
+        <x:v>https://moodyz.com/works/list/label/10174</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="14" t="str">
-        <x:v>moodyz.series</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B95" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C95" s="14" t="str">
-        <x:v>5427</x:v>
+        <x:v>11471</x:v>
       </x:c>
       <x:c r="D95" s="14" t="str">
-        <x:v>series_000002</x:v>
+        <x:v>label_000057</x:v>
       </x:c>
       <x:c r="E95" s="14" t="str">
         <x:v>approved</x:v>
@@ -5875,21 +6446,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G95" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/series/5427</x:v>
+        <x:v>https://moodyz.com/works/list/label/11471</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="14" t="str">
-        <x:v>s1.label</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B96" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C96" s="14" t="str">
-        <x:v>4355</x:v>
+        <x:v>12798</x:v>
       </x:c>
       <x:c r="D96" s="14" t="str">
-        <x:v>label_000081</x:v>
+        <x:v>label_000002</x:v>
       </x:c>
       <x:c r="E96" s="14" t="str">
         <x:v>approved</x:v>
@@ -5898,21 +6469,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G96" s="14" t="str">
-        <x:v>https://s1s1s1.com/works/list/label/4355</x:v>
+        <x:v>https://moodyz.com/works/list/label/12798</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="14" t="str">
-        <x:v>s1.series</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B97" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C97" s="14" t="str">
-        <x:v>414</x:v>
+        <x:v>5046</x:v>
       </x:c>
       <x:c r="D97" s="14" t="str">
-        <x:v>series_000001</x:v>
+        <x:v>label_000039</x:v>
       </x:c>
       <x:c r="E97" s="14" t="str">
         <x:v>approved</x:v>
@@ -5921,21 +6492,21 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G97" s="14" t="str">
-        <x:v>https://s1s1s1.com/works/list/series/414</x:v>
+        <x:v>https://moodyz.com/works/list/label/5046</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="14" t="str">
-        <x:v>s1.series</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B98" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C98" s="14" t="str">
-        <x:v>422</x:v>
+        <x:v>5047</x:v>
       </x:c>
       <x:c r="D98" s="14" t="str">
-        <x:v>series_000005</x:v>
+        <x:v>label_000038</x:v>
       </x:c>
       <x:c r="E98" s="14" t="str">
         <x:v>approved</x:v>
@@ -5944,29 +6515,466 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="G98" s="14" t="str">
-        <x:v>https://s1s1s1.com/works/list/series/422</x:v>
+        <x:v>https://moodyz.com/works/list/label/5047</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B99" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C99" s="14" t="str">
+        <x:v>5048</x:v>
+      </x:c>
+      <x:c r="D99" s="14" t="str">
+        <x:v>label_000001</x:v>
+      </x:c>
+      <x:c r="E99" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F99" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G99" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5048</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B100" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C100" s="14" t="str">
+        <x:v>5049</x:v>
+      </x:c>
+      <x:c r="D100" s="14" t="str">
+        <x:v>label_000045</x:v>
+      </x:c>
+      <x:c r="E100" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F100" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G100" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5049</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B101" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C101" s="14" t="str">
+        <x:v>5090</x:v>
+      </x:c>
+      <x:c r="D101" s="14" t="str">
+        <x:v>label_000044</x:v>
+      </x:c>
+      <x:c r="E101" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F101" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G101" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5090</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B102" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C102" s="14" t="str">
+        <x:v>5409</x:v>
+      </x:c>
+      <x:c r="D102" s="14" t="str">
+        <x:v>label_000049</x:v>
+      </x:c>
+      <x:c r="E102" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F102" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G102" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5409</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B103" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C103" s="14" t="str">
+        <x:v>6879</x:v>
+      </x:c>
+      <x:c r="D103" s="14" t="str">
+        <x:v>label_000040</x:v>
+      </x:c>
+      <x:c r="E103" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F103" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G103" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/6879</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B104" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C104" s="14" t="str">
+        <x:v>85265</x:v>
+      </x:c>
+      <x:c r="D104" s="14" t="str">
+        <x:v>label_000056</x:v>
+      </x:c>
+      <x:c r="E104" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F104" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G104" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/85265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B105" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C105" s="14" t="str">
+        <x:v>8916</x:v>
+      </x:c>
+      <x:c r="D105" s="14" t="str">
+        <x:v>label_000051</x:v>
+      </x:c>
+      <x:c r="E105" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F105" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G105" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/8916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B106" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C106" s="14" t="str">
+        <x:v>8917</x:v>
+      </x:c>
+      <x:c r="D106" s="14" t="str">
+        <x:v>label_000055</x:v>
+      </x:c>
+      <x:c r="E106" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F106" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G106" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/8917</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B107" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C107" s="14" t="str">
+        <x:v>9288</x:v>
+      </x:c>
+      <x:c r="D107" s="14" t="str">
+        <x:v>label_000054</x:v>
+      </x:c>
+      <x:c r="E107" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F107" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G107" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9288</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B108" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C108" s="14" t="str">
+        <x:v>9308</x:v>
+      </x:c>
+      <x:c r="D108" s="14" t="str">
+        <x:v>label_000043</x:v>
+      </x:c>
+      <x:c r="E108" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F108" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G108" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B109" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C109" s="14" t="str">
+        <x:v>9397</x:v>
+      </x:c>
+      <x:c r="D109" s="14" t="str">
+        <x:v>label_000052</x:v>
+      </x:c>
+      <x:c r="E109" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F109" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G109" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9397</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B110" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C110" s="14" t="str">
+        <x:v>9458</x:v>
+      </x:c>
+      <x:c r="D110" s="14" t="str">
+        <x:v>label_000048</x:v>
+      </x:c>
+      <x:c r="E110" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F110" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G110" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9458</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B111" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C111" s="14" t="str">
+        <x:v>9483</x:v>
+      </x:c>
+      <x:c r="D111" s="14" t="str">
+        <x:v>label_000059</x:v>
+      </x:c>
+      <x:c r="E111" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F111" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G111" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9483</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B112" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C112" s="14" t="str">
+        <x:v>9732</x:v>
+      </x:c>
+      <x:c r="D112" s="14" t="str">
+        <x:v>label_000042</x:v>
+      </x:c>
+      <x:c r="E112" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F112" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G112" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9732</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B113" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C113" s="14" t="str">
+        <x:v>9782</x:v>
+      </x:c>
+      <x:c r="D113" s="14" t="str">
+        <x:v>label_000041</x:v>
+      </x:c>
+      <x:c r="E113" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F113" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G113" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9782</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="14" t="str">
+        <x:v>moodyz.series</x:v>
+      </x:c>
+      <x:c r="B114" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C114" s="14" t="str">
+        <x:v>5427</x:v>
+      </x:c>
+      <x:c r="D114" s="14" t="str">
+        <x:v>series_000002</x:v>
+      </x:c>
+      <x:c r="E114" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F114" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G114" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/5427</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="14" t="str">
+        <x:v>s1.label</x:v>
+      </x:c>
+      <x:c r="B115" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C115" s="14" t="str">
+        <x:v>4355</x:v>
+      </x:c>
+      <x:c r="D115" s="14" t="str">
+        <x:v>label_000081</x:v>
+      </x:c>
+      <x:c r="E115" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F115" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G115" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/label/4355</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="14" t="str">
         <x:v>s1.series</x:v>
       </x:c>
-      <x:c r="B99" s="14" t="str">
+      <x:c r="B116" s="14" t="str">
         <x:v>series</x:v>
       </x:c>
-      <x:c r="C99" s="14" t="str">
+      <x:c r="C116" s="14" t="str">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="D116" s="14" t="str">
+        <x:v>series_000001</x:v>
+      </x:c>
+      <x:c r="E116" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F116" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G116" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/414</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="B117" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C117" s="14" t="str">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="D117" s="14" t="str">
+        <x:v>series_000005</x:v>
+      </x:c>
+      <x:c r="E117" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F117" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G117" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/422</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="B118" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C118" s="14" t="str">
         <x:v>570</x:v>
       </x:c>
-      <x:c r="D99" s="14" t="str">
+      <x:c r="D118" s="14" t="str">
         <x:v>series_000006</x:v>
       </x:c>
-      <x:c r="E99" s="14" t="str">
-        <x:v>approved</x:v>
-      </x:c>
-      <x:c r="F99" s="14" t="str">
-        <x:v>2026-09-04</x:v>
-      </x:c>
-      <x:c r="G99" s="14" t="str">
+      <x:c r="E118" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F118" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="G118" s="14" t="str">
         <x:v>https://s1s1s1.com/works/list/series/570</x:v>
       </x:c>
     </x:row>
@@ -6084,23 +7092,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C2" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>attackers.label</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E2" s="14" t="str">
-        <x:v>5048</x:v>
+        <x:v>10077</x:v>
       </x:c>
       <x:c r="F2" s="14" t="str">
-        <x:v>MOODYZ DIVA</x:v>
+        <x:v>AVグランプリ</x:v>
       </x:c>
       <x:c r="G2" s="14" t="str">
-        <x:v>label_000001</x:v>
+        <x:v>label_000016</x:v>
       </x:c>
       <x:c r="H2" s="14" t="str"/>
       <x:c r="I2" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5048</x:v>
+        <x:v>https://attackers.net/works/list/label/10077</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -6111,23 +7119,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C3" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>attackers.label</x:v>
       </x:c>
       <x:c r="D3" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E3" s="14" t="str">
-        <x:v>12798</x:v>
+        <x:v>10142</x:v>
       </x:c>
       <x:c r="F3" s="14" t="str">
-        <x:v>みんなのキカタン</x:v>
+        <x:v>おっぱい祭り</x:v>
       </x:c>
       <x:c r="G3" s="14" t="str">
-        <x:v>label_000002</x:v>
+        <x:v>label_000017</x:v>
       </x:c>
       <x:c r="H3" s="14" t="str"/>
       <x:c r="I3" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/12798</x:v>
+        <x:v>https://attackers.net/works/list/label/10142</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -6138,23 +7146,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C4" s="14" t="str">
-        <x:v>s1.series</x:v>
+        <x:v>attackers.label</x:v>
       </x:c>
       <x:c r="D4" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="E4" s="14" t="str">
-        <x:v>414</x:v>
+        <x:v>10144</x:v>
       </x:c>
       <x:c r="F4" s="14" t="str">
-        <x:v>新人NO.1STYLE</x:v>
+        <x:v>秋のシコシコ強化月間</x:v>
       </x:c>
       <x:c r="G4" s="14" t="str">
-        <x:v>series_000001</x:v>
+        <x:v>label_000018</x:v>
       </x:c>
       <x:c r="H4" s="14" t="str"/>
       <x:c r="I4" s="14" t="str">
-        <x:v>https://s1s1s1.com/works/list/series/414</x:v>
+        <x:v>https://attackers.net/works/list/label/10144</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -6165,23 +7173,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
-        <x:v>moodyz.series</x:v>
+        <x:v>attackers.label</x:v>
       </x:c>
       <x:c r="D5" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="E5" s="14" t="str">
-        <x:v>5427</x:v>
+        <x:v>10151</x:v>
       </x:c>
       <x:c r="F5" s="14" t="str">
-        <x:v>カラミざかり</x:v>
+        <x:v>背徳ビチョビチョ！NTR大放出</x:v>
       </x:c>
       <x:c r="G5" s="14" t="str">
-        <x:v>series_000002</x:v>
+        <x:v>label_000019</x:v>
       </x:c>
       <x:c r="H5" s="14" t="str"/>
       <x:c r="I5" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/series/5427</x:v>
+        <x:v>https://attackers.net/works/list/label/10151</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -6192,23 +7200,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C6" s="14" t="str">
-        <x:v>ideapocket.series</x:v>
+        <x:v>attackers.label</x:v>
       </x:c>
       <x:c r="D6" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="E6" s="14" t="str">
-        <x:v>863</x:v>
+        <x:v>12605</x:v>
       </x:c>
       <x:c r="F6" s="14" t="str">
-        <x:v>死ぬほど大嫌いな上司とまさかの相部屋に</x:v>
+        <x:v>誘女</x:v>
       </x:c>
       <x:c r="G6" s="14" t="str">
-        <x:v>series_000003</x:v>
+        <x:v>label_000011</x:v>
       </x:c>
       <x:c r="H6" s="14" t="str"/>
       <x:c r="I6" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/series/863</x:v>
+        <x:v>https://attackers.net/works/list/label/12605</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -6219,23 +7227,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C7" s="14" t="str">
-        <x:v>ideapocket.series</x:v>
+        <x:v>attackers.label</x:v>
       </x:c>
       <x:c r="D7" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="E7" s="14" t="str">
-        <x:v>1011</x:v>
+        <x:v>2735</x:v>
       </x:c>
       <x:c r="F7" s="14" t="str">
-        <x:v>うちの妻を犯して下さい</x:v>
+        <x:v>アタッカーズ・アンソロジー</x:v>
       </x:c>
       <x:c r="G7" s="14" t="str">
-        <x:v>series_000004</x:v>
+        <x:v>label_000009</x:v>
       </x:c>
       <x:c r="H7" s="14" t="str"/>
       <x:c r="I7" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/series/1011</x:v>
+        <x:v>https://attackers.net/works/list/label/2735</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -6252,17 +7260,17 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="E8" s="14" t="str">
-        <x:v>2754</x:v>
+        <x:v>2737</x:v>
       </x:c>
       <x:c r="F8" s="14" t="str">
-        <x:v>死夜悪</x:v>
+        <x:v>淫魔</x:v>
       </x:c>
       <x:c r="G8" s="14" t="str">
-        <x:v>label_000003</x:v>
+        <x:v>label_000006</x:v>
       </x:c>
       <x:c r="H8" s="14" t="str"/>
       <x:c r="I8" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/2754</x:v>
+        <x:v>https://attackers.net/works/list/label/2737</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -6279,17 +7287,17 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="E9" s="14" t="str">
-        <x:v>2751</x:v>
+        <x:v>2739</x:v>
       </x:c>
       <x:c r="F9" s="14" t="str">
-        <x:v>龍縛</x:v>
+        <x:v>Attackers</x:v>
       </x:c>
       <x:c r="G9" s="14" t="str">
-        <x:v>label_000004</x:v>
+        <x:v>label_000007</x:v>
       </x:c>
       <x:c r="H9" s="14" t="str"/>
       <x:c r="I9" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/2751</x:v>
+        <x:v>https://attackers.net/works/list/label/2739</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -6306,17 +7314,17 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="E10" s="14" t="str">
-        <x:v>9455</x:v>
+        <x:v>2749</x:v>
       </x:c>
       <x:c r="F10" s="14" t="str">
-        <x:v>大人のドラマ</x:v>
+        <x:v>蛇縛</x:v>
       </x:c>
       <x:c r="G10" s="14" t="str">
-        <x:v>label_000005</x:v>
+        <x:v>label_000008</x:v>
       </x:c>
       <x:c r="H10" s="14" t="str"/>
       <x:c r="I10" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/9455</x:v>
+        <x:v>https://attackers.net/works/list/label/2749</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -6333,17 +7341,17 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="E11" s="14" t="str">
-        <x:v>2737</x:v>
+        <x:v>2751</x:v>
       </x:c>
       <x:c r="F11" s="14" t="str">
-        <x:v>淫魔</x:v>
+        <x:v>龍縛</x:v>
       </x:c>
       <x:c r="G11" s="14" t="str">
-        <x:v>label_000006</x:v>
+        <x:v>label_000004</x:v>
       </x:c>
       <x:c r="H11" s="14" t="str"/>
       <x:c r="I11" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/2737</x:v>
+        <x:v>https://attackers.net/works/list/label/2751</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -6360,17 +7368,17 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="E12" s="14" t="str">
-        <x:v>2739</x:v>
+        <x:v>2754</x:v>
       </x:c>
       <x:c r="F12" s="14" t="str">
-        <x:v>Attackers</x:v>
+        <x:v>死夜悪</x:v>
       </x:c>
       <x:c r="G12" s="14" t="str">
-        <x:v>label_000007</x:v>
+        <x:v>label_000003</x:v>
       </x:c>
       <x:c r="H12" s="14" t="str"/>
       <x:c r="I12" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/2739</x:v>
+        <x:v>https://attackers.net/works/list/label/2754</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -6387,17 +7395,17 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="E13" s="14" t="str">
-        <x:v>2749</x:v>
+        <x:v>2756</x:v>
       </x:c>
       <x:c r="F13" s="14" t="str">
-        <x:v>蛇縛</x:v>
+        <x:v>SUPER SPECIAL</x:v>
       </x:c>
       <x:c r="G13" s="14" t="str">
-        <x:v>label_000008</x:v>
+        <x:v>label_000010</x:v>
       </x:c>
       <x:c r="H13" s="14" t="str"/>
       <x:c r="I13" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/2749</x:v>
+        <x:v>https://attackers.net/works/list/label/2756</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -6414,17 +7422,17 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="E14" s="14" t="str">
-        <x:v>2735</x:v>
+        <x:v>5245</x:v>
       </x:c>
       <x:c r="F14" s="14" t="str">
-        <x:v>アタッカーズ・アンソロジー</x:v>
+        <x:v>アタックゾーン</x:v>
       </x:c>
       <x:c r="G14" s="14" t="str">
-        <x:v>label_000009</x:v>
+        <x:v>label_000013</x:v>
       </x:c>
       <x:c r="H14" s="14" t="str"/>
       <x:c r="I14" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/2735</x:v>
+        <x:v>https://attackers.net/works/list/label/5245</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -6441,17 +7449,17 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="E15" s="14" t="str">
-        <x:v>2756</x:v>
+        <x:v>81348</x:v>
       </x:c>
       <x:c r="F15" s="14" t="str">
-        <x:v>SUPER SPECIAL</x:v>
+        <x:v>アタッカーズVR</x:v>
       </x:c>
       <x:c r="G15" s="14" t="str">
-        <x:v>label_000010</x:v>
+        <x:v>label_000012</x:v>
       </x:c>
       <x:c r="H15" s="14" t="str"/>
       <x:c r="I15" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/2756</x:v>
+        <x:v>https://attackers.net/works/list/label/81348</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -6468,17 +7476,17 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="E16" s="14" t="str">
-        <x:v>12605</x:v>
+        <x:v>85265</x:v>
       </x:c>
       <x:c r="F16" s="14" t="str">
-        <x:v>誘女</x:v>
+        <x:v>春のパンツまつり</x:v>
       </x:c>
       <x:c r="G16" s="14" t="str">
-        <x:v>label_000011</x:v>
+        <x:v>label_000014</x:v>
       </x:c>
       <x:c r="H16" s="14" t="str"/>
       <x:c r="I16" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/12605</x:v>
+        <x:v>https://attackers.net/works/list/label/85265</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -6495,17 +7503,17 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="E17" s="14" t="str">
-        <x:v>81348</x:v>
+        <x:v>9455</x:v>
       </x:c>
       <x:c r="F17" s="14" t="str">
-        <x:v>アタッカーズVR</x:v>
+        <x:v>大人のドラマ</x:v>
       </x:c>
       <x:c r="G17" s="14" t="str">
-        <x:v>label_000012</x:v>
+        <x:v>label_000005</x:v>
       </x:c>
       <x:c r="H17" s="14" t="str"/>
       <x:c r="I17" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/81348</x:v>
+        <x:v>https://attackers.net/works/list/label/9455</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -6522,17 +7530,17 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="E18" s="14" t="str">
-        <x:v>5245</x:v>
+        <x:v>9483</x:v>
       </x:c>
       <x:c r="F18" s="14" t="str">
-        <x:v>アタックゾーン</x:v>
+        <x:v>AVOPEN</x:v>
       </x:c>
       <x:c r="G18" s="14" t="str">
-        <x:v>label_000013</x:v>
+        <x:v>label_000015</x:v>
       </x:c>
       <x:c r="H18" s="14" t="str"/>
       <x:c r="I18" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/5245</x:v>
+        <x:v>https://attackers.net/works/list/label/9483</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -6543,23 +7551,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C19" s="14" t="str">
-        <x:v>attackers.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="D19" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E19" s="14" t="str">
-        <x:v>85265</x:v>
+        <x:v>2253</x:v>
       </x:c>
       <x:c r="F19" s="14" t="str">
-        <x:v>春のパンツまつり</x:v>
+        <x:v>アナル奴隷白書</x:v>
       </x:c>
       <x:c r="G19" s="14" t="str">
-        <x:v>label_000014</x:v>
+        <x:v>series_000018</x:v>
       </x:c>
       <x:c r="H19" s="14" t="str"/>
       <x:c r="I19" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/85265</x:v>
+        <x:v>https://attackers.net/works/list/series/2253</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -6570,23 +7578,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
-        <x:v>attackers.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="D20" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E20" s="14" t="str">
-        <x:v>9483</x:v>
+        <x:v>2254</x:v>
       </x:c>
       <x:c r="F20" s="14" t="str">
-        <x:v>AVOPEN</x:v>
+        <x:v>夫の目の前で犯されて</x:v>
       </x:c>
       <x:c r="G20" s="14" t="str">
-        <x:v>label_000015</x:v>
+        <x:v>series_000019</x:v>
       </x:c>
       <x:c r="H20" s="14" t="str"/>
       <x:c r="I20" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/9483</x:v>
+        <x:v>https://attackers.net/works/list/series/2254</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -6597,23 +7605,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
-        <x:v>attackers.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="D21" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E21" s="14" t="str">
-        <x:v>10077</x:v>
+        <x:v>2255</x:v>
       </x:c>
       <x:c r="F21" s="14" t="str">
-        <x:v>AVグランプリ</x:v>
+        <x:v>地獄の女神</x:v>
       </x:c>
       <x:c r="G21" s="14" t="str">
-        <x:v>label_000016</x:v>
+        <x:v>series_000020</x:v>
       </x:c>
       <x:c r="H21" s="14" t="str"/>
       <x:c r="I21" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/10077</x:v>
+        <x:v>https://attackers.net/works/list/series/2255</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -6624,23 +7632,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
-        <x:v>attackers.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="D22" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E22" s="14" t="str">
-        <x:v>10142</x:v>
+        <x:v>2256</x:v>
       </x:c>
       <x:c r="F22" s="14" t="str">
-        <x:v>おっぱい祭り</x:v>
+        <x:v>奴隷島</x:v>
       </x:c>
       <x:c r="G22" s="14" t="str">
-        <x:v>label_000017</x:v>
+        <x:v>series_000011</x:v>
       </x:c>
       <x:c r="H22" s="14" t="str"/>
       <x:c r="I22" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/10142</x:v>
+        <x:v>https://attackers.net/works/list/series/2256</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -6651,23 +7659,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C23" s="14" t="str">
-        <x:v>attackers.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="D23" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E23" s="14" t="str">
-        <x:v>10144</x:v>
+        <x:v>2257</x:v>
       </x:c>
       <x:c r="F23" s="14" t="str">
-        <x:v>秋のシコシコ強化月間</x:v>
+        <x:v>絶対調教</x:v>
       </x:c>
       <x:c r="G23" s="14" t="str">
-        <x:v>label_000018</x:v>
+        <x:v>series_000021</x:v>
       </x:c>
       <x:c r="H23" s="14" t="str"/>
       <x:c r="I23" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/10144</x:v>
+        <x:v>https://attackers.net/works/list/series/2257</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -6678,23 +7686,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C24" s="14" t="str">
-        <x:v>attackers.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="D24" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E24" s="14" t="str">
-        <x:v>10151</x:v>
+        <x:v>2258</x:v>
       </x:c>
       <x:c r="F24" s="14" t="str">
-        <x:v>背徳ビチョビチョ！NTR大放出</x:v>
+        <x:v>淫乱奴隷の強制快楽</x:v>
       </x:c>
       <x:c r="G24" s="14" t="str">
-        <x:v>label_000019</x:v>
+        <x:v>series_000022</x:v>
       </x:c>
       <x:c r="H24" s="14" t="str"/>
       <x:c r="I24" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/10151</x:v>
+        <x:v>https://attackers.net/works/list/series/2258</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -6705,23 +7713,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C25" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="D25" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E25" s="14" t="str">
-        <x:v>3669</x:v>
+        <x:v>2259</x:v>
       </x:c>
       <x:c r="F25" s="14" t="str">
-        <x:v>Madonna</x:v>
+        <x:v>貞操帯の女</x:v>
       </x:c>
       <x:c r="G25" s="14" t="str">
-        <x:v>label_000020</x:v>
+        <x:v>series_000023</x:v>
       </x:c>
       <x:c r="H25" s="14" t="str"/>
       <x:c r="I25" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/3669</x:v>
+        <x:v>https://attackers.net/works/list/series/2259</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -6732,23 +7740,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C26" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="D26" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E26" s="14" t="str">
-        <x:v>12490</x:v>
+        <x:v>2260</x:v>
       </x:c>
       <x:c r="F26" s="14" t="str">
-        <x:v>MONROE</x:v>
+        <x:v>楠木女学院</x:v>
       </x:c>
       <x:c r="G26" s="14" t="str">
-        <x:v>label_000021</x:v>
+        <x:v>series_000024</x:v>
       </x:c>
       <x:c r="H26" s="14" t="str"/>
       <x:c r="I26" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/12490</x:v>
+        <x:v>https://attackers.net/works/list/series/2260</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -6759,23 +7767,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C27" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="D27" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E27" s="14" t="str">
-        <x:v>9387</x:v>
+        <x:v>2261</x:v>
       </x:c>
       <x:c r="F27" s="14" t="str">
-        <x:v>Obasan</x:v>
+        <x:v>鬼畜輪姦</x:v>
       </x:c>
       <x:c r="G27" s="14" t="str">
-        <x:v>label_000022</x:v>
+        <x:v>series_000025</x:v>
       </x:c>
       <x:c r="H27" s="14" t="str"/>
       <x:c r="I27" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/9387</x:v>
+        <x:v>https://attackers.net/works/list/series/2261</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -6786,23 +7794,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C28" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="D28" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E28" s="14" t="str">
-        <x:v>9789</x:v>
+        <x:v>2263</x:v>
       </x:c>
       <x:c r="F28" s="14" t="str">
-        <x:v>MadonnaVR</x:v>
+        <x:v>女豹</x:v>
       </x:c>
       <x:c r="G28" s="14" t="str">
-        <x:v>label_000023</x:v>
+        <x:v>series_000026</x:v>
       </x:c>
       <x:c r="H28" s="14" t="str"/>
       <x:c r="I28" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/9789</x:v>
+        <x:v>https://attackers.net/works/list/series/2263</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -6813,23 +7821,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C29" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="D29" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E29" s="14" t="str">
-        <x:v>7354</x:v>
+        <x:v>2269</x:v>
       </x:c>
       <x:c r="F29" s="14" t="str">
-        <x:v>Fitch</x:v>
+        <x:v>あなたに愛されたくて。</x:v>
       </x:c>
       <x:c r="G29" s="14" t="str">
-        <x:v>label_000024</x:v>
+        <x:v>series_000008</x:v>
       </x:c>
       <x:c r="H29" s="14" t="str"/>
       <x:c r="I29" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/7354</x:v>
+        <x:v>https://attackers.net/works/list/series/2269</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -6840,23 +7848,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C30" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="D30" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E30" s="14" t="str">
-        <x:v>9419</x:v>
+        <x:v>2270</x:v>
       </x:c>
       <x:c r="F30" s="14" t="str">
-        <x:v>熟れコミ</x:v>
+        <x:v>あなた、許して…。</x:v>
       </x:c>
       <x:c r="G30" s="14" t="str">
-        <x:v>label_000025</x:v>
+        <x:v>series_000009</x:v>
       </x:c>
       <x:c r="H30" s="14" t="str"/>
       <x:c r="I30" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/9419</x:v>
+        <x:v>https://attackers.net/works/list/series/2270</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -6867,23 +7875,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C31" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="D31" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E31" s="14" t="str">
-        <x:v>12603</x:v>
+        <x:v>2274</x:v>
       </x:c>
       <x:c r="F31" s="14" t="str">
-        <x:v>ACHIJO(アチージョ)</x:v>
+        <x:v>犯される度に美しく</x:v>
       </x:c>
       <x:c r="G31" s="14" t="str">
-        <x:v>label_000026</x:v>
+        <x:v>series_000012</x:v>
       </x:c>
       <x:c r="H31" s="14" t="str"/>
       <x:c r="I31" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/12603</x:v>
+        <x:v>https://attackers.net/works/list/series/2274</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -6894,23 +7902,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C32" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="D32" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E32" s="14" t="str">
-        <x:v>12502</x:v>
+        <x:v>2293</x:v>
       </x:c>
       <x:c r="F32" s="14" t="str">
-        <x:v>MADOOOON!!!!</x:v>
+        <x:v>脱獄者</x:v>
       </x:c>
       <x:c r="G32" s="14" t="str">
-        <x:v>label_000027</x:v>
+        <x:v>series_000010</x:v>
       </x:c>
       <x:c r="H32" s="14" t="str"/>
       <x:c r="I32" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/12502</x:v>
+        <x:v>https://attackers.net/works/list/series/2293</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -6921,23 +7929,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C33" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="D33" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E33" s="14" t="str">
-        <x:v>10130</x:v>
+        <x:v>2325</x:v>
       </x:c>
       <x:c r="F33" s="14" t="str">
-        <x:v>Re:Madonna/AIリマスター</x:v>
+        <x:v>団鬼六</x:v>
       </x:c>
       <x:c r="G33" s="14" t="str">
-        <x:v>label_000028</x:v>
+        <x:v>series_000013</x:v>
       </x:c>
       <x:c r="H33" s="14" t="str"/>
       <x:c r="I33" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10130</x:v>
+        <x:v>https://attackers.net/works/list/series/2325</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -6948,23 +7956,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C34" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="D34" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E34" s="14" t="str">
-        <x:v>7993</x:v>
+        <x:v>2402</x:v>
       </x:c>
       <x:c r="F34" s="14" t="str">
-        <x:v>Fitch　BEST</x:v>
+        <x:v>侵入者</x:v>
       </x:c>
       <x:c r="G34" s="14" t="str">
-        <x:v>label_000029</x:v>
+        <x:v>series_000007</x:v>
       </x:c>
       <x:c r="H34" s="14" t="str"/>
       <x:c r="I34" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/7993</x:v>
+        <x:v>https://attackers.net/works/list/series/2402</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -6975,23 +7983,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C35" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="D35" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E35" s="14" t="str">
-        <x:v>10159</x:v>
+        <x:v>5317</x:v>
       </x:c>
       <x:c r="F35" s="14" t="str">
-        <x:v>性録ch</x:v>
+        <x:v>調教志願</x:v>
       </x:c>
       <x:c r="G35" s="14" t="str">
-        <x:v>label_000030</x:v>
+        <x:v>series_000014</x:v>
       </x:c>
       <x:c r="H35" s="14" t="str"/>
       <x:c r="I35" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10159</x:v>
+        <x:v>https://attackers.net/works/list/series/5317</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -7002,23 +8010,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C36" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="D36" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E36" s="14" t="str">
-        <x:v>10119</x:v>
+        <x:v>10077</x:v>
       </x:c>
       <x:c r="F36" s="14" t="str">
-        <x:v>※スマホ推奨タテ動画※マドーンショート</x:v>
+        <x:v>AVグランプリ</x:v>
       </x:c>
       <x:c r="G36" s="14" t="str">
-        <x:v>label_000031</x:v>
+        <x:v>label_000076</x:v>
       </x:c>
       <x:c r="H36" s="14" t="str"/>
       <x:c r="I36" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10119</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10077</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -7029,23 +8037,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C37" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="D37" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E37" s="14" t="str">
-        <x:v>85265</x:v>
+        <x:v>10103</x:v>
       </x:c>
       <x:c r="F37" s="14" t="str">
-        <x:v>春のパンツまつり</x:v>
+        <x:v>SELECTED</x:v>
       </x:c>
       <x:c r="G37" s="14" t="str">
-        <x:v>label_000032</x:v>
+        <x:v>label_000073</x:v>
       </x:c>
       <x:c r="H37" s="14" t="str"/>
       <x:c r="I37" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/85265</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10103</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -7056,23 +8064,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C38" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="D38" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E38" s="14" t="str">
-        <x:v>9483</x:v>
+        <x:v>10142</x:v>
       </x:c>
       <x:c r="F38" s="14" t="str">
-        <x:v>AVOPEN</x:v>
+        <x:v>おっぱい祭り</x:v>
       </x:c>
       <x:c r="G38" s="14" t="str">
-        <x:v>label_000033</x:v>
+        <x:v>label_000077</x:v>
       </x:c>
       <x:c r="H38" s="14" t="str"/>
       <x:c r="I38" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/9483</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10142</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -7083,23 +8091,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C39" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="D39" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E39" s="14" t="str">
-        <x:v>10142</x:v>
+        <x:v>10144</x:v>
       </x:c>
       <x:c r="F39" s="14" t="str">
-        <x:v>おっぱい祭り</x:v>
+        <x:v>秋のシコシコ強化月間</x:v>
       </x:c>
       <x:c r="G39" s="14" t="str">
-        <x:v>label_000034</x:v>
+        <x:v>label_000080</x:v>
       </x:c>
       <x:c r="H39" s="14" t="str"/>
       <x:c r="I39" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10142</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10144</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -7110,23 +8118,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C40" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="D40" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E40" s="14" t="str">
-        <x:v>10077</x:v>
+        <x:v>10151</x:v>
       </x:c>
       <x:c r="F40" s="14" t="str">
-        <x:v>AVグランプリ</x:v>
+        <x:v>背徳ビチョビチョ！NTR大放出</x:v>
       </x:c>
       <x:c r="G40" s="14" t="str">
-        <x:v>label_000035</x:v>
+        <x:v>label_000078</x:v>
       </x:c>
       <x:c r="H40" s="14" t="str"/>
       <x:c r="I40" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10077</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10151</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -7137,23 +8145,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C41" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="D41" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E41" s="14" t="str">
-        <x:v>10151</x:v>
+        <x:v>12442</x:v>
       </x:c>
       <x:c r="F41" s="14" t="str">
-        <x:v>背徳ビチョビチョ！NTR大放出</x:v>
+        <x:v>アイポケ逸材発掘プロジェクト</x:v>
       </x:c>
       <x:c r="G41" s="14" t="str">
-        <x:v>label_000036</x:v>
+        <x:v>label_000069</x:v>
       </x:c>
       <x:c r="H41" s="14" t="str"/>
       <x:c r="I41" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10151</x:v>
+        <x:v>https://ideapocket.com/works/list/label/12442</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -7164,23 +8172,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C42" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="D42" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E42" s="14" t="str">
-        <x:v>3125</x:v>
+        <x:v>12835</x:v>
       </x:c>
       <x:c r="F42" s="14" t="str">
-        <x:v>bizarre　amaturs</x:v>
+        <x:v>ゆるポケ</x:v>
       </x:c>
       <x:c r="G42" s="14" t="str">
-        <x:v>label_000037</x:v>
+        <x:v>label_000071</x:v>
       </x:c>
       <x:c r="H42" s="14" t="str"/>
       <x:c r="I42" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/3125</x:v>
+        <x:v>https://ideapocket.com/works/list/label/12835</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -7191,23 +8199,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C43" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="D43" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E43" s="14" t="str">
-        <x:v>5047</x:v>
+        <x:v>2758</x:v>
       </x:c>
       <x:c r="F43" s="14" t="str">
-        <x:v>MOODYZ BEST</x:v>
+        <x:v>Angel</x:v>
       </x:c>
       <x:c r="G43" s="14" t="str">
-        <x:v>label_000038</x:v>
+        <x:v>label_000072</x:v>
       </x:c>
       <x:c r="H43" s="14" t="str"/>
       <x:c r="I43" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5047</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2758</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -7218,23 +8226,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C44" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="D44" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E44" s="14" t="str">
-        <x:v>5046</x:v>
+        <x:v>2760</x:v>
       </x:c>
       <x:c r="F44" s="14" t="str">
-        <x:v>MOODYZ ACID</x:v>
+        <x:v>Angel PREMIUM</x:v>
       </x:c>
       <x:c r="G44" s="14" t="str">
-        <x:v>label_000039</x:v>
+        <x:v>label_000079</x:v>
       </x:c>
       <x:c r="H44" s="14" t="str"/>
       <x:c r="I44" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5046</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2760</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -7245,23 +8253,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C45" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="D45" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E45" s="14" t="str">
-        <x:v>6879</x:v>
+        <x:v>2767</x:v>
       </x:c>
       <x:c r="F45" s="14" t="str">
-        <x:v>MOODYZ GATI</x:v>
+        <x:v>HIGH-SCHOOL Pink</x:v>
       </x:c>
       <x:c r="G45" s="14" t="str">
-        <x:v>label_000040</x:v>
+        <x:v>label_000070</x:v>
       </x:c>
       <x:c r="H45" s="14" t="str"/>
       <x:c r="I45" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/6879</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2767</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -7272,23 +8280,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C46" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="D46" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E46" s="14" t="str">
-        <x:v>9782</x:v>
+        <x:v>2769</x:v>
       </x:c>
       <x:c r="F46" s="14" t="str">
-        <x:v>MOODYZ VR</x:v>
+        <x:v>アイデアポケットBEST</x:v>
       </x:c>
       <x:c r="G46" s="14" t="str">
-        <x:v>label_000041</x:v>
+        <x:v>label_000066</x:v>
       </x:c>
       <x:c r="H46" s="14" t="str"/>
       <x:c r="I46" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9782</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2769</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -7299,23 +8307,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C47" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="D47" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E47" s="14" t="str">
-        <x:v>9732</x:v>
+        <x:v>2771</x:v>
       </x:c>
       <x:c r="F47" s="14" t="str">
-        <x:v>MOODYZ Fresh</x:v>
+        <x:v>ティッシュ</x:v>
       </x:c>
       <x:c r="G47" s="14" t="str">
-        <x:v>label_000042</x:v>
+        <x:v>label_000065</x:v>
       </x:c>
       <x:c r="H47" s="14" t="str"/>
       <x:c r="I47" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9732</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2771</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -7326,23 +8334,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C48" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="D48" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E48" s="14" t="str">
-        <x:v>9308</x:v>
+        <x:v>2776</x:v>
       </x:c>
       <x:c r="F48" s="14" t="str">
-        <x:v>まんきつ</x:v>
+        <x:v>Supreme</x:v>
       </x:c>
       <x:c r="G48" s="14" t="str">
-        <x:v>label_000043</x:v>
+        <x:v>label_000068</x:v>
       </x:c>
       <x:c r="H48" s="14" t="str"/>
       <x:c r="I48" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9308</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2776</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -7353,23 +8361,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C49" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="D49" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E49" s="14" t="str">
-        <x:v>5090</x:v>
+        <x:v>85265</x:v>
       </x:c>
       <x:c r="F49" s="14" t="str">
-        <x:v>MOODYZ REAL</x:v>
+        <x:v>春のパンツまつり</x:v>
       </x:c>
       <x:c r="G49" s="14" t="str">
-        <x:v>label_000044</x:v>
+        <x:v>label_000075</x:v>
       </x:c>
       <x:c r="H49" s="14" t="str"/>
       <x:c r="I49" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5090</x:v>
+        <x:v>https://ideapocket.com/works/list/label/85265</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -7380,23 +8388,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C50" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="D50" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E50" s="14" t="str">
-        <x:v>5049</x:v>
+        <x:v>9483</x:v>
       </x:c>
       <x:c r="F50" s="14" t="str">
-        <x:v>MOODYZ ISM</x:v>
+        <x:v>AVOPEN</x:v>
       </x:c>
       <x:c r="G50" s="14" t="str">
-        <x:v>label_000045</x:v>
+        <x:v>label_000074</x:v>
       </x:c>
       <x:c r="H50" s="14" t="str"/>
       <x:c r="I50" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5049</x:v>
+        <x:v>https://ideapocket.com/works/list/label/9483</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -7407,23 +8415,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C51" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="D51" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E51" s="14" t="str">
-        <x:v>10107</x:v>
+        <x:v>9790</x:v>
       </x:c>
       <x:c r="F51" s="14" t="str">
-        <x:v>きれいなお姉さんは好きですか</x:v>
+        <x:v>IP-VR</x:v>
       </x:c>
       <x:c r="G51" s="14" t="str">
-        <x:v>label_000046</x:v>
+        <x:v>label_000067</x:v>
       </x:c>
       <x:c r="H51" s="14" t="str"/>
       <x:c r="I51" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10107</x:v>
+        <x:v>https://ideapocket.com/works/list/label/9790</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -7434,23 +8442,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C52" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>ideapocket.series</x:v>
       </x:c>
       <x:c r="D52" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E52" s="14" t="str">
-        <x:v>10131</x:v>
+        <x:v>1011</x:v>
       </x:c>
       <x:c r="F52" s="14" t="str">
-        <x:v>MOODYZ ニュージーニアス</x:v>
+        <x:v>うちの妻を犯して下さい</x:v>
       </x:c>
       <x:c r="G52" s="14" t="str">
-        <x:v>label_000047</x:v>
+        <x:v>series_000004</x:v>
       </x:c>
       <x:c r="H52" s="14" t="str"/>
       <x:c r="I52" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10131</x:v>
+        <x:v>https://ideapocket.com/works/list/series/1011</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -7461,23 +8469,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C53" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>ideapocket.series</x:v>
       </x:c>
       <x:c r="D53" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E53" s="14" t="str">
-        <x:v>9458</x:v>
+        <x:v>863</x:v>
       </x:c>
       <x:c r="F53" s="14" t="str">
-        <x:v>MUTTURI</x:v>
+        <x:v>死ぬほど大嫌いな上司とまさかの相部屋に</x:v>
       </x:c>
       <x:c r="G53" s="14" t="str">
-        <x:v>label_000048</x:v>
+        <x:v>series_000003</x:v>
       </x:c>
       <x:c r="H53" s="14" t="str"/>
       <x:c r="I53" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9458</x:v>
+        <x:v>https://ideapocket.com/works/list/series/863</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -7488,23 +8496,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C54" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="D54" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E54" s="14" t="str">
-        <x:v>5409</x:v>
+        <x:v>10077</x:v>
       </x:c>
       <x:c r="F54" s="14" t="str">
-        <x:v>MOODYZ VALUE</x:v>
+        <x:v>AVグランプリ</x:v>
       </x:c>
       <x:c r="G54" s="14" t="str">
-        <x:v>label_000049</x:v>
+        <x:v>label_000035</x:v>
       </x:c>
       <x:c r="H54" s="14" t="str"/>
       <x:c r="I54" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5409</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10077</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -7515,23 +8523,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C55" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="D55" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E55" s="14" t="str">
-        <x:v>10174</x:v>
+        <x:v>10119</x:v>
       </x:c>
       <x:c r="F55" s="14" t="str">
-        <x:v>ハメドリ</x:v>
+        <x:v>※スマホ推奨タテ動画※マドーンショート</x:v>
       </x:c>
       <x:c r="G55" s="14" t="str">
-        <x:v>label_000050</x:v>
+        <x:v>label_000031</x:v>
       </x:c>
       <x:c r="H55" s="14" t="str"/>
       <x:c r="I55" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10174</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10119</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -7542,23 +8550,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C56" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="D56" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E56" s="14" t="str">
-        <x:v>8916</x:v>
+        <x:v>10130</x:v>
       </x:c>
       <x:c r="F56" s="14" t="str">
-        <x:v>MOODYZ ASS</x:v>
+        <x:v>Re:Madonna/AIリマスター</x:v>
       </x:c>
       <x:c r="G56" s="14" t="str">
-        <x:v>label_000051</x:v>
+        <x:v>label_000028</x:v>
       </x:c>
       <x:c r="H56" s="14" t="str"/>
       <x:c r="I56" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/8916</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10130</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -7569,23 +8577,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C57" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="D57" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E57" s="14" t="str">
-        <x:v>9397</x:v>
+        <x:v>10142</x:v>
       </x:c>
       <x:c r="F57" s="14" t="str">
-        <x:v>Q-EYE</x:v>
+        <x:v>おっぱい祭り</x:v>
       </x:c>
       <x:c r="G57" s="14" t="str">
-        <x:v>label_000052</x:v>
+        <x:v>label_000034</x:v>
       </x:c>
       <x:c r="H57" s="14" t="str"/>
       <x:c r="I57" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9397</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10142</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -7596,23 +8604,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C58" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="D58" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E58" s="14" t="str">
-        <x:v>10106</x:v>
+        <x:v>10151</x:v>
       </x:c>
       <x:c r="F58" s="14" t="str">
-        <x:v>エロい！</x:v>
+        <x:v>背徳ビチョビチョ！NTR大放出</x:v>
       </x:c>
       <x:c r="G58" s="14" t="str">
-        <x:v>label_000053</x:v>
+        <x:v>label_000036</x:v>
       </x:c>
       <x:c r="H58" s="14" t="str"/>
       <x:c r="I58" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10106</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10151</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -7623,23 +8631,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C59" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="D59" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E59" s="14" t="str">
-        <x:v>9288</x:v>
+        <x:v>10159</x:v>
       </x:c>
       <x:c r="F59" s="14" t="str">
-        <x:v>寝取られ本舗</x:v>
+        <x:v>性録ch</x:v>
       </x:c>
       <x:c r="G59" s="14" t="str">
-        <x:v>label_000054</x:v>
+        <x:v>label_000030</x:v>
       </x:c>
       <x:c r="H59" s="14" t="str"/>
       <x:c r="I59" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9288</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10159</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -7650,23 +8658,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C60" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="D60" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E60" s="14" t="str">
-        <x:v>8917</x:v>
+        <x:v>12490</x:v>
       </x:c>
       <x:c r="F60" s="14" t="str">
-        <x:v>MOODYZ ES</x:v>
+        <x:v>MONROE</x:v>
       </x:c>
       <x:c r="G60" s="14" t="str">
-        <x:v>label_000055</x:v>
+        <x:v>label_000021</x:v>
       </x:c>
       <x:c r="H60" s="14" t="str"/>
       <x:c r="I60" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/8917</x:v>
+        <x:v>https://madonna-av.com/works/list/label/12490</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -7677,23 +8685,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C61" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="D61" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E61" s="14" t="str">
-        <x:v>85265</x:v>
+        <x:v>12502</x:v>
       </x:c>
       <x:c r="F61" s="14" t="str">
-        <x:v>春のパンツまつり</x:v>
+        <x:v>MADOOOON!!!!</x:v>
       </x:c>
       <x:c r="G61" s="14" t="str">
-        <x:v>label_000056</x:v>
+        <x:v>label_000027</x:v>
       </x:c>
       <x:c r="H61" s="14" t="str"/>
       <x:c r="I61" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/85265</x:v>
+        <x:v>https://madonna-av.com/works/list/label/12502</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -7704,23 +8712,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C62" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="D62" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E62" s="14" t="str">
-        <x:v>11471</x:v>
+        <x:v>12603</x:v>
       </x:c>
       <x:c r="F62" s="14" t="str">
-        <x:v>BD-MOODYZ DIVA</x:v>
+        <x:v>ACHIJO(アチージョ)</x:v>
       </x:c>
       <x:c r="G62" s="14" t="str">
-        <x:v>label_000057</x:v>
+        <x:v>label_000026</x:v>
       </x:c>
       <x:c r="H62" s="14" t="str"/>
       <x:c r="I62" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/11471</x:v>
+        <x:v>https://madonna-av.com/works/list/label/12603</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -7731,23 +8739,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C63" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="D63" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E63" s="14" t="str">
-        <x:v>10157</x:v>
+        <x:v>3125</x:v>
       </x:c>
       <x:c r="F63" s="14" t="str">
-        <x:v>MOODYZ HARD</x:v>
+        <x:v>bizarre　amaturs</x:v>
       </x:c>
       <x:c r="G63" s="14" t="str">
-        <x:v>label_000058</x:v>
+        <x:v>label_000037</x:v>
       </x:c>
       <x:c r="H63" s="14" t="str"/>
       <x:c r="I63" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10157</x:v>
+        <x:v>https://madonna-av.com/works/list/label/3125</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -7758,23 +8766,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C64" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="D64" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E64" s="14" t="str">
-        <x:v>9483</x:v>
+        <x:v>3669</x:v>
       </x:c>
       <x:c r="F64" s="14" t="str">
-        <x:v>AVOPEN</x:v>
+        <x:v>Madonna</x:v>
       </x:c>
       <x:c r="G64" s="14" t="str">
-        <x:v>label_000059</x:v>
+        <x:v>label_000020</x:v>
       </x:c>
       <x:c r="H64" s="14" t="str"/>
       <x:c r="I64" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9483</x:v>
+        <x:v>https://madonna-av.com/works/list/label/3669</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -7785,23 +8793,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C65" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="D65" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E65" s="14" t="str">
-        <x:v>10142</x:v>
+        <x:v>7354</x:v>
       </x:c>
       <x:c r="F65" s="14" t="str">
-        <x:v>おっぱい祭り</x:v>
+        <x:v>Fitch</x:v>
       </x:c>
       <x:c r="G65" s="14" t="str">
-        <x:v>label_000060</x:v>
+        <x:v>label_000024</x:v>
       </x:c>
       <x:c r="H65" s="14" t="str"/>
       <x:c r="I65" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10142</x:v>
+        <x:v>https://madonna-av.com/works/list/label/7354</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -7812,23 +8820,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C66" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="D66" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E66" s="14" t="str">
-        <x:v>10144</x:v>
+        <x:v>7993</x:v>
       </x:c>
       <x:c r="F66" s="14" t="str">
-        <x:v>秋のシコシコ強化月間</x:v>
+        <x:v>Fitch　BEST</x:v>
       </x:c>
       <x:c r="G66" s="14" t="str">
-        <x:v>label_000061</x:v>
+        <x:v>label_000029</x:v>
       </x:c>
       <x:c r="H66" s="14" t="str"/>
       <x:c r="I66" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10144</x:v>
+        <x:v>https://madonna-av.com/works/list/label/7993</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -7839,23 +8847,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C67" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="D67" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E67" s="14" t="str">
-        <x:v>10151</x:v>
+        <x:v>85265</x:v>
       </x:c>
       <x:c r="F67" s="14" t="str">
-        <x:v>背徳ビチョビチョ！NTR大放出</x:v>
+        <x:v>春のパンツまつり</x:v>
       </x:c>
       <x:c r="G67" s="14" t="str">
-        <x:v>label_000062</x:v>
+        <x:v>label_000032</x:v>
       </x:c>
       <x:c r="H67" s="14" t="str"/>
       <x:c r="I67" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10151</x:v>
+        <x:v>https://madonna-av.com/works/list/label/85265</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -7866,23 +8874,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C68" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="D68" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E68" s="14" t="str">
-        <x:v>10077</x:v>
+        <x:v>9387</x:v>
       </x:c>
       <x:c r="F68" s="14" t="str">
-        <x:v>AVグランプリ</x:v>
+        <x:v>Obasan</x:v>
       </x:c>
       <x:c r="G68" s="14" t="str">
-        <x:v>label_000063</x:v>
+        <x:v>label_000022</x:v>
       </x:c>
       <x:c r="H68" s="14" t="str"/>
       <x:c r="I68" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10077</x:v>
+        <x:v>https://madonna-av.com/works/list/label/9387</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -7893,23 +8901,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C69" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="D69" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E69" s="14" t="str">
-        <x:v>10172</x:v>
+        <x:v>9419</x:v>
       </x:c>
       <x:c r="F69" s="14" t="str">
-        <x:v>MOODYZショート</x:v>
+        <x:v>熟れコミ</x:v>
       </x:c>
       <x:c r="G69" s="14" t="str">
-        <x:v>label_000064</x:v>
+        <x:v>label_000025</x:v>
       </x:c>
       <x:c r="H69" s="14" t="str"/>
       <x:c r="I69" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10172</x:v>
+        <x:v>https://madonna-av.com/works/list/label/9419</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -7920,23 +8928,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C70" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="D70" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E70" s="14" t="str">
-        <x:v>2771</x:v>
+        <x:v>9483</x:v>
       </x:c>
       <x:c r="F70" s="14" t="str">
-        <x:v>ティッシュ</x:v>
+        <x:v>AVOPEN</x:v>
       </x:c>
       <x:c r="G70" s="14" t="str">
-        <x:v>label_000065</x:v>
+        <x:v>label_000033</x:v>
       </x:c>
       <x:c r="H70" s="14" t="str"/>
       <x:c r="I70" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2771</x:v>
+        <x:v>https://madonna-av.com/works/list/label/9483</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -7947,23 +8955,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C71" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="D71" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E71" s="14" t="str">
-        <x:v>2769</x:v>
+        <x:v>9789</x:v>
       </x:c>
       <x:c r="F71" s="14" t="str">
-        <x:v>アイデアポケットBEST</x:v>
+        <x:v>MadonnaVR</x:v>
       </x:c>
       <x:c r="G71" s="14" t="str">
-        <x:v>label_000066</x:v>
+        <x:v>label_000023</x:v>
       </x:c>
       <x:c r="H71" s="14" t="str"/>
       <x:c r="I71" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2769</x:v>
+        <x:v>https://madonna-av.com/works/list/label/9789</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -7974,23 +8982,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C72" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="D72" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E72" s="14" t="str">
-        <x:v>9790</x:v>
+        <x:v>1549</x:v>
       </x:c>
       <x:c r="F72" s="14" t="str">
-        <x:v>IP-VR</x:v>
+        <x:v>となりの奥さん</x:v>
       </x:c>
       <x:c r="G72" s="14" t="str">
-        <x:v>label_000067</x:v>
+        <x:v>series_000027</x:v>
       </x:c>
       <x:c r="H72" s="14" t="str"/>
       <x:c r="I72" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/9790</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1549</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -8001,23 +9009,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C73" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="D73" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E73" s="14" t="str">
-        <x:v>2776</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="F73" s="14" t="str">
-        <x:v>Supreme</x:v>
+        <x:v>美熟女と黒人</x:v>
       </x:c>
       <x:c r="G73" s="14" t="str">
-        <x:v>label_000068</x:v>
+        <x:v>series_000028</x:v>
       </x:c>
       <x:c r="H73" s="14" t="str"/>
       <x:c r="I73" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2776</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1550</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -8028,23 +9036,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C74" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="D74" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E74" s="14" t="str">
-        <x:v>12442</x:v>
+        <x:v>1551</x:v>
       </x:c>
       <x:c r="F74" s="14" t="str">
-        <x:v>アイポケ逸材発掘プロジェクト</x:v>
+        <x:v>愛する夫の目の前で・・・</x:v>
       </x:c>
       <x:c r="G74" s="14" t="str">
-        <x:v>label_000069</x:v>
+        <x:v>series_000029</x:v>
       </x:c>
       <x:c r="H74" s="14" t="str"/>
       <x:c r="I74" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/12442</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1551</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -8055,23 +9063,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C75" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="D75" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E75" s="14" t="str">
-        <x:v>2767</x:v>
+        <x:v>1552</x:v>
       </x:c>
       <x:c r="F75" s="14" t="str">
-        <x:v>HIGH-SCHOOL Pink</x:v>
+        <x:v>特選 友達の母</x:v>
       </x:c>
       <x:c r="G75" s="14" t="str">
-        <x:v>label_000070</x:v>
+        <x:v>series_000030</x:v>
       </x:c>
       <x:c r="H75" s="14" t="str"/>
       <x:c r="I75" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2767</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1552</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -8082,23 +9090,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C76" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="D76" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E76" s="14" t="str">
-        <x:v>12835</x:v>
+        <x:v>1553</x:v>
       </x:c>
       <x:c r="F76" s="14" t="str">
-        <x:v>ゆるポケ</x:v>
+        <x:v>僕のおばさん</x:v>
       </x:c>
       <x:c r="G76" s="14" t="str">
-        <x:v>label_000071</x:v>
+        <x:v>series_000031</x:v>
       </x:c>
       <x:c r="H76" s="14" t="str"/>
       <x:c r="I76" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/12835</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1553</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -8109,23 +9117,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C77" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="D77" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E77" s="14" t="str">
-        <x:v>2758</x:v>
+        <x:v>1554</x:v>
       </x:c>
       <x:c r="F77" s="14" t="str">
-        <x:v>Angel</x:v>
+        <x:v>素人人妻ナンパ総集編4時間</x:v>
       </x:c>
       <x:c r="G77" s="14" t="str">
-        <x:v>label_000072</x:v>
+        <x:v>series_000032</x:v>
       </x:c>
       <x:c r="H77" s="14" t="str"/>
       <x:c r="I77" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2758</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1554</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -8136,23 +9144,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C78" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="D78" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E78" s="14" t="str">
-        <x:v>10103</x:v>
+        <x:v>1555</x:v>
       </x:c>
       <x:c r="F78" s="14" t="str">
-        <x:v>SELECTED</x:v>
+        <x:v>五十路熟女18人4時間</x:v>
       </x:c>
       <x:c r="G78" s="14" t="str">
-        <x:v>label_000073</x:v>
+        <x:v>series_000033</x:v>
       </x:c>
       <x:c r="H78" s="14" t="str"/>
       <x:c r="I78" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10103</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1555</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -8163,23 +9171,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C79" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="D79" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E79" s="14" t="str">
-        <x:v>9483</x:v>
+        <x:v>1556</x:v>
       </x:c>
       <x:c r="F79" s="14" t="str">
-        <x:v>AVOPEN</x:v>
+        <x:v>団地妻20人4時間</x:v>
       </x:c>
       <x:c r="G79" s="14" t="str">
-        <x:v>label_000074</x:v>
+        <x:v>series_000034</x:v>
       </x:c>
       <x:c r="H79" s="14" t="str"/>
       <x:c r="I79" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/9483</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1556</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -8190,23 +9198,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C80" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="D80" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E80" s="14" t="str">
-        <x:v>85265</x:v>
+        <x:v>1557</x:v>
       </x:c>
       <x:c r="F80" s="14" t="str">
-        <x:v>春のパンツまつり</x:v>
+        <x:v>犯された熟女たち総集編4時間</x:v>
       </x:c>
       <x:c r="G80" s="14" t="str">
-        <x:v>label_000075</x:v>
+        <x:v>series_000035</x:v>
       </x:c>
       <x:c r="H80" s="14" t="str"/>
       <x:c r="I80" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/85265</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1557</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -8217,23 +9225,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C81" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="D81" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E81" s="14" t="str">
-        <x:v>10077</x:v>
+        <x:v>1558</x:v>
       </x:c>
       <x:c r="F81" s="14" t="str">
-        <x:v>AVグランプリ</x:v>
+        <x:v>妖艶おんな愛戯</x:v>
       </x:c>
       <x:c r="G81" s="14" t="str">
-        <x:v>label_000076</x:v>
+        <x:v>series_000036</x:v>
       </x:c>
       <x:c r="H81" s="14" t="str"/>
       <x:c r="I81" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10077</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1558</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -8244,23 +9252,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C82" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="D82" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E82" s="14" t="str">
-        <x:v>10142</x:v>
+        <x:v>1749</x:v>
       </x:c>
       <x:c r="F82" s="14" t="str">
-        <x:v>おっぱい祭り</x:v>
+        <x:v>夫の上司に飾られた　人妻ボディアクセサリー</x:v>
       </x:c>
       <x:c r="G82" s="14" t="str">
-        <x:v>label_000077</x:v>
+        <x:v>series_000017</x:v>
       </x:c>
       <x:c r="H82" s="14" t="str"/>
       <x:c r="I82" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10142</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1749</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -8271,23 +9279,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C83" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="D83" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E83" s="14" t="str">
-        <x:v>10151</x:v>
+        <x:v>1846</x:v>
       </x:c>
       <x:c r="F83" s="14" t="str">
-        <x:v>背徳ビチョビチョ！NTR大放出</x:v>
+        <x:v>年下レズビアンに愛された私</x:v>
       </x:c>
       <x:c r="G83" s="14" t="str">
-        <x:v>label_000078</x:v>
+        <x:v>series_000015</x:v>
       </x:c>
       <x:c r="H83" s="14" t="str"/>
       <x:c r="I83" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10151</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1846</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -8298,23 +9306,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C84" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="D84" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="E84" s="14" t="str">
-        <x:v>2760</x:v>
+        <x:v>1891</x:v>
       </x:c>
       <x:c r="F84" s="14" t="str">
-        <x:v>Angel PREMIUM</x:v>
+        <x:v>廃業寸前</x:v>
       </x:c>
       <x:c r="G84" s="14" t="str">
-        <x:v>label_000079</x:v>
+        <x:v>series_000016</x:v>
       </x:c>
       <x:c r="H84" s="14" t="str"/>
       <x:c r="I84" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2760</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1891</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -8325,23 +9333,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C85" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="D85" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E85" s="14" t="str">
-        <x:v>10144</x:v>
+        <x:v>10077</x:v>
       </x:c>
       <x:c r="F85" s="14" t="str">
-        <x:v>秋のシコシコ強化月間</x:v>
+        <x:v>AVグランプリ</x:v>
       </x:c>
       <x:c r="G85" s="14" t="str">
-        <x:v>label_000080</x:v>
+        <x:v>label_000063</x:v>
       </x:c>
       <x:c r="H85" s="14" t="str"/>
       <x:c r="I85" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10144</x:v>
+        <x:v>https://moodyz.com/works/list/label/10077</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -8352,23 +9360,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C86" s="14" t="str">
-        <x:v>s1.label</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="D86" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="E86" s="14" t="str">
-        <x:v>4355</x:v>
+        <x:v>10106</x:v>
       </x:c>
       <x:c r="F86" s="14" t="str">
-        <x:v>S1 NO.1 STYLE</x:v>
+        <x:v>エロい！</x:v>
       </x:c>
       <x:c r="G86" s="14" t="str">
-        <x:v>label_000081</x:v>
+        <x:v>label_000053</x:v>
       </x:c>
       <x:c r="H86" s="14" t="str"/>
       <x:c r="I86" s="14" t="str">
-        <x:v>https://s1s1s1.com/works/list/label/4355</x:v>
+        <x:v>https://moodyz.com/works/list/label/10106</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -8379,23 +9387,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C87" s="14" t="str">
-        <x:v>s1.series</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="D87" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="E87" s="14" t="str">
-        <x:v>422</x:v>
+        <x:v>10107</x:v>
       </x:c>
       <x:c r="F87" s="14" t="str">
-        <x:v>おま●こ、くぱぁ</x:v>
+        <x:v>きれいなお姉さんは好きですか</x:v>
       </x:c>
       <x:c r="G87" s="14" t="str">
-        <x:v>series_000005</x:v>
+        <x:v>label_000046</x:v>
       </x:c>
       <x:c r="H87" s="14" t="str"/>
       <x:c r="I87" s="14" t="str">
-        <x:v>https://s1s1s1.com/works/list/series/422</x:v>
+        <x:v>https://moodyz.com/works/list/label/10107</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -8406,23 +9414,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C88" s="14" t="str">
-        <x:v>s1.series</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="D88" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="E88" s="14" t="str">
-        <x:v>570</x:v>
+        <x:v>10131</x:v>
       </x:c>
       <x:c r="F88" s="14" t="str">
-        <x:v>ラブキモメン</x:v>
+        <x:v>MOODYZ ニュージーニアス</x:v>
       </x:c>
       <x:c r="G88" s="14" t="str">
-        <x:v>series_000006</x:v>
+        <x:v>label_000047</x:v>
       </x:c>
       <x:c r="H88" s="14" t="str"/>
       <x:c r="I88" s="14" t="str">
-        <x:v>https://s1s1s1.com/works/list/series/570</x:v>
+        <x:v>https://moodyz.com/works/list/label/10131</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -8433,23 +9441,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C89" s="14" t="str">
-        <x:v>attackers.series</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="D89" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="E89" s="14" t="str">
-        <x:v>2402</x:v>
+        <x:v>10142</x:v>
       </x:c>
       <x:c r="F89" s="14" t="str">
-        <x:v>侵入者</x:v>
+        <x:v>おっぱい祭り</x:v>
       </x:c>
       <x:c r="G89" s="14" t="str">
-        <x:v>series_000007</x:v>
+        <x:v>label_000060</x:v>
       </x:c>
       <x:c r="H89" s="14" t="str"/>
       <x:c r="I89" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2402</x:v>
+        <x:v>https://moodyz.com/works/list/label/10142</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -8460,23 +9468,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C90" s="14" t="str">
-        <x:v>attackers.series</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="D90" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="E90" s="14" t="str">
-        <x:v>2269</x:v>
+        <x:v>10144</x:v>
       </x:c>
       <x:c r="F90" s="14" t="str">
-        <x:v>あなたに愛されたくて。</x:v>
+        <x:v>秋のシコシコ強化月間</x:v>
       </x:c>
       <x:c r="G90" s="14" t="str">
-        <x:v>series_000008</x:v>
+        <x:v>label_000061</x:v>
       </x:c>
       <x:c r="H90" s="14" t="str"/>
       <x:c r="I90" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2269</x:v>
+        <x:v>https://moodyz.com/works/list/label/10144</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -8487,23 +9495,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C91" s="14" t="str">
-        <x:v>attackers.series</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="D91" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="E91" s="14" t="str">
-        <x:v>2270</x:v>
+        <x:v>10151</x:v>
       </x:c>
       <x:c r="F91" s="14" t="str">
-        <x:v>あなた、許して…。</x:v>
+        <x:v>背徳ビチョビチョ！NTR大放出</x:v>
       </x:c>
       <x:c r="G91" s="14" t="str">
-        <x:v>series_000009</x:v>
+        <x:v>label_000062</x:v>
       </x:c>
       <x:c r="H91" s="14" t="str"/>
       <x:c r="I91" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2270</x:v>
+        <x:v>https://moodyz.com/works/list/label/10151</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -8514,23 +9522,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C92" s="14" t="str">
-        <x:v>attackers.series</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="D92" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="E92" s="14" t="str">
-        <x:v>2293</x:v>
+        <x:v>10157</x:v>
       </x:c>
       <x:c r="F92" s="14" t="str">
-        <x:v>脱獄者</x:v>
+        <x:v>MOODYZ HARD</x:v>
       </x:c>
       <x:c r="G92" s="14" t="str">
-        <x:v>series_000010</x:v>
+        <x:v>label_000058</x:v>
       </x:c>
       <x:c r="H92" s="14" t="str"/>
       <x:c r="I92" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2293</x:v>
+        <x:v>https://moodyz.com/works/list/label/10157</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -8541,23 +9549,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C93" s="14" t="str">
-        <x:v>attackers.series</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="D93" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="E93" s="14" t="str">
-        <x:v>2256</x:v>
+        <x:v>10172</x:v>
       </x:c>
       <x:c r="F93" s="14" t="str">
-        <x:v>奴隷島</x:v>
+        <x:v>MOODYZショート</x:v>
       </x:c>
       <x:c r="G93" s="14" t="str">
-        <x:v>series_000011</x:v>
+        <x:v>label_000064</x:v>
       </x:c>
       <x:c r="H93" s="14" t="str"/>
       <x:c r="I93" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2256</x:v>
+        <x:v>https://moodyz.com/works/list/label/10172</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -8568,23 +9576,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C94" s="14" t="str">
-        <x:v>attackers.series</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="D94" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="E94" s="14" t="str">
-        <x:v>2274</x:v>
+        <x:v>10174</x:v>
       </x:c>
       <x:c r="F94" s="14" t="str">
-        <x:v>犯される度に美しく</x:v>
+        <x:v>ハメドリ</x:v>
       </x:c>
       <x:c r="G94" s="14" t="str">
-        <x:v>series_000012</x:v>
+        <x:v>label_000050</x:v>
       </x:c>
       <x:c r="H94" s="14" t="str"/>
       <x:c r="I94" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2274</x:v>
+        <x:v>https://moodyz.com/works/list/label/10174</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -8595,23 +9603,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C95" s="14" t="str">
-        <x:v>attackers.series</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="D95" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="E95" s="14" t="str">
-        <x:v>2325</x:v>
+        <x:v>11471</x:v>
       </x:c>
       <x:c r="F95" s="14" t="str">
-        <x:v>団鬼六</x:v>
+        <x:v>BD-MOODYZ DIVA</x:v>
       </x:c>
       <x:c r="G95" s="14" t="str">
-        <x:v>series_000013</x:v>
+        <x:v>label_000057</x:v>
       </x:c>
       <x:c r="H95" s="14" t="str"/>
       <x:c r="I95" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2325</x:v>
+        <x:v>https://moodyz.com/works/list/label/11471</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -8622,23 +9630,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C96" s="14" t="str">
-        <x:v>attackers.series</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="D96" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="E96" s="14" t="str">
-        <x:v>5317</x:v>
+        <x:v>12798</x:v>
       </x:c>
       <x:c r="F96" s="14" t="str">
-        <x:v>調教志願</x:v>
+        <x:v>みんなのキカタン</x:v>
       </x:c>
       <x:c r="G96" s="14" t="str">
-        <x:v>series_000014</x:v>
+        <x:v>label_000002</x:v>
       </x:c>
       <x:c r="H96" s="14" t="str"/>
       <x:c r="I96" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/5317</x:v>
+        <x:v>https://moodyz.com/works/list/label/12798</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -8649,23 +9657,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C97" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="D97" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="E97" s="14" t="str">
-        <x:v>1846</x:v>
+        <x:v>5046</x:v>
       </x:c>
       <x:c r="F97" s="14" t="str">
-        <x:v>年下レズビアンに愛された私</x:v>
+        <x:v>MOODYZ ACID</x:v>
       </x:c>
       <x:c r="G97" s="14" t="str">
-        <x:v>series_000015</x:v>
+        <x:v>label_000039</x:v>
       </x:c>
       <x:c r="H97" s="14" t="str"/>
       <x:c r="I97" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1846</x:v>
+        <x:v>https://moodyz.com/works/list/label/5046</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -8676,23 +9684,23 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C98" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="D98" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="E98" s="14" t="str">
-        <x:v>1891</x:v>
+        <x:v>5047</x:v>
       </x:c>
       <x:c r="F98" s="14" t="str">
-        <x:v>廃業寸前</x:v>
+        <x:v>MOODYZ BEST</x:v>
       </x:c>
       <x:c r="G98" s="14" t="str">
-        <x:v>series_000016</x:v>
+        <x:v>label_000038</x:v>
       </x:c>
       <x:c r="H98" s="14" t="str"/>
       <x:c r="I98" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1891</x:v>
+        <x:v>https://moodyz.com/works/list/label/5047</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -8703,23 +9711,536 @@
         <x:v>approved-external-id</x:v>
       </x:c>
       <x:c r="C99" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="D99" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="E99" s="14" t="str">
-        <x:v>1749</x:v>
+        <x:v>5048</x:v>
       </x:c>
       <x:c r="F99" s="14" t="str">
-        <x:v>夫の上司に飾られた　人妻ボディアクセサリー</x:v>
+        <x:v>MOODYZ DIVA</x:v>
       </x:c>
       <x:c r="G99" s="14" t="str">
-        <x:v>series_000017</x:v>
+        <x:v>label_000001</x:v>
       </x:c>
       <x:c r="H99" s="14" t="str"/>
       <x:c r="I99" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1749</x:v>
+        <x:v>https://moodyz.com/works/list/label/5048</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B100" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C100" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D100" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E100" s="14" t="str">
+        <x:v>5049</x:v>
+      </x:c>
+      <x:c r="F100" s="14" t="str">
+        <x:v>MOODYZ ISM</x:v>
+      </x:c>
+      <x:c r="G100" s="14" t="str">
+        <x:v>label_000045</x:v>
+      </x:c>
+      <x:c r="H100" s="14" t="str"/>
+      <x:c r="I100" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5049</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B101" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C101" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D101" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E101" s="14" t="str">
+        <x:v>5090</x:v>
+      </x:c>
+      <x:c r="F101" s="14" t="str">
+        <x:v>MOODYZ REAL</x:v>
+      </x:c>
+      <x:c r="G101" s="14" t="str">
+        <x:v>label_000044</x:v>
+      </x:c>
+      <x:c r="H101" s="14" t="str"/>
+      <x:c r="I101" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5090</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B102" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C102" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D102" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E102" s="14" t="str">
+        <x:v>5409</x:v>
+      </x:c>
+      <x:c r="F102" s="14" t="str">
+        <x:v>MOODYZ VALUE</x:v>
+      </x:c>
+      <x:c r="G102" s="14" t="str">
+        <x:v>label_000049</x:v>
+      </x:c>
+      <x:c r="H102" s="14" t="str"/>
+      <x:c r="I102" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5409</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B103" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C103" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D103" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E103" s="14" t="str">
+        <x:v>6879</x:v>
+      </x:c>
+      <x:c r="F103" s="14" t="str">
+        <x:v>MOODYZ GATI</x:v>
+      </x:c>
+      <x:c r="G103" s="14" t="str">
+        <x:v>label_000040</x:v>
+      </x:c>
+      <x:c r="H103" s="14" t="str"/>
+      <x:c r="I103" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/6879</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B104" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C104" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D104" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E104" s="14" t="str">
+        <x:v>85265</x:v>
+      </x:c>
+      <x:c r="F104" s="14" t="str">
+        <x:v>春のパンツまつり</x:v>
+      </x:c>
+      <x:c r="G104" s="14" t="str">
+        <x:v>label_000056</x:v>
+      </x:c>
+      <x:c r="H104" s="14" t="str"/>
+      <x:c r="I104" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/85265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B105" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C105" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D105" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E105" s="14" t="str">
+        <x:v>8916</x:v>
+      </x:c>
+      <x:c r="F105" s="14" t="str">
+        <x:v>MOODYZ ASS</x:v>
+      </x:c>
+      <x:c r="G105" s="14" t="str">
+        <x:v>label_000051</x:v>
+      </x:c>
+      <x:c r="H105" s="14" t="str"/>
+      <x:c r="I105" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/8916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B106" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C106" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D106" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E106" s="14" t="str">
+        <x:v>8917</x:v>
+      </x:c>
+      <x:c r="F106" s="14" t="str">
+        <x:v>MOODYZ ES</x:v>
+      </x:c>
+      <x:c r="G106" s="14" t="str">
+        <x:v>label_000055</x:v>
+      </x:c>
+      <x:c r="H106" s="14" t="str"/>
+      <x:c r="I106" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/8917</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B107" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C107" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D107" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E107" s="14" t="str">
+        <x:v>9288</x:v>
+      </x:c>
+      <x:c r="F107" s="14" t="str">
+        <x:v>寝取られ本舗</x:v>
+      </x:c>
+      <x:c r="G107" s="14" t="str">
+        <x:v>label_000054</x:v>
+      </x:c>
+      <x:c r="H107" s="14" t="str"/>
+      <x:c r="I107" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9288</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B108" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C108" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D108" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E108" s="14" t="str">
+        <x:v>9308</x:v>
+      </x:c>
+      <x:c r="F108" s="14" t="str">
+        <x:v>まんきつ</x:v>
+      </x:c>
+      <x:c r="G108" s="14" t="str">
+        <x:v>label_000043</x:v>
+      </x:c>
+      <x:c r="H108" s="14" t="str"/>
+      <x:c r="I108" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B109" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C109" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D109" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E109" s="14" t="str">
+        <x:v>9397</x:v>
+      </x:c>
+      <x:c r="F109" s="14" t="str">
+        <x:v>Q-EYE</x:v>
+      </x:c>
+      <x:c r="G109" s="14" t="str">
+        <x:v>label_000052</x:v>
+      </x:c>
+      <x:c r="H109" s="14" t="str"/>
+      <x:c r="I109" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9397</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B110" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C110" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D110" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E110" s="14" t="str">
+        <x:v>9458</x:v>
+      </x:c>
+      <x:c r="F110" s="14" t="str">
+        <x:v>MUTTURI</x:v>
+      </x:c>
+      <x:c r="G110" s="14" t="str">
+        <x:v>label_000048</x:v>
+      </x:c>
+      <x:c r="H110" s="14" t="str"/>
+      <x:c r="I110" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9458</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B111" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C111" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D111" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E111" s="14" t="str">
+        <x:v>9483</x:v>
+      </x:c>
+      <x:c r="F111" s="14" t="str">
+        <x:v>AVOPEN</x:v>
+      </x:c>
+      <x:c r="G111" s="14" t="str">
+        <x:v>label_000059</x:v>
+      </x:c>
+      <x:c r="H111" s="14" t="str"/>
+      <x:c r="I111" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9483</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B112" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C112" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D112" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E112" s="14" t="str">
+        <x:v>9732</x:v>
+      </x:c>
+      <x:c r="F112" s="14" t="str">
+        <x:v>MOODYZ Fresh</x:v>
+      </x:c>
+      <x:c r="G112" s="14" t="str">
+        <x:v>label_000042</x:v>
+      </x:c>
+      <x:c r="H112" s="14" t="str"/>
+      <x:c r="I112" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9732</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B113" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C113" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="D113" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E113" s="14" t="str">
+        <x:v>9782</x:v>
+      </x:c>
+      <x:c r="F113" s="14" t="str">
+        <x:v>MOODYZ VR</x:v>
+      </x:c>
+      <x:c r="G113" s="14" t="str">
+        <x:v>label_000041</x:v>
+      </x:c>
+      <x:c r="H113" s="14" t="str"/>
+      <x:c r="I113" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9782</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B114" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C114" s="14" t="str">
+        <x:v>moodyz.series</x:v>
+      </x:c>
+      <x:c r="D114" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="E114" s="14" t="str">
+        <x:v>5427</x:v>
+      </x:c>
+      <x:c r="F114" s="14" t="str">
+        <x:v>カラミざかり</x:v>
+      </x:c>
+      <x:c r="G114" s="14" t="str">
+        <x:v>series_000002</x:v>
+      </x:c>
+      <x:c r="H114" s="14" t="str"/>
+      <x:c r="I114" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/5427</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B115" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C115" s="14" t="str">
+        <x:v>s1.label</x:v>
+      </x:c>
+      <x:c r="D115" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="E115" s="14" t="str">
+        <x:v>4355</x:v>
+      </x:c>
+      <x:c r="F115" s="14" t="str">
+        <x:v>S1 NO.1 STYLE</x:v>
+      </x:c>
+      <x:c r="G115" s="14" t="str">
+        <x:v>label_000081</x:v>
+      </x:c>
+      <x:c r="H115" s="14" t="str"/>
+      <x:c r="I115" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/label/4355</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B116" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C116" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="D116" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="E116" s="14" t="str">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="F116" s="14" t="str">
+        <x:v>新人NO.1STYLE</x:v>
+      </x:c>
+      <x:c r="G116" s="14" t="str">
+        <x:v>series_000001</x:v>
+      </x:c>
+      <x:c r="H116" s="14" t="str"/>
+      <x:c r="I116" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/414</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B117" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C117" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="D117" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="E117" s="14" t="str">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="F117" s="14" t="str">
+        <x:v>おま●こ、くぱぁ</x:v>
+      </x:c>
+      <x:c r="G117" s="14" t="str">
+        <x:v>series_000005</x:v>
+      </x:c>
+      <x:c r="H117" s="14" t="str"/>
+      <x:c r="I117" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/422</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="14" t="str">
+        <x:v>auto-applied</x:v>
+      </x:c>
+      <x:c r="B118" s="14" t="str">
+        <x:v>approved-external-id</x:v>
+      </x:c>
+      <x:c r="C118" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="D118" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="E118" s="14" t="str">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="F118" s="14" t="str">
+        <x:v>ラブキモメン</x:v>
+      </x:c>
+      <x:c r="G118" s="14" t="str">
+        <x:v>series_000006</x:v>
+      </x:c>
+      <x:c r="H118" s="14" t="str"/>
+      <x:c r="I118" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/570</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8862,21 +10383,74 @@
         <x:v>Source URL</x:v>
       </x:c>
     </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="58" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="72" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Decision</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>External ID</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>Snapshot ID</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>Community ID</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>日本語</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>Maker ID</x:v>
+      </x:c>
+      <x:c r="H1" s="6" t="str">
+        <x:v>Reviewed</x:v>
+      </x:c>
+      <x:c r="I1" s="6" t="str">
+        <x:v>Source URL</x:v>
+      </x:c>
+      <x:c r="J1" s="6" t="str">
+        <x:v>Reason</x:v>
+      </x:c>
+    </x:row>
     <x:row r="2">
       <x:c r="A2" s="14" t="str">
-        <x:v>candidate-new</x:v>
+        <x:v>publish</x:v>
       </x:c>
       <x:c r="B2" s="14" t="str">
-        <x:v>unmapped-official-series-id</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C2" s="14" t="str">
-        <x:v>attackers.series</x:v>
+        <x:v>2253</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
         <x:v>attackers-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E2" s="14" t="str">
-        <x:v>2253</x:v>
+        <x:v>series_000018</x:v>
       </x:c>
       <x:c r="F2" s="14" t="str">
         <x:v>アナル奴隷白書</x:v>
@@ -8884,27 +10458,31 @@
       <x:c r="G2" s="14" t="str">
         <x:v>maker_000004</x:v>
       </x:c>
-      <x:c r="H2" s="14" t="str"/>
-      <x:c r="I2" s="14" t="str"/>
+      <x:c r="H2" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="I2" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2253</x:v>
+      </x:c>
       <x:c r="J2" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2253</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="14" t="str">
-        <x:v>candidate-new</x:v>
+        <x:v>publish</x:v>
       </x:c>
       <x:c r="B3" s="14" t="str">
-        <x:v>unmapped-official-series-id</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C3" s="14" t="str">
-        <x:v>attackers.series</x:v>
+        <x:v>2254</x:v>
       </x:c>
       <x:c r="D3" s="14" t="str">
         <x:v>attackers-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E3" s="14" t="str">
-        <x:v>2254</x:v>
+        <x:v>series_000019</x:v>
       </x:c>
       <x:c r="F3" s="14" t="str">
         <x:v>夫の目の前で犯されて</x:v>
@@ -8912,27 +10490,31 @@
       <x:c r="G3" s="14" t="str">
         <x:v>maker_000004</x:v>
       </x:c>
-      <x:c r="H3" s="14" t="str"/>
-      <x:c r="I3" s="14" t="str"/>
+      <x:c r="H3" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="I3" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2254</x:v>
+      </x:c>
       <x:c r="J3" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2254</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="14" t="str">
-        <x:v>candidate-new</x:v>
+        <x:v>publish</x:v>
       </x:c>
       <x:c r="B4" s="14" t="str">
-        <x:v>unmapped-official-series-id</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C4" s="14" t="str">
-        <x:v>attackers.series</x:v>
+        <x:v>2255</x:v>
       </x:c>
       <x:c r="D4" s="14" t="str">
         <x:v>attackers-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E4" s="14" t="str">
-        <x:v>2255</x:v>
+        <x:v>series_000020</x:v>
       </x:c>
       <x:c r="F4" s="14" t="str">
         <x:v>地獄の女神</x:v>
@@ -8940,27 +10522,31 @@
       <x:c r="G4" s="14" t="str">
         <x:v>maker_000004</x:v>
       </x:c>
-      <x:c r="H4" s="14" t="str"/>
-      <x:c r="I4" s="14" t="str"/>
+      <x:c r="H4" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="I4" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2255</x:v>
+      </x:c>
       <x:c r="J4" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2255</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14" t="str">
-        <x:v>candidate-new</x:v>
+        <x:v>publish</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>unmapped-official-series-id</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
-        <x:v>attackers.series</x:v>
+        <x:v>2257</x:v>
       </x:c>
       <x:c r="D5" s="14" t="str">
         <x:v>attackers-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E5" s="14" t="str">
-        <x:v>2257</x:v>
+        <x:v>series_000021</x:v>
       </x:c>
       <x:c r="F5" s="14" t="str">
         <x:v>絶対調教</x:v>
@@ -8968,27 +10554,31 @@
       <x:c r="G5" s="14" t="str">
         <x:v>maker_000004</x:v>
       </x:c>
-      <x:c r="H5" s="14" t="str"/>
-      <x:c r="I5" s="14" t="str"/>
+      <x:c r="H5" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="I5" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2257</x:v>
+      </x:c>
       <x:c r="J5" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2257</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="14" t="str">
-        <x:v>candidate-new</x:v>
+        <x:v>publish</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
-        <x:v>unmapped-official-series-id</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C6" s="14" t="str">
-        <x:v>attackers.series</x:v>
+        <x:v>2258</x:v>
       </x:c>
       <x:c r="D6" s="14" t="str">
         <x:v>attackers-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E6" s="14" t="str">
-        <x:v>2258</x:v>
+        <x:v>series_000022</x:v>
       </x:c>
       <x:c r="F6" s="14" t="str">
         <x:v>淫乱奴隷の強制快楽</x:v>
@@ -8996,27 +10586,31 @@
       <x:c r="G6" s="14" t="str">
         <x:v>maker_000004</x:v>
       </x:c>
-      <x:c r="H6" s="14" t="str"/>
-      <x:c r="I6" s="14" t="str"/>
+      <x:c r="H6" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="I6" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2258</x:v>
+      </x:c>
       <x:c r="J6" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2258</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="14" t="str">
-        <x:v>candidate-new</x:v>
+        <x:v>publish</x:v>
       </x:c>
       <x:c r="B7" s="14" t="str">
-        <x:v>unmapped-official-series-id</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C7" s="14" t="str">
-        <x:v>attackers.series</x:v>
+        <x:v>2259</x:v>
       </x:c>
       <x:c r="D7" s="14" t="str">
         <x:v>attackers-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E7" s="14" t="str">
-        <x:v>2259</x:v>
+        <x:v>series_000023</x:v>
       </x:c>
       <x:c r="F7" s="14" t="str">
         <x:v>貞操帯の女</x:v>
@@ -9024,27 +10618,31 @@
       <x:c r="G7" s="14" t="str">
         <x:v>maker_000004</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="str"/>
-      <x:c r="I7" s="14" t="str"/>
+      <x:c r="H7" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="I7" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2259</x:v>
+      </x:c>
       <x:c r="J7" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2259</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="14" t="str">
-        <x:v>candidate-new</x:v>
+        <x:v>publish</x:v>
       </x:c>
       <x:c r="B8" s="14" t="str">
-        <x:v>unmapped-official-series-id</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C8" s="14" t="str">
-        <x:v>attackers.series</x:v>
+        <x:v>2260</x:v>
       </x:c>
       <x:c r="D8" s="14" t="str">
         <x:v>attackers-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E8" s="14" t="str">
-        <x:v>2260</x:v>
+        <x:v>series_000024</x:v>
       </x:c>
       <x:c r="F8" s="14" t="str">
         <x:v>楠木女学院</x:v>
@@ -9052,27 +10650,31 @@
       <x:c r="G8" s="14" t="str">
         <x:v>maker_000004</x:v>
       </x:c>
-      <x:c r="H8" s="14" t="str"/>
-      <x:c r="I8" s="14" t="str"/>
+      <x:c r="H8" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="I8" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2260</x:v>
+      </x:c>
       <x:c r="J8" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2260</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="14" t="str">
-        <x:v>candidate-new</x:v>
+        <x:v>publish</x:v>
       </x:c>
       <x:c r="B9" s="14" t="str">
-        <x:v>unmapped-official-series-id</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C9" s="14" t="str">
-        <x:v>attackers.series</x:v>
+        <x:v>2261</x:v>
       </x:c>
       <x:c r="D9" s="14" t="str">
         <x:v>attackers-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E9" s="14" t="str">
-        <x:v>2261</x:v>
+        <x:v>series_000025</x:v>
       </x:c>
       <x:c r="F9" s="14" t="str">
         <x:v>鬼畜輪姦</x:v>
@@ -9080,27 +10682,31 @@
       <x:c r="G9" s="14" t="str">
         <x:v>maker_000004</x:v>
       </x:c>
-      <x:c r="H9" s="14" t="str"/>
-      <x:c r="I9" s="14" t="str"/>
+      <x:c r="H9" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="I9" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2261</x:v>
+      </x:c>
       <x:c r="J9" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2261</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="14" t="str">
-        <x:v>candidate-new</x:v>
+        <x:v>publish</x:v>
       </x:c>
       <x:c r="B10" s="14" t="str">
-        <x:v>unmapped-official-series-id</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C10" s="14" t="str">
-        <x:v>attackers.series</x:v>
+        <x:v>2263</x:v>
       </x:c>
       <x:c r="D10" s="14" t="str">
         <x:v>attackers-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E10" s="14" t="str">
-        <x:v>2263</x:v>
+        <x:v>series_000026</x:v>
       </x:c>
       <x:c r="F10" s="14" t="str">
         <x:v>女豹</x:v>
@@ -9108,27 +10714,31 @@
       <x:c r="G10" s="14" t="str">
         <x:v>maker_000004</x:v>
       </x:c>
-      <x:c r="H10" s="14" t="str"/>
-      <x:c r="I10" s="14" t="str"/>
+      <x:c r="H10" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="I10" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2263</x:v>
+      </x:c>
       <x:c r="J10" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2263</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="14" t="str">
-        <x:v>candidate-new</x:v>
+        <x:v>publish</x:v>
       </x:c>
       <x:c r="B11" s="14" t="str">
-        <x:v>unmapped-official-series-id</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C11" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>1549</x:v>
       </x:c>
       <x:c r="D11" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E11" s="14" t="str">
-        <x:v>1549</x:v>
+        <x:v>series_000027</x:v>
       </x:c>
       <x:c r="F11" s="14" t="str">
         <x:v>となりの奥さん</x:v>
@@ -9136,27 +10746,31 @@
       <x:c r="G11" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
-      <x:c r="H11" s="14" t="str"/>
-      <x:c r="I11" s="14" t="str"/>
+      <x:c r="H11" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="I11" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1549</x:v>
+      </x:c>
       <x:c r="J11" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1549</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="14" t="str">
-        <x:v>candidate-new</x:v>
+        <x:v>publish</x:v>
       </x:c>
       <x:c r="B12" s="14" t="str">
-        <x:v>unmapped-official-series-id</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C12" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D12" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E12" s="14" t="str">
-        <x:v>1550</x:v>
+        <x:v>series_000028</x:v>
       </x:c>
       <x:c r="F12" s="14" t="str">
         <x:v>美熟女と黒人</x:v>
@@ -9164,27 +10778,31 @@
       <x:c r="G12" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
-      <x:c r="H12" s="14" t="str"/>
-      <x:c r="I12" s="14" t="str"/>
+      <x:c r="H12" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="I12" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1550</x:v>
+      </x:c>
       <x:c r="J12" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1550</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="14" t="str">
-        <x:v>candidate-new</x:v>
+        <x:v>publish</x:v>
       </x:c>
       <x:c r="B13" s="14" t="str">
-        <x:v>unmapped-official-series-id</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>1551</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E13" s="14" t="str">
-        <x:v>1551</x:v>
+        <x:v>series_000029</x:v>
       </x:c>
       <x:c r="F13" s="14" t="str">
         <x:v>愛する夫の目の前で・・・</x:v>
@@ -9192,27 +10810,31 @@
       <x:c r="G13" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
-      <x:c r="H13" s="14" t="str"/>
-      <x:c r="I13" s="14" t="str"/>
+      <x:c r="H13" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="I13" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1551</x:v>
+      </x:c>
       <x:c r="J13" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1551</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="14" t="str">
-        <x:v>candidate-new</x:v>
+        <x:v>publish</x:v>
       </x:c>
       <x:c r="B14" s="14" t="str">
-        <x:v>unmapped-official-series-id</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>1552</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E14" s="14" t="str">
-        <x:v>1552</x:v>
+        <x:v>series_000030</x:v>
       </x:c>
       <x:c r="F14" s="14" t="str">
         <x:v>特選 友達の母</x:v>
@@ -9220,27 +10842,31 @@
       <x:c r="G14" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
-      <x:c r="H14" s="14" t="str"/>
-      <x:c r="I14" s="14" t="str"/>
+      <x:c r="H14" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="I14" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1552</x:v>
+      </x:c>
       <x:c r="J14" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1552</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="14" t="str">
-        <x:v>candidate-new</x:v>
+        <x:v>publish</x:v>
       </x:c>
       <x:c r="B15" s="14" t="str">
-        <x:v>unmapped-official-series-id</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C15" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>1553</x:v>
       </x:c>
       <x:c r="D15" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E15" s="14" t="str">
-        <x:v>1553</x:v>
+        <x:v>series_000031</x:v>
       </x:c>
       <x:c r="F15" s="14" t="str">
         <x:v>僕のおばさん</x:v>
@@ -9248,27 +10874,31 @@
       <x:c r="G15" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
-      <x:c r="H15" s="14" t="str"/>
-      <x:c r="I15" s="14" t="str"/>
+      <x:c r="H15" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="I15" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1553</x:v>
+      </x:c>
       <x:c r="J15" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1553</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="14" t="str">
-        <x:v>candidate-new</x:v>
+        <x:v>publish</x:v>
       </x:c>
       <x:c r="B16" s="14" t="str">
-        <x:v>unmapped-official-series-id</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C16" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>1554</x:v>
       </x:c>
       <x:c r="D16" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E16" s="14" t="str">
-        <x:v>1554</x:v>
+        <x:v>series_000032</x:v>
       </x:c>
       <x:c r="F16" s="14" t="str">
         <x:v>素人人妻ナンパ総集編4時間</x:v>
@@ -9276,27 +10906,31 @@
       <x:c r="G16" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
-      <x:c r="H16" s="14" t="str"/>
-      <x:c r="I16" s="14" t="str"/>
+      <x:c r="H16" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="I16" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1554</x:v>
+      </x:c>
       <x:c r="J16" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1554</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="14" t="str">
-        <x:v>candidate-new</x:v>
+        <x:v>publish</x:v>
       </x:c>
       <x:c r="B17" s="14" t="str">
-        <x:v>unmapped-official-series-id</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C17" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>1555</x:v>
       </x:c>
       <x:c r="D17" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E17" s="14" t="str">
-        <x:v>1555</x:v>
+        <x:v>series_000033</x:v>
       </x:c>
       <x:c r="F17" s="14" t="str">
         <x:v>五十路熟女18人4時間</x:v>
@@ -9304,27 +10938,31 @@
       <x:c r="G17" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
-      <x:c r="H17" s="14" t="str"/>
-      <x:c r="I17" s="14" t="str"/>
+      <x:c r="H17" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="I17" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1555</x:v>
+      </x:c>
       <x:c r="J17" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1555</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="14" t="str">
-        <x:v>candidate-new</x:v>
+        <x:v>publish</x:v>
       </x:c>
       <x:c r="B18" s="14" t="str">
-        <x:v>unmapped-official-series-id</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C18" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>1556</x:v>
       </x:c>
       <x:c r="D18" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E18" s="14" t="str">
-        <x:v>1556</x:v>
+        <x:v>series_000034</x:v>
       </x:c>
       <x:c r="F18" s="14" t="str">
         <x:v>団地妻20人4時間</x:v>
@@ -9332,27 +10970,31 @@
       <x:c r="G18" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
-      <x:c r="H18" s="14" t="str"/>
-      <x:c r="I18" s="14" t="str"/>
+      <x:c r="H18" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="I18" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1556</x:v>
+      </x:c>
       <x:c r="J18" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1556</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="14" t="str">
-        <x:v>candidate-new</x:v>
+        <x:v>publish</x:v>
       </x:c>
       <x:c r="B19" s="14" t="str">
-        <x:v>unmapped-official-series-id</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C19" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>1557</x:v>
       </x:c>
       <x:c r="D19" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E19" s="14" t="str">
-        <x:v>1557</x:v>
+        <x:v>series_000035</x:v>
       </x:c>
       <x:c r="F19" s="14" t="str">
         <x:v>犯された熟女たち総集編4時間</x:v>
@@ -9360,27 +11002,31 @@
       <x:c r="G19" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
-      <x:c r="H19" s="14" t="str"/>
-      <x:c r="I19" s="14" t="str"/>
+      <x:c r="H19" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="I19" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1557</x:v>
+      </x:c>
       <x:c r="J19" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1557</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="14" t="str">
-        <x:v>candidate-new</x:v>
+        <x:v>publish</x:v>
       </x:c>
       <x:c r="B20" s="14" t="str">
-        <x:v>unmapped-official-series-id</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>1558</x:v>
       </x:c>
       <x:c r="D20" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E20" s="14" t="str">
-        <x:v>1558</x:v>
+        <x:v>series_000036</x:v>
       </x:c>
       <x:c r="F20" s="14" t="str">
         <x:v>妖艶おんな愛戯</x:v>
@@ -9388,10 +11034,14 @@
       <x:c r="G20" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
-      <x:c r="H20" s="14" t="str"/>
-      <x:c r="I20" s="14" t="str"/>
+      <x:c r="H20" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="I20" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1558</x:v>
+      </x:c>
       <x:c r="J20" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1558</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/exports/xlsx/organization-series-registry.xlsx
+++ b/exports/xlsx/organization-series-registry.xlsx
@@ -2,12 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organizations" sheetId="1" r:id="R43b553cf99ba42c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series" sheetId="2" r:id="Rfdba7010d8c44a40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Registry" sheetId="3" r:id="R56505284b37b47c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External ID Mapping" sheetId="4" r:id="R3738a673478e450f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Candidate Reviews" sheetId="5" r:id="R48b69166c1534dfa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Index Candidates" sheetId="6" r:id="Rcdeb45c6c8a84782"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organizations" sheetId="1" r:id="R2993ec19aeca44c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series" sheetId="2" r:id="R1a7b460c3c5641ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Registry" sheetId="3" r:id="R5c41bb66fc8a4a0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External ID Mapping" sheetId="4" r:id="R0f2ce31f408b4913"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Candidate Reviews" sheetId="5" r:id="R849e654077724a7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Index Candidates" sheetId="6" r:id="R840c7420a3fe48e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Latest Snapshots" sheetId="7" r:id="R4326c1f830b6475d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2744,7 +2745,7 @@
     <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="54" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="56" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -4358,6 +4359,1020 @@
       </x:c>
       <x:c r="H62" s="14" t="str">
         <x:v>madonna.series:1564</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="14" t="str">
+        <x:v>series_000062</x:v>
+      </x:c>
+      <x:c r="B63" s="14" t="str">
+        <x:v>不埒な姦係</x:v>
+      </x:c>
+      <x:c r="C63" s="14" t="str">
+        <x:v>不端的奸系</x:v>
+      </x:c>
+      <x:c r="D63" s="14" t="str">
+        <x:v>Indecent Affair</x:v>
+      </x:c>
+      <x:c r="E63" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="F63" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G63" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2287</x:v>
+      </x:c>
+      <x:c r="H63" s="14" t="str">
+        <x:v>attackers.series:2287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="14" t="str">
+        <x:v>series_000063</x:v>
+      </x:c>
+      <x:c r="B64" s="14" t="str">
+        <x:v>あなたが欲しくて</x:v>
+      </x:c>
+      <x:c r="C64" s="14" t="str">
+        <x:v>渴望拥有你</x:v>
+      </x:c>
+      <x:c r="D64" s="14" t="str">
+        <x:v>Wanting You</x:v>
+      </x:c>
+      <x:c r="E64" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="F64" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G64" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2288</x:v>
+      </x:c>
+      <x:c r="H64" s="14" t="str">
+        <x:v>attackers.series:2288</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="14" t="str">
+        <x:v>series_000064</x:v>
+      </x:c>
+      <x:c r="B65" s="14" t="str">
+        <x:v>背徳の契り</x:v>
+      </x:c>
+      <x:c r="C65" s="14" t="str">
+        <x:v>背德之契</x:v>
+      </x:c>
+      <x:c r="D65" s="14" t="str">
+        <x:v>Pact of Immorality</x:v>
+      </x:c>
+      <x:c r="E65" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="F65" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G65" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2290</x:v>
+      </x:c>
+      <x:c r="H65" s="14" t="str">
+        <x:v>attackers.series:2290</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="14" t="str">
+        <x:v>series_000065</x:v>
+      </x:c>
+      <x:c r="B66" s="14" t="str">
+        <x:v>鬱勃起</x:v>
+      </x:c>
+      <x:c r="C66" s="14" t="str">
+        <x:v>抑郁勃起</x:v>
+      </x:c>
+      <x:c r="D66" s="14" t="str">
+        <x:v>Depressive Erection</x:v>
+      </x:c>
+      <x:c r="E66" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="F66" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G66" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2291</x:v>
+      </x:c>
+      <x:c r="H66" s="14" t="str">
+        <x:v>attackers.series:2291</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="14" t="str">
+        <x:v>series_000066</x:v>
+      </x:c>
+      <x:c r="B67" s="14" t="str">
+        <x:v>抱かれるための出社</x:v>
+      </x:c>
+      <x:c r="C67" s="14" t="str">
+        <x:v>为了被拥抱而上班</x:v>
+      </x:c>
+      <x:c r="D67" s="14" t="str">
+        <x:v>Going to Work to Be Taken</x:v>
+      </x:c>
+      <x:c r="E67" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="F67" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G67" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2292</x:v>
+      </x:c>
+      <x:c r="H67" s="14" t="str">
+        <x:v>attackers.series:2292</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="14" t="str">
+        <x:v>series_000067</x:v>
+      </x:c>
+      <x:c r="B68" s="14" t="str">
+        <x:v>舐め犯し</x:v>
+      </x:c>
+      <x:c r="C68" s="14" t="str">
+        <x:v>舔舐侵犯</x:v>
+      </x:c>
+      <x:c r="D68" s="14" t="str">
+        <x:v>Licked and Violated</x:v>
+      </x:c>
+      <x:c r="E68" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="F68" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G68" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2295</x:v>
+      </x:c>
+      <x:c r="H68" s="14" t="str">
+        <x:v>attackers.series:2295</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="14" t="str">
+        <x:v>series_000068</x:v>
+      </x:c>
+      <x:c r="B69" s="14" t="str">
+        <x:v>素人強姦面接</x:v>
+      </x:c>
+      <x:c r="C69" s="14" t="str">
+        <x:v>素人强奸面试</x:v>
+      </x:c>
+      <x:c r="D69" s="14" t="str">
+        <x:v>Amateur Rape Interview</x:v>
+      </x:c>
+      <x:c r="E69" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="F69" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G69" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2298</x:v>
+      </x:c>
+      <x:c r="H69" s="14" t="str">
+        <x:v>attackers.series:2298</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="14" t="str">
+        <x:v>series_000069</x:v>
+      </x:c>
+      <x:c r="B70" s="14" t="str">
+        <x:v>死夜悪アンソロジー</x:v>
+      </x:c>
+      <x:c r="C70" s="14" t="str">
+        <x:v>死夜恶选集</x:v>
+      </x:c>
+      <x:c r="D70" s="14" t="str">
+        <x:v>Shiyaaku Anthology</x:v>
+      </x:c>
+      <x:c r="E70" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="F70" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G70" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2299</x:v>
+      </x:c>
+      <x:c r="H70" s="14" t="str">
+        <x:v>attackers.series:2299</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="14" t="str">
+        <x:v>series_000070</x:v>
+      </x:c>
+      <x:c r="B71" s="14" t="str">
+        <x:v>蛇縛の拷問折檻</x:v>
+      </x:c>
+      <x:c r="C71" s="14" t="str">
+        <x:v>蛇缚的拷问惩戒</x:v>
+      </x:c>
+      <x:c r="D71" s="14" t="str">
+        <x:v>Jabaku Torture and Punishment</x:v>
+      </x:c>
+      <x:c r="E71" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="F71" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G71" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2300</x:v>
+      </x:c>
+      <x:c r="H71" s="14" t="str">
+        <x:v>attackers.series:2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="14" t="str">
+        <x:v>series_000071</x:v>
+      </x:c>
+      <x:c r="B72" s="14" t="str">
+        <x:v>BEST</x:v>
+      </x:c>
+      <x:c r="C72" s="14" t="str">
+        <x:v>BEST精选</x:v>
+      </x:c>
+      <x:c r="D72" s="14" t="str">
+        <x:v>BEST</x:v>
+      </x:c>
+      <x:c r="E72" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="F72" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G72" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2301</x:v>
+      </x:c>
+      <x:c r="H72" s="14" t="str">
+        <x:v>attackers.series:2301</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="14" t="str">
+        <x:v>series_000072</x:v>
+      </x:c>
+      <x:c r="B73" s="14" t="str">
+        <x:v>凌辱大捜査線</x:v>
+      </x:c>
+      <x:c r="C73" s="14" t="str">
+        <x:v>凌辱大搜查线</x:v>
+      </x:c>
+      <x:c r="D73" s="14" t="str">
+        <x:v>Humiliation Investigation Line</x:v>
+      </x:c>
+      <x:c r="E73" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="F73" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G73" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2302</x:v>
+      </x:c>
+      <x:c r="H73" s="14" t="str">
+        <x:v>attackers.series:2302</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="14" t="str">
+        <x:v>series_000073</x:v>
+      </x:c>
+      <x:c r="B74" s="14" t="str">
+        <x:v>これで最後にしてください。</x:v>
+      </x:c>
+      <x:c r="C74" s="14" t="str">
+        <x:v>请让这成为最后一次。</x:v>
+      </x:c>
+      <x:c r="D74" s="14" t="str">
+        <x:v>Please Let This Be the Last Time</x:v>
+      </x:c>
+      <x:c r="E74" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="F74" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G74" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2303</x:v>
+      </x:c>
+      <x:c r="H74" s="14" t="str">
+        <x:v>attackers.series:2303</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="14" t="str">
+        <x:v>series_000074</x:v>
+      </x:c>
+      <x:c r="B75" s="14" t="str">
+        <x:v>女優名鑑</x:v>
+      </x:c>
+      <x:c r="C75" s="14" t="str">
+        <x:v>女优名鉴</x:v>
+      </x:c>
+      <x:c r="D75" s="14" t="str">
+        <x:v>Actress Directory</x:v>
+      </x:c>
+      <x:c r="E75" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="F75" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G75" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2305</x:v>
+      </x:c>
+      <x:c r="H75" s="14" t="str">
+        <x:v>attackers.series:2305</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="14" t="str">
+        <x:v>series_000075</x:v>
+      </x:c>
+      <x:c r="B76" s="14" t="str">
+        <x:v>遺伝子の悲劇</x:v>
+      </x:c>
+      <x:c r="C76" s="14" t="str">
+        <x:v>基因的悲剧</x:v>
+      </x:c>
+      <x:c r="D76" s="14" t="str">
+        <x:v>Tragedy of the Genes</x:v>
+      </x:c>
+      <x:c r="E76" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="F76" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G76" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2306</x:v>
+      </x:c>
+      <x:c r="H76" s="14" t="str">
+        <x:v>attackers.series:2306</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="14" t="str">
+        <x:v>series_000076</x:v>
+      </x:c>
+      <x:c r="B77" s="14" t="str">
+        <x:v>昭和哀歌</x:v>
+      </x:c>
+      <x:c r="C77" s="14" t="str">
+        <x:v>昭和哀歌</x:v>
+      </x:c>
+      <x:c r="D77" s="14" t="str">
+        <x:v>Showa Elegy</x:v>
+      </x:c>
+      <x:c r="E77" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="F77" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G77" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2307</x:v>
+      </x:c>
+      <x:c r="H77" s="14" t="str">
+        <x:v>attackers.series:2307</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="14" t="str">
+        <x:v>series_000077</x:v>
+      </x:c>
+      <x:c r="B78" s="14" t="str">
+        <x:v>声を出せない私</x:v>
+      </x:c>
+      <x:c r="C78" s="14" t="str">
+        <x:v>无法发出声音的我</x:v>
+      </x:c>
+      <x:c r="D78" s="14" t="str">
+        <x:v>I Cannot Make a Sound</x:v>
+      </x:c>
+      <x:c r="E78" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="F78" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G78" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2308</x:v>
+      </x:c>
+      <x:c r="H78" s="14" t="str">
+        <x:v>attackers.series:2308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="14" t="str">
+        <x:v>series_000078</x:v>
+      </x:c>
+      <x:c r="B79" s="14" t="str">
+        <x:v>極道の女</x:v>
+      </x:c>
+      <x:c r="C79" s="14" t="str">
+        <x:v>极道之女</x:v>
+      </x:c>
+      <x:c r="D79" s="14" t="str">
+        <x:v>Yakuza Woman</x:v>
+      </x:c>
+      <x:c r="E79" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="F79" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G79" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2309</x:v>
+      </x:c>
+      <x:c r="H79" s="14" t="str">
+        <x:v>attackers.series:2309</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="14" t="str">
+        <x:v>series_000079</x:v>
+      </x:c>
+      <x:c r="B80" s="14" t="str">
+        <x:v>くノ一拷問凌辱</x:v>
+      </x:c>
+      <x:c r="C80" s="14" t="str">
+        <x:v>女忍者拷问凌辱</x:v>
+      </x:c>
+      <x:c r="D80" s="14" t="str">
+        <x:v>Kunoichi Torture and Humiliation</x:v>
+      </x:c>
+      <x:c r="E80" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="F80" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G80" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2311</x:v>
+      </x:c>
+      <x:c r="H80" s="14" t="str">
+        <x:v>attackers.series:2311</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="14" t="str">
+        <x:v>series_000080</x:v>
+      </x:c>
+      <x:c r="B81" s="14" t="str">
+        <x:v>奴隷色のステージ</x:v>
+      </x:c>
+      <x:c r="C81" s="14" t="str">
+        <x:v>奴隶色的舞台</x:v>
+      </x:c>
+      <x:c r="D81" s="14" t="str">
+        <x:v>Slave-Colored Stage</x:v>
+      </x:c>
+      <x:c r="E81" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="F81" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G81" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2312</x:v>
+      </x:c>
+      <x:c r="H81" s="14" t="str">
+        <x:v>attackers.series:2312</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="14" t="str">
+        <x:v>series_000081</x:v>
+      </x:c>
+      <x:c r="B82" s="14" t="str">
+        <x:v>出張先のビジネスホテルでずっと憧れていた女上司と</x:v>
+      </x:c>
+      <x:c r="C82" s="14" t="str">
+        <x:v>在出差地的商务酒店与一直憧憬的女上司</x:v>
+      </x:c>
+      <x:c r="D82" s="14" t="str">
+        <x:v>With the Female Boss I Always Admired at a Business Hotel</x:v>
+      </x:c>
+      <x:c r="E82" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="F82" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G82" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1565</x:v>
+      </x:c>
+      <x:c r="H82" s="14" t="str">
+        <x:v>madonna.series:1565</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="14" t="str">
+        <x:v>series_000082</x:v>
+      </x:c>
+      <x:c r="B83" s="14" t="str">
+        <x:v>人妻秘書、汗と接吻に満ちた社長室中出し性交</x:v>
+      </x:c>
+      <x:c r="C83" s="14" t="str">
+        <x:v>人妻秘书，充满汗水与接吻的社长室中出性交</x:v>
+      </x:c>
+      <x:c r="D83" s="14" t="str">
+        <x:v>Married Secretary: Sweaty Kisses and Office Creampie Sex</x:v>
+      </x:c>
+      <x:c r="E83" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="F83" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G83" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1566</x:v>
+      </x:c>
+      <x:c r="H83" s="14" t="str">
+        <x:v>madonna.series:1566</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="14" t="str">
+        <x:v>series_000083</x:v>
+      </x:c>
+      <x:c r="B84" s="14" t="str">
+        <x:v>働くおばさん!</x:v>
+      </x:c>
+      <x:c r="C84" s="14" t="str">
+        <x:v>工作的熟女！</x:v>
+      </x:c>
+      <x:c r="D84" s="14" t="str">
+        <x:v>Working Mature Woman!</x:v>
+      </x:c>
+      <x:c r="E84" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="F84" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G84" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1570</x:v>
+      </x:c>
+      <x:c r="H84" s="14" t="str">
+        <x:v>madonna.series:1570</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="14" t="str">
+        <x:v>series_000084</x:v>
+      </x:c>
+      <x:c r="B85" s="14" t="str">
+        <x:v>四十路の性</x:v>
+      </x:c>
+      <x:c r="C85" s="14" t="str">
+        <x:v>四十岁的性</x:v>
+      </x:c>
+      <x:c r="D85" s="14" t="str">
+        <x:v>Sex in the Forties</x:v>
+      </x:c>
+      <x:c r="E85" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="F85" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G85" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1571</x:v>
+      </x:c>
+      <x:c r="H85" s="14" t="str">
+        <x:v>madonna.series:1571</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="14" t="str">
+        <x:v>series_000085</x:v>
+      </x:c>
+      <x:c r="B86" s="14" t="str">
+        <x:v>最高の筆おろし!</x:v>
+      </x:c>
+      <x:c r="C86" s="14" t="str">
+        <x:v>最棒的初体验！</x:v>
+      </x:c>
+      <x:c r="D86" s="14" t="str">
+        <x:v>The Best First Experience!</x:v>
+      </x:c>
+      <x:c r="E86" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="F86" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G86" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1572</x:v>
+      </x:c>
+      <x:c r="H86" s="14" t="str">
+        <x:v>madonna.series:1572</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="14" t="str">
+        <x:v>series_000086</x:v>
+      </x:c>
+      <x:c r="B87" s="14" t="str">
+        <x:v>ハメ狂い淫乱熟女</x:v>
+      </x:c>
+      <x:c r="C87" s="14" t="str">
+        <x:v>疯狂交媾的淫乱熟女</x:v>
+      </x:c>
+      <x:c r="D87" s="14" t="str">
+        <x:v>Sex-Crazed Mature Woman</x:v>
+      </x:c>
+      <x:c r="E87" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="F87" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G87" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1573</x:v>
+      </x:c>
+      <x:c r="H87" s="14" t="str">
+        <x:v>madonna.series:1573</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="14" t="str">
+        <x:v>series_000087</x:v>
+      </x:c>
+      <x:c r="B88" s="14" t="str">
+        <x:v>犯されたセールスレディ</x:v>
+      </x:c>
+      <x:c r="C88" s="14" t="str">
+        <x:v>被侵犯的女销售员</x:v>
+      </x:c>
+      <x:c r="D88" s="14" t="str">
+        <x:v>Violated Saleswoman</x:v>
+      </x:c>
+      <x:c r="E88" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="F88" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G88" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1574</x:v>
+      </x:c>
+      <x:c r="H88" s="14" t="str">
+        <x:v>madonna.series:1574</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="14" t="str">
+        <x:v>series_000088</x:v>
+      </x:c>
+      <x:c r="B89" s="14" t="str">
+        <x:v>娘のカレシにイカされた母</x:v>
+      </x:c>
+      <x:c r="C89" s="14" t="str">
+        <x:v>被女儿男友弄到高潮的母亲</x:v>
+      </x:c>
+      <x:c r="D89" s="14" t="str">
+        <x:v>Mother Brought to Climax by Her Daughter's Boyfriend</x:v>
+      </x:c>
+      <x:c r="E89" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="F89" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G89" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1579</x:v>
+      </x:c>
+      <x:c r="H89" s="14" t="str">
+        <x:v>madonna.series:1579</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="14" t="str">
+        <x:v>series_000089</x:v>
+      </x:c>
+      <x:c r="B90" s="14" t="str">
+        <x:v>昼下がりのふしだら奥さん</x:v>
+      </x:c>
+      <x:c r="C90" s="14" t="str">
+        <x:v>午后的放荡人妻</x:v>
+      </x:c>
+      <x:c r="D90" s="14" t="str">
+        <x:v>Indecent Wife in the Afternoon</x:v>
+      </x:c>
+      <x:c r="E90" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="F90" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G90" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1581</x:v>
+      </x:c>
+      <x:c r="H90" s="14" t="str">
+        <x:v>madonna.series:1581</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="14" t="str">
+        <x:v>series_000090</x:v>
+      </x:c>
+      <x:c r="B91" s="14" t="str">
+        <x:v>豊潤麗し競泳水着</x:v>
+      </x:c>
+      <x:c r="C91" s="14" t="str">
+        <x:v>丰润美丽的竞泳泳装</x:v>
+      </x:c>
+      <x:c r="D91" s="14" t="str">
+        <x:v>Lush Beauty in Competition Swimsuits</x:v>
+      </x:c>
+      <x:c r="E91" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="F91" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G91" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1585</x:v>
+      </x:c>
+      <x:c r="H91" s="14" t="str">
+        <x:v>madonna.series:1585</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="14" t="str">
+        <x:v>series_000091</x:v>
+      </x:c>
+      <x:c r="B92" s="14" t="str">
+        <x:v>悶絶美熟女の卑猥な日常</x:v>
+      </x:c>
+      <x:c r="C92" s="14" t="str">
+        <x:v>悶绝美熟女的淫靡日常</x:v>
+      </x:c>
+      <x:c r="D92" s="14" t="str">
+        <x:v>Obscene Daily Life of a Beautiful Mature Woman</x:v>
+      </x:c>
+      <x:c r="E92" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="F92" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G92" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1586</x:v>
+      </x:c>
+      <x:c r="H92" s="14" t="str">
+        <x:v>madonna.series:1586</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="14" t="str">
+        <x:v>series_000092</x:v>
+      </x:c>
+      <x:c r="B93" s="14" t="str">
+        <x:v>MADAM QUEEN × DANCING FUCK</x:v>
+      </x:c>
+      <x:c r="C93" s="14" t="str">
+        <x:v>MADAM QUEEN × DANCING FUCK</x:v>
+      </x:c>
+      <x:c r="D93" s="14" t="str">
+        <x:v>MADAM QUEEN × DANCING FUCK</x:v>
+      </x:c>
+      <x:c r="E93" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="F93" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G93" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1587</x:v>
+      </x:c>
+      <x:c r="H93" s="14" t="str">
+        <x:v>madonna.series:1587</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="14" t="str">
+        <x:v>series_000093</x:v>
+      </x:c>
+      <x:c r="B94" s="14" t="str">
+        <x:v>濡れ透け婦人の甘い疼き</x:v>
+      </x:c>
+      <x:c r="C94" s="14" t="str">
+        <x:v>湿透夫人的甜蜜悸动</x:v>
+      </x:c>
+      <x:c r="D94" s="14" t="str">
+        <x:v>Sweet Throbbing of a Soaked-Through Lady</x:v>
+      </x:c>
+      <x:c r="E94" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="F94" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G94" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1588</x:v>
+      </x:c>
+      <x:c r="H94" s="14" t="str">
+        <x:v>madonna.series:1588</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="14" t="str">
+        <x:v>series_000094</x:v>
+      </x:c>
+      <x:c r="B95" s="14" t="str">
+        <x:v>溢れだす美熟女の泉</x:v>
+      </x:c>
+      <x:c r="C95" s="14" t="str">
+        <x:v>美熟女涌出的泉水</x:v>
+      </x:c>
+      <x:c r="D95" s="14" t="str">
+        <x:v>Overflowing Fountain of a Beautiful Mature Woman</x:v>
+      </x:c>
+      <x:c r="E95" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="F95" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G95" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1589</x:v>
+      </x:c>
+      <x:c r="H95" s="14" t="str">
+        <x:v>madonna.series:1589</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="14" t="str">
+        <x:v>series_000095</x:v>
+      </x:c>
+      <x:c r="B96" s="14" t="str">
+        <x:v>匂いたつパンストの誘惑</x:v>
+      </x:c>
+      <x:c r="C96" s="14" t="str">
+        <x:v>散发香气的丝袜诱惑</x:v>
+      </x:c>
+      <x:c r="D96" s="14" t="str">
+        <x:v>Temptation of Fragrant Pantyhose</x:v>
+      </x:c>
+      <x:c r="E96" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="F96" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G96" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1590</x:v>
+      </x:c>
+      <x:c r="H96" s="14" t="str">
+        <x:v>madonna.series:1590</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="14" t="str">
+        <x:v>series_000096</x:v>
+      </x:c>
+      <x:c r="B97" s="14" t="str">
+        <x:v>ムッチリ美熟女ハミ出し水着</x:v>
+      </x:c>
+      <x:c r="C97" s="14" t="str">
+        <x:v>丰满美熟女的爆出泳装</x:v>
+      </x:c>
+      <x:c r="D97" s="14" t="str">
+        <x:v>Curvy Mature Beauty in Overflowing Swimwear</x:v>
+      </x:c>
+      <x:c r="E97" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="F97" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G97" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1591</x:v>
+      </x:c>
+      <x:c r="H97" s="14" t="str">
+        <x:v>madonna.series:1591</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="14" t="str">
+        <x:v>series_000097</x:v>
+      </x:c>
+      <x:c r="B98" s="14" t="str">
+        <x:v>巨尻誘惑</x:v>
+      </x:c>
+      <x:c r="C98" s="14" t="str">
+        <x:v>巨臀诱惑</x:v>
+      </x:c>
+      <x:c r="D98" s="14" t="str">
+        <x:v>Big-Bottom Temptation</x:v>
+      </x:c>
+      <x:c r="E98" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="F98" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G98" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1592</x:v>
+      </x:c>
+      <x:c r="H98" s="14" t="str">
+        <x:v>madonna.series:1592</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="14" t="str">
+        <x:v>series_000098</x:v>
+      </x:c>
+      <x:c r="B99" s="14" t="str">
+        <x:v>堕ちた万引き妻</x:v>
+      </x:c>
+      <x:c r="C99" s="14" t="str">
+        <x:v>堕落的偷窃人妻</x:v>
+      </x:c>
+      <x:c r="D99" s="14" t="str">
+        <x:v>Fallen Shoplifting Wife</x:v>
+      </x:c>
+      <x:c r="E99" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="F99" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G99" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1593</x:v>
+      </x:c>
+      <x:c r="H99" s="14" t="str">
+        <x:v>madonna.series:1593</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="14" t="str">
+        <x:v>series_000099</x:v>
+      </x:c>
+      <x:c r="B100" s="14" t="str">
+        <x:v>義母の舌と接吻</x:v>
+      </x:c>
+      <x:c r="C100" s="14" t="str">
+        <x:v>继母的舌与接吻</x:v>
+      </x:c>
+      <x:c r="D100" s="14" t="str">
+        <x:v>Kissing with My Mother-in-Law's Tongue</x:v>
+      </x:c>
+      <x:c r="E100" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="F100" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G100" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1594</x:v>
+      </x:c>
+      <x:c r="H100" s="14" t="str">
+        <x:v>madonna.series:1594</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="14" t="str">
+        <x:v>series_000100</x:v>
+      </x:c>
+      <x:c r="B101" s="14" t="str">
+        <x:v>狙われたパート妻</x:v>
+      </x:c>
+      <x:c r="C101" s="14" t="str">
+        <x:v>被盯上的兼职人妻</x:v>
+      </x:c>
+      <x:c r="D101" s="14" t="str">
+        <x:v>Targeted Part-Time Working Wife</x:v>
+      </x:c>
+      <x:c r="E101" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="F101" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G101" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1595</x:v>
+      </x:c>
+      <x:c r="H101" s="14" t="str">
+        <x:v>madonna.series:1595</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4372,8 +5387,8 @@
     <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="78" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="88" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="80" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="90" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -4472,10 +5487,10 @@
         <x:v>no</x:v>
       </x:c>
       <x:c r="D6" s="14" t="str">
-        <x:v>maker: 1/1, unrecognized=0, complete=yes; label: 17/17, unrecognized=0, complete=yes; series: 33/34, unrecognized=1, complete=no</x:v>
+        <x:v>maker: 1/1, unrecognized=0, complete=yes; label: 17/17, unrecognized=0, complete=yes; series: 52/53, unrecognized=1, complete=no</x:v>
       </x:c>
       <x:c r="E6" s="14" t="str">
-        <x:v>ATTACKERS 两批 partial Series Snapshot 联合发现并审核 34 个 Series：33 个已发布，series/2273 因官方规范名仅为“１”暂时 hold；Snapshot 仍非完整索引遍历。</x:v>
+        <x:v>ATTACKERS 三批 partial Series Snapshot 联合发现并审核 53 个 Series：52 个已发布，series/2273 因官方规范名仅为“１”继续 hold；最新 Snapshot 仍非完整索引遍历。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -4489,10 +5504,10 @@
         <x:v>no</x:v>
       </x:c>
       <x:c r="D7" s="14" t="str">
-        <x:v>maker: 1/1, unrecognized=0, complete=yes; label: 18/18, unrecognized=0, complete=yes; series: 22/22, unrecognized=0, complete=no</x:v>
+        <x:v>maker: 1/1, unrecognized=0, complete=yes; label: 18/18, unrecognized=0, complete=yes; series: 42/42, unrecognized=0, complete=no</x:v>
       </x:c>
       <x:c r="E7" s="14" t="str">
-        <x:v>Madonna 已通过两批 partial Series Snapshot 联合审核并发布 22 个 Series；最新 Snapshot 仍不是完整索引遍历，因此 Series 与来源级 completeTraversal 继续为 false。</x:v>
+        <x:v>Madonna 已通过三批 partial Series Snapshot 联合审核并发布 42 个 Series；最新 Snapshot 仍不是完整索引遍历，因此 Series 与来源级 completeTraversal 继续为 false。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4509,7 +5524,7 @@
     <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="58" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="60" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -5460,16 +6475,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C48" s="14" t="str">
-        <x:v>2293</x:v>
+        <x:v>2287</x:v>
       </x:c>
       <x:c r="D48" s="14" t="str">
-        <x:v>series_000010</x:v>
+        <x:v>series_000062</x:v>
       </x:c>
       <x:c r="E48" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F48" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2293</x:v>
+        <x:v>https://attackers.net/works/list/series/2287</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -5480,16 +6495,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C49" s="14" t="str">
-        <x:v>2325</x:v>
+        <x:v>2288</x:v>
       </x:c>
       <x:c r="D49" s="14" t="str">
-        <x:v>series_000013</x:v>
+        <x:v>series_000063</x:v>
       </x:c>
       <x:c r="E49" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F49" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2325</x:v>
+        <x:v>https://attackers.net/works/list/series/2288</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -5500,16 +6515,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C50" s="14" t="str">
-        <x:v>2402</x:v>
+        <x:v>2290</x:v>
       </x:c>
       <x:c r="D50" s="14" t="str">
-        <x:v>series_000007</x:v>
+        <x:v>series_000064</x:v>
       </x:c>
       <x:c r="E50" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F50" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2402</x:v>
+        <x:v>https://attackers.net/works/list/series/2290</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -5520,441 +6535,441 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C51" s="14" t="str">
-        <x:v>5317</x:v>
+        <x:v>2291</x:v>
       </x:c>
       <x:c r="D51" s="14" t="str">
-        <x:v>series_000014</x:v>
+        <x:v>series_000065</x:v>
       </x:c>
       <x:c r="E51" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F51" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/5317</x:v>
+        <x:v>https://attackers.net/works/list/series/2291</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B52" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C52" s="14" t="str">
-        <x:v>10077</x:v>
+        <x:v>2292</x:v>
       </x:c>
       <x:c r="D52" s="14" t="str">
-        <x:v>label_000076</x:v>
+        <x:v>series_000066</x:v>
       </x:c>
       <x:c r="E52" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F52" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10077</x:v>
+        <x:v>https://attackers.net/works/list/series/2292</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B53" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C53" s="14" t="str">
-        <x:v>10103</x:v>
+        <x:v>2293</x:v>
       </x:c>
       <x:c r="D53" s="14" t="str">
-        <x:v>label_000073</x:v>
+        <x:v>series_000010</x:v>
       </x:c>
       <x:c r="E53" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F53" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10103</x:v>
+        <x:v>https://attackers.net/works/list/series/2293</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B54" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C54" s="14" t="str">
-        <x:v>10142</x:v>
+        <x:v>2295</x:v>
       </x:c>
       <x:c r="D54" s="14" t="str">
-        <x:v>label_000077</x:v>
+        <x:v>series_000067</x:v>
       </x:c>
       <x:c r="E54" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F54" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10142</x:v>
+        <x:v>https://attackers.net/works/list/series/2295</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B55" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C55" s="14" t="str">
-        <x:v>10144</x:v>
+        <x:v>2298</x:v>
       </x:c>
       <x:c r="D55" s="14" t="str">
-        <x:v>label_000080</x:v>
+        <x:v>series_000068</x:v>
       </x:c>
       <x:c r="E55" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F55" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10144</x:v>
+        <x:v>https://attackers.net/works/list/series/2298</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B56" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C56" s="14" t="str">
-        <x:v>10151</x:v>
+        <x:v>2299</x:v>
       </x:c>
       <x:c r="D56" s="14" t="str">
-        <x:v>label_000078</x:v>
+        <x:v>series_000069</x:v>
       </x:c>
       <x:c r="E56" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F56" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10151</x:v>
+        <x:v>https://attackers.net/works/list/series/2299</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B57" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C57" s="14" t="str">
-        <x:v>12442</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="D57" s="14" t="str">
-        <x:v>label_000069</x:v>
+        <x:v>series_000070</x:v>
       </x:c>
       <x:c r="E57" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F57" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/12442</x:v>
+        <x:v>https://attackers.net/works/list/series/2300</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B58" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C58" s="14" t="str">
-        <x:v>12835</x:v>
+        <x:v>2301</x:v>
       </x:c>
       <x:c r="D58" s="14" t="str">
-        <x:v>label_000071</x:v>
+        <x:v>series_000071</x:v>
       </x:c>
       <x:c r="E58" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F58" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/12835</x:v>
+        <x:v>https://attackers.net/works/list/series/2301</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B59" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C59" s="14" t="str">
-        <x:v>2758</x:v>
+        <x:v>2302</x:v>
       </x:c>
       <x:c r="D59" s="14" t="str">
-        <x:v>label_000072</x:v>
+        <x:v>series_000072</x:v>
       </x:c>
       <x:c r="E59" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F59" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2758</x:v>
+        <x:v>https://attackers.net/works/list/series/2302</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B60" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C60" s="14" t="str">
-        <x:v>2760</x:v>
+        <x:v>2303</x:v>
       </x:c>
       <x:c r="D60" s="14" t="str">
-        <x:v>label_000079</x:v>
+        <x:v>series_000073</x:v>
       </x:c>
       <x:c r="E60" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F60" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2760</x:v>
+        <x:v>https://attackers.net/works/list/series/2303</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B61" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C61" s="14" t="str">
-        <x:v>2767</x:v>
+        <x:v>2305</x:v>
       </x:c>
       <x:c r="D61" s="14" t="str">
-        <x:v>label_000070</x:v>
+        <x:v>series_000074</x:v>
       </x:c>
       <x:c r="E61" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F61" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2767</x:v>
+        <x:v>https://attackers.net/works/list/series/2305</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B62" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C62" s="14" t="str">
-        <x:v>2769</x:v>
+        <x:v>2306</x:v>
       </x:c>
       <x:c r="D62" s="14" t="str">
-        <x:v>label_000066</x:v>
+        <x:v>series_000075</x:v>
       </x:c>
       <x:c r="E62" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F62" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2769</x:v>
+        <x:v>https://attackers.net/works/list/series/2306</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B63" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C63" s="14" t="str">
-        <x:v>2771</x:v>
+        <x:v>2307</x:v>
       </x:c>
       <x:c r="D63" s="14" t="str">
-        <x:v>label_000065</x:v>
+        <x:v>series_000076</x:v>
       </x:c>
       <x:c r="E63" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F63" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2771</x:v>
+        <x:v>https://attackers.net/works/list/series/2307</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B64" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C64" s="14" t="str">
-        <x:v>2776</x:v>
+        <x:v>2308</x:v>
       </x:c>
       <x:c r="D64" s="14" t="str">
-        <x:v>label_000068</x:v>
+        <x:v>series_000077</x:v>
       </x:c>
       <x:c r="E64" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F64" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2776</x:v>
+        <x:v>https://attackers.net/works/list/series/2308</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B65" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C65" s="14" t="str">
-        <x:v>85265</x:v>
+        <x:v>2309</x:v>
       </x:c>
       <x:c r="D65" s="14" t="str">
-        <x:v>label_000075</x:v>
+        <x:v>series_000078</x:v>
       </x:c>
       <x:c r="E65" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F65" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/85265</x:v>
+        <x:v>https://attackers.net/works/list/series/2309</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B66" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C66" s="14" t="str">
-        <x:v>9483</x:v>
+        <x:v>2311</x:v>
       </x:c>
       <x:c r="D66" s="14" t="str">
-        <x:v>label_000074</x:v>
+        <x:v>series_000079</x:v>
       </x:c>
       <x:c r="E66" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F66" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/9483</x:v>
+        <x:v>https://attackers.net/works/list/series/2311</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="14" t="str">
-        <x:v>ideapocket.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B67" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C67" s="14" t="str">
-        <x:v>9790</x:v>
+        <x:v>2312</x:v>
       </x:c>
       <x:c r="D67" s="14" t="str">
-        <x:v>label_000067</x:v>
+        <x:v>series_000080</x:v>
       </x:c>
       <x:c r="E67" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F67" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/9790</x:v>
+        <x:v>https://attackers.net/works/list/series/2312</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="14" t="str">
-        <x:v>ideapocket.series</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B68" s="14" t="str">
         <x:v>series</x:v>
       </x:c>
       <x:c r="C68" s="14" t="str">
-        <x:v>1011</x:v>
+        <x:v>2325</x:v>
       </x:c>
       <x:c r="D68" s="14" t="str">
-        <x:v>series_000004</x:v>
+        <x:v>series_000013</x:v>
       </x:c>
       <x:c r="E68" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F68" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/series/1011</x:v>
+        <x:v>https://attackers.net/works/list/series/2325</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="14" t="str">
-        <x:v>ideapocket.series</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B69" s="14" t="str">
         <x:v>series</x:v>
       </x:c>
       <x:c r="C69" s="14" t="str">
-        <x:v>863</x:v>
+        <x:v>2402</x:v>
       </x:c>
       <x:c r="D69" s="14" t="str">
-        <x:v>series_000003</x:v>
+        <x:v>series_000007</x:v>
       </x:c>
       <x:c r="E69" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F69" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/series/863</x:v>
+        <x:v>https://attackers.net/works/list/series/2402</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="B70" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C70" s="14" t="str">
-        <x:v>10077</x:v>
+        <x:v>5317</x:v>
       </x:c>
       <x:c r="D70" s="14" t="str">
-        <x:v>label_000035</x:v>
+        <x:v>series_000014</x:v>
       </x:c>
       <x:c r="E70" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F70" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10077</x:v>
+        <x:v>https://attackers.net/works/list/series/5317</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B71" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C71" s="14" t="str">
-        <x:v>10119</x:v>
+        <x:v>10077</x:v>
       </x:c>
       <x:c r="D71" s="14" t="str">
-        <x:v>label_000031</x:v>
+        <x:v>label_000076</x:v>
       </x:c>
       <x:c r="E71" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F71" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10119</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10077</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B72" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C72" s="14" t="str">
-        <x:v>10130</x:v>
+        <x:v>10103</x:v>
       </x:c>
       <x:c r="D72" s="14" t="str">
-        <x:v>label_000028</x:v>
+        <x:v>label_000073</x:v>
       </x:c>
       <x:c r="E72" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F72" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10130</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10103</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B73" s="14" t="str">
         <x:v>label</x:v>
@@ -5963,673 +6978,673 @@
         <x:v>10142</x:v>
       </x:c>
       <x:c r="D73" s="14" t="str">
-        <x:v>label_000034</x:v>
+        <x:v>label_000077</x:v>
       </x:c>
       <x:c r="E73" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F73" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10142</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10142</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B74" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C74" s="14" t="str">
-        <x:v>10151</x:v>
+        <x:v>10144</x:v>
       </x:c>
       <x:c r="D74" s="14" t="str">
-        <x:v>label_000036</x:v>
+        <x:v>label_000080</x:v>
       </x:c>
       <x:c r="E74" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F74" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10151</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10144</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B75" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C75" s="14" t="str">
-        <x:v>10159</x:v>
+        <x:v>10151</x:v>
       </x:c>
       <x:c r="D75" s="14" t="str">
-        <x:v>label_000030</x:v>
+        <x:v>label_000078</x:v>
       </x:c>
       <x:c r="E75" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F75" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10159</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10151</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B76" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C76" s="14" t="str">
-        <x:v>12490</x:v>
+        <x:v>12442</x:v>
       </x:c>
       <x:c r="D76" s="14" t="str">
-        <x:v>label_000021</x:v>
+        <x:v>label_000069</x:v>
       </x:c>
       <x:c r="E76" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F76" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/12490</x:v>
+        <x:v>https://ideapocket.com/works/list/label/12442</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B77" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C77" s="14" t="str">
-        <x:v>12502</x:v>
+        <x:v>12835</x:v>
       </x:c>
       <x:c r="D77" s="14" t="str">
-        <x:v>label_000027</x:v>
+        <x:v>label_000071</x:v>
       </x:c>
       <x:c r="E77" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F77" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/12502</x:v>
+        <x:v>https://ideapocket.com/works/list/label/12835</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B78" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C78" s="14" t="str">
-        <x:v>12603</x:v>
+        <x:v>2758</x:v>
       </x:c>
       <x:c r="D78" s="14" t="str">
-        <x:v>label_000026</x:v>
+        <x:v>label_000072</x:v>
       </x:c>
       <x:c r="E78" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F78" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/12603</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2758</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B79" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C79" s="14" t="str">
-        <x:v>3125</x:v>
+        <x:v>2760</x:v>
       </x:c>
       <x:c r="D79" s="14" t="str">
-        <x:v>label_000037</x:v>
+        <x:v>label_000079</x:v>
       </x:c>
       <x:c r="E79" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F79" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/3125</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2760</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B80" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C80" s="14" t="str">
-        <x:v>3669</x:v>
+        <x:v>2767</x:v>
       </x:c>
       <x:c r="D80" s="14" t="str">
-        <x:v>label_000020</x:v>
+        <x:v>label_000070</x:v>
       </x:c>
       <x:c r="E80" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F80" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/3669</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2767</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B81" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C81" s="14" t="str">
-        <x:v>7354</x:v>
+        <x:v>2769</x:v>
       </x:c>
       <x:c r="D81" s="14" t="str">
-        <x:v>label_000024</x:v>
+        <x:v>label_000066</x:v>
       </x:c>
       <x:c r="E81" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F81" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/7354</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2769</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B82" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C82" s="14" t="str">
-        <x:v>7993</x:v>
+        <x:v>2771</x:v>
       </x:c>
       <x:c r="D82" s="14" t="str">
-        <x:v>label_000029</x:v>
+        <x:v>label_000065</x:v>
       </x:c>
       <x:c r="E82" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F82" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/7993</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2771</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B83" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C83" s="14" t="str">
-        <x:v>85265</x:v>
+        <x:v>2776</x:v>
       </x:c>
       <x:c r="D83" s="14" t="str">
-        <x:v>label_000032</x:v>
+        <x:v>label_000068</x:v>
       </x:c>
       <x:c r="E83" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F83" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/85265</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2776</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B84" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C84" s="14" t="str">
-        <x:v>9387</x:v>
+        <x:v>85265</x:v>
       </x:c>
       <x:c r="D84" s="14" t="str">
-        <x:v>label_000022</x:v>
+        <x:v>label_000075</x:v>
       </x:c>
       <x:c r="E84" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F84" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/9387</x:v>
+        <x:v>https://ideapocket.com/works/list/label/85265</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B85" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C85" s="14" t="str">
-        <x:v>9419</x:v>
+        <x:v>9483</x:v>
       </x:c>
       <x:c r="D85" s="14" t="str">
-        <x:v>label_000025</x:v>
+        <x:v>label_000074</x:v>
       </x:c>
       <x:c r="E85" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F85" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/9419</x:v>
+        <x:v>https://ideapocket.com/works/list/label/9483</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.label</x:v>
       </x:c>
       <x:c r="B86" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C86" s="14" t="str">
-        <x:v>9483</x:v>
+        <x:v>9790</x:v>
       </x:c>
       <x:c r="D86" s="14" t="str">
-        <x:v>label_000033</x:v>
+        <x:v>label_000067</x:v>
       </x:c>
       <x:c r="E86" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F86" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/9483</x:v>
+        <x:v>https://ideapocket.com/works/list/label/9790</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.series</x:v>
       </x:c>
       <x:c r="B87" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C87" s="14" t="str">
-        <x:v>9789</x:v>
+        <x:v>1011</x:v>
       </x:c>
       <x:c r="D87" s="14" t="str">
-        <x:v>label_000023</x:v>
+        <x:v>series_000004</x:v>
       </x:c>
       <x:c r="E87" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F87" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/9789</x:v>
+        <x:v>https://ideapocket.com/works/list/series/1011</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>ideapocket.series</x:v>
       </x:c>
       <x:c r="B88" s="14" t="str">
         <x:v>series</x:v>
       </x:c>
       <x:c r="C88" s="14" t="str">
-        <x:v>1546</x:v>
+        <x:v>863</x:v>
       </x:c>
       <x:c r="D88" s="14" t="str">
-        <x:v>series_000053</x:v>
+        <x:v>series_000003</x:v>
       </x:c>
       <x:c r="E88" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F88" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1546</x:v>
+        <x:v>https://ideapocket.com/works/list/series/863</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B89" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C89" s="14" t="str">
-        <x:v>1547</x:v>
+        <x:v>10077</x:v>
       </x:c>
       <x:c r="D89" s="14" t="str">
-        <x:v>series_000054</x:v>
+        <x:v>label_000035</x:v>
       </x:c>
       <x:c r="E89" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F89" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1547</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10077</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B90" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C90" s="14" t="str">
-        <x:v>1548</x:v>
+        <x:v>10119</x:v>
       </x:c>
       <x:c r="D90" s="14" t="str">
-        <x:v>series_000055</x:v>
+        <x:v>label_000031</x:v>
       </x:c>
       <x:c r="E90" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F90" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1548</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10119</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B91" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C91" s="14" t="str">
-        <x:v>1549</x:v>
+        <x:v>10130</x:v>
       </x:c>
       <x:c r="D91" s="14" t="str">
-        <x:v>series_000027</x:v>
+        <x:v>label_000028</x:v>
       </x:c>
       <x:c r="E91" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F91" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1549</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10130</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B92" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C92" s="14" t="str">
-        <x:v>1550</x:v>
+        <x:v>10142</x:v>
       </x:c>
       <x:c r="D92" s="14" t="str">
-        <x:v>series_000028</x:v>
+        <x:v>label_000034</x:v>
       </x:c>
       <x:c r="E92" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F92" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1550</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10142</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B93" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C93" s="14" t="str">
-        <x:v>1551</x:v>
+        <x:v>10151</x:v>
       </x:c>
       <x:c r="D93" s="14" t="str">
-        <x:v>series_000029</x:v>
+        <x:v>label_000036</x:v>
       </x:c>
       <x:c r="E93" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F93" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1551</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10151</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B94" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C94" s="14" t="str">
-        <x:v>1552</x:v>
+        <x:v>10159</x:v>
       </x:c>
       <x:c r="D94" s="14" t="str">
-        <x:v>series_000030</x:v>
+        <x:v>label_000030</x:v>
       </x:c>
       <x:c r="E94" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F94" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1552</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10159</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B95" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C95" s="14" t="str">
-        <x:v>1553</x:v>
+        <x:v>12490</x:v>
       </x:c>
       <x:c r="D95" s="14" t="str">
-        <x:v>series_000031</x:v>
+        <x:v>label_000021</x:v>
       </x:c>
       <x:c r="E95" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F95" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1553</x:v>
+        <x:v>https://madonna-av.com/works/list/label/12490</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B96" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C96" s="14" t="str">
-        <x:v>1554</x:v>
+        <x:v>12502</x:v>
       </x:c>
       <x:c r="D96" s="14" t="str">
-        <x:v>series_000032</x:v>
+        <x:v>label_000027</x:v>
       </x:c>
       <x:c r="E96" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F96" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1554</x:v>
+        <x:v>https://madonna-av.com/works/list/label/12502</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B97" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C97" s="14" t="str">
-        <x:v>1555</x:v>
+        <x:v>12603</x:v>
       </x:c>
       <x:c r="D97" s="14" t="str">
-        <x:v>series_000033</x:v>
+        <x:v>label_000026</x:v>
       </x:c>
       <x:c r="E97" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F97" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1555</x:v>
+        <x:v>https://madonna-av.com/works/list/label/12603</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B98" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C98" s="14" t="str">
-        <x:v>1556</x:v>
+        <x:v>3125</x:v>
       </x:c>
       <x:c r="D98" s="14" t="str">
-        <x:v>series_000034</x:v>
+        <x:v>label_000037</x:v>
       </x:c>
       <x:c r="E98" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F98" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1556</x:v>
+        <x:v>https://madonna-av.com/works/list/label/3125</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B99" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C99" s="14" t="str">
-        <x:v>1557</x:v>
+        <x:v>3669</x:v>
       </x:c>
       <x:c r="D99" s="14" t="str">
-        <x:v>series_000035</x:v>
+        <x:v>label_000020</x:v>
       </x:c>
       <x:c r="E99" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F99" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1557</x:v>
+        <x:v>https://madonna-av.com/works/list/label/3669</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B100" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C100" s="14" t="str">
-        <x:v>1558</x:v>
+        <x:v>7354</x:v>
       </x:c>
       <x:c r="D100" s="14" t="str">
-        <x:v>series_000036</x:v>
+        <x:v>label_000024</x:v>
       </x:c>
       <x:c r="E100" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F100" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1558</x:v>
+        <x:v>https://madonna-av.com/works/list/label/7354</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B101" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C101" s="14" t="str">
-        <x:v>1559</x:v>
+        <x:v>7993</x:v>
       </x:c>
       <x:c r="D101" s="14" t="str">
-        <x:v>series_000056</x:v>
+        <x:v>label_000029</x:v>
       </x:c>
       <x:c r="E101" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F101" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1559</x:v>
+        <x:v>https://madonna-av.com/works/list/label/7993</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B102" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C102" s="14" t="str">
-        <x:v>1560</x:v>
+        <x:v>85265</x:v>
       </x:c>
       <x:c r="D102" s="14" t="str">
-        <x:v>series_000057</x:v>
+        <x:v>label_000032</x:v>
       </x:c>
       <x:c r="E102" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F102" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1560</x:v>
+        <x:v>https://madonna-av.com/works/list/label/85265</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B103" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C103" s="14" t="str">
-        <x:v>1561</x:v>
+        <x:v>9387</x:v>
       </x:c>
       <x:c r="D103" s="14" t="str">
-        <x:v>series_000058</x:v>
+        <x:v>label_000022</x:v>
       </x:c>
       <x:c r="E103" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F103" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1561</x:v>
+        <x:v>https://madonna-av.com/works/list/label/9387</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B104" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C104" s="14" t="str">
-        <x:v>1562</x:v>
+        <x:v>9419</x:v>
       </x:c>
       <x:c r="D104" s="14" t="str">
-        <x:v>series_000059</x:v>
+        <x:v>label_000025</x:v>
       </x:c>
       <x:c r="E104" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F104" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1562</x:v>
+        <x:v>https://madonna-av.com/works/list/label/9419</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B105" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C105" s="14" t="str">
-        <x:v>1563</x:v>
+        <x:v>9483</x:v>
       </x:c>
       <x:c r="D105" s="14" t="str">
-        <x:v>series_000060</x:v>
+        <x:v>label_000033</x:v>
       </x:c>
       <x:c r="E105" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F105" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1563</x:v>
+        <x:v>https://madonna-av.com/works/list/label/9483</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B106" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C106" s="14" t="str">
-        <x:v>1564</x:v>
+        <x:v>9789</x:v>
       </x:c>
       <x:c r="D106" s="14" t="str">
-        <x:v>series_000061</x:v>
+        <x:v>label_000023</x:v>
       </x:c>
       <x:c r="E106" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F106" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1564</x:v>
+        <x:v>https://madonna-av.com/works/list/label/9789</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -6640,16 +7655,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C107" s="14" t="str">
-        <x:v>1749</x:v>
+        <x:v>1546</x:v>
       </x:c>
       <x:c r="D107" s="14" t="str">
-        <x:v>series_000017</x:v>
+        <x:v>series_000053</x:v>
       </x:c>
       <x:c r="E107" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F107" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1749</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1546</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -6660,16 +7675,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C108" s="14" t="str">
-        <x:v>1846</x:v>
+        <x:v>1547</x:v>
       </x:c>
       <x:c r="D108" s="14" t="str">
-        <x:v>series_000015</x:v>
+        <x:v>series_000054</x:v>
       </x:c>
       <x:c r="E108" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F108" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1846</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1547</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -6680,695 +7695,1475 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C109" s="14" t="str">
-        <x:v>1891</x:v>
+        <x:v>1548</x:v>
       </x:c>
       <x:c r="D109" s="14" t="str">
-        <x:v>series_000016</x:v>
+        <x:v>series_000055</x:v>
       </x:c>
       <x:c r="E109" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F109" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1891</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1548</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B110" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C110" s="14" t="str">
-        <x:v>10077</x:v>
+        <x:v>1549</x:v>
       </x:c>
       <x:c r="D110" s="14" t="str">
-        <x:v>label_000063</x:v>
+        <x:v>series_000027</x:v>
       </x:c>
       <x:c r="E110" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F110" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10077</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1549</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B111" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C111" s="14" t="str">
-        <x:v>10106</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D111" s="14" t="str">
-        <x:v>label_000053</x:v>
+        <x:v>series_000028</x:v>
       </x:c>
       <x:c r="E111" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F111" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10106</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1550</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B112" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C112" s="14" t="str">
-        <x:v>10107</x:v>
+        <x:v>1551</x:v>
       </x:c>
       <x:c r="D112" s="14" t="str">
-        <x:v>label_000046</x:v>
+        <x:v>series_000029</x:v>
       </x:c>
       <x:c r="E112" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F112" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10107</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1551</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B113" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C113" s="14" t="str">
-        <x:v>10131</x:v>
+        <x:v>1552</x:v>
       </x:c>
       <x:c r="D113" s="14" t="str">
-        <x:v>label_000047</x:v>
+        <x:v>series_000030</x:v>
       </x:c>
       <x:c r="E113" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F113" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10131</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1552</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B114" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C114" s="14" t="str">
-        <x:v>10142</x:v>
+        <x:v>1553</x:v>
       </x:c>
       <x:c r="D114" s="14" t="str">
-        <x:v>label_000060</x:v>
+        <x:v>series_000031</x:v>
       </x:c>
       <x:c r="E114" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F114" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10142</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1553</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B115" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C115" s="14" t="str">
-        <x:v>10144</x:v>
+        <x:v>1554</x:v>
       </x:c>
       <x:c r="D115" s="14" t="str">
-        <x:v>label_000061</x:v>
+        <x:v>series_000032</x:v>
       </x:c>
       <x:c r="E115" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F115" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10144</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1554</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B116" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C116" s="14" t="str">
-        <x:v>10151</x:v>
+        <x:v>1555</x:v>
       </x:c>
       <x:c r="D116" s="14" t="str">
-        <x:v>label_000062</x:v>
+        <x:v>series_000033</x:v>
       </x:c>
       <x:c r="E116" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F116" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10151</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1555</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B117" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C117" s="14" t="str">
-        <x:v>10157</x:v>
+        <x:v>1556</x:v>
       </x:c>
       <x:c r="D117" s="14" t="str">
-        <x:v>label_000058</x:v>
+        <x:v>series_000034</x:v>
       </x:c>
       <x:c r="E117" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F117" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10157</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1556</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B118" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C118" s="14" t="str">
-        <x:v>10172</x:v>
+        <x:v>1557</x:v>
       </x:c>
       <x:c r="D118" s="14" t="str">
-        <x:v>label_000064</x:v>
+        <x:v>series_000035</x:v>
       </x:c>
       <x:c r="E118" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F118" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10172</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1557</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B119" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C119" s="14" t="str">
-        <x:v>10174</x:v>
+        <x:v>1558</x:v>
       </x:c>
       <x:c r="D119" s="14" t="str">
-        <x:v>label_000050</x:v>
+        <x:v>series_000036</x:v>
       </x:c>
       <x:c r="E119" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F119" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10174</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1558</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B120" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C120" s="14" t="str">
-        <x:v>11471</x:v>
+        <x:v>1559</x:v>
       </x:c>
       <x:c r="D120" s="14" t="str">
-        <x:v>label_000057</x:v>
+        <x:v>series_000056</x:v>
       </x:c>
       <x:c r="E120" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F120" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/11471</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1559</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B121" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C121" s="14" t="str">
-        <x:v>12798</x:v>
+        <x:v>1560</x:v>
       </x:c>
       <x:c r="D121" s="14" t="str">
-        <x:v>label_000002</x:v>
+        <x:v>series_000057</x:v>
       </x:c>
       <x:c r="E121" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F121" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/12798</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1560</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B122" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C122" s="14" t="str">
-        <x:v>5046</x:v>
+        <x:v>1561</x:v>
       </x:c>
       <x:c r="D122" s="14" t="str">
-        <x:v>label_000039</x:v>
+        <x:v>series_000058</x:v>
       </x:c>
       <x:c r="E122" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F122" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5046</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1561</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B123" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C123" s="14" t="str">
-        <x:v>5047</x:v>
+        <x:v>1562</x:v>
       </x:c>
       <x:c r="D123" s="14" t="str">
-        <x:v>label_000038</x:v>
+        <x:v>series_000059</x:v>
       </x:c>
       <x:c r="E123" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F123" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5047</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1562</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B124" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C124" s="14" t="str">
-        <x:v>5048</x:v>
+        <x:v>1563</x:v>
       </x:c>
       <x:c r="D124" s="14" t="str">
-        <x:v>label_000001</x:v>
+        <x:v>series_000060</x:v>
       </x:c>
       <x:c r="E124" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F124" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5048</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1563</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B125" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C125" s="14" t="str">
-        <x:v>5049</x:v>
+        <x:v>1564</x:v>
       </x:c>
       <x:c r="D125" s="14" t="str">
-        <x:v>label_000045</x:v>
+        <x:v>series_000061</x:v>
       </x:c>
       <x:c r="E125" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F125" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5049</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1564</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B126" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C126" s="14" t="str">
-        <x:v>5090</x:v>
+        <x:v>1565</x:v>
       </x:c>
       <x:c r="D126" s="14" t="str">
-        <x:v>label_000044</x:v>
+        <x:v>series_000081</x:v>
       </x:c>
       <x:c r="E126" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F126" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5090</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1565</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B127" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C127" s="14" t="str">
-        <x:v>5409</x:v>
+        <x:v>1566</x:v>
       </x:c>
       <x:c r="D127" s="14" t="str">
-        <x:v>label_000049</x:v>
+        <x:v>series_000082</x:v>
       </x:c>
       <x:c r="E127" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F127" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5409</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1566</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B128" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C128" s="14" t="str">
-        <x:v>6879</x:v>
+        <x:v>1570</x:v>
       </x:c>
       <x:c r="D128" s="14" t="str">
-        <x:v>label_000040</x:v>
+        <x:v>series_000083</x:v>
       </x:c>
       <x:c r="E128" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F128" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/6879</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1570</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B129" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C129" s="14" t="str">
-        <x:v>85265</x:v>
+        <x:v>1571</x:v>
       </x:c>
       <x:c r="D129" s="14" t="str">
-        <x:v>label_000056</x:v>
+        <x:v>series_000084</x:v>
       </x:c>
       <x:c r="E129" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F129" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/85265</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1571</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B130" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C130" s="14" t="str">
-        <x:v>8916</x:v>
+        <x:v>1572</x:v>
       </x:c>
       <x:c r="D130" s="14" t="str">
-        <x:v>label_000051</x:v>
+        <x:v>series_000085</x:v>
       </x:c>
       <x:c r="E130" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F130" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/8916</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1572</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B131" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C131" s="14" t="str">
-        <x:v>8917</x:v>
+        <x:v>1573</x:v>
       </x:c>
       <x:c r="D131" s="14" t="str">
-        <x:v>label_000055</x:v>
+        <x:v>series_000086</x:v>
       </x:c>
       <x:c r="E131" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F131" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/8917</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1573</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B132" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C132" s="14" t="str">
-        <x:v>9288</x:v>
+        <x:v>1574</x:v>
       </x:c>
       <x:c r="D132" s="14" t="str">
-        <x:v>label_000054</x:v>
+        <x:v>series_000087</x:v>
       </x:c>
       <x:c r="E132" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F132" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9288</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1574</x:v>
       </x:c>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B133" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C133" s="14" t="str">
-        <x:v>9308</x:v>
+        <x:v>1579</x:v>
       </x:c>
       <x:c r="D133" s="14" t="str">
-        <x:v>label_000043</x:v>
+        <x:v>series_000088</x:v>
       </x:c>
       <x:c r="E133" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F133" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9308</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1579</x:v>
       </x:c>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B134" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C134" s="14" t="str">
-        <x:v>9397</x:v>
+        <x:v>1581</x:v>
       </x:c>
       <x:c r="D134" s="14" t="str">
-        <x:v>label_000052</x:v>
+        <x:v>series_000089</x:v>
       </x:c>
       <x:c r="E134" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F134" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9397</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1581</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B135" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C135" s="14" t="str">
-        <x:v>9458</x:v>
+        <x:v>1585</x:v>
       </x:c>
       <x:c r="D135" s="14" t="str">
-        <x:v>label_000048</x:v>
+        <x:v>series_000090</x:v>
       </x:c>
       <x:c r="E135" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F135" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9458</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1585</x:v>
       </x:c>
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B136" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C136" s="14" t="str">
-        <x:v>9483</x:v>
+        <x:v>1586</x:v>
       </x:c>
       <x:c r="D136" s="14" t="str">
-        <x:v>label_000059</x:v>
+        <x:v>series_000091</x:v>
       </x:c>
       <x:c r="E136" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F136" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9483</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1586</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B137" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C137" s="14" t="str">
-        <x:v>9732</x:v>
+        <x:v>1587</x:v>
       </x:c>
       <x:c r="D137" s="14" t="str">
-        <x:v>label_000042</x:v>
+        <x:v>series_000092</x:v>
       </x:c>
       <x:c r="E137" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F137" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9732</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1587</x:v>
       </x:c>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B138" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C138" s="14" t="str">
-        <x:v>9782</x:v>
+        <x:v>1588</x:v>
       </x:c>
       <x:c r="D138" s="14" t="str">
-        <x:v>label_000041</x:v>
+        <x:v>series_000093</x:v>
       </x:c>
       <x:c r="E138" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F138" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9782</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1588</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="14" t="str">
-        <x:v>moodyz.series</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B139" s="14" t="str">
         <x:v>series</x:v>
       </x:c>
       <x:c r="C139" s="14" t="str">
-        <x:v>5427</x:v>
+        <x:v>1589</x:v>
       </x:c>
       <x:c r="D139" s="14" t="str">
-        <x:v>series_000002</x:v>
+        <x:v>series_000094</x:v>
       </x:c>
       <x:c r="E139" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F139" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/series/5427</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1589</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="14" t="str">
-        <x:v>s1.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B140" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C140" s="14" t="str">
-        <x:v>4355</x:v>
+        <x:v>1590</x:v>
       </x:c>
       <x:c r="D140" s="14" t="str">
-        <x:v>label_000081</x:v>
+        <x:v>series_000095</x:v>
       </x:c>
       <x:c r="E140" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F140" s="14" t="str">
-        <x:v>https://s1s1s1.com/works/list/label/4355</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1590</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="14" t="str">
-        <x:v>s1.series</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B141" s="14" t="str">
         <x:v>series</x:v>
       </x:c>
       <x:c r="C141" s="14" t="str">
-        <x:v>414</x:v>
+        <x:v>1591</x:v>
       </x:c>
       <x:c r="D141" s="14" t="str">
-        <x:v>series_000001</x:v>
+        <x:v>series_000096</x:v>
       </x:c>
       <x:c r="E141" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F141" s="14" t="str">
-        <x:v>https://s1s1s1.com/works/list/series/414</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1591</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="14" t="str">
-        <x:v>s1.series</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B142" s="14" t="str">
         <x:v>series</x:v>
       </x:c>
       <x:c r="C142" s="14" t="str">
-        <x:v>422</x:v>
+        <x:v>1592</x:v>
       </x:c>
       <x:c r="D142" s="14" t="str">
-        <x:v>series_000005</x:v>
+        <x:v>series_000097</x:v>
       </x:c>
       <x:c r="E142" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F142" s="14" t="str">
-        <x:v>https://s1s1s1.com/works/list/series/422</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1592</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="14" t="str">
-        <x:v>s1.series</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B143" s="14" t="str">
         <x:v>series</x:v>
       </x:c>
       <x:c r="C143" s="14" t="str">
+        <x:v>1593</x:v>
+      </x:c>
+      <x:c r="D143" s="14" t="str">
+        <x:v>series_000098</x:v>
+      </x:c>
+      <x:c r="E143" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F143" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1593</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="B144" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C144" s="14" t="str">
+        <x:v>1594</x:v>
+      </x:c>
+      <x:c r="D144" s="14" t="str">
+        <x:v>series_000099</x:v>
+      </x:c>
+      <x:c r="E144" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F144" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1594</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="B145" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C145" s="14" t="str">
+        <x:v>1595</x:v>
+      </x:c>
+      <x:c r="D145" s="14" t="str">
+        <x:v>series_000100</x:v>
+      </x:c>
+      <x:c r="E145" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F145" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1595</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="B146" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C146" s="14" t="str">
+        <x:v>1749</x:v>
+      </x:c>
+      <x:c r="D146" s="14" t="str">
+        <x:v>series_000017</x:v>
+      </x:c>
+      <x:c r="E146" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F146" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1749</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="B147" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C147" s="14" t="str">
+        <x:v>1846</x:v>
+      </x:c>
+      <x:c r="D147" s="14" t="str">
+        <x:v>series_000015</x:v>
+      </x:c>
+      <x:c r="E147" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F147" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1846</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="B148" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C148" s="14" t="str">
+        <x:v>1891</x:v>
+      </x:c>
+      <x:c r="D148" s="14" t="str">
+        <x:v>series_000016</x:v>
+      </x:c>
+      <x:c r="E148" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F148" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1891</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B149" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C149" s="14" t="str">
+        <x:v>10077</x:v>
+      </x:c>
+      <x:c r="D149" s="14" t="str">
+        <x:v>label_000063</x:v>
+      </x:c>
+      <x:c r="E149" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F149" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10077</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B150" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C150" s="14" t="str">
+        <x:v>10106</x:v>
+      </x:c>
+      <x:c r="D150" s="14" t="str">
+        <x:v>label_000053</x:v>
+      </x:c>
+      <x:c r="E150" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F150" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B151" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C151" s="14" t="str">
+        <x:v>10107</x:v>
+      </x:c>
+      <x:c r="D151" s="14" t="str">
+        <x:v>label_000046</x:v>
+      </x:c>
+      <x:c r="E151" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F151" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B152" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C152" s="14" t="str">
+        <x:v>10131</x:v>
+      </x:c>
+      <x:c r="D152" s="14" t="str">
+        <x:v>label_000047</x:v>
+      </x:c>
+      <x:c r="E152" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F152" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B153" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C153" s="14" t="str">
+        <x:v>10142</x:v>
+      </x:c>
+      <x:c r="D153" s="14" t="str">
+        <x:v>label_000060</x:v>
+      </x:c>
+      <x:c r="E153" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F153" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B154" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C154" s="14" t="str">
+        <x:v>10144</x:v>
+      </x:c>
+      <x:c r="D154" s="14" t="str">
+        <x:v>label_000061</x:v>
+      </x:c>
+      <x:c r="E154" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F154" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B155" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C155" s="14" t="str">
+        <x:v>10151</x:v>
+      </x:c>
+      <x:c r="D155" s="14" t="str">
+        <x:v>label_000062</x:v>
+      </x:c>
+      <x:c r="E155" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F155" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B156" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C156" s="14" t="str">
+        <x:v>10157</x:v>
+      </x:c>
+      <x:c r="D156" s="14" t="str">
+        <x:v>label_000058</x:v>
+      </x:c>
+      <x:c r="E156" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F156" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B157" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C157" s="14" t="str">
+        <x:v>10172</x:v>
+      </x:c>
+      <x:c r="D157" s="14" t="str">
+        <x:v>label_000064</x:v>
+      </x:c>
+      <x:c r="E157" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F157" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B158" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C158" s="14" t="str">
+        <x:v>10174</x:v>
+      </x:c>
+      <x:c r="D158" s="14" t="str">
+        <x:v>label_000050</x:v>
+      </x:c>
+      <x:c r="E158" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F158" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/10174</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B159" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C159" s="14" t="str">
+        <x:v>11471</x:v>
+      </x:c>
+      <x:c r="D159" s="14" t="str">
+        <x:v>label_000057</x:v>
+      </x:c>
+      <x:c r="E159" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F159" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/11471</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B160" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C160" s="14" t="str">
+        <x:v>12798</x:v>
+      </x:c>
+      <x:c r="D160" s="14" t="str">
+        <x:v>label_000002</x:v>
+      </x:c>
+      <x:c r="E160" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F160" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/12798</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B161" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C161" s="14" t="str">
+        <x:v>5046</x:v>
+      </x:c>
+      <x:c r="D161" s="14" t="str">
+        <x:v>label_000039</x:v>
+      </x:c>
+      <x:c r="E161" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F161" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5046</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B162" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C162" s="14" t="str">
+        <x:v>5047</x:v>
+      </x:c>
+      <x:c r="D162" s="14" t="str">
+        <x:v>label_000038</x:v>
+      </x:c>
+      <x:c r="E162" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F162" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5047</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B163" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C163" s="14" t="str">
+        <x:v>5048</x:v>
+      </x:c>
+      <x:c r="D163" s="14" t="str">
+        <x:v>label_000001</x:v>
+      </x:c>
+      <x:c r="E163" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F163" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5048</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B164" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C164" s="14" t="str">
+        <x:v>5049</x:v>
+      </x:c>
+      <x:c r="D164" s="14" t="str">
+        <x:v>label_000045</x:v>
+      </x:c>
+      <x:c r="E164" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F164" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5049</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B165" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C165" s="14" t="str">
+        <x:v>5090</x:v>
+      </x:c>
+      <x:c r="D165" s="14" t="str">
+        <x:v>label_000044</x:v>
+      </x:c>
+      <x:c r="E165" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F165" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5090</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B166" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C166" s="14" t="str">
+        <x:v>5409</x:v>
+      </x:c>
+      <x:c r="D166" s="14" t="str">
+        <x:v>label_000049</x:v>
+      </x:c>
+      <x:c r="E166" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F166" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/5409</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B167" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C167" s="14" t="str">
+        <x:v>6879</x:v>
+      </x:c>
+      <x:c r="D167" s="14" t="str">
+        <x:v>label_000040</x:v>
+      </x:c>
+      <x:c r="E167" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F167" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/6879</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B168" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C168" s="14" t="str">
+        <x:v>85265</x:v>
+      </x:c>
+      <x:c r="D168" s="14" t="str">
+        <x:v>label_000056</x:v>
+      </x:c>
+      <x:c r="E168" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F168" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/85265</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B169" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C169" s="14" t="str">
+        <x:v>8916</x:v>
+      </x:c>
+      <x:c r="D169" s="14" t="str">
+        <x:v>label_000051</x:v>
+      </x:c>
+      <x:c r="E169" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F169" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/8916</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B170" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C170" s="14" t="str">
+        <x:v>8917</x:v>
+      </x:c>
+      <x:c r="D170" s="14" t="str">
+        <x:v>label_000055</x:v>
+      </x:c>
+      <x:c r="E170" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F170" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/8917</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B171" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C171" s="14" t="str">
+        <x:v>9288</x:v>
+      </x:c>
+      <x:c r="D171" s="14" t="str">
+        <x:v>label_000054</x:v>
+      </x:c>
+      <x:c r="E171" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F171" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9288</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B172" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C172" s="14" t="str">
+        <x:v>9308</x:v>
+      </x:c>
+      <x:c r="D172" s="14" t="str">
+        <x:v>label_000043</x:v>
+      </x:c>
+      <x:c r="E172" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F172" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9308</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B173" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C173" s="14" t="str">
+        <x:v>9397</x:v>
+      </x:c>
+      <x:c r="D173" s="14" t="str">
+        <x:v>label_000052</x:v>
+      </x:c>
+      <x:c r="E173" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F173" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9397</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B174" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C174" s="14" t="str">
+        <x:v>9458</x:v>
+      </x:c>
+      <x:c r="D174" s="14" t="str">
+        <x:v>label_000048</x:v>
+      </x:c>
+      <x:c r="E174" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F174" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9458</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B175" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C175" s="14" t="str">
+        <x:v>9483</x:v>
+      </x:c>
+      <x:c r="D175" s="14" t="str">
+        <x:v>label_000059</x:v>
+      </x:c>
+      <x:c r="E175" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F175" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9483</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B176" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C176" s="14" t="str">
+        <x:v>9732</x:v>
+      </x:c>
+      <x:c r="D176" s="14" t="str">
+        <x:v>label_000042</x:v>
+      </x:c>
+      <x:c r="E176" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F176" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9732</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" s="14" t="str">
+        <x:v>moodyz.label</x:v>
+      </x:c>
+      <x:c r="B177" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C177" s="14" t="str">
+        <x:v>9782</x:v>
+      </x:c>
+      <x:c r="D177" s="14" t="str">
+        <x:v>label_000041</x:v>
+      </x:c>
+      <x:c r="E177" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F177" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/label/9782</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" s="14" t="str">
+        <x:v>moodyz.series</x:v>
+      </x:c>
+      <x:c r="B178" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C178" s="14" t="str">
+        <x:v>5427</x:v>
+      </x:c>
+      <x:c r="D178" s="14" t="str">
+        <x:v>series_000002</x:v>
+      </x:c>
+      <x:c r="E178" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F178" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/5427</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" s="14" t="str">
+        <x:v>s1.label</x:v>
+      </x:c>
+      <x:c r="B179" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C179" s="14" t="str">
+        <x:v>4355</x:v>
+      </x:c>
+      <x:c r="D179" s="14" t="str">
+        <x:v>label_000081</x:v>
+      </x:c>
+      <x:c r="E179" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F179" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/label/4355</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="B180" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C180" s="14" t="str">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="D180" s="14" t="str">
+        <x:v>series_000001</x:v>
+      </x:c>
+      <x:c r="E180" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F180" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/414</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="B181" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C181" s="14" t="str">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="D181" s="14" t="str">
+        <x:v>series_000005</x:v>
+      </x:c>
+      <x:c r="E181" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F181" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/422</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="B182" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C182" s="14" t="str">
         <x:v>570</x:v>
       </x:c>
-      <x:c r="D143" s="14" t="str">
+      <x:c r="D182" s="14" t="str">
         <x:v>series_000006</x:v>
       </x:c>
-      <x:c r="E143" s="14" t="str">
-        <x:v>approved</x:v>
-      </x:c>
-      <x:c r="F143" s="14" t="str">
+      <x:c r="E182" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F182" s="14" t="str">
         <x:v>https://s1s1s1.com/works/list/series/570</x:v>
       </x:c>
     </x:row>
@@ -7388,8 +9183,8 @@
     <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="58" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="76" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="60" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="78" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -8178,28 +9973,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B28" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C28" s="14" t="str">
-        <x:v>1546</x:v>
+        <x:v>2287</x:v>
       </x:c>
       <x:c r="D28" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+        <x:v>attackers-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E28" s="14" t="str">
-        <x:v>series_000053</x:v>
+        <x:v>series_000062</x:v>
       </x:c>
       <x:c r="F28" s="14" t="str">
-        <x:v>もう一つの熟バス</x:v>
+        <x:v>不埒な姦係</x:v>
       </x:c>
       <x:c r="G28" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000004</x:v>
       </x:c>
       <x:c r="H28" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1546</x:v>
+        <x:v>https://attackers.net/works/list/series/2287</x:v>
       </x:c>
       <x:c r="I28" s="14" t="str">
-        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -8207,28 +10002,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B29" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C29" s="14" t="str">
-        <x:v>1547</x:v>
+        <x:v>2288</x:v>
       </x:c>
       <x:c r="D29" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+        <x:v>attackers-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E29" s="14" t="str">
-        <x:v>series_000054</x:v>
+        <x:v>series_000063</x:v>
       </x:c>
       <x:c r="F29" s="14" t="str">
-        <x:v>母さんとしたい!</x:v>
+        <x:v>あなたが欲しくて</x:v>
       </x:c>
       <x:c r="G29" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000004</x:v>
       </x:c>
       <x:c r="H29" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1547</x:v>
+        <x:v>https://attackers.net/works/list/series/2288</x:v>
       </x:c>
       <x:c r="I29" s="14" t="str">
-        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -8236,28 +10031,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B30" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C30" s="14" t="str">
-        <x:v>1548</x:v>
+        <x:v>2290</x:v>
       </x:c>
       <x:c r="D30" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+        <x:v>attackers-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E30" s="14" t="str">
-        <x:v>series_000055</x:v>
+        <x:v>series_000064</x:v>
       </x:c>
       <x:c r="F30" s="14" t="str">
-        <x:v>義父に犯されて・・・ 美嫁いぢり</x:v>
+        <x:v>背徳の契り</x:v>
       </x:c>
       <x:c r="G30" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000004</x:v>
       </x:c>
       <x:c r="H30" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1548</x:v>
+        <x:v>https://attackers.net/works/list/series/2290</x:v>
       </x:c>
       <x:c r="I30" s="14" t="str">
-        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -8265,28 +10060,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B31" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C31" s="14" t="str">
-        <x:v>1549</x:v>
+        <x:v>2291</x:v>
       </x:c>
       <x:c r="D31" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+        <x:v>attackers-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E31" s="14" t="str">
-        <x:v>series_000027</x:v>
+        <x:v>series_000065</x:v>
       </x:c>
       <x:c r="F31" s="14" t="str">
-        <x:v>となりの奥さん</x:v>
+        <x:v>鬱勃起</x:v>
       </x:c>
       <x:c r="G31" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000004</x:v>
       </x:c>
       <x:c r="H31" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1549</x:v>
+        <x:v>https://attackers.net/works/list/series/2291</x:v>
       </x:c>
       <x:c r="I31" s="14" t="str">
-        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -8294,28 +10089,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B32" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C32" s="14" t="str">
-        <x:v>1550</x:v>
+        <x:v>2292</x:v>
       </x:c>
       <x:c r="D32" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+        <x:v>attackers-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E32" s="14" t="str">
-        <x:v>series_000028</x:v>
+        <x:v>series_000066</x:v>
       </x:c>
       <x:c r="F32" s="14" t="str">
-        <x:v>美熟女と黒人</x:v>
+        <x:v>抱かれるための出社</x:v>
       </x:c>
       <x:c r="G32" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000004</x:v>
       </x:c>
       <x:c r="H32" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1550</x:v>
+        <x:v>https://attackers.net/works/list/series/2292</x:v>
       </x:c>
       <x:c r="I32" s="14" t="str">
-        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -8323,28 +10118,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B33" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C33" s="14" t="str">
-        <x:v>1551</x:v>
+        <x:v>2295</x:v>
       </x:c>
       <x:c r="D33" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+        <x:v>attackers-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E33" s="14" t="str">
-        <x:v>series_000029</x:v>
+        <x:v>series_000067</x:v>
       </x:c>
       <x:c r="F33" s="14" t="str">
-        <x:v>愛する夫の目の前で・・・</x:v>
+        <x:v>舐め犯し</x:v>
       </x:c>
       <x:c r="G33" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000004</x:v>
       </x:c>
       <x:c r="H33" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1551</x:v>
+        <x:v>https://attackers.net/works/list/series/2295</x:v>
       </x:c>
       <x:c r="I33" s="14" t="str">
-        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -8352,28 +10147,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B34" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C34" s="14" t="str">
-        <x:v>1552</x:v>
+        <x:v>2298</x:v>
       </x:c>
       <x:c r="D34" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+        <x:v>attackers-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E34" s="14" t="str">
-        <x:v>series_000030</x:v>
+        <x:v>series_000068</x:v>
       </x:c>
       <x:c r="F34" s="14" t="str">
-        <x:v>特選 友達の母</x:v>
+        <x:v>素人強姦面接</x:v>
       </x:c>
       <x:c r="G34" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000004</x:v>
       </x:c>
       <x:c r="H34" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1552</x:v>
+        <x:v>https://attackers.net/works/list/series/2298</x:v>
       </x:c>
       <x:c r="I34" s="14" t="str">
-        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -8381,28 +10176,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B35" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C35" s="14" t="str">
-        <x:v>1553</x:v>
+        <x:v>2299</x:v>
       </x:c>
       <x:c r="D35" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+        <x:v>attackers-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E35" s="14" t="str">
-        <x:v>series_000031</x:v>
+        <x:v>series_000069</x:v>
       </x:c>
       <x:c r="F35" s="14" t="str">
-        <x:v>僕のおばさん</x:v>
+        <x:v>死夜悪アンソロジー</x:v>
       </x:c>
       <x:c r="G35" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000004</x:v>
       </x:c>
       <x:c r="H35" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1553</x:v>
+        <x:v>https://attackers.net/works/list/series/2299</x:v>
       </x:c>
       <x:c r="I35" s="14" t="str">
-        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -8410,28 +10205,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B36" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C36" s="14" t="str">
-        <x:v>1554</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="D36" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+        <x:v>attackers-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E36" s="14" t="str">
-        <x:v>series_000032</x:v>
+        <x:v>series_000070</x:v>
       </x:c>
       <x:c r="F36" s="14" t="str">
-        <x:v>素人人妻ナンパ総集編4時間</x:v>
+        <x:v>蛇縛の拷問折檻</x:v>
       </x:c>
       <x:c r="G36" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000004</x:v>
       </x:c>
       <x:c r="H36" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1554</x:v>
+        <x:v>https://attackers.net/works/list/series/2300</x:v>
       </x:c>
       <x:c r="I36" s="14" t="str">
-        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -8439,28 +10234,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B37" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C37" s="14" t="str">
-        <x:v>1555</x:v>
+        <x:v>2301</x:v>
       </x:c>
       <x:c r="D37" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+        <x:v>attackers-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E37" s="14" t="str">
-        <x:v>series_000033</x:v>
+        <x:v>series_000071</x:v>
       </x:c>
       <x:c r="F37" s="14" t="str">
-        <x:v>五十路熟女18人4時間</x:v>
+        <x:v>BEST</x:v>
       </x:c>
       <x:c r="G37" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000004</x:v>
       </x:c>
       <x:c r="H37" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1555</x:v>
+        <x:v>https://attackers.net/works/list/series/2301</x:v>
       </x:c>
       <x:c r="I37" s="14" t="str">
-        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -8468,28 +10263,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B38" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C38" s="14" t="str">
-        <x:v>1556</x:v>
+        <x:v>2302</x:v>
       </x:c>
       <x:c r="D38" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+        <x:v>attackers-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E38" s="14" t="str">
-        <x:v>series_000034</x:v>
+        <x:v>series_000072</x:v>
       </x:c>
       <x:c r="F38" s="14" t="str">
-        <x:v>団地妻20人4時間</x:v>
+        <x:v>凌辱大捜査線</x:v>
       </x:c>
       <x:c r="G38" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000004</x:v>
       </x:c>
       <x:c r="H38" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1556</x:v>
+        <x:v>https://attackers.net/works/list/series/2302</x:v>
       </x:c>
       <x:c r="I38" s="14" t="str">
-        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -8497,28 +10292,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B39" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C39" s="14" t="str">
-        <x:v>1557</x:v>
+        <x:v>2303</x:v>
       </x:c>
       <x:c r="D39" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+        <x:v>attackers-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E39" s="14" t="str">
-        <x:v>series_000035</x:v>
+        <x:v>series_000073</x:v>
       </x:c>
       <x:c r="F39" s="14" t="str">
-        <x:v>犯された熟女たち総集編4時間</x:v>
+        <x:v>これで最後にしてください。</x:v>
       </x:c>
       <x:c r="G39" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000004</x:v>
       </x:c>
       <x:c r="H39" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1557</x:v>
+        <x:v>https://attackers.net/works/list/series/2303</x:v>
       </x:c>
       <x:c r="I39" s="14" t="str">
-        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -8526,28 +10321,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B40" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C40" s="14" t="str">
-        <x:v>1558</x:v>
+        <x:v>2305</x:v>
       </x:c>
       <x:c r="D40" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+        <x:v>attackers-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E40" s="14" t="str">
-        <x:v>series_000036</x:v>
+        <x:v>series_000074</x:v>
       </x:c>
       <x:c r="F40" s="14" t="str">
-        <x:v>妖艶おんな愛戯</x:v>
+        <x:v>女優名鑑</x:v>
       </x:c>
       <x:c r="G40" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000004</x:v>
       </x:c>
       <x:c r="H40" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1558</x:v>
+        <x:v>https://attackers.net/works/list/series/2305</x:v>
       </x:c>
       <x:c r="I40" s="14" t="str">
-        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -8555,28 +10350,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B41" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C41" s="14" t="str">
-        <x:v>1559</x:v>
+        <x:v>2306</x:v>
       </x:c>
       <x:c r="D41" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+        <x:v>attackers-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E41" s="14" t="str">
-        <x:v>series_000056</x:v>
+        <x:v>series_000075</x:v>
       </x:c>
       <x:c r="F41" s="14" t="str">
-        <x:v>五十路の性</x:v>
+        <x:v>遺伝子の悲劇</x:v>
       </x:c>
       <x:c r="G41" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000004</x:v>
       </x:c>
       <x:c r="H41" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1559</x:v>
+        <x:v>https://attackers.net/works/list/series/2306</x:v>
       </x:c>
       <x:c r="I41" s="14" t="str">
-        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -8584,28 +10379,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B42" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C42" s="14" t="str">
-        <x:v>1560</x:v>
+        <x:v>2307</x:v>
       </x:c>
       <x:c r="D42" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+        <x:v>attackers-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E42" s="14" t="str">
-        <x:v>series_000057</x:v>
+        <x:v>series_000076</x:v>
       </x:c>
       <x:c r="F42" s="14" t="str">
-        <x:v>新・素人人妻ナンパ</x:v>
+        <x:v>昭和哀歌</x:v>
       </x:c>
       <x:c r="G42" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000004</x:v>
       </x:c>
       <x:c r="H42" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1560</x:v>
+        <x:v>https://attackers.net/works/list/series/2307</x:v>
       </x:c>
       <x:c r="I42" s="14" t="str">
-        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -8613,28 +10408,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B43" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C43" s="14" t="str">
-        <x:v>1561</x:v>
+        <x:v>2308</x:v>
       </x:c>
       <x:c r="D43" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+        <x:v>attackers-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E43" s="14" t="str">
-        <x:v>series_000058</x:v>
+        <x:v>series_000077</x:v>
       </x:c>
       <x:c r="F43" s="14" t="str">
-        <x:v>こちらマドンナ独身寮・ただいま満室</x:v>
+        <x:v>声を出せない私</x:v>
       </x:c>
       <x:c r="G43" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000004</x:v>
       </x:c>
       <x:c r="H43" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1561</x:v>
+        <x:v>https://attackers.net/works/list/series/2308</x:v>
       </x:c>
       <x:c r="I43" s="14" t="str">
-        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -8642,28 +10437,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B44" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C44" s="14" t="str">
-        <x:v>1562</x:v>
+        <x:v>2309</x:v>
       </x:c>
       <x:c r="D44" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+        <x:v>attackers-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E44" s="14" t="str">
-        <x:v>series_000059</x:v>
+        <x:v>series_000078</x:v>
       </x:c>
       <x:c r="F44" s="14" t="str">
-        <x:v>3D作品</x:v>
+        <x:v>極道の女</x:v>
       </x:c>
       <x:c r="G44" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000004</x:v>
       </x:c>
       <x:c r="H44" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1562</x:v>
+        <x:v>https://attackers.net/works/list/series/2309</x:v>
       </x:c>
       <x:c r="I44" s="14" t="str">
-        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -8671,28 +10466,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B45" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C45" s="14" t="str">
-        <x:v>1563</x:v>
+        <x:v>2311</x:v>
       </x:c>
       <x:c r="D45" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+        <x:v>attackers-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E45" s="14" t="str">
-        <x:v>series_000060</x:v>
+        <x:v>series_000079</x:v>
       </x:c>
       <x:c r="F45" s="14" t="str">
-        <x:v>密着セックス</x:v>
+        <x:v>くノ一拷問凌辱</x:v>
       </x:c>
       <x:c r="G45" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000004</x:v>
       </x:c>
       <x:c r="H45" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1563</x:v>
+        <x:v>https://attackers.net/works/list/series/2311</x:v>
       </x:c>
       <x:c r="I45" s="14" t="str">
-        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -8700,28 +10495,1159 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B46" s="14" t="str">
+        <x:v>attackers.series</x:v>
+      </x:c>
+      <x:c r="C46" s="14" t="str">
+        <x:v>2312</x:v>
+      </x:c>
+      <x:c r="D46" s="14" t="str">
+        <x:v>attackers-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E46" s="14" t="str">
+        <x:v>series_000080</x:v>
+      </x:c>
+      <x:c r="F46" s="14" t="str">
+        <x:v>奴隷色のステージ</x:v>
+      </x:c>
+      <x:c r="G46" s="14" t="str">
+        <x:v>maker_000004</x:v>
+      </x:c>
+      <x:c r="H46" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2312</x:v>
+      </x:c>
+      <x:c r="I46" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B47" s="14" t="str">
         <x:v>madonna.series</x:v>
       </x:c>
-      <x:c r="C46" s="14" t="str">
+      <x:c r="C47" s="14" t="str">
+        <x:v>1546</x:v>
+      </x:c>
+      <x:c r="D47" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+      </x:c>
+      <x:c r="E47" s="14" t="str">
+        <x:v>series_000053</x:v>
+      </x:c>
+      <x:c r="F47" s="14" t="str">
+        <x:v>もう一つの熟バス</x:v>
+      </x:c>
+      <x:c r="G47" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H47" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1546</x:v>
+      </x:c>
+      <x:c r="I47" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B48" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C48" s="14" t="str">
+        <x:v>1547</x:v>
+      </x:c>
+      <x:c r="D48" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+      </x:c>
+      <x:c r="E48" s="14" t="str">
+        <x:v>series_000054</x:v>
+      </x:c>
+      <x:c r="F48" s="14" t="str">
+        <x:v>母さんとしたい!</x:v>
+      </x:c>
+      <x:c r="G48" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H48" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1547</x:v>
+      </x:c>
+      <x:c r="I48" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B49" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C49" s="14" t="str">
+        <x:v>1548</x:v>
+      </x:c>
+      <x:c r="D49" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+      </x:c>
+      <x:c r="E49" s="14" t="str">
+        <x:v>series_000055</x:v>
+      </x:c>
+      <x:c r="F49" s="14" t="str">
+        <x:v>義父に犯されて・・・ 美嫁いぢり</x:v>
+      </x:c>
+      <x:c r="G49" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H49" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1548</x:v>
+      </x:c>
+      <x:c r="I49" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B50" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C50" s="14" t="str">
+        <x:v>1549</x:v>
+      </x:c>
+      <x:c r="D50" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E50" s="14" t="str">
+        <x:v>series_000027</x:v>
+      </x:c>
+      <x:c r="F50" s="14" t="str">
+        <x:v>となりの奥さん</x:v>
+      </x:c>
+      <x:c r="G50" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H50" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1549</x:v>
+      </x:c>
+      <x:c r="I50" s="14" t="str">
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B51" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C51" s="14" t="str">
+        <x:v>1550</x:v>
+      </x:c>
+      <x:c r="D51" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E51" s="14" t="str">
+        <x:v>series_000028</x:v>
+      </x:c>
+      <x:c r="F51" s="14" t="str">
+        <x:v>美熟女と黒人</x:v>
+      </x:c>
+      <x:c r="G51" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H51" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1550</x:v>
+      </x:c>
+      <x:c r="I51" s="14" t="str">
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B52" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C52" s="14" t="str">
+        <x:v>1551</x:v>
+      </x:c>
+      <x:c r="D52" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E52" s="14" t="str">
+        <x:v>series_000029</x:v>
+      </x:c>
+      <x:c r="F52" s="14" t="str">
+        <x:v>愛する夫の目の前で・・・</x:v>
+      </x:c>
+      <x:c r="G52" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H52" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1551</x:v>
+      </x:c>
+      <x:c r="I52" s="14" t="str">
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B53" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C53" s="14" t="str">
+        <x:v>1552</x:v>
+      </x:c>
+      <x:c r="D53" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E53" s="14" t="str">
+        <x:v>series_000030</x:v>
+      </x:c>
+      <x:c r="F53" s="14" t="str">
+        <x:v>特選 友達の母</x:v>
+      </x:c>
+      <x:c r="G53" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H53" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1552</x:v>
+      </x:c>
+      <x:c r="I53" s="14" t="str">
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B54" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C54" s="14" t="str">
+        <x:v>1553</x:v>
+      </x:c>
+      <x:c r="D54" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E54" s="14" t="str">
+        <x:v>series_000031</x:v>
+      </x:c>
+      <x:c r="F54" s="14" t="str">
+        <x:v>僕のおばさん</x:v>
+      </x:c>
+      <x:c r="G54" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H54" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1553</x:v>
+      </x:c>
+      <x:c r="I54" s="14" t="str">
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B55" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C55" s="14" t="str">
+        <x:v>1554</x:v>
+      </x:c>
+      <x:c r="D55" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E55" s="14" t="str">
+        <x:v>series_000032</x:v>
+      </x:c>
+      <x:c r="F55" s="14" t="str">
+        <x:v>素人人妻ナンパ総集編4時間</x:v>
+      </x:c>
+      <x:c r="G55" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H55" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1554</x:v>
+      </x:c>
+      <x:c r="I55" s="14" t="str">
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B56" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C56" s="14" t="str">
+        <x:v>1555</x:v>
+      </x:c>
+      <x:c r="D56" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E56" s="14" t="str">
+        <x:v>series_000033</x:v>
+      </x:c>
+      <x:c r="F56" s="14" t="str">
+        <x:v>五十路熟女18人4時間</x:v>
+      </x:c>
+      <x:c r="G56" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H56" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1555</x:v>
+      </x:c>
+      <x:c r="I56" s="14" t="str">
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B57" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C57" s="14" t="str">
+        <x:v>1556</x:v>
+      </x:c>
+      <x:c r="D57" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E57" s="14" t="str">
+        <x:v>series_000034</x:v>
+      </x:c>
+      <x:c r="F57" s="14" t="str">
+        <x:v>団地妻20人4時間</x:v>
+      </x:c>
+      <x:c r="G57" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H57" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1556</x:v>
+      </x:c>
+      <x:c r="I57" s="14" t="str">
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B58" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C58" s="14" t="str">
+        <x:v>1557</x:v>
+      </x:c>
+      <x:c r="D58" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E58" s="14" t="str">
+        <x:v>series_000035</x:v>
+      </x:c>
+      <x:c r="F58" s="14" t="str">
+        <x:v>犯された熟女たち総集編4時間</x:v>
+      </x:c>
+      <x:c r="G58" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H58" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1557</x:v>
+      </x:c>
+      <x:c r="I58" s="14" t="str">
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B59" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C59" s="14" t="str">
+        <x:v>1558</x:v>
+      </x:c>
+      <x:c r="D59" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E59" s="14" t="str">
+        <x:v>series_000036</x:v>
+      </x:c>
+      <x:c r="F59" s="14" t="str">
+        <x:v>妖艶おんな愛戯</x:v>
+      </x:c>
+      <x:c r="G59" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H59" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1558</x:v>
+      </x:c>
+      <x:c r="I59" s="14" t="str">
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B60" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C60" s="14" t="str">
+        <x:v>1559</x:v>
+      </x:c>
+      <x:c r="D60" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+      </x:c>
+      <x:c r="E60" s="14" t="str">
+        <x:v>series_000056</x:v>
+      </x:c>
+      <x:c r="F60" s="14" t="str">
+        <x:v>五十路の性</x:v>
+      </x:c>
+      <x:c r="G60" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H60" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1559</x:v>
+      </x:c>
+      <x:c r="I60" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B61" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C61" s="14" t="str">
+        <x:v>1560</x:v>
+      </x:c>
+      <x:c r="D61" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+      </x:c>
+      <x:c r="E61" s="14" t="str">
+        <x:v>series_000057</x:v>
+      </x:c>
+      <x:c r="F61" s="14" t="str">
+        <x:v>新・素人人妻ナンパ</x:v>
+      </x:c>
+      <x:c r="G61" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H61" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1560</x:v>
+      </x:c>
+      <x:c r="I61" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B62" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C62" s="14" t="str">
+        <x:v>1561</x:v>
+      </x:c>
+      <x:c r="D62" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+      </x:c>
+      <x:c r="E62" s="14" t="str">
+        <x:v>series_000058</x:v>
+      </x:c>
+      <x:c r="F62" s="14" t="str">
+        <x:v>こちらマドンナ独身寮・ただいま満室</x:v>
+      </x:c>
+      <x:c r="G62" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H62" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1561</x:v>
+      </x:c>
+      <x:c r="I62" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B63" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C63" s="14" t="str">
+        <x:v>1562</x:v>
+      </x:c>
+      <x:c r="D63" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+      </x:c>
+      <x:c r="E63" s="14" t="str">
+        <x:v>series_000059</x:v>
+      </x:c>
+      <x:c r="F63" s="14" t="str">
+        <x:v>3D作品</x:v>
+      </x:c>
+      <x:c r="G63" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H63" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1562</x:v>
+      </x:c>
+      <x:c r="I63" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B64" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C64" s="14" t="str">
+        <x:v>1563</x:v>
+      </x:c>
+      <x:c r="D64" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+      </x:c>
+      <x:c r="E64" s="14" t="str">
+        <x:v>series_000060</x:v>
+      </x:c>
+      <x:c r="F64" s="14" t="str">
+        <x:v>密着セックス</x:v>
+      </x:c>
+      <x:c r="G64" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H64" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1563</x:v>
+      </x:c>
+      <x:c r="I64" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B65" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C65" s="14" t="str">
         <x:v>1564</x:v>
       </x:c>
-      <x:c r="D46" s="14" t="str">
+      <x:c r="D65" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-002</x:v>
       </x:c>
-      <x:c r="E46" s="14" t="str">
+      <x:c r="E65" s="14" t="str">
         <x:v>series_000061</x:v>
       </x:c>
-      <x:c r="F46" s="14" t="str">
+      <x:c r="F65" s="14" t="str">
         <x:v>交換夫婦NTR</x:v>
       </x:c>
-      <x:c r="G46" s="14" t="str">
+      <x:c r="G65" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
-      <x:c r="H46" s="14" t="str">
+      <x:c r="H65" s="14" t="str">
         <x:v>https://madonna-av.com/works/list/series/1564</x:v>
       </x:c>
-      <x:c r="I46" s="14" t="str">
+      <x:c r="I65" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B66" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C66" s="14" t="str">
+        <x:v>1565</x:v>
+      </x:c>
+      <x:c r="D66" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E66" s="14" t="str">
+        <x:v>series_000081</x:v>
+      </x:c>
+      <x:c r="F66" s="14" t="str">
+        <x:v>出張先のビジネスホテルでずっと憧れていた女上司と</x:v>
+      </x:c>
+      <x:c r="G66" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H66" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1565</x:v>
+      </x:c>
+      <x:c r="I66" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B67" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C67" s="14" t="str">
+        <x:v>1566</x:v>
+      </x:c>
+      <x:c r="D67" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E67" s="14" t="str">
+        <x:v>series_000082</x:v>
+      </x:c>
+      <x:c r="F67" s="14" t="str">
+        <x:v>人妻秘書、汗と接吻に満ちた社長室中出し性交</x:v>
+      </x:c>
+      <x:c r="G67" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H67" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1566</x:v>
+      </x:c>
+      <x:c r="I67" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B68" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C68" s="14" t="str">
+        <x:v>1570</x:v>
+      </x:c>
+      <x:c r="D68" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E68" s="14" t="str">
+        <x:v>series_000083</x:v>
+      </x:c>
+      <x:c r="F68" s="14" t="str">
+        <x:v>働くおばさん!</x:v>
+      </x:c>
+      <x:c r="G68" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H68" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1570</x:v>
+      </x:c>
+      <x:c r="I68" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B69" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C69" s="14" t="str">
+        <x:v>1571</x:v>
+      </x:c>
+      <x:c r="D69" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E69" s="14" t="str">
+        <x:v>series_000084</x:v>
+      </x:c>
+      <x:c r="F69" s="14" t="str">
+        <x:v>四十路の性</x:v>
+      </x:c>
+      <x:c r="G69" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H69" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1571</x:v>
+      </x:c>
+      <x:c r="I69" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B70" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C70" s="14" t="str">
+        <x:v>1572</x:v>
+      </x:c>
+      <x:c r="D70" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E70" s="14" t="str">
+        <x:v>series_000085</x:v>
+      </x:c>
+      <x:c r="F70" s="14" t="str">
+        <x:v>最高の筆おろし!</x:v>
+      </x:c>
+      <x:c r="G70" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H70" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1572</x:v>
+      </x:c>
+      <x:c r="I70" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B71" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C71" s="14" t="str">
+        <x:v>1573</x:v>
+      </x:c>
+      <x:c r="D71" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E71" s="14" t="str">
+        <x:v>series_000086</x:v>
+      </x:c>
+      <x:c r="F71" s="14" t="str">
+        <x:v>ハメ狂い淫乱熟女</x:v>
+      </x:c>
+      <x:c r="G71" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H71" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1573</x:v>
+      </x:c>
+      <x:c r="I71" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B72" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C72" s="14" t="str">
+        <x:v>1574</x:v>
+      </x:c>
+      <x:c r="D72" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E72" s="14" t="str">
+        <x:v>series_000087</x:v>
+      </x:c>
+      <x:c r="F72" s="14" t="str">
+        <x:v>犯されたセールスレディ</x:v>
+      </x:c>
+      <x:c r="G72" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H72" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1574</x:v>
+      </x:c>
+      <x:c r="I72" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B73" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C73" s="14" t="str">
+        <x:v>1579</x:v>
+      </x:c>
+      <x:c r="D73" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E73" s="14" t="str">
+        <x:v>series_000088</x:v>
+      </x:c>
+      <x:c r="F73" s="14" t="str">
+        <x:v>娘のカレシにイカされた母</x:v>
+      </x:c>
+      <x:c r="G73" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H73" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1579</x:v>
+      </x:c>
+      <x:c r="I73" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B74" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C74" s="14" t="str">
+        <x:v>1581</x:v>
+      </x:c>
+      <x:c r="D74" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E74" s="14" t="str">
+        <x:v>series_000089</x:v>
+      </x:c>
+      <x:c r="F74" s="14" t="str">
+        <x:v>昼下がりのふしだら奥さん</x:v>
+      </x:c>
+      <x:c r="G74" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H74" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1581</x:v>
+      </x:c>
+      <x:c r="I74" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B75" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C75" s="14" t="str">
+        <x:v>1585</x:v>
+      </x:c>
+      <x:c r="D75" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E75" s="14" t="str">
+        <x:v>series_000090</x:v>
+      </x:c>
+      <x:c r="F75" s="14" t="str">
+        <x:v>豊潤麗し競泳水着</x:v>
+      </x:c>
+      <x:c r="G75" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H75" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1585</x:v>
+      </x:c>
+      <x:c r="I75" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B76" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C76" s="14" t="str">
+        <x:v>1586</x:v>
+      </x:c>
+      <x:c r="D76" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E76" s="14" t="str">
+        <x:v>series_000091</x:v>
+      </x:c>
+      <x:c r="F76" s="14" t="str">
+        <x:v>悶絶美熟女の卑猥な日常</x:v>
+      </x:c>
+      <x:c r="G76" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H76" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1586</x:v>
+      </x:c>
+      <x:c r="I76" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B77" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C77" s="14" t="str">
+        <x:v>1587</x:v>
+      </x:c>
+      <x:c r="D77" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E77" s="14" t="str">
+        <x:v>series_000092</x:v>
+      </x:c>
+      <x:c r="F77" s="14" t="str">
+        <x:v>MADAM QUEEN × DANCING FUCK</x:v>
+      </x:c>
+      <x:c r="G77" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H77" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1587</x:v>
+      </x:c>
+      <x:c r="I77" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B78" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C78" s="14" t="str">
+        <x:v>1588</x:v>
+      </x:c>
+      <x:c r="D78" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E78" s="14" t="str">
+        <x:v>series_000093</x:v>
+      </x:c>
+      <x:c r="F78" s="14" t="str">
+        <x:v>濡れ透け婦人の甘い疼き</x:v>
+      </x:c>
+      <x:c r="G78" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H78" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1588</x:v>
+      </x:c>
+      <x:c r="I78" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B79" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C79" s="14" t="str">
+        <x:v>1589</x:v>
+      </x:c>
+      <x:c r="D79" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E79" s="14" t="str">
+        <x:v>series_000094</x:v>
+      </x:c>
+      <x:c r="F79" s="14" t="str">
+        <x:v>溢れだす美熟女の泉</x:v>
+      </x:c>
+      <x:c r="G79" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H79" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1589</x:v>
+      </x:c>
+      <x:c r="I79" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B80" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C80" s="14" t="str">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="D80" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E80" s="14" t="str">
+        <x:v>series_000095</x:v>
+      </x:c>
+      <x:c r="F80" s="14" t="str">
+        <x:v>匂いたつパンストの誘惑</x:v>
+      </x:c>
+      <x:c r="G80" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H80" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1590</x:v>
+      </x:c>
+      <x:c r="I80" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B81" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C81" s="14" t="str">
+        <x:v>1591</x:v>
+      </x:c>
+      <x:c r="D81" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E81" s="14" t="str">
+        <x:v>series_000096</x:v>
+      </x:c>
+      <x:c r="F81" s="14" t="str">
+        <x:v>ムッチリ美熟女ハミ出し水着</x:v>
+      </x:c>
+      <x:c r="G81" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H81" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1591</x:v>
+      </x:c>
+      <x:c r="I81" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B82" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C82" s="14" t="str">
+        <x:v>1592</x:v>
+      </x:c>
+      <x:c r="D82" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E82" s="14" t="str">
+        <x:v>series_000097</x:v>
+      </x:c>
+      <x:c r="F82" s="14" t="str">
+        <x:v>巨尻誘惑</x:v>
+      </x:c>
+      <x:c r="G82" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H82" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1592</x:v>
+      </x:c>
+      <x:c r="I82" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B83" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C83" s="14" t="str">
+        <x:v>1593</x:v>
+      </x:c>
+      <x:c r="D83" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E83" s="14" t="str">
+        <x:v>series_000098</x:v>
+      </x:c>
+      <x:c r="F83" s="14" t="str">
+        <x:v>堕ちた万引き妻</x:v>
+      </x:c>
+      <x:c r="G83" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H83" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1593</x:v>
+      </x:c>
+      <x:c r="I83" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B84" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C84" s="14" t="str">
+        <x:v>1594</x:v>
+      </x:c>
+      <x:c r="D84" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E84" s="14" t="str">
+        <x:v>series_000099</x:v>
+      </x:c>
+      <x:c r="F84" s="14" t="str">
+        <x:v>義母の舌と接吻</x:v>
+      </x:c>
+      <x:c r="G84" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H84" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1594</x:v>
+      </x:c>
+      <x:c r="I84" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B85" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C85" s="14" t="str">
+        <x:v>1595</x:v>
+      </x:c>
+      <x:c r="D85" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E85" s="14" t="str">
+        <x:v>series_000100</x:v>
+      </x:c>
+      <x:c r="F85" s="14" t="str">
+        <x:v>狙われたパート妻</x:v>
+      </x:c>
+      <x:c r="G85" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H85" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1595</x:v>
+      </x:c>
+      <x:c r="I85" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8739,7 +11665,7 @@
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="58" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="60" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -8765,25 +11691,61 @@
         <x:v>Source URL</x:v>
       </x:c>
     </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="44" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Snapshot ID</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>Entries</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>Complete</x:v>
+      </x:c>
+    </x:row>
     <x:row r="2">
       <x:c r="A2" s="14" t="str">
-        <x:v>candidate-new</x:v>
+        <x:v>attackers-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="B2" s="14" t="str">
-        <x:v>unmapped-official-series-id</x:v>
-      </x:c>
-      <x:c r="C2" s="14" t="str">
         <x:v>attackers.series</x:v>
       </x:c>
+      <x:c r="C2" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
       <x:c r="D2" s="14" t="str">
-        <x:v>2273</x:v>
-      </x:c>
-      <x:c r="E2" s="14" t="str">
-        <x:v>１</x:v>
-      </x:c>
-      <x:c r="F2" s="14" t="str"/>
-      <x:c r="G2" s="14" t="str">
-        <x:v>https://attackers.net/works/list/series/2273</x:v>
+        <x:v>no</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="B3" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C3" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="str">
+        <x:v>no</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/exports/xlsx/organization-series-registry.xlsx
+++ b/exports/xlsx/organization-series-registry.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organizations" sheetId="1" r:id="R2993ec19aeca44c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series" sheetId="2" r:id="R1a7b460c3c5641ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Registry" sheetId="3" r:id="R5c41bb66fc8a4a0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External ID Mapping" sheetId="4" r:id="R0f2ce31f408b4913"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Candidate Reviews" sheetId="5" r:id="R849e654077724a7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Index Candidates" sheetId="6" r:id="R840c7420a3fe48e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Latest Snapshots" sheetId="7" r:id="R4326c1f830b6475d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organizations" sheetId="1" r:id="Rbfe9a01710b340db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series" sheetId="2" r:id="R9383bcfb1dd44e51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Index Providers" sheetId="3" r:id="R40ffd3400bbc4c3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Registry" sheetId="4" r:id="R63decdd6ea384e36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External ID Mapping" sheetId="5" r:id="Rd43854066e46482d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Candidate Reviews" sheetId="6" r:id="Rd8410ce0836c4b09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Latest Snapshots" sheetId="7" r:id="Rd2c4b8b37b1d4b42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Index Candidates" sheetId="8" r:id="Re9d45c7e0dec4cd2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2747,6 +2748,7 @@
     <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="56" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -2774,6 +2776,9 @@
       <x:c r="H1" s="6" t="str">
         <x:v>External IDs</x:v>
       </x:c>
+      <x:c r="I1" s="6" t="str">
+        <x:v>First Published</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="14" t="str">
@@ -2800,6 +2805,9 @@
       <x:c r="H2" s="14" t="str">
         <x:v>s1.series:414</x:v>
       </x:c>
+      <x:c r="I2" s="14" t="str">
+        <x:v>0.4.0</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="14" t="str">
@@ -2826,6 +2834,9 @@
       <x:c r="H3" s="14" t="str">
         <x:v>moodyz.series:5427</x:v>
       </x:c>
+      <x:c r="I3" s="14" t="str">
+        <x:v>0.4.0</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="14" t="str">
@@ -2852,6 +2863,9 @@
       <x:c r="H4" s="14" t="str">
         <x:v>ideapocket.series:863</x:v>
       </x:c>
+      <x:c r="I4" s="14" t="str">
+        <x:v>0.4.0</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14" t="str">
@@ -2878,6 +2892,9 @@
       <x:c r="H5" s="14" t="str">
         <x:v>ideapocket.series:1011</x:v>
       </x:c>
+      <x:c r="I5" s="14" t="str">
+        <x:v>0.4.0</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="14" t="str">
@@ -2904,6 +2921,9 @@
       <x:c r="H6" s="14" t="str">
         <x:v>s1.series:422</x:v>
       </x:c>
+      <x:c r="I6" s="14" t="str">
+        <x:v>0.4.3</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="14" t="str">
@@ -2930,6 +2950,9 @@
       <x:c r="H7" s="14" t="str">
         <x:v>s1.series:570</x:v>
       </x:c>
+      <x:c r="I7" s="14" t="str">
+        <x:v>0.4.3</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="14" t="str">
@@ -2956,6 +2979,9 @@
       <x:c r="H8" s="14" t="str">
         <x:v>attackers.series:2402</x:v>
       </x:c>
+      <x:c r="I8" s="14" t="str">
+        <x:v>0.4.3</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="14" t="str">
@@ -2982,6 +3008,9 @@
       <x:c r="H9" s="14" t="str">
         <x:v>attackers.series:2269</x:v>
       </x:c>
+      <x:c r="I9" s="14" t="str">
+        <x:v>0.4.3</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="14" t="str">
@@ -3008,6 +3037,9 @@
       <x:c r="H10" s="14" t="str">
         <x:v>attackers.series:2270</x:v>
       </x:c>
+      <x:c r="I10" s="14" t="str">
+        <x:v>0.4.3</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="14" t="str">
@@ -3034,6 +3066,9 @@
       <x:c r="H11" s="14" t="str">
         <x:v>attackers.series:2293</x:v>
       </x:c>
+      <x:c r="I11" s="14" t="str">
+        <x:v>0.4.3</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="14" t="str">
@@ -3060,6 +3095,9 @@
       <x:c r="H12" s="14" t="str">
         <x:v>attackers.series:2256</x:v>
       </x:c>
+      <x:c r="I12" s="14" t="str">
+        <x:v>0.4.3</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="14" t="str">
@@ -3086,6 +3124,9 @@
       <x:c r="H13" s="14" t="str">
         <x:v>attackers.series:2274</x:v>
       </x:c>
+      <x:c r="I13" s="14" t="str">
+        <x:v>0.4.3</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="14" t="str">
@@ -3112,6 +3153,9 @@
       <x:c r="H14" s="14" t="str">
         <x:v>attackers.series:2325</x:v>
       </x:c>
+      <x:c r="I14" s="14" t="str">
+        <x:v>0.4.3</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="14" t="str">
@@ -3138,6 +3182,9 @@
       <x:c r="H15" s="14" t="str">
         <x:v>attackers.series:5317</x:v>
       </x:c>
+      <x:c r="I15" s="14" t="str">
+        <x:v>0.4.3</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="14" t="str">
@@ -3164,6 +3211,9 @@
       <x:c r="H16" s="14" t="str">
         <x:v>madonna.series:1846</x:v>
       </x:c>
+      <x:c r="I16" s="14" t="str">
+        <x:v>0.4.3</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="14" t="str">
@@ -3190,6 +3240,9 @@
       <x:c r="H17" s="14" t="str">
         <x:v>madonna.series:1891</x:v>
       </x:c>
+      <x:c r="I17" s="14" t="str">
+        <x:v>0.4.3</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="14" t="str">
@@ -3216,6 +3269,9 @@
       <x:c r="H18" s="14" t="str">
         <x:v>madonna.series:1749</x:v>
       </x:c>
+      <x:c r="I18" s="14" t="str">
+        <x:v>0.4.3</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="14" t="str">
@@ -3242,6 +3298,9 @@
       <x:c r="H19" s="14" t="str">
         <x:v>attackers.series:2253</x:v>
       </x:c>
+      <x:c r="I19" s="14" t="str">
+        <x:v>0.4.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="14" t="str">
@@ -3268,6 +3327,9 @@
       <x:c r="H20" s="14" t="str">
         <x:v>attackers.series:2254</x:v>
       </x:c>
+      <x:c r="I20" s="14" t="str">
+        <x:v>0.4.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="14" t="str">
@@ -3294,6 +3356,9 @@
       <x:c r="H21" s="14" t="str">
         <x:v>attackers.series:2255</x:v>
       </x:c>
+      <x:c r="I21" s="14" t="str">
+        <x:v>0.4.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="14" t="str">
@@ -3320,6 +3385,9 @@
       <x:c r="H22" s="14" t="str">
         <x:v>attackers.series:2257</x:v>
       </x:c>
+      <x:c r="I22" s="14" t="str">
+        <x:v>0.4.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="14" t="str">
@@ -3346,6 +3414,9 @@
       <x:c r="H23" s="14" t="str">
         <x:v>attackers.series:2258</x:v>
       </x:c>
+      <x:c r="I23" s="14" t="str">
+        <x:v>0.4.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="14" t="str">
@@ -3372,6 +3443,9 @@
       <x:c r="H24" s="14" t="str">
         <x:v>attackers.series:2259</x:v>
       </x:c>
+      <x:c r="I24" s="14" t="str">
+        <x:v>0.4.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="14" t="str">
@@ -3398,6 +3472,9 @@
       <x:c r="H25" s="14" t="str">
         <x:v>attackers.series:2260</x:v>
       </x:c>
+      <x:c r="I25" s="14" t="str">
+        <x:v>0.4.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="14" t="str">
@@ -3424,6 +3501,9 @@
       <x:c r="H26" s="14" t="str">
         <x:v>attackers.series:2261</x:v>
       </x:c>
+      <x:c r="I26" s="14" t="str">
+        <x:v>0.4.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="14" t="str">
@@ -3450,6 +3530,9 @@
       <x:c r="H27" s="14" t="str">
         <x:v>attackers.series:2263</x:v>
       </x:c>
+      <x:c r="I27" s="14" t="str">
+        <x:v>0.4.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="14" t="str">
@@ -3476,6 +3559,9 @@
       <x:c r="H28" s="14" t="str">
         <x:v>madonna.series:1549</x:v>
       </x:c>
+      <x:c r="I28" s="14" t="str">
+        <x:v>0.4.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="14" t="str">
@@ -3502,6 +3588,9 @@
       <x:c r="H29" s="14" t="str">
         <x:v>madonna.series:1550</x:v>
       </x:c>
+      <x:c r="I29" s="14" t="str">
+        <x:v>0.4.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="14" t="str">
@@ -3528,6 +3617,9 @@
       <x:c r="H30" s="14" t="str">
         <x:v>madonna.series:1551</x:v>
       </x:c>
+      <x:c r="I30" s="14" t="str">
+        <x:v>0.4.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="14" t="str">
@@ -3554,6 +3646,9 @@
       <x:c r="H31" s="14" t="str">
         <x:v>madonna.series:1552</x:v>
       </x:c>
+      <x:c r="I31" s="14" t="str">
+        <x:v>0.4.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="14" t="str">
@@ -3580,6 +3675,9 @@
       <x:c r="H32" s="14" t="str">
         <x:v>madonna.series:1553</x:v>
       </x:c>
+      <x:c r="I32" s="14" t="str">
+        <x:v>0.4.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="14" t="str">
@@ -3606,6 +3704,9 @@
       <x:c r="H33" s="14" t="str">
         <x:v>madonna.series:1554</x:v>
       </x:c>
+      <x:c r="I33" s="14" t="str">
+        <x:v>0.4.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="14" t="str">
@@ -3632,6 +3733,9 @@
       <x:c r="H34" s="14" t="str">
         <x:v>madonna.series:1555</x:v>
       </x:c>
+      <x:c r="I34" s="14" t="str">
+        <x:v>0.4.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="14" t="str">
@@ -3658,6 +3762,9 @@
       <x:c r="H35" s="14" t="str">
         <x:v>madonna.series:1556</x:v>
       </x:c>
+      <x:c r="I35" s="14" t="str">
+        <x:v>0.4.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="14" t="str">
@@ -3684,6 +3791,9 @@
       <x:c r="H36" s="14" t="str">
         <x:v>madonna.series:1557</x:v>
       </x:c>
+      <x:c r="I36" s="14" t="str">
+        <x:v>0.4.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="14" t="str">
@@ -3710,6 +3820,9 @@
       <x:c r="H37" s="14" t="str">
         <x:v>madonna.series:1558</x:v>
       </x:c>
+      <x:c r="I37" s="14" t="str">
+        <x:v>0.4.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="14" t="str">
@@ -3736,6 +3849,9 @@
       <x:c r="H38" s="14" t="str">
         <x:v>attackers.series:2264</x:v>
       </x:c>
+      <x:c r="I38" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="14" t="str">
@@ -3762,6 +3878,9 @@
       <x:c r="H39" s="14" t="str">
         <x:v>attackers.series:2265</x:v>
       </x:c>
+      <x:c r="I39" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="14" t="str">
@@ -3788,6 +3907,9 @@
       <x:c r="H40" s="14" t="str">
         <x:v>attackers.series:2266</x:v>
       </x:c>
+      <x:c r="I40" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="14" t="str">
@@ -3814,6 +3936,9 @@
       <x:c r="H41" s="14" t="str">
         <x:v>attackers.series:2267</x:v>
       </x:c>
+      <x:c r="I41" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="14" t="str">
@@ -3840,6 +3965,9 @@
       <x:c r="H42" s="14" t="str">
         <x:v>attackers.series:2268</x:v>
       </x:c>
+      <x:c r="I42" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="14" t="str">
@@ -3866,6 +3994,9 @@
       <x:c r="H43" s="14" t="str">
         <x:v>attackers.series:2271</x:v>
       </x:c>
+      <x:c r="I43" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="14" t="str">
@@ -3892,6 +4023,9 @@
       <x:c r="H44" s="14" t="str">
         <x:v>attackers.series:2272</x:v>
       </x:c>
+      <x:c r="I44" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="14" t="str">
@@ -3918,6 +4052,9 @@
       <x:c r="H45" s="14" t="str">
         <x:v>attackers.series:2275</x:v>
       </x:c>
+      <x:c r="I45" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="14" t="str">
@@ -3944,6 +4081,9 @@
       <x:c r="H46" s="14" t="str">
         <x:v>attackers.series:2277</x:v>
       </x:c>
+      <x:c r="I46" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="14" t="str">
@@ -3970,6 +4110,9 @@
       <x:c r="H47" s="14" t="str">
         <x:v>attackers.series:2278</x:v>
       </x:c>
+      <x:c r="I47" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="14" t="str">
@@ -3996,6 +4139,9 @@
       <x:c r="H48" s="14" t="str">
         <x:v>attackers.series:2279</x:v>
       </x:c>
+      <x:c r="I48" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="14" t="str">
@@ -4022,6 +4168,9 @@
       <x:c r="H49" s="14" t="str">
         <x:v>attackers.series:2280</x:v>
       </x:c>
+      <x:c r="I49" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="14" t="str">
@@ -4048,6 +4197,9 @@
       <x:c r="H50" s="14" t="str">
         <x:v>attackers.series:2281</x:v>
       </x:c>
+      <x:c r="I50" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="14" t="str">
@@ -4074,6 +4226,9 @@
       <x:c r="H51" s="14" t="str">
         <x:v>attackers.series:2282</x:v>
       </x:c>
+      <x:c r="I51" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="14" t="str">
@@ -4100,6 +4255,9 @@
       <x:c r="H52" s="14" t="str">
         <x:v>attackers.series:2284</x:v>
       </x:c>
+      <x:c r="I52" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="14" t="str">
@@ -4126,6 +4284,9 @@
       <x:c r="H53" s="14" t="str">
         <x:v>attackers.series:2286</x:v>
       </x:c>
+      <x:c r="I53" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="14" t="str">
@@ -4152,6 +4313,9 @@
       <x:c r="H54" s="14" t="str">
         <x:v>madonna.series:1546</x:v>
       </x:c>
+      <x:c r="I54" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="14" t="str">
@@ -4178,6 +4342,9 @@
       <x:c r="H55" s="14" t="str">
         <x:v>madonna.series:1547</x:v>
       </x:c>
+      <x:c r="I55" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="14" t="str">
@@ -4204,6 +4371,9 @@
       <x:c r="H56" s="14" t="str">
         <x:v>madonna.series:1548</x:v>
       </x:c>
+      <x:c r="I56" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="14" t="str">
@@ -4230,6 +4400,9 @@
       <x:c r="H57" s="14" t="str">
         <x:v>madonna.series:1559</x:v>
       </x:c>
+      <x:c r="I57" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="14" t="str">
@@ -4256,6 +4429,9 @@
       <x:c r="H58" s="14" t="str">
         <x:v>madonna.series:1560</x:v>
       </x:c>
+      <x:c r="I58" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="14" t="str">
@@ -4282,6 +4458,9 @@
       <x:c r="H59" s="14" t="str">
         <x:v>madonna.series:1561</x:v>
       </x:c>
+      <x:c r="I59" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="14" t="str">
@@ -4308,6 +4487,9 @@
       <x:c r="H60" s="14" t="str">
         <x:v>madonna.series:1562</x:v>
       </x:c>
+      <x:c r="I60" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="14" t="str">
@@ -4334,6 +4516,9 @@
       <x:c r="H61" s="14" t="str">
         <x:v>madonna.series:1563</x:v>
       </x:c>
+      <x:c r="I61" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="14" t="str">
@@ -4360,6 +4545,9 @@
       <x:c r="H62" s="14" t="str">
         <x:v>madonna.series:1564</x:v>
       </x:c>
+      <x:c r="I62" s="14" t="str">
+        <x:v>0.4.6</x:v>
+      </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="14" t="str">
@@ -4386,6 +4574,9 @@
       <x:c r="H63" s="14" t="str">
         <x:v>attackers.series:2287</x:v>
       </x:c>
+      <x:c r="I63" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="14" t="str">
@@ -4412,6 +4603,9 @@
       <x:c r="H64" s="14" t="str">
         <x:v>attackers.series:2288</x:v>
       </x:c>
+      <x:c r="I64" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="14" t="str">
@@ -4438,6 +4632,9 @@
       <x:c r="H65" s="14" t="str">
         <x:v>attackers.series:2290</x:v>
       </x:c>
+      <x:c r="I65" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="14" t="str">
@@ -4464,6 +4661,9 @@
       <x:c r="H66" s="14" t="str">
         <x:v>attackers.series:2291</x:v>
       </x:c>
+      <x:c r="I66" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="14" t="str">
@@ -4490,6 +4690,9 @@
       <x:c r="H67" s="14" t="str">
         <x:v>attackers.series:2292</x:v>
       </x:c>
+      <x:c r="I67" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="14" t="str">
@@ -4516,6 +4719,9 @@
       <x:c r="H68" s="14" t="str">
         <x:v>attackers.series:2295</x:v>
       </x:c>
+      <x:c r="I68" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="14" t="str">
@@ -4542,6 +4748,9 @@
       <x:c r="H69" s="14" t="str">
         <x:v>attackers.series:2298</x:v>
       </x:c>
+      <x:c r="I69" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="14" t="str">
@@ -4568,6 +4777,9 @@
       <x:c r="H70" s="14" t="str">
         <x:v>attackers.series:2299</x:v>
       </x:c>
+      <x:c r="I70" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="14" t="str">
@@ -4594,6 +4806,9 @@
       <x:c r="H71" s="14" t="str">
         <x:v>attackers.series:2300</x:v>
       </x:c>
+      <x:c r="I71" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="14" t="str">
@@ -4620,6 +4835,9 @@
       <x:c r="H72" s="14" t="str">
         <x:v>attackers.series:2301</x:v>
       </x:c>
+      <x:c r="I72" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="14" t="str">
@@ -4646,6 +4864,9 @@
       <x:c r="H73" s="14" t="str">
         <x:v>attackers.series:2302</x:v>
       </x:c>
+      <x:c r="I73" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="14" t="str">
@@ -4672,6 +4893,9 @@
       <x:c r="H74" s="14" t="str">
         <x:v>attackers.series:2303</x:v>
       </x:c>
+      <x:c r="I74" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="14" t="str">
@@ -4698,6 +4922,9 @@
       <x:c r="H75" s="14" t="str">
         <x:v>attackers.series:2305</x:v>
       </x:c>
+      <x:c r="I75" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="14" t="str">
@@ -4724,6 +4951,9 @@
       <x:c r="H76" s="14" t="str">
         <x:v>attackers.series:2306</x:v>
       </x:c>
+      <x:c r="I76" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="14" t="str">
@@ -4750,6 +4980,9 @@
       <x:c r="H77" s="14" t="str">
         <x:v>attackers.series:2307</x:v>
       </x:c>
+      <x:c r="I77" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="14" t="str">
@@ -4776,6 +5009,9 @@
       <x:c r="H78" s="14" t="str">
         <x:v>attackers.series:2308</x:v>
       </x:c>
+      <x:c r="I78" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="14" t="str">
@@ -4802,6 +5038,9 @@
       <x:c r="H79" s="14" t="str">
         <x:v>attackers.series:2309</x:v>
       </x:c>
+      <x:c r="I79" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="14" t="str">
@@ -4828,6 +5067,9 @@
       <x:c r="H80" s="14" t="str">
         <x:v>attackers.series:2311</x:v>
       </x:c>
+      <x:c r="I80" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="14" t="str">
@@ -4854,6 +5096,9 @@
       <x:c r="H81" s="14" t="str">
         <x:v>attackers.series:2312</x:v>
       </x:c>
+      <x:c r="I81" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="14" t="str">
@@ -4880,6 +5125,9 @@
       <x:c r="H82" s="14" t="str">
         <x:v>madonna.series:1565</x:v>
       </x:c>
+      <x:c r="I82" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="14" t="str">
@@ -4906,6 +5154,9 @@
       <x:c r="H83" s="14" t="str">
         <x:v>madonna.series:1566</x:v>
       </x:c>
+      <x:c r="I83" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="14" t="str">
@@ -4932,6 +5183,9 @@
       <x:c r="H84" s="14" t="str">
         <x:v>madonna.series:1570</x:v>
       </x:c>
+      <x:c r="I84" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="14" t="str">
@@ -4958,6 +5212,9 @@
       <x:c r="H85" s="14" t="str">
         <x:v>madonna.series:1571</x:v>
       </x:c>
+      <x:c r="I85" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="14" t="str">
@@ -4984,6 +5241,9 @@
       <x:c r="H86" s="14" t="str">
         <x:v>madonna.series:1572</x:v>
       </x:c>
+      <x:c r="I86" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="14" t="str">
@@ -5010,6 +5270,9 @@
       <x:c r="H87" s="14" t="str">
         <x:v>madonna.series:1573</x:v>
       </x:c>
+      <x:c r="I87" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="14" t="str">
@@ -5036,6 +5299,9 @@
       <x:c r="H88" s="14" t="str">
         <x:v>madonna.series:1574</x:v>
       </x:c>
+      <x:c r="I88" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="14" t="str">
@@ -5062,6 +5328,9 @@
       <x:c r="H89" s="14" t="str">
         <x:v>madonna.series:1579</x:v>
       </x:c>
+      <x:c r="I89" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="14" t="str">
@@ -5088,6 +5357,9 @@
       <x:c r="H90" s="14" t="str">
         <x:v>madonna.series:1581</x:v>
       </x:c>
+      <x:c r="I90" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="14" t="str">
@@ -5114,6 +5386,9 @@
       <x:c r="H91" s="14" t="str">
         <x:v>madonna.series:1585</x:v>
       </x:c>
+      <x:c r="I91" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="14" t="str">
@@ -5140,6 +5415,9 @@
       <x:c r="H92" s="14" t="str">
         <x:v>madonna.series:1586</x:v>
       </x:c>
+      <x:c r="I92" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="14" t="str">
@@ -5166,6 +5444,9 @@
       <x:c r="H93" s="14" t="str">
         <x:v>madonna.series:1587</x:v>
       </x:c>
+      <x:c r="I93" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="14" t="str">
@@ -5192,6 +5473,9 @@
       <x:c r="H94" s="14" t="str">
         <x:v>madonna.series:1588</x:v>
       </x:c>
+      <x:c r="I94" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="14" t="str">
@@ -5218,6 +5502,9 @@
       <x:c r="H95" s="14" t="str">
         <x:v>madonna.series:1589</x:v>
       </x:c>
+      <x:c r="I95" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="14" t="str">
@@ -5244,6 +5531,9 @@
       <x:c r="H96" s="14" t="str">
         <x:v>madonna.series:1590</x:v>
       </x:c>
+      <x:c r="I96" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="14" t="str">
@@ -5270,6 +5560,9 @@
       <x:c r="H97" s="14" t="str">
         <x:v>madonna.series:1591</x:v>
       </x:c>
+      <x:c r="I97" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="14" t="str">
@@ -5296,6 +5589,9 @@
       <x:c r="H98" s="14" t="str">
         <x:v>madonna.series:1592</x:v>
       </x:c>
+      <x:c r="I98" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="14" t="str">
@@ -5322,6 +5618,9 @@
       <x:c r="H99" s="14" t="str">
         <x:v>madonna.series:1593</x:v>
       </x:c>
+      <x:c r="I99" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="14" t="str">
@@ -5348,6 +5647,9 @@
       <x:c r="H100" s="14" t="str">
         <x:v>madonna.series:1594</x:v>
       </x:c>
+      <x:c r="I100" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="14" t="str">
@@ -5373,6 +5675,125 @@
       </x:c>
       <x:c r="H101" s="14" t="str">
         <x:v>madonna.series:1595</x:v>
+      </x:c>
+      <x:c r="I101" s="14" t="str">
+        <x:v>0.4.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="14" t="str">
+        <x:v>series_000101</x:v>
+      </x:c>
+      <x:c r="B102" s="14" t="str">
+        <x:v>聖水くらぶ</x:v>
+      </x:c>
+      <x:c r="C102" s="14" t="str">
+        <x:v>圣水俱乐部</x:v>
+      </x:c>
+      <x:c r="D102" s="14" t="str">
+        <x:v>Holy Water Club</x:v>
+      </x:c>
+      <x:c r="E102" s="14" t="str">
+        <x:v>MOODYZ</x:v>
+      </x:c>
+      <x:c r="F102" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G102" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3489</x:v>
+      </x:c>
+      <x:c r="H102" s="14" t="str">
+        <x:v>moodyz.series:3489</x:v>
+      </x:c>
+      <x:c r="I102" s="14" t="str">
+        <x:v>0.4.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="14" t="str">
+        <x:v>series_000102</x:v>
+      </x:c>
+      <x:c r="B103" s="14" t="str">
+        <x:v>W CAST</x:v>
+      </x:c>
+      <x:c r="C103" s="14" t="str">
+        <x:v>W CAST</x:v>
+      </x:c>
+      <x:c r="D103" s="14" t="str">
+        <x:v>W CAST</x:v>
+      </x:c>
+      <x:c r="E103" s="14" t="str">
+        <x:v>MOODYZ</x:v>
+      </x:c>
+      <x:c r="F103" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G103" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3519</x:v>
+      </x:c>
+      <x:c r="H103" s="14" t="str">
+        <x:v>moodyz.series:3519</x:v>
+      </x:c>
+      <x:c r="I103" s="14" t="str">
+        <x:v>0.4.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="14" t="str">
+        <x:v>series_000103</x:v>
+      </x:c>
+      <x:c r="B104" s="14" t="str">
+        <x:v>聖水痴女ハーレム</x:v>
+      </x:c>
+      <x:c r="C104" s="14" t="str">
+        <x:v>圣水痴女后宫</x:v>
+      </x:c>
+      <x:c r="D104" s="14" t="str">
+        <x:v>Holy Water Temptress Harem</x:v>
+      </x:c>
+      <x:c r="E104" s="14" t="str">
+        <x:v>MOODYZ</x:v>
+      </x:c>
+      <x:c r="F104" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G104" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3562</x:v>
+      </x:c>
+      <x:c r="H104" s="14" t="str">
+        <x:v>moodyz.series:3562</x:v>
+      </x:c>
+      <x:c r="I104" s="14" t="str">
+        <x:v>0.4.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="14" t="str">
+        <x:v>series_000104</x:v>
+      </x:c>
+      <x:c r="B105" s="14" t="str">
+        <x:v>見つめる愛情イラマチオ</x:v>
+      </x:c>
+      <x:c r="C105" s="14" t="str">
+        <x:v>凝视的爱情深喉</x:v>
+      </x:c>
+      <x:c r="D105" s="14" t="str">
+        <x:v>Affectionate Irrumatio with Eye Contact</x:v>
+      </x:c>
+      <x:c r="E105" s="14" t="str">
+        <x:v>アイデアポケット</x:v>
+      </x:c>
+      <x:c r="F105" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G105" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/series/939</x:v>
+      </x:c>
+      <x:c r="H105" s="14" t="str">
+        <x:v>ideapocket.series:939</x:v>
+      </x:c>
+      <x:c r="I105" s="14" t="str">
+        <x:v>0.4.8</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5384,130 +5805,151 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="80" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="90" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="48" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="58" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="6" t="str">
+        <x:v>Key</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>Maker</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
         <x:v>Source ID</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
-        <x:v>名称</x:v>
-      </x:c>
-      <x:c r="C1" s="6" t="str">
-        <x:v>来源完整</x:v>
-      </x:c>
-      <x:c r="D1" s="6" t="str">
-        <x:v>实体类型覆盖</x:v>
-      </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>已知限制</x:v>
+        <x:v>Index URL</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>Detail URL Template</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>Single Page</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="14" t="str">
-        <x:v>source_ideapocket_official</x:v>
+        <x:v>attackers</x:v>
       </x:c>
       <x:c r="B2" s="14" t="str">
-        <x:v>IDEAPOCKET 官方作品目录</x:v>
+        <x:v>attackers.series</x:v>
       </x:c>
       <x:c r="C2" s="14" t="str">
-        <x:v>no</x:v>
+        <x:v>ATTACKERS</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
-        <x:v>label: 16/16, unrecognized=0, complete=yes; series: 2/2, unrecognized=0, complete=no</x:v>
+        <x:v>source_attackers_official</x:v>
       </x:c>
       <x:c r="E2" s="14" t="str">
-        <x:v>IDEAPOCKET 当前官方 Label Index 已完整遍历；Series 仍未完整枚举，因此来源级 completeTraversal 继续为 false。历史已删除/隐藏 Label 与其他实体类型不在本批次完整性声明内。</x:v>
+        <x:v>https://attackers.net/works/series</x:v>
+      </x:c>
+      <x:c r="F2" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/&lt;id&gt;</x:v>
+      </x:c>
+      <x:c r="G2" s="14" t="str">
+        <x:v>yes</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="14" t="str">
-        <x:v>source_moodyz_official</x:v>
+        <x:v>ideapocket</x:v>
       </x:c>
       <x:c r="B3" s="14" t="str">
-        <x:v>MOODYZ 官方作品目录</x:v>
+        <x:v>ideapocket.series</x:v>
       </x:c>
       <x:c r="C3" s="14" t="str">
+        <x:v>アイデアポケット</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="str">
+        <x:v>source_ideapocket_official</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="str">
+        <x:v>https://ideapocket.com/works/series</x:v>
+      </x:c>
+      <x:c r="F3" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/series/&lt;id&gt;</x:v>
+      </x:c>
+      <x:c r="G3" s="14" t="str">
         <x:v>no</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="str">
-        <x:v>label: 29/29, unrecognized=0, complete=yes; series: 1/1, unrecognized=0, complete=no</x:v>
-      </x:c>
-      <x:c r="E3" s="14" t="str">
-        <x:v>MOODYZ 当前官方 Label Index 已完整遍历；Series 仍未完整枚举，因此来源级 completeTraversal 继续为 false。历史已删除/隐藏 Label 与其他实体类型不在本批次完整性声明内。</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="14" t="str">
-        <x:v>source_s1_official</x:v>
+        <x:v>madonna</x:v>
       </x:c>
       <x:c r="B4" s="14" t="str">
-        <x:v>S1 NO.1 STYLE 官方作品目录</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C4" s="14" t="str">
-        <x:v>no</x:v>
+        <x:v>マドンナ</x:v>
       </x:c>
       <x:c r="D4" s="14" t="str">
-        <x:v>label: 1/1, unrecognized=0, complete=no; series: 3/3, unrecognized=0, complete=no</x:v>
+        <x:v>source_madonna_official</x:v>
       </x:c>
       <x:c r="E4" s="14" t="str">
-        <x:v>S1 主 Label 4355 与 3 个 Series 已逐项核验，但官方索引在当前采集环境中未形成可证明的完整枚举快照，因此 Label 与 Series coverage 均保持 incomplete。</x:v>
+        <x:v>https://madonna-av.com/works/series</x:v>
+      </x:c>
+      <x:c r="F4" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/&lt;id&gt;</x:v>
+      </x:c>
+      <x:c r="G4" s="14" t="str">
+        <x:v>yes</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14" t="str">
-        <x:v>source_will_company</x:v>
+        <x:v>moodyz</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>株式会社WILL 官方公司页</x:v>
+        <x:v>moodyz.series</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
-        <x:v>yes</x:v>
+        <x:v>MOODYZ</x:v>
       </x:c>
       <x:c r="D5" s="14" t="str">
-        <x:v>company: 0/1, unrecognized=0, complete=yes</x:v>
+        <x:v>source_moodyz_official</x:v>
       </x:c>
       <x:c r="E5" s="14" t="str">
-        <x:v>Localogue 当前正式 OrganizationKind 尚未把 company 作为一等消费类型，因此先进入 Staging，不伪装成 Maker。</x:v>
+        <x:v>https://moodyz.com/works/series</x:v>
+      </x:c>
+      <x:c r="F5" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/&lt;id&gt;</x:v>
+      </x:c>
+      <x:c r="G5" s="14" t="str">
+        <x:v>no</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="14" t="str">
-        <x:v>source_attackers_official</x:v>
+        <x:v>s1</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
-        <x:v>ATTACKERS 官方 Maker / Label 目录</x:v>
+        <x:v>s1.series</x:v>
       </x:c>
       <x:c r="C6" s="14" t="str">
+        <x:v>エスワン</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="str">
+        <x:v>source_s1_official</x:v>
+      </x:c>
+      <x:c r="E6" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/series</x:v>
+      </x:c>
+      <x:c r="F6" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/&lt;id&gt;</x:v>
+      </x:c>
+      <x:c r="G6" s="14" t="str">
         <x:v>no</x:v>
-      </x:c>
-      <x:c r="D6" s="14" t="str">
-        <x:v>maker: 1/1, unrecognized=0, complete=yes; label: 17/17, unrecognized=0, complete=yes; series: 52/53, unrecognized=1, complete=no</x:v>
-      </x:c>
-      <x:c r="E6" s="14" t="str">
-        <x:v>ATTACKERS 三批 partial Series Snapshot 联合发现并审核 53 个 Series：52 个已发布，series/2273 因官方规范名仅为“１”继续 hold；最新 Snapshot 仍非完整索引遍历。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="14" t="str">
-        <x:v>source_madonna_official</x:v>
-      </x:c>
-      <x:c r="B7" s="14" t="str">
-        <x:v>Madonna 官方 Maker / Label 目录</x:v>
-      </x:c>
-      <x:c r="C7" s="14" t="str">
-        <x:v>no</x:v>
-      </x:c>
-      <x:c r="D7" s="14" t="str">
-        <x:v>maker: 1/1, unrecognized=0, complete=yes; label: 18/18, unrecognized=0, complete=yes; series: 42/42, unrecognized=0, complete=no</x:v>
-      </x:c>
-      <x:c r="E7" s="14" t="str">
-        <x:v>Madonna 已通过三批 partial Series Snapshot 联合审核并发布 42 个 Series；最新 Snapshot 仍不是完整索引遍历，因此 Series 与来源级 completeTraversal 继续为 false。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5516,6 +5958,141 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="86" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="92" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Source ID</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>名称</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>来源完整</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>实体类型覆盖</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>已知限制</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="14" t="str">
+        <x:v>source_ideapocket_official</x:v>
+      </x:c>
+      <x:c r="B2" s="14" t="str">
+        <x:v>IDEAPOCKET 官方作品目录</x:v>
+      </x:c>
+      <x:c r="C2" s="14" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="D2" s="14" t="str">
+        <x:v>label: 16/16, unrecognized=0, complete=yes; series: 3/3, unrecognized=0, complete=no</x:v>
+      </x:c>
+      <x:c r="E2" s="14" t="str">
+        <x:v>IDEAPOCKET 当前官方 Label Index 已完整覆盖；0.4.8 首次纳入 Series Index Provider，并建立 3 条官方可核验的 partial Snapshot 样本。Series 仍未完整枚举，因此来源级 completeTraversal=false。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="14" t="str">
+        <x:v>source_moodyz_official</x:v>
+      </x:c>
+      <x:c r="B3" s="14" t="str">
+        <x:v>MOODYZ 官方作品目录</x:v>
+      </x:c>
+      <x:c r="C3" s="14" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="str">
+        <x:v>label: 29/29, unrecognized=0, complete=yes; series: 4/4, unrecognized=0, complete=no</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="str">
+        <x:v>MOODYZ 当前官方 Label Index 已完整覆盖；0.4.8 首次纳入 Series Index Provider，并建立 4 条官方可核验的 partial Snapshot 样本。Series 仍未完整枚举，因此来源级 completeTraversal=false。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="14" t="str">
+        <x:v>source_s1_official</x:v>
+      </x:c>
+      <x:c r="B4" s="14" t="str">
+        <x:v>S1 NO.1 STYLE 官方作品目录</x:v>
+      </x:c>
+      <x:c r="C4" s="14" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="D4" s="14" t="str">
+        <x:v>label: 1/1, unrecognized=0, complete=no; series: 3/3, unrecognized=0, complete=no</x:v>
+      </x:c>
+      <x:c r="E4" s="14" t="str">
+        <x:v>S1 当前主 Label 与 3 个 Series 均已核验；0.4.8 将 S1 正式纳入 Series Index Provider Registry，并用首份 partial Snapshot 验证既有 Mapping。尚未形成可证明的完整 Series Index 快照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="14" t="str">
+        <x:v>source_will_company</x:v>
+      </x:c>
+      <x:c r="B5" s="14" t="str">
+        <x:v>株式会社WILL 官方公司页</x:v>
+      </x:c>
+      <x:c r="C5" s="14" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="D5" s="14" t="str">
+        <x:v>company: 0/1, unrecognized=0, complete=yes</x:v>
+      </x:c>
+      <x:c r="E5" s="14" t="str">
+        <x:v>Localogue 当前正式 OrganizationKind 尚未把 company 作为一等消费类型，因此先进入 Staging，不伪装成 Maker。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="14" t="str">
+        <x:v>source_attackers_official</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="str">
+        <x:v>ATTACKERS 官方 Maker / Label 目录</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="str">
+        <x:v>maker: 1/1, unrecognized=0, complete=yes; label: 17/17, unrecognized=0, complete=yes; series: 52/53, unrecognized=1, complete=no</x:v>
+      </x:c>
+      <x:c r="E6" s="14" t="str">
+        <x:v>ATTACKERS 三批 partial Series Snapshot 联合发现并审核 53 个 Series：52 个已发布，series/2273 因官方规范名仅为“１”继续 hold；最新 Snapshot 仍非完整索引遍历。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="14" t="str">
+        <x:v>source_madonna_official</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="str">
+        <x:v>Madonna 官方 Maker / Label 目录</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="str">
+        <x:v>maker: 1/1, unrecognized=0, complete=yes; label: 18/18, unrecognized=0, complete=yes; series: 42/42, unrecognized=0, complete=no</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="str">
+        <x:v>Madonna 已通过三批 partial Series Snapshot 联合审核并发布 42 个 Series；最新 Snapshot 仍不是完整索引遍历，因此 Series 与来源级 completeTraversal 继续为 false。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -7289,22 +7866,22 @@
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.series</x:v>
       </x:c>
       <x:c r="B89" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C89" s="14" t="str">
-        <x:v>10077</x:v>
+        <x:v>939</x:v>
       </x:c>
       <x:c r="D89" s="14" t="str">
-        <x:v>label_000035</x:v>
+        <x:v>series_000104</x:v>
       </x:c>
       <x:c r="E89" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F89" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10077</x:v>
+        <x:v>https://ideapocket.com/works/list/series/939</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -7315,16 +7892,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C90" s="14" t="str">
-        <x:v>10119</x:v>
+        <x:v>10077</x:v>
       </x:c>
       <x:c r="D90" s="14" t="str">
-        <x:v>label_000031</x:v>
+        <x:v>label_000035</x:v>
       </x:c>
       <x:c r="E90" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F90" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10119</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10077</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -7335,16 +7912,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C91" s="14" t="str">
-        <x:v>10130</x:v>
+        <x:v>10119</x:v>
       </x:c>
       <x:c r="D91" s="14" t="str">
-        <x:v>label_000028</x:v>
+        <x:v>label_000031</x:v>
       </x:c>
       <x:c r="E91" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F91" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10130</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10119</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -7355,16 +7932,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C92" s="14" t="str">
-        <x:v>10142</x:v>
+        <x:v>10130</x:v>
       </x:c>
       <x:c r="D92" s="14" t="str">
-        <x:v>label_000034</x:v>
+        <x:v>label_000028</x:v>
       </x:c>
       <x:c r="E92" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F92" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10142</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10130</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -7375,16 +7952,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C93" s="14" t="str">
-        <x:v>10151</x:v>
+        <x:v>10142</x:v>
       </x:c>
       <x:c r="D93" s="14" t="str">
-        <x:v>label_000036</x:v>
+        <x:v>label_000034</x:v>
       </x:c>
       <x:c r="E93" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F93" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10151</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10142</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -7395,16 +7972,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C94" s="14" t="str">
-        <x:v>10159</x:v>
+        <x:v>10151</x:v>
       </x:c>
       <x:c r="D94" s="14" t="str">
-        <x:v>label_000030</x:v>
+        <x:v>label_000036</x:v>
       </x:c>
       <x:c r="E94" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F94" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10159</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10151</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -7415,16 +7992,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C95" s="14" t="str">
-        <x:v>12490</x:v>
+        <x:v>10159</x:v>
       </x:c>
       <x:c r="D95" s="14" t="str">
-        <x:v>label_000021</x:v>
+        <x:v>label_000030</x:v>
       </x:c>
       <x:c r="E95" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F95" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/12490</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10159</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -7435,16 +8012,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C96" s="14" t="str">
-        <x:v>12502</x:v>
+        <x:v>12490</x:v>
       </x:c>
       <x:c r="D96" s="14" t="str">
-        <x:v>label_000027</x:v>
+        <x:v>label_000021</x:v>
       </x:c>
       <x:c r="E96" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F96" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/12502</x:v>
+        <x:v>https://madonna-av.com/works/list/label/12490</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -7455,16 +8032,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C97" s="14" t="str">
-        <x:v>12603</x:v>
+        <x:v>12502</x:v>
       </x:c>
       <x:c r="D97" s="14" t="str">
-        <x:v>label_000026</x:v>
+        <x:v>label_000027</x:v>
       </x:c>
       <x:c r="E97" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F97" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/12603</x:v>
+        <x:v>https://madonna-av.com/works/list/label/12502</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -7475,16 +8052,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C98" s="14" t="str">
-        <x:v>3125</x:v>
+        <x:v>12603</x:v>
       </x:c>
       <x:c r="D98" s="14" t="str">
-        <x:v>label_000037</x:v>
+        <x:v>label_000026</x:v>
       </x:c>
       <x:c r="E98" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F98" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/3125</x:v>
+        <x:v>https://madonna-av.com/works/list/label/12603</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -7495,16 +8072,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C99" s="14" t="str">
-        <x:v>3669</x:v>
+        <x:v>3125</x:v>
       </x:c>
       <x:c r="D99" s="14" t="str">
-        <x:v>label_000020</x:v>
+        <x:v>label_000037</x:v>
       </x:c>
       <x:c r="E99" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F99" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/3669</x:v>
+        <x:v>https://madonna-av.com/works/list/label/3125</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -7515,16 +8092,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C100" s="14" t="str">
-        <x:v>7354</x:v>
+        <x:v>3669</x:v>
       </x:c>
       <x:c r="D100" s="14" t="str">
-        <x:v>label_000024</x:v>
+        <x:v>label_000020</x:v>
       </x:c>
       <x:c r="E100" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F100" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/7354</x:v>
+        <x:v>https://madonna-av.com/works/list/label/3669</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -7535,16 +8112,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C101" s="14" t="str">
-        <x:v>7993</x:v>
+        <x:v>7354</x:v>
       </x:c>
       <x:c r="D101" s="14" t="str">
-        <x:v>label_000029</x:v>
+        <x:v>label_000024</x:v>
       </x:c>
       <x:c r="E101" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F101" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/7993</x:v>
+        <x:v>https://madonna-av.com/works/list/label/7354</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -7555,16 +8132,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C102" s="14" t="str">
-        <x:v>85265</x:v>
+        <x:v>7993</x:v>
       </x:c>
       <x:c r="D102" s="14" t="str">
-        <x:v>label_000032</x:v>
+        <x:v>label_000029</x:v>
       </x:c>
       <x:c r="E102" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F102" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/85265</x:v>
+        <x:v>https://madonna-av.com/works/list/label/7993</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -7575,16 +8152,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C103" s="14" t="str">
-        <x:v>9387</x:v>
+        <x:v>85265</x:v>
       </x:c>
       <x:c r="D103" s="14" t="str">
-        <x:v>label_000022</x:v>
+        <x:v>label_000032</x:v>
       </x:c>
       <x:c r="E103" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F103" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/9387</x:v>
+        <x:v>https://madonna-av.com/works/list/label/85265</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -7595,16 +8172,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C104" s="14" t="str">
-        <x:v>9419</x:v>
+        <x:v>9387</x:v>
       </x:c>
       <x:c r="D104" s="14" t="str">
-        <x:v>label_000025</x:v>
+        <x:v>label_000022</x:v>
       </x:c>
       <x:c r="E104" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F104" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/9419</x:v>
+        <x:v>https://madonna-av.com/works/list/label/9387</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -7615,16 +8192,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C105" s="14" t="str">
-        <x:v>9483</x:v>
+        <x:v>9419</x:v>
       </x:c>
       <x:c r="D105" s="14" t="str">
-        <x:v>label_000033</x:v>
+        <x:v>label_000025</x:v>
       </x:c>
       <x:c r="E105" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F105" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/9483</x:v>
+        <x:v>https://madonna-av.com/works/list/label/9419</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -7635,36 +8212,36 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C106" s="14" t="str">
-        <x:v>9789</x:v>
+        <x:v>9483</x:v>
       </x:c>
       <x:c r="D106" s="14" t="str">
-        <x:v>label_000023</x:v>
+        <x:v>label_000033</x:v>
       </x:c>
       <x:c r="E106" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F106" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/9789</x:v>
+        <x:v>https://madonna-av.com/works/list/label/9483</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B107" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C107" s="14" t="str">
-        <x:v>1546</x:v>
+        <x:v>9789</x:v>
       </x:c>
       <x:c r="D107" s="14" t="str">
-        <x:v>series_000053</x:v>
+        <x:v>label_000023</x:v>
       </x:c>
       <x:c r="E107" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F107" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1546</x:v>
+        <x:v>https://madonna-av.com/works/list/label/9789</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -7675,16 +8252,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C108" s="14" t="str">
-        <x:v>1547</x:v>
+        <x:v>1546</x:v>
       </x:c>
       <x:c r="D108" s="14" t="str">
-        <x:v>series_000054</x:v>
+        <x:v>series_000053</x:v>
       </x:c>
       <x:c r="E108" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F108" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1547</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1546</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -7695,16 +8272,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C109" s="14" t="str">
-        <x:v>1548</x:v>
+        <x:v>1547</x:v>
       </x:c>
       <x:c r="D109" s="14" t="str">
-        <x:v>series_000055</x:v>
+        <x:v>series_000054</x:v>
       </x:c>
       <x:c r="E109" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F109" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1548</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1547</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -7715,16 +8292,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C110" s="14" t="str">
-        <x:v>1549</x:v>
+        <x:v>1548</x:v>
       </x:c>
       <x:c r="D110" s="14" t="str">
-        <x:v>series_000027</x:v>
+        <x:v>series_000055</x:v>
       </x:c>
       <x:c r="E110" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F110" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1549</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1548</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -7735,16 +8312,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C111" s="14" t="str">
-        <x:v>1550</x:v>
+        <x:v>1549</x:v>
       </x:c>
       <x:c r="D111" s="14" t="str">
-        <x:v>series_000028</x:v>
+        <x:v>series_000027</x:v>
       </x:c>
       <x:c r="E111" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F111" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1550</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1549</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -7755,16 +8332,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C112" s="14" t="str">
-        <x:v>1551</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D112" s="14" t="str">
-        <x:v>series_000029</x:v>
+        <x:v>series_000028</x:v>
       </x:c>
       <x:c r="E112" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F112" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1551</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1550</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -7775,16 +8352,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C113" s="14" t="str">
-        <x:v>1552</x:v>
+        <x:v>1551</x:v>
       </x:c>
       <x:c r="D113" s="14" t="str">
-        <x:v>series_000030</x:v>
+        <x:v>series_000029</x:v>
       </x:c>
       <x:c r="E113" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F113" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1552</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1551</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -7795,16 +8372,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C114" s="14" t="str">
-        <x:v>1553</x:v>
+        <x:v>1552</x:v>
       </x:c>
       <x:c r="D114" s="14" t="str">
-        <x:v>series_000031</x:v>
+        <x:v>series_000030</x:v>
       </x:c>
       <x:c r="E114" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F114" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1553</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1552</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -7815,16 +8392,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C115" s="14" t="str">
-        <x:v>1554</x:v>
+        <x:v>1553</x:v>
       </x:c>
       <x:c r="D115" s="14" t="str">
-        <x:v>series_000032</x:v>
+        <x:v>series_000031</x:v>
       </x:c>
       <x:c r="E115" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F115" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1554</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1553</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -7835,16 +8412,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C116" s="14" t="str">
-        <x:v>1555</x:v>
+        <x:v>1554</x:v>
       </x:c>
       <x:c r="D116" s="14" t="str">
-        <x:v>series_000033</x:v>
+        <x:v>series_000032</x:v>
       </x:c>
       <x:c r="E116" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F116" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1555</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1554</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -7855,16 +8432,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C117" s="14" t="str">
-        <x:v>1556</x:v>
+        <x:v>1555</x:v>
       </x:c>
       <x:c r="D117" s="14" t="str">
-        <x:v>series_000034</x:v>
+        <x:v>series_000033</x:v>
       </x:c>
       <x:c r="E117" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F117" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1556</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1555</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -7875,16 +8452,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C118" s="14" t="str">
-        <x:v>1557</x:v>
+        <x:v>1556</x:v>
       </x:c>
       <x:c r="D118" s="14" t="str">
-        <x:v>series_000035</x:v>
+        <x:v>series_000034</x:v>
       </x:c>
       <x:c r="E118" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F118" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1557</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1556</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -7895,16 +8472,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C119" s="14" t="str">
-        <x:v>1558</x:v>
+        <x:v>1557</x:v>
       </x:c>
       <x:c r="D119" s="14" t="str">
-        <x:v>series_000036</x:v>
+        <x:v>series_000035</x:v>
       </x:c>
       <x:c r="E119" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F119" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1558</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1557</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -7915,16 +8492,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C120" s="14" t="str">
-        <x:v>1559</x:v>
+        <x:v>1558</x:v>
       </x:c>
       <x:c r="D120" s="14" t="str">
-        <x:v>series_000056</x:v>
+        <x:v>series_000036</x:v>
       </x:c>
       <x:c r="E120" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F120" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1559</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1558</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
@@ -7935,16 +8512,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C121" s="14" t="str">
-        <x:v>1560</x:v>
+        <x:v>1559</x:v>
       </x:c>
       <x:c r="D121" s="14" t="str">
-        <x:v>series_000057</x:v>
+        <x:v>series_000056</x:v>
       </x:c>
       <x:c r="E121" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F121" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1560</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1559</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
@@ -7955,16 +8532,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C122" s="14" t="str">
-        <x:v>1561</x:v>
+        <x:v>1560</x:v>
       </x:c>
       <x:c r="D122" s="14" t="str">
-        <x:v>series_000058</x:v>
+        <x:v>series_000057</x:v>
       </x:c>
       <x:c r="E122" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F122" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1561</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1560</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -7975,16 +8552,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C123" s="14" t="str">
-        <x:v>1562</x:v>
+        <x:v>1561</x:v>
       </x:c>
       <x:c r="D123" s="14" t="str">
-        <x:v>series_000059</x:v>
+        <x:v>series_000058</x:v>
       </x:c>
       <x:c r="E123" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F123" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1562</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1561</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
@@ -7995,16 +8572,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C124" s="14" t="str">
-        <x:v>1563</x:v>
+        <x:v>1562</x:v>
       </x:c>
       <x:c r="D124" s="14" t="str">
-        <x:v>series_000060</x:v>
+        <x:v>series_000059</x:v>
       </x:c>
       <x:c r="E124" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F124" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1563</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1562</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
@@ -8015,16 +8592,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C125" s="14" t="str">
-        <x:v>1564</x:v>
+        <x:v>1563</x:v>
       </x:c>
       <x:c r="D125" s="14" t="str">
-        <x:v>series_000061</x:v>
+        <x:v>series_000060</x:v>
       </x:c>
       <x:c r="E125" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F125" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1564</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1563</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -8035,16 +8612,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C126" s="14" t="str">
-        <x:v>1565</x:v>
+        <x:v>1564</x:v>
       </x:c>
       <x:c r="D126" s="14" t="str">
-        <x:v>series_000081</x:v>
+        <x:v>series_000061</x:v>
       </x:c>
       <x:c r="E126" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F126" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1565</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1564</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
@@ -8055,16 +8632,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C127" s="14" t="str">
-        <x:v>1566</x:v>
+        <x:v>1565</x:v>
       </x:c>
       <x:c r="D127" s="14" t="str">
-        <x:v>series_000082</x:v>
+        <x:v>series_000081</x:v>
       </x:c>
       <x:c r="E127" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F127" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1566</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1565</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
@@ -8075,16 +8652,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C128" s="14" t="str">
-        <x:v>1570</x:v>
+        <x:v>1566</x:v>
       </x:c>
       <x:c r="D128" s="14" t="str">
-        <x:v>series_000083</x:v>
+        <x:v>series_000082</x:v>
       </x:c>
       <x:c r="E128" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F128" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1570</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1566</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
@@ -8095,16 +8672,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C129" s="14" t="str">
-        <x:v>1571</x:v>
+        <x:v>1570</x:v>
       </x:c>
       <x:c r="D129" s="14" t="str">
-        <x:v>series_000084</x:v>
+        <x:v>series_000083</x:v>
       </x:c>
       <x:c r="E129" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F129" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1571</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1570</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
@@ -8115,16 +8692,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C130" s="14" t="str">
-        <x:v>1572</x:v>
+        <x:v>1571</x:v>
       </x:c>
       <x:c r="D130" s="14" t="str">
-        <x:v>series_000085</x:v>
+        <x:v>series_000084</x:v>
       </x:c>
       <x:c r="E130" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F130" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1572</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1571</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
@@ -8135,16 +8712,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C131" s="14" t="str">
-        <x:v>1573</x:v>
+        <x:v>1572</x:v>
       </x:c>
       <x:c r="D131" s="14" t="str">
-        <x:v>series_000086</x:v>
+        <x:v>series_000085</x:v>
       </x:c>
       <x:c r="E131" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F131" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1573</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1572</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
@@ -8155,16 +8732,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C132" s="14" t="str">
-        <x:v>1574</x:v>
+        <x:v>1573</x:v>
       </x:c>
       <x:c r="D132" s="14" t="str">
-        <x:v>series_000087</x:v>
+        <x:v>series_000086</x:v>
       </x:c>
       <x:c r="E132" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F132" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1574</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1573</x:v>
       </x:c>
     </x:row>
     <x:row r="133">
@@ -8175,16 +8752,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C133" s="14" t="str">
-        <x:v>1579</x:v>
+        <x:v>1574</x:v>
       </x:c>
       <x:c r="D133" s="14" t="str">
-        <x:v>series_000088</x:v>
+        <x:v>series_000087</x:v>
       </x:c>
       <x:c r="E133" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F133" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1579</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1574</x:v>
       </x:c>
     </x:row>
     <x:row r="134">
@@ -8195,16 +8772,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C134" s="14" t="str">
-        <x:v>1581</x:v>
+        <x:v>1579</x:v>
       </x:c>
       <x:c r="D134" s="14" t="str">
-        <x:v>series_000089</x:v>
+        <x:v>series_000088</x:v>
       </x:c>
       <x:c r="E134" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F134" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1581</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1579</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
@@ -8215,16 +8792,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C135" s="14" t="str">
-        <x:v>1585</x:v>
+        <x:v>1581</x:v>
       </x:c>
       <x:c r="D135" s="14" t="str">
-        <x:v>series_000090</x:v>
+        <x:v>series_000089</x:v>
       </x:c>
       <x:c r="E135" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F135" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1585</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1581</x:v>
       </x:c>
     </x:row>
     <x:row r="136">
@@ -8235,16 +8812,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C136" s="14" t="str">
-        <x:v>1586</x:v>
+        <x:v>1585</x:v>
       </x:c>
       <x:c r="D136" s="14" t="str">
-        <x:v>series_000091</x:v>
+        <x:v>series_000090</x:v>
       </x:c>
       <x:c r="E136" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F136" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1586</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1585</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
@@ -8255,16 +8832,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C137" s="14" t="str">
-        <x:v>1587</x:v>
+        <x:v>1586</x:v>
       </x:c>
       <x:c r="D137" s="14" t="str">
-        <x:v>series_000092</x:v>
+        <x:v>series_000091</x:v>
       </x:c>
       <x:c r="E137" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F137" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1587</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1586</x:v>
       </x:c>
     </x:row>
     <x:row r="138">
@@ -8275,16 +8852,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C138" s="14" t="str">
-        <x:v>1588</x:v>
+        <x:v>1587</x:v>
       </x:c>
       <x:c r="D138" s="14" t="str">
-        <x:v>series_000093</x:v>
+        <x:v>series_000092</x:v>
       </x:c>
       <x:c r="E138" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F138" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1588</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1587</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
@@ -8295,16 +8872,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C139" s="14" t="str">
-        <x:v>1589</x:v>
+        <x:v>1588</x:v>
       </x:c>
       <x:c r="D139" s="14" t="str">
-        <x:v>series_000094</x:v>
+        <x:v>series_000093</x:v>
       </x:c>
       <x:c r="E139" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F139" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1589</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1588</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -8315,16 +8892,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C140" s="14" t="str">
-        <x:v>1590</x:v>
+        <x:v>1589</x:v>
       </x:c>
       <x:c r="D140" s="14" t="str">
-        <x:v>series_000095</x:v>
+        <x:v>series_000094</x:v>
       </x:c>
       <x:c r="E140" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F140" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1590</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1589</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
@@ -8335,16 +8912,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C141" s="14" t="str">
-        <x:v>1591</x:v>
+        <x:v>1590</x:v>
       </x:c>
       <x:c r="D141" s="14" t="str">
-        <x:v>series_000096</x:v>
+        <x:v>series_000095</x:v>
       </x:c>
       <x:c r="E141" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F141" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1591</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1590</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
@@ -8355,16 +8932,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C142" s="14" t="str">
-        <x:v>1592</x:v>
+        <x:v>1591</x:v>
       </x:c>
       <x:c r="D142" s="14" t="str">
-        <x:v>series_000097</x:v>
+        <x:v>series_000096</x:v>
       </x:c>
       <x:c r="E142" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F142" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1592</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1591</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
@@ -8375,16 +8952,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C143" s="14" t="str">
-        <x:v>1593</x:v>
+        <x:v>1592</x:v>
       </x:c>
       <x:c r="D143" s="14" t="str">
-        <x:v>series_000098</x:v>
+        <x:v>series_000097</x:v>
       </x:c>
       <x:c r="E143" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F143" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1593</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1592</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -8395,16 +8972,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C144" s="14" t="str">
-        <x:v>1594</x:v>
+        <x:v>1593</x:v>
       </x:c>
       <x:c r="D144" s="14" t="str">
-        <x:v>series_000099</x:v>
+        <x:v>series_000098</x:v>
       </x:c>
       <x:c r="E144" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F144" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1594</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1593</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -8415,16 +8992,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C145" s="14" t="str">
-        <x:v>1595</x:v>
+        <x:v>1594</x:v>
       </x:c>
       <x:c r="D145" s="14" t="str">
-        <x:v>series_000100</x:v>
+        <x:v>series_000099</x:v>
       </x:c>
       <x:c r="E145" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F145" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1595</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1594</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
@@ -8435,16 +9012,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C146" s="14" t="str">
-        <x:v>1749</x:v>
+        <x:v>1595</x:v>
       </x:c>
       <x:c r="D146" s="14" t="str">
-        <x:v>series_000017</x:v>
+        <x:v>series_000100</x:v>
       </x:c>
       <x:c r="E146" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F146" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1749</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1595</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
@@ -8455,16 +9032,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C147" s="14" t="str">
-        <x:v>1846</x:v>
+        <x:v>1749</x:v>
       </x:c>
       <x:c r="D147" s="14" t="str">
-        <x:v>series_000015</x:v>
+        <x:v>series_000017</x:v>
       </x:c>
       <x:c r="E147" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F147" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1846</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1749</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
@@ -8475,36 +9052,36 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C148" s="14" t="str">
-        <x:v>1891</x:v>
+        <x:v>1846</x:v>
       </x:c>
       <x:c r="D148" s="14" t="str">
-        <x:v>series_000016</x:v>
+        <x:v>series_000015</x:v>
       </x:c>
       <x:c r="E148" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F148" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1891</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1846</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B149" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C149" s="14" t="str">
-        <x:v>10077</x:v>
+        <x:v>1891</x:v>
       </x:c>
       <x:c r="D149" s="14" t="str">
-        <x:v>label_000063</x:v>
+        <x:v>series_000016</x:v>
       </x:c>
       <x:c r="E149" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F149" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10077</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1891</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
@@ -8515,16 +9092,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C150" s="14" t="str">
-        <x:v>10106</x:v>
+        <x:v>10077</x:v>
       </x:c>
       <x:c r="D150" s="14" t="str">
-        <x:v>label_000053</x:v>
+        <x:v>label_000063</x:v>
       </x:c>
       <x:c r="E150" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F150" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10106</x:v>
+        <x:v>https://moodyz.com/works/list/label/10077</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
@@ -8535,16 +9112,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C151" s="14" t="str">
-        <x:v>10107</x:v>
+        <x:v>10106</x:v>
       </x:c>
       <x:c r="D151" s="14" t="str">
-        <x:v>label_000046</x:v>
+        <x:v>label_000053</x:v>
       </x:c>
       <x:c r="E151" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F151" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10107</x:v>
+        <x:v>https://moodyz.com/works/list/label/10106</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
@@ -8555,16 +9132,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C152" s="14" t="str">
-        <x:v>10131</x:v>
+        <x:v>10107</x:v>
       </x:c>
       <x:c r="D152" s="14" t="str">
-        <x:v>label_000047</x:v>
+        <x:v>label_000046</x:v>
       </x:c>
       <x:c r="E152" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F152" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10131</x:v>
+        <x:v>https://moodyz.com/works/list/label/10107</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
@@ -8575,16 +9152,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C153" s="14" t="str">
-        <x:v>10142</x:v>
+        <x:v>10131</x:v>
       </x:c>
       <x:c r="D153" s="14" t="str">
-        <x:v>label_000060</x:v>
+        <x:v>label_000047</x:v>
       </x:c>
       <x:c r="E153" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F153" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10142</x:v>
+        <x:v>https://moodyz.com/works/list/label/10131</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
@@ -8595,16 +9172,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C154" s="14" t="str">
-        <x:v>10144</x:v>
+        <x:v>10142</x:v>
       </x:c>
       <x:c r="D154" s="14" t="str">
-        <x:v>label_000061</x:v>
+        <x:v>label_000060</x:v>
       </x:c>
       <x:c r="E154" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F154" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10144</x:v>
+        <x:v>https://moodyz.com/works/list/label/10142</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
@@ -8615,16 +9192,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C155" s="14" t="str">
-        <x:v>10151</x:v>
+        <x:v>10144</x:v>
       </x:c>
       <x:c r="D155" s="14" t="str">
-        <x:v>label_000062</x:v>
+        <x:v>label_000061</x:v>
       </x:c>
       <x:c r="E155" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F155" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10151</x:v>
+        <x:v>https://moodyz.com/works/list/label/10144</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
@@ -8635,16 +9212,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C156" s="14" t="str">
-        <x:v>10157</x:v>
+        <x:v>10151</x:v>
       </x:c>
       <x:c r="D156" s="14" t="str">
-        <x:v>label_000058</x:v>
+        <x:v>label_000062</x:v>
       </x:c>
       <x:c r="E156" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F156" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10157</x:v>
+        <x:v>https://moodyz.com/works/list/label/10151</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
@@ -8655,16 +9232,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C157" s="14" t="str">
-        <x:v>10172</x:v>
+        <x:v>10157</x:v>
       </x:c>
       <x:c r="D157" s="14" t="str">
-        <x:v>label_000064</x:v>
+        <x:v>label_000058</x:v>
       </x:c>
       <x:c r="E157" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F157" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10172</x:v>
+        <x:v>https://moodyz.com/works/list/label/10157</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
@@ -8675,16 +9252,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C158" s="14" t="str">
-        <x:v>10174</x:v>
+        <x:v>10172</x:v>
       </x:c>
       <x:c r="D158" s="14" t="str">
-        <x:v>label_000050</x:v>
+        <x:v>label_000064</x:v>
       </x:c>
       <x:c r="E158" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F158" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10174</x:v>
+        <x:v>https://moodyz.com/works/list/label/10172</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
@@ -8695,16 +9272,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C159" s="14" t="str">
-        <x:v>11471</x:v>
+        <x:v>10174</x:v>
       </x:c>
       <x:c r="D159" s="14" t="str">
-        <x:v>label_000057</x:v>
+        <x:v>label_000050</x:v>
       </x:c>
       <x:c r="E159" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F159" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/11471</x:v>
+        <x:v>https://moodyz.com/works/list/label/10174</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
@@ -8715,16 +9292,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C160" s="14" t="str">
-        <x:v>12798</x:v>
+        <x:v>11471</x:v>
       </x:c>
       <x:c r="D160" s="14" t="str">
-        <x:v>label_000002</x:v>
+        <x:v>label_000057</x:v>
       </x:c>
       <x:c r="E160" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F160" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/12798</x:v>
+        <x:v>https://moodyz.com/works/list/label/11471</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
@@ -8735,16 +9312,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C161" s="14" t="str">
-        <x:v>5046</x:v>
+        <x:v>12798</x:v>
       </x:c>
       <x:c r="D161" s="14" t="str">
-        <x:v>label_000039</x:v>
+        <x:v>label_000002</x:v>
       </x:c>
       <x:c r="E161" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F161" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5046</x:v>
+        <x:v>https://moodyz.com/works/list/label/12798</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
@@ -8755,16 +9332,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C162" s="14" t="str">
-        <x:v>5047</x:v>
+        <x:v>5046</x:v>
       </x:c>
       <x:c r="D162" s="14" t="str">
-        <x:v>label_000038</x:v>
+        <x:v>label_000039</x:v>
       </x:c>
       <x:c r="E162" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F162" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5047</x:v>
+        <x:v>https://moodyz.com/works/list/label/5046</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
@@ -8775,16 +9352,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C163" s="14" t="str">
-        <x:v>5048</x:v>
+        <x:v>5047</x:v>
       </x:c>
       <x:c r="D163" s="14" t="str">
-        <x:v>label_000001</x:v>
+        <x:v>label_000038</x:v>
       </x:c>
       <x:c r="E163" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F163" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5048</x:v>
+        <x:v>https://moodyz.com/works/list/label/5047</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
@@ -8795,16 +9372,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C164" s="14" t="str">
-        <x:v>5049</x:v>
+        <x:v>5048</x:v>
       </x:c>
       <x:c r="D164" s="14" t="str">
-        <x:v>label_000045</x:v>
+        <x:v>label_000001</x:v>
       </x:c>
       <x:c r="E164" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F164" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5049</x:v>
+        <x:v>https://moodyz.com/works/list/label/5048</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
@@ -8815,16 +9392,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C165" s="14" t="str">
-        <x:v>5090</x:v>
+        <x:v>5049</x:v>
       </x:c>
       <x:c r="D165" s="14" t="str">
-        <x:v>label_000044</x:v>
+        <x:v>label_000045</x:v>
       </x:c>
       <x:c r="E165" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F165" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5090</x:v>
+        <x:v>https://moodyz.com/works/list/label/5049</x:v>
       </x:c>
     </x:row>
     <x:row r="166">
@@ -8835,16 +9412,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C166" s="14" t="str">
-        <x:v>5409</x:v>
+        <x:v>5090</x:v>
       </x:c>
       <x:c r="D166" s="14" t="str">
-        <x:v>label_000049</x:v>
+        <x:v>label_000044</x:v>
       </x:c>
       <x:c r="E166" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F166" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5409</x:v>
+        <x:v>https://moodyz.com/works/list/label/5090</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
@@ -8855,16 +9432,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C167" s="14" t="str">
-        <x:v>6879</x:v>
+        <x:v>5409</x:v>
       </x:c>
       <x:c r="D167" s="14" t="str">
-        <x:v>label_000040</x:v>
+        <x:v>label_000049</x:v>
       </x:c>
       <x:c r="E167" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F167" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/6879</x:v>
+        <x:v>https://moodyz.com/works/list/label/5409</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
@@ -8875,16 +9452,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C168" s="14" t="str">
-        <x:v>85265</x:v>
+        <x:v>6879</x:v>
       </x:c>
       <x:c r="D168" s="14" t="str">
-        <x:v>label_000056</x:v>
+        <x:v>label_000040</x:v>
       </x:c>
       <x:c r="E168" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F168" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/85265</x:v>
+        <x:v>https://moodyz.com/works/list/label/6879</x:v>
       </x:c>
     </x:row>
     <x:row r="169">
@@ -8895,16 +9472,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C169" s="14" t="str">
-        <x:v>8916</x:v>
+        <x:v>85265</x:v>
       </x:c>
       <x:c r="D169" s="14" t="str">
-        <x:v>label_000051</x:v>
+        <x:v>label_000056</x:v>
       </x:c>
       <x:c r="E169" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F169" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/8916</x:v>
+        <x:v>https://moodyz.com/works/list/label/85265</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
@@ -8915,16 +9492,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C170" s="14" t="str">
-        <x:v>8917</x:v>
+        <x:v>8916</x:v>
       </x:c>
       <x:c r="D170" s="14" t="str">
-        <x:v>label_000055</x:v>
+        <x:v>label_000051</x:v>
       </x:c>
       <x:c r="E170" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F170" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/8917</x:v>
+        <x:v>https://moodyz.com/works/list/label/8916</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
@@ -8935,16 +9512,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C171" s="14" t="str">
-        <x:v>9288</x:v>
+        <x:v>8917</x:v>
       </x:c>
       <x:c r="D171" s="14" t="str">
-        <x:v>label_000054</x:v>
+        <x:v>label_000055</x:v>
       </x:c>
       <x:c r="E171" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F171" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9288</x:v>
+        <x:v>https://moodyz.com/works/list/label/8917</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -8955,16 +9532,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C172" s="14" t="str">
-        <x:v>9308</x:v>
+        <x:v>9288</x:v>
       </x:c>
       <x:c r="D172" s="14" t="str">
-        <x:v>label_000043</x:v>
+        <x:v>label_000054</x:v>
       </x:c>
       <x:c r="E172" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F172" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9308</x:v>
+        <x:v>https://moodyz.com/works/list/label/9288</x:v>
       </x:c>
     </x:row>
     <x:row r="173">
@@ -8975,16 +9552,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C173" s="14" t="str">
-        <x:v>9397</x:v>
+        <x:v>9308</x:v>
       </x:c>
       <x:c r="D173" s="14" t="str">
-        <x:v>label_000052</x:v>
+        <x:v>label_000043</x:v>
       </x:c>
       <x:c r="E173" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F173" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9397</x:v>
+        <x:v>https://moodyz.com/works/list/label/9308</x:v>
       </x:c>
     </x:row>
     <x:row r="174">
@@ -8995,16 +9572,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C174" s="14" t="str">
-        <x:v>9458</x:v>
+        <x:v>9397</x:v>
       </x:c>
       <x:c r="D174" s="14" t="str">
-        <x:v>label_000048</x:v>
+        <x:v>label_000052</x:v>
       </x:c>
       <x:c r="E174" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F174" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9458</x:v>
+        <x:v>https://moodyz.com/works/list/label/9397</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -9015,16 +9592,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C175" s="14" t="str">
-        <x:v>9483</x:v>
+        <x:v>9458</x:v>
       </x:c>
       <x:c r="D175" s="14" t="str">
-        <x:v>label_000059</x:v>
+        <x:v>label_000048</x:v>
       </x:c>
       <x:c r="E175" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F175" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9483</x:v>
+        <x:v>https://moodyz.com/works/list/label/9458</x:v>
       </x:c>
     </x:row>
     <x:row r="176">
@@ -9035,16 +9612,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C176" s="14" t="str">
-        <x:v>9732</x:v>
+        <x:v>9483</x:v>
       </x:c>
       <x:c r="D176" s="14" t="str">
-        <x:v>label_000042</x:v>
+        <x:v>label_000059</x:v>
       </x:c>
       <x:c r="E176" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F176" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9732</x:v>
+        <x:v>https://moodyz.com/works/list/label/9483</x:v>
       </x:c>
     </x:row>
     <x:row r="177">
@@ -9055,115 +9632,195 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C177" s="14" t="str">
-        <x:v>9782</x:v>
+        <x:v>9732</x:v>
       </x:c>
       <x:c r="D177" s="14" t="str">
-        <x:v>label_000041</x:v>
+        <x:v>label_000042</x:v>
       </x:c>
       <x:c r="E177" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F177" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9782</x:v>
+        <x:v>https://moodyz.com/works/list/label/9732</x:v>
       </x:c>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="14" t="str">
-        <x:v>moodyz.series</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B178" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C178" s="14" t="str">
-        <x:v>5427</x:v>
+        <x:v>9782</x:v>
       </x:c>
       <x:c r="D178" s="14" t="str">
-        <x:v>series_000002</x:v>
+        <x:v>label_000041</x:v>
       </x:c>
       <x:c r="E178" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F178" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/series/5427</x:v>
+        <x:v>https://moodyz.com/works/list/label/9782</x:v>
       </x:c>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="14" t="str">
-        <x:v>s1.label</x:v>
+        <x:v>moodyz.series</x:v>
       </x:c>
       <x:c r="B179" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C179" s="14" t="str">
-        <x:v>4355</x:v>
+        <x:v>3489</x:v>
       </x:c>
       <x:c r="D179" s="14" t="str">
-        <x:v>label_000081</x:v>
+        <x:v>series_000101</x:v>
       </x:c>
       <x:c r="E179" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F179" s="14" t="str">
-        <x:v>https://s1s1s1.com/works/list/label/4355</x:v>
+        <x:v>https://moodyz.com/works/list/series/3489</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="14" t="str">
-        <x:v>s1.series</x:v>
+        <x:v>moodyz.series</x:v>
       </x:c>
       <x:c r="B180" s="14" t="str">
         <x:v>series</x:v>
       </x:c>
       <x:c r="C180" s="14" t="str">
-        <x:v>414</x:v>
+        <x:v>3519</x:v>
       </x:c>
       <x:c r="D180" s="14" t="str">
-        <x:v>series_000001</x:v>
+        <x:v>series_000102</x:v>
       </x:c>
       <x:c r="E180" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F180" s="14" t="str">
-        <x:v>https://s1s1s1.com/works/list/series/414</x:v>
+        <x:v>https://moodyz.com/works/list/series/3519</x:v>
       </x:c>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="14" t="str">
-        <x:v>s1.series</x:v>
+        <x:v>moodyz.series</x:v>
       </x:c>
       <x:c r="B181" s="14" t="str">
         <x:v>series</x:v>
       </x:c>
       <x:c r="C181" s="14" t="str">
-        <x:v>422</x:v>
+        <x:v>3562</x:v>
       </x:c>
       <x:c r="D181" s="14" t="str">
-        <x:v>series_000005</x:v>
+        <x:v>series_000103</x:v>
       </x:c>
       <x:c r="E181" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F181" s="14" t="str">
-        <x:v>https://s1s1s1.com/works/list/series/422</x:v>
+        <x:v>https://moodyz.com/works/list/series/3562</x:v>
       </x:c>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="14" t="str">
-        <x:v>s1.series</x:v>
+        <x:v>moodyz.series</x:v>
       </x:c>
       <x:c r="B182" s="14" t="str">
         <x:v>series</x:v>
       </x:c>
       <x:c r="C182" s="14" t="str">
+        <x:v>5427</x:v>
+      </x:c>
+      <x:c r="D182" s="14" t="str">
+        <x:v>series_000002</x:v>
+      </x:c>
+      <x:c r="E182" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F182" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/5427</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" s="14" t="str">
+        <x:v>s1.label</x:v>
+      </x:c>
+      <x:c r="B183" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C183" s="14" t="str">
+        <x:v>4355</x:v>
+      </x:c>
+      <x:c r="D183" s="14" t="str">
+        <x:v>label_000081</x:v>
+      </x:c>
+      <x:c r="E183" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F183" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/label/4355</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="B184" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C184" s="14" t="str">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="D184" s="14" t="str">
+        <x:v>series_000001</x:v>
+      </x:c>
+      <x:c r="E184" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F184" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/414</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="B185" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C185" s="14" t="str">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="D185" s="14" t="str">
+        <x:v>series_000005</x:v>
+      </x:c>
+      <x:c r="E185" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F185" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/422</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="B186" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C186" s="14" t="str">
         <x:v>570</x:v>
       </x:c>
-      <x:c r="D182" s="14" t="str">
+      <x:c r="D186" s="14" t="str">
         <x:v>series_000006</x:v>
       </x:c>
-      <x:c r="E182" s="14" t="str">
-        <x:v>approved</x:v>
-      </x:c>
-      <x:c r="F182" s="14" t="str">
+      <x:c r="E186" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F186" s="14" t="str">
         <x:v>https://s1s1s1.com/works/list/series/570</x:v>
       </x:c>
     </x:row>
@@ -9172,19 +9829,19 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="46" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="60" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="78" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="80" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -10524,28 +11181,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B47" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>ideapocket.series</x:v>
       </x:c>
       <x:c r="C47" s="14" t="str">
-        <x:v>1546</x:v>
+        <x:v>939</x:v>
       </x:c>
       <x:c r="D47" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+        <x:v>ideapocket-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E47" s="14" t="str">
-        <x:v>series_000053</x:v>
+        <x:v>series_000104</x:v>
       </x:c>
       <x:c r="F47" s="14" t="str">
-        <x:v>もう一つの熟バス</x:v>
+        <x:v>見つめる愛情イラマチオ</x:v>
       </x:c>
       <x:c r="G47" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000001</x:v>
       </x:c>
       <x:c r="H47" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1546</x:v>
+        <x:v>https://ideapocket.com/works/list/series/939</x:v>
       </x:c>
       <x:c r="I47" s="14" t="str">
-        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 0.4.8 跨 Provider partial Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -10556,22 +11213,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C48" s="14" t="str">
-        <x:v>1547</x:v>
+        <x:v>1546</x:v>
       </x:c>
       <x:c r="D48" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="E48" s="14" t="str">
-        <x:v>series_000054</x:v>
+        <x:v>series_000053</x:v>
       </x:c>
       <x:c r="F48" s="14" t="str">
-        <x:v>母さんとしたい!</x:v>
+        <x:v>もう一つの熟バス</x:v>
       </x:c>
       <x:c r="G48" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H48" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1547</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1546</x:v>
       </x:c>
       <x:c r="I48" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -10585,22 +11242,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C49" s="14" t="str">
-        <x:v>1548</x:v>
+        <x:v>1547</x:v>
       </x:c>
       <x:c r="D49" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="E49" s="14" t="str">
-        <x:v>series_000055</x:v>
+        <x:v>series_000054</x:v>
       </x:c>
       <x:c r="F49" s="14" t="str">
-        <x:v>義父に犯されて・・・ 美嫁いぢり</x:v>
+        <x:v>母さんとしたい!</x:v>
       </x:c>
       <x:c r="G49" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H49" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1548</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1547</x:v>
       </x:c>
       <x:c r="I49" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -10614,25 +11271,25 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C50" s="14" t="str">
-        <x:v>1549</x:v>
+        <x:v>1548</x:v>
       </x:c>
       <x:c r="D50" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+        <x:v>madonna-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="E50" s="14" t="str">
-        <x:v>series_000027</x:v>
+        <x:v>series_000055</x:v>
       </x:c>
       <x:c r="F50" s="14" t="str">
-        <x:v>となりの奥さん</x:v>
+        <x:v>義父に犯されて・・・ 美嫁いぢり</x:v>
       </x:c>
       <x:c r="G50" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H50" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1549</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1548</x:v>
       </x:c>
       <x:c r="I50" s="14" t="str">
-        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -10643,22 +11300,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C51" s="14" t="str">
-        <x:v>1550</x:v>
+        <x:v>1549</x:v>
       </x:c>
       <x:c r="D51" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E51" s="14" t="str">
-        <x:v>series_000028</x:v>
+        <x:v>series_000027</x:v>
       </x:c>
       <x:c r="F51" s="14" t="str">
-        <x:v>美熟女と黒人</x:v>
+        <x:v>となりの奥さん</x:v>
       </x:c>
       <x:c r="G51" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H51" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1550</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1549</x:v>
       </x:c>
       <x:c r="I51" s="14" t="str">
         <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -10672,22 +11329,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C52" s="14" t="str">
-        <x:v>1551</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D52" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E52" s="14" t="str">
-        <x:v>series_000029</x:v>
+        <x:v>series_000028</x:v>
       </x:c>
       <x:c r="F52" s="14" t="str">
-        <x:v>愛する夫の目の前で・・・</x:v>
+        <x:v>美熟女と黒人</x:v>
       </x:c>
       <x:c r="G52" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H52" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1551</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1550</x:v>
       </x:c>
       <x:c r="I52" s="14" t="str">
         <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -10701,22 +11358,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C53" s="14" t="str">
-        <x:v>1552</x:v>
+        <x:v>1551</x:v>
       </x:c>
       <x:c r="D53" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E53" s="14" t="str">
-        <x:v>series_000030</x:v>
+        <x:v>series_000029</x:v>
       </x:c>
       <x:c r="F53" s="14" t="str">
-        <x:v>特選 友達の母</x:v>
+        <x:v>愛する夫の目の前で・・・</x:v>
       </x:c>
       <x:c r="G53" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H53" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1552</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1551</x:v>
       </x:c>
       <x:c r="I53" s="14" t="str">
         <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -10730,22 +11387,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C54" s="14" t="str">
-        <x:v>1553</x:v>
+        <x:v>1552</x:v>
       </x:c>
       <x:c r="D54" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E54" s="14" t="str">
-        <x:v>series_000031</x:v>
+        <x:v>series_000030</x:v>
       </x:c>
       <x:c r="F54" s="14" t="str">
-        <x:v>僕のおばさん</x:v>
+        <x:v>特選 友達の母</x:v>
       </x:c>
       <x:c r="G54" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H54" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1553</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1552</x:v>
       </x:c>
       <x:c r="I54" s="14" t="str">
         <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -10759,22 +11416,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C55" s="14" t="str">
-        <x:v>1554</x:v>
+        <x:v>1553</x:v>
       </x:c>
       <x:c r="D55" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E55" s="14" t="str">
-        <x:v>series_000032</x:v>
+        <x:v>series_000031</x:v>
       </x:c>
       <x:c r="F55" s="14" t="str">
-        <x:v>素人人妻ナンパ総集編4時間</x:v>
+        <x:v>僕のおばさん</x:v>
       </x:c>
       <x:c r="G55" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H55" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1554</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1553</x:v>
       </x:c>
       <x:c r="I55" s="14" t="str">
         <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -10788,22 +11445,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C56" s="14" t="str">
-        <x:v>1555</x:v>
+        <x:v>1554</x:v>
       </x:c>
       <x:c r="D56" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E56" s="14" t="str">
-        <x:v>series_000033</x:v>
+        <x:v>series_000032</x:v>
       </x:c>
       <x:c r="F56" s="14" t="str">
-        <x:v>五十路熟女18人4時間</x:v>
+        <x:v>素人人妻ナンパ総集編4時間</x:v>
       </x:c>
       <x:c r="G56" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H56" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1555</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1554</x:v>
       </x:c>
       <x:c r="I56" s="14" t="str">
         <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -10817,22 +11474,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C57" s="14" t="str">
-        <x:v>1556</x:v>
+        <x:v>1555</x:v>
       </x:c>
       <x:c r="D57" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E57" s="14" t="str">
-        <x:v>series_000034</x:v>
+        <x:v>series_000033</x:v>
       </x:c>
       <x:c r="F57" s="14" t="str">
-        <x:v>団地妻20人4時間</x:v>
+        <x:v>五十路熟女18人4時間</x:v>
       </x:c>
       <x:c r="G57" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H57" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1556</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1555</x:v>
       </x:c>
       <x:c r="I57" s="14" t="str">
         <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -10846,22 +11503,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C58" s="14" t="str">
-        <x:v>1557</x:v>
+        <x:v>1556</x:v>
       </x:c>
       <x:c r="D58" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E58" s="14" t="str">
-        <x:v>series_000035</x:v>
+        <x:v>series_000034</x:v>
       </x:c>
       <x:c r="F58" s="14" t="str">
-        <x:v>犯された熟女たち総集編4時間</x:v>
+        <x:v>団地妻20人4時間</x:v>
       </x:c>
       <x:c r="G58" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H58" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1557</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1556</x:v>
       </x:c>
       <x:c r="I58" s="14" t="str">
         <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -10875,22 +11532,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C59" s="14" t="str">
-        <x:v>1558</x:v>
+        <x:v>1557</x:v>
       </x:c>
       <x:c r="D59" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E59" s="14" t="str">
-        <x:v>series_000036</x:v>
+        <x:v>series_000035</x:v>
       </x:c>
       <x:c r="F59" s="14" t="str">
-        <x:v>妖艶おんな愛戯</x:v>
+        <x:v>犯された熟女たち総集編4時間</x:v>
       </x:c>
       <x:c r="G59" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H59" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1558</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1557</x:v>
       </x:c>
       <x:c r="I59" s="14" t="str">
         <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -10904,25 +11561,25 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C60" s="14" t="str">
-        <x:v>1559</x:v>
+        <x:v>1558</x:v>
       </x:c>
       <x:c r="D60" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E60" s="14" t="str">
-        <x:v>series_000056</x:v>
+        <x:v>series_000036</x:v>
       </x:c>
       <x:c r="F60" s="14" t="str">
-        <x:v>五十路の性</x:v>
+        <x:v>妖艶おんな愛戯</x:v>
       </x:c>
       <x:c r="G60" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H60" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1559</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1558</x:v>
       </x:c>
       <x:c r="I60" s="14" t="str">
-        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -10933,22 +11590,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C61" s="14" t="str">
-        <x:v>1560</x:v>
+        <x:v>1559</x:v>
       </x:c>
       <x:c r="D61" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="E61" s="14" t="str">
-        <x:v>series_000057</x:v>
+        <x:v>series_000056</x:v>
       </x:c>
       <x:c r="F61" s="14" t="str">
-        <x:v>新・素人人妻ナンパ</x:v>
+        <x:v>五十路の性</x:v>
       </x:c>
       <x:c r="G61" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H61" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1560</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1559</x:v>
       </x:c>
       <x:c r="I61" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -10962,22 +11619,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C62" s="14" t="str">
-        <x:v>1561</x:v>
+        <x:v>1560</x:v>
       </x:c>
       <x:c r="D62" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="E62" s="14" t="str">
-        <x:v>series_000058</x:v>
+        <x:v>series_000057</x:v>
       </x:c>
       <x:c r="F62" s="14" t="str">
-        <x:v>こちらマドンナ独身寮・ただいま満室</x:v>
+        <x:v>新・素人人妻ナンパ</x:v>
       </x:c>
       <x:c r="G62" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H62" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1561</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1560</x:v>
       </x:c>
       <x:c r="I62" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -10991,22 +11648,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C63" s="14" t="str">
-        <x:v>1562</x:v>
+        <x:v>1561</x:v>
       </x:c>
       <x:c r="D63" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="E63" s="14" t="str">
-        <x:v>series_000059</x:v>
+        <x:v>series_000058</x:v>
       </x:c>
       <x:c r="F63" s="14" t="str">
-        <x:v>3D作品</x:v>
+        <x:v>こちらマドンナ独身寮・ただいま満室</x:v>
       </x:c>
       <x:c r="G63" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H63" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1562</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1561</x:v>
       </x:c>
       <x:c r="I63" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11020,22 +11677,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C64" s="14" t="str">
-        <x:v>1563</x:v>
+        <x:v>1562</x:v>
       </x:c>
       <x:c r="D64" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="E64" s="14" t="str">
-        <x:v>series_000060</x:v>
+        <x:v>series_000059</x:v>
       </x:c>
       <x:c r="F64" s="14" t="str">
-        <x:v>密着セックス</x:v>
+        <x:v>3D作品</x:v>
       </x:c>
       <x:c r="G64" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H64" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1563</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1562</x:v>
       </x:c>
       <x:c r="I64" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11049,22 +11706,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C65" s="14" t="str">
-        <x:v>1564</x:v>
+        <x:v>1563</x:v>
       </x:c>
       <x:c r="D65" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="E65" s="14" t="str">
-        <x:v>series_000061</x:v>
+        <x:v>series_000060</x:v>
       </x:c>
       <x:c r="F65" s="14" t="str">
-        <x:v>交換夫婦NTR</x:v>
+        <x:v>密着セックス</x:v>
       </x:c>
       <x:c r="G65" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H65" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1564</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1563</x:v>
       </x:c>
       <x:c r="I65" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11078,25 +11735,25 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C66" s="14" t="str">
-        <x:v>1565</x:v>
+        <x:v>1564</x:v>
       </x:c>
       <x:c r="D66" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+        <x:v>madonna-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="E66" s="14" t="str">
-        <x:v>series_000081</x:v>
+        <x:v>series_000061</x:v>
       </x:c>
       <x:c r="F66" s="14" t="str">
-        <x:v>出張先のビジネスホテルでずっと憧れていた女上司と</x:v>
+        <x:v>交換夫婦NTR</x:v>
       </x:c>
       <x:c r="G66" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H66" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1565</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1564</x:v>
       </x:c>
       <x:c r="I66" s="14" t="str">
-        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -11107,22 +11764,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C67" s="14" t="str">
-        <x:v>1566</x:v>
+        <x:v>1565</x:v>
       </x:c>
       <x:c r="D67" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E67" s="14" t="str">
-        <x:v>series_000082</x:v>
+        <x:v>series_000081</x:v>
       </x:c>
       <x:c r="F67" s="14" t="str">
-        <x:v>人妻秘書、汗と接吻に満ちた社長室中出し性交</x:v>
+        <x:v>出張先のビジネスホテルでずっと憧れていた女上司と</x:v>
       </x:c>
       <x:c r="G67" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H67" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1566</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1565</x:v>
       </x:c>
       <x:c r="I67" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11136,22 +11793,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C68" s="14" t="str">
-        <x:v>1570</x:v>
+        <x:v>1566</x:v>
       </x:c>
       <x:c r="D68" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E68" s="14" t="str">
-        <x:v>series_000083</x:v>
+        <x:v>series_000082</x:v>
       </x:c>
       <x:c r="F68" s="14" t="str">
-        <x:v>働くおばさん!</x:v>
+        <x:v>人妻秘書、汗と接吻に満ちた社長室中出し性交</x:v>
       </x:c>
       <x:c r="G68" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H68" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1570</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1566</x:v>
       </x:c>
       <x:c r="I68" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11165,22 +11822,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C69" s="14" t="str">
-        <x:v>1571</x:v>
+        <x:v>1570</x:v>
       </x:c>
       <x:c r="D69" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E69" s="14" t="str">
-        <x:v>series_000084</x:v>
+        <x:v>series_000083</x:v>
       </x:c>
       <x:c r="F69" s="14" t="str">
-        <x:v>四十路の性</x:v>
+        <x:v>働くおばさん!</x:v>
       </x:c>
       <x:c r="G69" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H69" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1571</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1570</x:v>
       </x:c>
       <x:c r="I69" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11194,22 +11851,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C70" s="14" t="str">
-        <x:v>1572</x:v>
+        <x:v>1571</x:v>
       </x:c>
       <x:c r="D70" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E70" s="14" t="str">
-        <x:v>series_000085</x:v>
+        <x:v>series_000084</x:v>
       </x:c>
       <x:c r="F70" s="14" t="str">
-        <x:v>最高の筆おろし!</x:v>
+        <x:v>四十路の性</x:v>
       </x:c>
       <x:c r="G70" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H70" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1572</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1571</x:v>
       </x:c>
       <x:c r="I70" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11223,22 +11880,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C71" s="14" t="str">
-        <x:v>1573</x:v>
+        <x:v>1572</x:v>
       </x:c>
       <x:c r="D71" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E71" s="14" t="str">
-        <x:v>series_000086</x:v>
+        <x:v>series_000085</x:v>
       </x:c>
       <x:c r="F71" s="14" t="str">
-        <x:v>ハメ狂い淫乱熟女</x:v>
+        <x:v>最高の筆おろし!</x:v>
       </x:c>
       <x:c r="G71" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H71" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1573</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1572</x:v>
       </x:c>
       <x:c r="I71" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11252,22 +11909,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C72" s="14" t="str">
-        <x:v>1574</x:v>
+        <x:v>1573</x:v>
       </x:c>
       <x:c r="D72" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E72" s="14" t="str">
-        <x:v>series_000087</x:v>
+        <x:v>series_000086</x:v>
       </x:c>
       <x:c r="F72" s="14" t="str">
-        <x:v>犯されたセールスレディ</x:v>
+        <x:v>ハメ狂い淫乱熟女</x:v>
       </x:c>
       <x:c r="G72" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H72" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1574</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1573</x:v>
       </x:c>
       <x:c r="I72" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11281,22 +11938,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C73" s="14" t="str">
-        <x:v>1579</x:v>
+        <x:v>1574</x:v>
       </x:c>
       <x:c r="D73" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E73" s="14" t="str">
-        <x:v>series_000088</x:v>
+        <x:v>series_000087</x:v>
       </x:c>
       <x:c r="F73" s="14" t="str">
-        <x:v>娘のカレシにイカされた母</x:v>
+        <x:v>犯されたセールスレディ</x:v>
       </x:c>
       <x:c r="G73" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H73" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1579</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1574</x:v>
       </x:c>
       <x:c r="I73" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11310,22 +11967,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C74" s="14" t="str">
-        <x:v>1581</x:v>
+        <x:v>1579</x:v>
       </x:c>
       <x:c r="D74" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E74" s="14" t="str">
-        <x:v>series_000089</x:v>
+        <x:v>series_000088</x:v>
       </x:c>
       <x:c r="F74" s="14" t="str">
-        <x:v>昼下がりのふしだら奥さん</x:v>
+        <x:v>娘のカレシにイカされた母</x:v>
       </x:c>
       <x:c r="G74" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H74" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1581</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1579</x:v>
       </x:c>
       <x:c r="I74" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11339,22 +11996,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C75" s="14" t="str">
-        <x:v>1585</x:v>
+        <x:v>1581</x:v>
       </x:c>
       <x:c r="D75" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E75" s="14" t="str">
-        <x:v>series_000090</x:v>
+        <x:v>series_000089</x:v>
       </x:c>
       <x:c r="F75" s="14" t="str">
-        <x:v>豊潤麗し競泳水着</x:v>
+        <x:v>昼下がりのふしだら奥さん</x:v>
       </x:c>
       <x:c r="G75" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H75" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1585</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1581</x:v>
       </x:c>
       <x:c r="I75" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11368,22 +12025,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C76" s="14" t="str">
-        <x:v>1586</x:v>
+        <x:v>1585</x:v>
       </x:c>
       <x:c r="D76" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E76" s="14" t="str">
-        <x:v>series_000091</x:v>
+        <x:v>series_000090</x:v>
       </x:c>
       <x:c r="F76" s="14" t="str">
-        <x:v>悶絶美熟女の卑猥な日常</x:v>
+        <x:v>豊潤麗し競泳水着</x:v>
       </x:c>
       <x:c r="G76" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H76" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1586</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1585</x:v>
       </x:c>
       <x:c r="I76" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11397,22 +12054,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C77" s="14" t="str">
-        <x:v>1587</x:v>
+        <x:v>1586</x:v>
       </x:c>
       <x:c r="D77" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E77" s="14" t="str">
-        <x:v>series_000092</x:v>
+        <x:v>series_000091</x:v>
       </x:c>
       <x:c r="F77" s="14" t="str">
-        <x:v>MADAM QUEEN × DANCING FUCK</x:v>
+        <x:v>悶絶美熟女の卑猥な日常</x:v>
       </x:c>
       <x:c r="G77" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H77" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1587</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1586</x:v>
       </x:c>
       <x:c r="I77" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11426,22 +12083,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C78" s="14" t="str">
-        <x:v>1588</x:v>
+        <x:v>1587</x:v>
       </x:c>
       <x:c r="D78" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E78" s="14" t="str">
-        <x:v>series_000093</x:v>
+        <x:v>series_000092</x:v>
       </x:c>
       <x:c r="F78" s="14" t="str">
-        <x:v>濡れ透け婦人の甘い疼き</x:v>
+        <x:v>MADAM QUEEN × DANCING FUCK</x:v>
       </x:c>
       <x:c r="G78" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H78" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1588</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1587</x:v>
       </x:c>
       <x:c r="I78" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11455,22 +12112,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C79" s="14" t="str">
-        <x:v>1589</x:v>
+        <x:v>1588</x:v>
       </x:c>
       <x:c r="D79" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E79" s="14" t="str">
-        <x:v>series_000094</x:v>
+        <x:v>series_000093</x:v>
       </x:c>
       <x:c r="F79" s="14" t="str">
-        <x:v>溢れだす美熟女の泉</x:v>
+        <x:v>濡れ透け婦人の甘い疼き</x:v>
       </x:c>
       <x:c r="G79" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H79" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1589</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1588</x:v>
       </x:c>
       <x:c r="I79" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11484,22 +12141,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C80" s="14" t="str">
-        <x:v>1590</x:v>
+        <x:v>1589</x:v>
       </x:c>
       <x:c r="D80" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E80" s="14" t="str">
-        <x:v>series_000095</x:v>
+        <x:v>series_000094</x:v>
       </x:c>
       <x:c r="F80" s="14" t="str">
-        <x:v>匂いたつパンストの誘惑</x:v>
+        <x:v>溢れだす美熟女の泉</x:v>
       </x:c>
       <x:c r="G80" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H80" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1590</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1589</x:v>
       </x:c>
       <x:c r="I80" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11513,22 +12170,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C81" s="14" t="str">
-        <x:v>1591</x:v>
+        <x:v>1590</x:v>
       </x:c>
       <x:c r="D81" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E81" s="14" t="str">
-        <x:v>series_000096</x:v>
+        <x:v>series_000095</x:v>
       </x:c>
       <x:c r="F81" s="14" t="str">
-        <x:v>ムッチリ美熟女ハミ出し水着</x:v>
+        <x:v>匂いたつパンストの誘惑</x:v>
       </x:c>
       <x:c r="G81" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H81" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1591</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1590</x:v>
       </x:c>
       <x:c r="I81" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11542,22 +12199,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C82" s="14" t="str">
-        <x:v>1592</x:v>
+        <x:v>1591</x:v>
       </x:c>
       <x:c r="D82" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E82" s="14" t="str">
-        <x:v>series_000097</x:v>
+        <x:v>series_000096</x:v>
       </x:c>
       <x:c r="F82" s="14" t="str">
-        <x:v>巨尻誘惑</x:v>
+        <x:v>ムッチリ美熟女ハミ出し水着</x:v>
       </x:c>
       <x:c r="G82" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H82" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1592</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1591</x:v>
       </x:c>
       <x:c r="I82" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11571,22 +12228,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C83" s="14" t="str">
-        <x:v>1593</x:v>
+        <x:v>1592</x:v>
       </x:c>
       <x:c r="D83" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E83" s="14" t="str">
-        <x:v>series_000098</x:v>
+        <x:v>series_000097</x:v>
       </x:c>
       <x:c r="F83" s="14" t="str">
-        <x:v>堕ちた万引き妻</x:v>
+        <x:v>巨尻誘惑</x:v>
       </x:c>
       <x:c r="G83" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H83" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1593</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1592</x:v>
       </x:c>
       <x:c r="I83" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11600,22 +12257,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C84" s="14" t="str">
-        <x:v>1594</x:v>
+        <x:v>1593</x:v>
       </x:c>
       <x:c r="D84" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E84" s="14" t="str">
-        <x:v>series_000099</x:v>
+        <x:v>series_000098</x:v>
       </x:c>
       <x:c r="F84" s="14" t="str">
-        <x:v>義母の舌と接吻</x:v>
+        <x:v>堕ちた万引き妻</x:v>
       </x:c>
       <x:c r="G84" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H84" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1594</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1593</x:v>
       </x:c>
       <x:c r="I84" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11629,25 +12286,141 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C85" s="14" t="str">
-        <x:v>1595</x:v>
+        <x:v>1594</x:v>
       </x:c>
       <x:c r="D85" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E85" s="14" t="str">
-        <x:v>series_000100</x:v>
+        <x:v>series_000099</x:v>
       </x:c>
       <x:c r="F85" s="14" t="str">
-        <x:v>狙われたパート妻</x:v>
+        <x:v>義母の舌と接吻</x:v>
       </x:c>
       <x:c r="G85" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H85" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1595</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1594</x:v>
       </x:c>
       <x:c r="I85" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B86" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C86" s="14" t="str">
+        <x:v>1595</x:v>
+      </x:c>
+      <x:c r="D86" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E86" s="14" t="str">
+        <x:v>series_000100</x:v>
+      </x:c>
+      <x:c r="F86" s="14" t="str">
+        <x:v>狙われたパート妻</x:v>
+      </x:c>
+      <x:c r="G86" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H86" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1595</x:v>
+      </x:c>
+      <x:c r="I86" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B87" s="14" t="str">
+        <x:v>moodyz.series</x:v>
+      </x:c>
+      <x:c r="C87" s="14" t="str">
+        <x:v>3489</x:v>
+      </x:c>
+      <x:c r="D87" s="14" t="str">
+        <x:v>moodyz-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E87" s="14" t="str">
+        <x:v>series_000101</x:v>
+      </x:c>
+      <x:c r="F87" s="14" t="str">
+        <x:v>聖水くらぶ</x:v>
+      </x:c>
+      <x:c r="G87" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H87" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3489</x:v>
+      </x:c>
+      <x:c r="I87" s="14" t="str">
+        <x:v>官方 Series 详情页与 0.4.8 跨 Provider partial Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B88" s="14" t="str">
+        <x:v>moodyz.series</x:v>
+      </x:c>
+      <x:c r="C88" s="14" t="str">
+        <x:v>3519</x:v>
+      </x:c>
+      <x:c r="D88" s="14" t="str">
+        <x:v>moodyz-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E88" s="14" t="str">
+        <x:v>series_000102</x:v>
+      </x:c>
+      <x:c r="F88" s="14" t="str">
+        <x:v>W CAST</x:v>
+      </x:c>
+      <x:c r="G88" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H88" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3519</x:v>
+      </x:c>
+      <x:c r="I88" s="14" t="str">
+        <x:v>官方 Series 详情页与 0.4.8 跨 Provider partial Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B89" s="14" t="str">
+        <x:v>moodyz.series</x:v>
+      </x:c>
+      <x:c r="C89" s="14" t="str">
+        <x:v>3562</x:v>
+      </x:c>
+      <x:c r="D89" s="14" t="str">
+        <x:v>moodyz-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E89" s="14" t="str">
+        <x:v>series_000103</x:v>
+      </x:c>
+      <x:c r="F89" s="14" t="str">
+        <x:v>聖水痴女ハーレム</x:v>
+      </x:c>
+      <x:c r="G89" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H89" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3562</x:v>
+      </x:c>
+      <x:c r="I89" s="14" t="str">
+        <x:v>官方 Series 详情页与 0.4.8 跨 Provider partial Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11655,7 +12428,144 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="46" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Snapshot ID</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>Maker</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>Captured</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>Entries</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>Complete</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="14" t="str">
+        <x:v>attackers-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="B2" s="14" t="str">
+        <x:v>attackers.series</x:v>
+      </x:c>
+      <x:c r="C2" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="D2" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="E2" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F2" s="14" t="str">
+        <x:v>no</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="14" t="str">
+        <x:v>ideapocket-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="B3" s="14" t="str">
+        <x:v>ideapocket.series</x:v>
+      </x:c>
+      <x:c r="C3" s="14" t="str">
+        <x:v>アイデアポケット</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F3" s="14" t="str">
+        <x:v>no</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="B4" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C4" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="D4" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="E4" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F4" s="14" t="str">
+        <x:v>no</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="14" t="str">
+        <x:v>moodyz-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="B5" s="14" t="str">
+        <x:v>moodyz.series</x:v>
+      </x:c>
+      <x:c r="C5" s="14" t="str">
+        <x:v>MOODYZ</x:v>
+      </x:c>
+      <x:c r="D5" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="E5" s="14" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F5" s="14" t="str">
+        <x:v>no</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="14" t="str">
+        <x:v>s1-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="str">
+        <x:v>エスワン</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="str">
+        <x:v>2026-09-04</x:v>
+      </x:c>
+      <x:c r="E6" s="14" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F6" s="14" t="str">
+        <x:v>no</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -11694,61 +12604,4 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="44" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="6" t="str">
-        <x:v>Snapshot ID</x:v>
-      </x:c>
-      <x:c r="B1" s="6" t="str">
-        <x:v>Provider</x:v>
-      </x:c>
-      <x:c r="C1" s="6" t="str">
-        <x:v>Entries</x:v>
-      </x:c>
-      <x:c r="D1" s="6" t="str">
-        <x:v>Complete</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="14" t="str">
-        <x:v>attackers-series-2026-09-04-partial-003</x:v>
-      </x:c>
-      <x:c r="B2" s="14" t="str">
-        <x:v>attackers.series</x:v>
-      </x:c>
-      <x:c r="C2" s="14" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D2" s="14" t="str">
-        <x:v>no</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-003</x:v>
-      </x:c>
-      <x:c r="B3" s="14" t="str">
-        <x:v>madonna.series</x:v>
-      </x:c>
-      <x:c r="C3" s="14" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="str">
-        <x:v>no</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
 </file>
--- a/exports/xlsx/organization-series-registry.xlsx
+++ b/exports/xlsx/organization-series-registry.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organizations" sheetId="1" r:id="Rbfe9a01710b340db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series" sheetId="2" r:id="R9383bcfb1dd44e51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Index Providers" sheetId="3" r:id="R40ffd3400bbc4c3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Registry" sheetId="4" r:id="R63decdd6ea384e36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External ID Mapping" sheetId="5" r:id="Rd43854066e46482d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Candidate Reviews" sheetId="6" r:id="Rd8410ce0836c4b09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Latest Snapshots" sheetId="7" r:id="Rd2c4b8b37b1d4b42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Index Candidates" sheetId="8" r:id="Re9d45c7e0dec4cd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organizations" sheetId="1" r:id="Rb8bf91c6e1f74728"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series" sheetId="2" r:id="Rdd212fd0f1f04008"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Index Providers" sheetId="3" r:id="Re2de6957731347a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Registry" sheetId="4" r:id="R29063f2eff024c79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External ID Mapping" sheetId="5" r:id="R18161e3a313f49ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Candidate Reviews" sheetId="6" r:id="R1c7ff3dd77894792"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Latest Snapshots" sheetId="7" r:id="R719ec3c7f17f411a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Index Candidates" sheetId="8" r:id="Rf76d7fbd1b3b4f80"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2741,12 +2741,12 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="42" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="44" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="44" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="50" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="56" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="58" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
   </x:cols>
@@ -5794,6 +5794,441 @@
       </x:c>
       <x:c r="I105" s="14" t="str">
         <x:v>0.4.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="14" t="str">
+        <x:v>series_000105</x:v>
+      </x:c>
+      <x:c r="B106" s="14" t="str">
+        <x:v>おねだりバックピストン</x:v>
+      </x:c>
+      <x:c r="C106" s="14" t="str">
+        <x:v>央求后入抽插</x:v>
+      </x:c>
+      <x:c r="D106" s="14" t="str">
+        <x:v>Begging Backstroke Piston</x:v>
+      </x:c>
+      <x:c r="E106" s="14" t="str">
+        <x:v>MOODYZ</x:v>
+      </x:c>
+      <x:c r="F106" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G106" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3563</x:v>
+      </x:c>
+      <x:c r="H106" s="14" t="str">
+        <x:v>moodyz.series:3563</x:v>
+      </x:c>
+      <x:c r="I106" s="14" t="str">
+        <x:v>0.4.9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="14" t="str">
+        <x:v>series_000106</x:v>
+      </x:c>
+      <x:c r="B107" s="14" t="str">
+        <x:v>産後処女を義父に奪われ一度イッたら痙攣アクメが止まらなくなる妻</x:v>
+      </x:c>
+      <x:c r="C107" s="14" t="str">
+        <x:v>产后第一次被公公夺走、高潮后痉挛不止的妻子</x:v>
+      </x:c>
+      <x:c r="D107" s="14" t="str">
+        <x:v>Wife Whose Postpartum First Time Is Taken by Her Father-in-Law</x:v>
+      </x:c>
+      <x:c r="E107" s="14" t="str">
+        <x:v>MOODYZ</x:v>
+      </x:c>
+      <x:c r="F107" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G107" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3564</x:v>
+      </x:c>
+      <x:c r="H107" s="14" t="str">
+        <x:v>moodyz.series:3564</x:v>
+      </x:c>
+      <x:c r="I107" s="14" t="str">
+        <x:v>0.4.9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="14" t="str">
+        <x:v>series_000107</x:v>
+      </x:c>
+      <x:c r="B108" s="14" t="str">
+        <x:v>捜査官を辞めて妻になったのに…</x:v>
+      </x:c>
+      <x:c r="C108" s="14" t="str">
+        <x:v>明明辞去搜查官成为了妻子…</x:v>
+      </x:c>
+      <x:c r="D108" s="14" t="str">
+        <x:v>Even After Quitting as an Investigator to Become a Wife...</x:v>
+      </x:c>
+      <x:c r="E108" s="14" t="str">
+        <x:v>MOODYZ</x:v>
+      </x:c>
+      <x:c r="F108" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G108" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3565</x:v>
+      </x:c>
+      <x:c r="H108" s="14" t="str">
+        <x:v>moodyz.series:3565</x:v>
+      </x:c>
+      <x:c r="I108" s="14" t="str">
+        <x:v>0.4.9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="14" t="str">
+        <x:v>series_000108</x:v>
+      </x:c>
+      <x:c r="B109" s="14" t="str">
+        <x:v>おれに初めてセフレができたので彼女とはできないド変態プレイを</x:v>
+      </x:c>
+      <x:c r="C109" s="14" t="str">
+        <x:v>第一次有了炮友，尝试和女友做不了的重口变态玩法</x:v>
+      </x:c>
+      <x:c r="D109" s="14" t="str">
+        <x:v>Trying Extreme Kinks with My First Sex Friend</x:v>
+      </x:c>
+      <x:c r="E109" s="14" t="str">
+        <x:v>MOODYZ</x:v>
+      </x:c>
+      <x:c r="F109" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G109" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3566</x:v>
+      </x:c>
+      <x:c r="H109" s="14" t="str">
+        <x:v>moodyz.series:3566</x:v>
+      </x:c>
+      <x:c r="I109" s="14" t="str">
+        <x:v>0.4.9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="14" t="str">
+        <x:v>series_000109</x:v>
+      </x:c>
+      <x:c r="B110" s="14" t="str">
+        <x:v>突然の大雨で帰宅難民になった彼女の妹と朝まで…</x:v>
+      </x:c>
+      <x:c r="C110" s="14" t="str">
+        <x:v>突降暴雨无法回家，与女友的妹妹直到天亮…</x:v>
+      </x:c>
+      <x:c r="D110" s="14" t="str">
+        <x:v>Stranded by Sudden Heavy Rain with My Girlfriend’s Sister Until Morning...</x:v>
+      </x:c>
+      <x:c r="E110" s="14" t="str">
+        <x:v>MOODYZ</x:v>
+      </x:c>
+      <x:c r="F110" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G110" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3567</x:v>
+      </x:c>
+      <x:c r="H110" s="14" t="str">
+        <x:v>moodyz.series:3567</x:v>
+      </x:c>
+      <x:c r="I110" s="14" t="str">
+        <x:v>0.4.9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="14" t="str">
+        <x:v>series_000110</x:v>
+      </x:c>
+      <x:c r="B111" s="14" t="str">
+        <x:v>究極のパンストフェチエロティックス</x:v>
+      </x:c>
+      <x:c r="C111" s="14" t="str">
+        <x:v>终极丝袜恋物情色</x:v>
+      </x:c>
+      <x:c r="D111" s="14" t="str">
+        <x:v>Ultimate Pantyhose Fetish Erotics</x:v>
+      </x:c>
+      <x:c r="E111" s="14" t="str">
+        <x:v>アイデアポケット</x:v>
+      </x:c>
+      <x:c r="F111" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G111" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/series/940</x:v>
+      </x:c>
+      <x:c r="H111" s="14" t="str">
+        <x:v>ideapocket.series:940</x:v>
+      </x:c>
+      <x:c r="I111" s="14" t="str">
+        <x:v>0.4.9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="14" t="str">
+        <x:v>series_000111</x:v>
+      </x:c>
+      <x:c r="B112" s="14" t="str">
+        <x:v>キミがイクまで腰振るのをやめない!</x:v>
+      </x:c>
+      <x:c r="C112" s="14" t="str">
+        <x:v>直到你高潮我都不会停止摆腰!</x:v>
+      </x:c>
+      <x:c r="D112" s="14" t="str">
+        <x:v>I Won’t Stop Moving My Hips Until You Come!</x:v>
+      </x:c>
+      <x:c r="E112" s="14" t="str">
+        <x:v>アイデアポケット</x:v>
+      </x:c>
+      <x:c r="F112" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G112" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/series/941</x:v>
+      </x:c>
+      <x:c r="H112" s="14" t="str">
+        <x:v>ideapocket.series:941</x:v>
+      </x:c>
+      <x:c r="I112" s="14" t="str">
+        <x:v>0.4.9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" s="14" t="str">
+        <x:v>series_000112</x:v>
+      </x:c>
+      <x:c r="B113" s="14" t="str">
+        <x:v>汗だくSEX</x:v>
+      </x:c>
+      <x:c r="C113" s="14" t="str">
+        <x:v>汗流浃背SEX</x:v>
+      </x:c>
+      <x:c r="D113" s="14" t="str">
+        <x:v>Sweaty Sex</x:v>
+      </x:c>
+      <x:c r="E113" s="14" t="str">
+        <x:v>アイデアポケット</x:v>
+      </x:c>
+      <x:c r="F113" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G113" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/series/942</x:v>
+      </x:c>
+      <x:c r="H113" s="14" t="str">
+        <x:v>ideapocket.series:942</x:v>
+      </x:c>
+      <x:c r="I113" s="14" t="str">
+        <x:v>0.4.9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="14" t="str">
+        <x:v>series_000113</x:v>
+      </x:c>
+      <x:c r="B114" s="14" t="str">
+        <x:v>女子高生痴漢電車</x:v>
+      </x:c>
+      <x:c r="C114" s="14" t="str">
+        <x:v>女高中生痴汉电车</x:v>
+      </x:c>
+      <x:c r="D114" s="14" t="str">
+        <x:v>Schoolgirl Molestation Train</x:v>
+      </x:c>
+      <x:c r="E114" s="14" t="str">
+        <x:v>アイデアポケット</x:v>
+      </x:c>
+      <x:c r="F114" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G114" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/series/943</x:v>
+      </x:c>
+      <x:c r="H114" s="14" t="str">
+        <x:v>ideapocket.series:943</x:v>
+      </x:c>
+      <x:c r="I114" s="14" t="str">
+        <x:v>0.4.9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="14" t="str">
+        <x:v>series_000114</x:v>
+      </x:c>
+      <x:c r="B115" s="14" t="str">
+        <x:v>CLUBBER BITCHIZM</x:v>
+      </x:c>
+      <x:c r="C115" s="14" t="str">
+        <x:v>CLUBBER BITCHIZM</x:v>
+      </x:c>
+      <x:c r="D115" s="14" t="str">
+        <x:v>CLUBBER BITCHIZM</x:v>
+      </x:c>
+      <x:c r="E115" s="14" t="str">
+        <x:v>アイデアポケット</x:v>
+      </x:c>
+      <x:c r="F115" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G115" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/series/944</x:v>
+      </x:c>
+      <x:c r="H115" s="14" t="str">
+        <x:v>ideapocket.series:944</x:v>
+      </x:c>
+      <x:c r="I115" s="14" t="str">
+        <x:v>0.4.9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="14" t="str">
+        <x:v>series_000115</x:v>
+      </x:c>
+      <x:c r="B116" s="14" t="str">
+        <x:v>ブラックディックファック</x:v>
+      </x:c>
+      <x:c r="C116" s="14" t="str">
+        <x:v>黑色巨根性交</x:v>
+      </x:c>
+      <x:c r="D116" s="14" t="str">
+        <x:v>Black Dick Fuck</x:v>
+      </x:c>
+      <x:c r="E116" s="14" t="str">
+        <x:v>エスワン</x:v>
+      </x:c>
+      <x:c r="F116" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G116" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/571</x:v>
+      </x:c>
+      <x:c r="H116" s="14" t="str">
+        <x:v>s1.series:571</x:v>
+      </x:c>
+      <x:c r="I116" s="14" t="str">
+        <x:v>0.4.9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="14" t="str">
+        <x:v>series_000116</x:v>
+      </x:c>
+      <x:c r="B117" s="14" t="str">
+        <x:v>爆乳インストラクター</x:v>
+      </x:c>
+      <x:c r="C117" s="14" t="str">
+        <x:v>爆乳教练</x:v>
+      </x:c>
+      <x:c r="D117" s="14" t="str">
+        <x:v>Busty Instructor</x:v>
+      </x:c>
+      <x:c r="E117" s="14" t="str">
+        <x:v>エスワン</x:v>
+      </x:c>
+      <x:c r="F117" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G117" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/572</x:v>
+      </x:c>
+      <x:c r="H117" s="14" t="str">
+        <x:v>s1.series:572</x:v>
+      </x:c>
+      <x:c r="I117" s="14" t="str">
+        <x:v>0.4.9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="14" t="str">
+        <x:v>series_000117</x:v>
+      </x:c>
+      <x:c r="B118" s="14" t="str">
+        <x:v>おっぱい離れできないボク</x:v>
+      </x:c>
+      <x:c r="C118" s="14" t="str">
+        <x:v>离不开乳房的我</x:v>
+      </x:c>
+      <x:c r="D118" s="14" t="str">
+        <x:v>I Can’t Wean Myself Off Breasts</x:v>
+      </x:c>
+      <x:c r="E118" s="14" t="str">
+        <x:v>エスワン</x:v>
+      </x:c>
+      <x:c r="F118" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G118" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/573</x:v>
+      </x:c>
+      <x:c r="H118" s="14" t="str">
+        <x:v>s1.series:573</x:v>
+      </x:c>
+      <x:c r="I118" s="14" t="str">
+        <x:v>0.4.9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" s="14" t="str">
+        <x:v>series_000118</x:v>
+      </x:c>
+      <x:c r="B119" s="14" t="str">
+        <x:v>挿れッパ!!</x:v>
+      </x:c>
+      <x:c r="C119" s="14" t="str">
+        <x:v>一直插着!!</x:v>
+      </x:c>
+      <x:c r="D119" s="14" t="str">
+        <x:v>Keep It In!!</x:v>
+      </x:c>
+      <x:c r="E119" s="14" t="str">
+        <x:v>エスワン</x:v>
+      </x:c>
+      <x:c r="F119" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G119" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/574</x:v>
+      </x:c>
+      <x:c r="H119" s="14" t="str">
+        <x:v>s1.series:574</x:v>
+      </x:c>
+      <x:c r="I119" s="14" t="str">
+        <x:v>0.4.9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="14" t="str">
+        <x:v>series_000119</x:v>
+      </x:c>
+      <x:c r="B120" s="14" t="str">
+        <x:v>わたし、犯されにゆきます。</x:v>
+      </x:c>
+      <x:c r="C120" s="14" t="str">
+        <x:v>我将去被侵犯。</x:v>
+      </x:c>
+      <x:c r="D120" s="14" t="str">
+        <x:v>I’m Going to Be Violated.</x:v>
+      </x:c>
+      <x:c r="E120" s="14" t="str">
+        <x:v>エスワン</x:v>
+      </x:c>
+      <x:c r="F120" s="14" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G120" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/575</x:v>
+      </x:c>
+      <x:c r="H120" s="14" t="str">
+        <x:v>s1.series:575</x:v>
+      </x:c>
+      <x:c r="I120" s="14" t="str">
+        <x:v>0.4.9</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5964,8 +6399,8 @@
     <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="86" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="92" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="90" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="94" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -5996,10 +6431,10 @@
         <x:v>no</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
-        <x:v>label: 16/16, unrecognized=0, complete=yes; series: 3/3, unrecognized=0, complete=no</x:v>
+        <x:v>label: 16/16, unrecognized=0, complete=yes; series: 8/8, unrecognized=0, complete=no</x:v>
       </x:c>
       <x:c r="E2" s="14" t="str">
-        <x:v>IDEAPOCKET 当前官方 Label Index 已完整覆盖；0.4.8 首次纳入 Series Index Provider，并建立 3 条官方可核验的 partial Snapshot 样本。Series 仍未完整枚举，因此来源级 completeTraversal=false。</x:v>
+        <x:v>IDEAPOCKET 当前官方 Label Index 已完整覆盖；Series 已通过两份 partial Snapshot 扩展到 8 条全部审核发布，但尚未完整枚举，因此来源级 completeTraversal=false。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -6013,10 +6448,10 @@
         <x:v>no</x:v>
       </x:c>
       <x:c r="D3" s="14" t="str">
-        <x:v>label: 29/29, unrecognized=0, complete=yes; series: 4/4, unrecognized=0, complete=no</x:v>
+        <x:v>label: 29/29, unrecognized=0, complete=yes; series: 9/9, unrecognized=0, complete=no</x:v>
       </x:c>
       <x:c r="E3" s="14" t="str">
-        <x:v>MOODYZ 当前官方 Label Index 已完整覆盖；0.4.8 首次纳入 Series Index Provider，并建立 4 条官方可核验的 partial Snapshot 样本。Series 仍未完整枚举，因此来源级 completeTraversal=false。</x:v>
+        <x:v>MOODYZ 当前官方 Label Index 已完整覆盖；Series 已通过两份 partial Snapshot 扩展到 9 条全部审核发布，但尚未完整枚举，因此来源级 completeTraversal=false。</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -6030,10 +6465,10 @@
         <x:v>no</x:v>
       </x:c>
       <x:c r="D4" s="14" t="str">
-        <x:v>label: 1/1, unrecognized=0, complete=no; series: 3/3, unrecognized=0, complete=no</x:v>
+        <x:v>label: 1/1, unrecognized=0, complete=no; series: 8/8, unrecognized=0, complete=no</x:v>
       </x:c>
       <x:c r="E4" s="14" t="str">
-        <x:v>S1 当前主 Label 与 3 个 Series 均已核验；0.4.8 将 S1 正式纳入 Series Index Provider Registry，并用首份 partial Snapshot 验证既有 Mapping。尚未形成可证明的完整 Series Index 快照。</x:v>
+        <x:v>S1 当前主 Label 已核验；Series 已通过两份 partial Snapshot 扩展到 8 条全部审核发布，但尚未形成可证明的完整 Series Index 快照。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -6101,7 +6536,7 @@
     <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="60" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="62" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -6132,16 +6567,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C2" s="14" t="str">
-        <x:v>10077</x:v>
+        <x:v>2735</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
-        <x:v>label_000016</x:v>
+        <x:v>label_000009</x:v>
       </x:c>
       <x:c r="E2" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F2" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/10077</x:v>
+        <x:v>https://attackers.net/works/list/label/2735</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -6152,16 +6587,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C3" s="14" t="str">
-        <x:v>10142</x:v>
+        <x:v>2737</x:v>
       </x:c>
       <x:c r="D3" s="14" t="str">
-        <x:v>label_000017</x:v>
+        <x:v>label_000006</x:v>
       </x:c>
       <x:c r="E3" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F3" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/10142</x:v>
+        <x:v>https://attackers.net/works/list/label/2737</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -6172,16 +6607,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C4" s="14" t="str">
-        <x:v>10144</x:v>
+        <x:v>2739</x:v>
       </x:c>
       <x:c r="D4" s="14" t="str">
-        <x:v>label_000018</x:v>
+        <x:v>label_000007</x:v>
       </x:c>
       <x:c r="E4" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F4" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/10144</x:v>
+        <x:v>https://attackers.net/works/list/label/2739</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -6192,16 +6627,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
-        <x:v>10151</x:v>
+        <x:v>2749</x:v>
       </x:c>
       <x:c r="D5" s="14" t="str">
-        <x:v>label_000019</x:v>
+        <x:v>label_000008</x:v>
       </x:c>
       <x:c r="E5" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F5" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/10151</x:v>
+        <x:v>https://attackers.net/works/list/label/2749</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -6212,16 +6647,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C6" s="14" t="str">
-        <x:v>12605</x:v>
+        <x:v>2751</x:v>
       </x:c>
       <x:c r="D6" s="14" t="str">
-        <x:v>label_000011</x:v>
+        <x:v>label_000004</x:v>
       </x:c>
       <x:c r="E6" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F6" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/12605</x:v>
+        <x:v>https://attackers.net/works/list/label/2751</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -6232,16 +6667,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C7" s="14" t="str">
-        <x:v>2735</x:v>
+        <x:v>2754</x:v>
       </x:c>
       <x:c r="D7" s="14" t="str">
-        <x:v>label_000009</x:v>
+        <x:v>label_000003</x:v>
       </x:c>
       <x:c r="E7" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F7" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/2735</x:v>
+        <x:v>https://attackers.net/works/list/label/2754</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -6252,16 +6687,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C8" s="14" t="str">
-        <x:v>2737</x:v>
+        <x:v>2756</x:v>
       </x:c>
       <x:c r="D8" s="14" t="str">
-        <x:v>label_000006</x:v>
+        <x:v>label_000010</x:v>
       </x:c>
       <x:c r="E8" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F8" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/2737</x:v>
+        <x:v>https://attackers.net/works/list/label/2756</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -6272,16 +6707,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C9" s="14" t="str">
-        <x:v>2739</x:v>
+        <x:v>5245</x:v>
       </x:c>
       <x:c r="D9" s="14" t="str">
-        <x:v>label_000007</x:v>
+        <x:v>label_000013</x:v>
       </x:c>
       <x:c r="E9" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F9" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/2739</x:v>
+        <x:v>https://attackers.net/works/list/label/5245</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -6292,16 +6727,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C10" s="14" t="str">
-        <x:v>2749</x:v>
+        <x:v>9455</x:v>
       </x:c>
       <x:c r="D10" s="14" t="str">
-        <x:v>label_000008</x:v>
+        <x:v>label_000005</x:v>
       </x:c>
       <x:c r="E10" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F10" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/2749</x:v>
+        <x:v>https://attackers.net/works/list/label/9455</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -6312,16 +6747,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C11" s="14" t="str">
-        <x:v>2751</x:v>
+        <x:v>9483</x:v>
       </x:c>
       <x:c r="D11" s="14" t="str">
-        <x:v>label_000004</x:v>
+        <x:v>label_000015</x:v>
       </x:c>
       <x:c r="E11" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F11" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/2751</x:v>
+        <x:v>https://attackers.net/works/list/label/9483</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -6332,16 +6767,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C12" s="14" t="str">
-        <x:v>2754</x:v>
+        <x:v>10077</x:v>
       </x:c>
       <x:c r="D12" s="14" t="str">
-        <x:v>label_000003</x:v>
+        <x:v>label_000016</x:v>
       </x:c>
       <x:c r="E12" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F12" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/2754</x:v>
+        <x:v>https://attackers.net/works/list/label/10077</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -6352,16 +6787,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>2756</x:v>
+        <x:v>10142</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
-        <x:v>label_000010</x:v>
+        <x:v>label_000017</x:v>
       </x:c>
       <x:c r="E13" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F13" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/2756</x:v>
+        <x:v>https://attackers.net/works/list/label/10142</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -6372,16 +6807,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>5245</x:v>
+        <x:v>10144</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
-        <x:v>label_000013</x:v>
+        <x:v>label_000018</x:v>
       </x:c>
       <x:c r="E14" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F14" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/5245</x:v>
+        <x:v>https://attackers.net/works/list/label/10144</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -6392,16 +6827,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C15" s="14" t="str">
-        <x:v>81348</x:v>
+        <x:v>10151</x:v>
       </x:c>
       <x:c r="D15" s="14" t="str">
-        <x:v>label_000012</x:v>
+        <x:v>label_000019</x:v>
       </x:c>
       <x:c r="E15" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F15" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/81348</x:v>
+        <x:v>https://attackers.net/works/list/label/10151</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -6412,16 +6847,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C16" s="14" t="str">
-        <x:v>85265</x:v>
+        <x:v>12605</x:v>
       </x:c>
       <x:c r="D16" s="14" t="str">
-        <x:v>label_000014</x:v>
+        <x:v>label_000011</x:v>
       </x:c>
       <x:c r="E16" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F16" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/85265</x:v>
+        <x:v>https://attackers.net/works/list/label/12605</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -6432,16 +6867,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C17" s="14" t="str">
-        <x:v>9455</x:v>
+        <x:v>81348</x:v>
       </x:c>
       <x:c r="D17" s="14" t="str">
-        <x:v>label_000005</x:v>
+        <x:v>label_000012</x:v>
       </x:c>
       <x:c r="E17" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F17" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/9455</x:v>
+        <x:v>https://attackers.net/works/list/label/81348</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -6452,16 +6887,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C18" s="14" t="str">
-        <x:v>9483</x:v>
+        <x:v>85265</x:v>
       </x:c>
       <x:c r="D18" s="14" t="str">
-        <x:v>label_000015</x:v>
+        <x:v>label_000014</x:v>
       </x:c>
       <x:c r="E18" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F18" s="14" t="str">
-        <x:v>https://attackers.net/works/list/label/9483</x:v>
+        <x:v>https://attackers.net/works/list/label/85265</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -7512,16 +7947,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C71" s="14" t="str">
-        <x:v>10077</x:v>
+        <x:v>2758</x:v>
       </x:c>
       <x:c r="D71" s="14" t="str">
-        <x:v>label_000076</x:v>
+        <x:v>label_000072</x:v>
       </x:c>
       <x:c r="E71" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F71" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10077</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2758</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -7532,16 +7967,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C72" s="14" t="str">
-        <x:v>10103</x:v>
+        <x:v>2760</x:v>
       </x:c>
       <x:c r="D72" s="14" t="str">
-        <x:v>label_000073</x:v>
+        <x:v>label_000079</x:v>
       </x:c>
       <x:c r="E72" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F72" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10103</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2760</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -7552,16 +7987,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C73" s="14" t="str">
-        <x:v>10142</x:v>
+        <x:v>2767</x:v>
       </x:c>
       <x:c r="D73" s="14" t="str">
-        <x:v>label_000077</x:v>
+        <x:v>label_000070</x:v>
       </x:c>
       <x:c r="E73" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F73" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10142</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2767</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -7572,16 +8007,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C74" s="14" t="str">
-        <x:v>10144</x:v>
+        <x:v>2769</x:v>
       </x:c>
       <x:c r="D74" s="14" t="str">
-        <x:v>label_000080</x:v>
+        <x:v>label_000066</x:v>
       </x:c>
       <x:c r="E74" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F74" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10144</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2769</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -7592,16 +8027,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C75" s="14" t="str">
-        <x:v>10151</x:v>
+        <x:v>2771</x:v>
       </x:c>
       <x:c r="D75" s="14" t="str">
-        <x:v>label_000078</x:v>
+        <x:v>label_000065</x:v>
       </x:c>
       <x:c r="E75" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F75" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/10151</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2771</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -7612,16 +8047,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C76" s="14" t="str">
-        <x:v>12442</x:v>
+        <x:v>2776</x:v>
       </x:c>
       <x:c r="D76" s="14" t="str">
-        <x:v>label_000069</x:v>
+        <x:v>label_000068</x:v>
       </x:c>
       <x:c r="E76" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F76" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/12442</x:v>
+        <x:v>https://ideapocket.com/works/list/label/2776</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -7632,16 +8067,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C77" s="14" t="str">
-        <x:v>12835</x:v>
+        <x:v>9483</x:v>
       </x:c>
       <x:c r="D77" s="14" t="str">
-        <x:v>label_000071</x:v>
+        <x:v>label_000074</x:v>
       </x:c>
       <x:c r="E77" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F77" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/12835</x:v>
+        <x:v>https://ideapocket.com/works/list/label/9483</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -7652,16 +8087,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C78" s="14" t="str">
-        <x:v>2758</x:v>
+        <x:v>9790</x:v>
       </x:c>
       <x:c r="D78" s="14" t="str">
-        <x:v>label_000072</x:v>
+        <x:v>label_000067</x:v>
       </x:c>
       <x:c r="E78" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F78" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2758</x:v>
+        <x:v>https://ideapocket.com/works/list/label/9790</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -7672,16 +8107,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C79" s="14" t="str">
-        <x:v>2760</x:v>
+        <x:v>10077</x:v>
       </x:c>
       <x:c r="D79" s="14" t="str">
-        <x:v>label_000079</x:v>
+        <x:v>label_000076</x:v>
       </x:c>
       <x:c r="E79" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F79" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2760</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10077</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -7692,16 +8127,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C80" s="14" t="str">
-        <x:v>2767</x:v>
+        <x:v>10103</x:v>
       </x:c>
       <x:c r="D80" s="14" t="str">
-        <x:v>label_000070</x:v>
+        <x:v>label_000073</x:v>
       </x:c>
       <x:c r="E80" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F80" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2767</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10103</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -7712,16 +8147,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C81" s="14" t="str">
-        <x:v>2769</x:v>
+        <x:v>10142</x:v>
       </x:c>
       <x:c r="D81" s="14" t="str">
-        <x:v>label_000066</x:v>
+        <x:v>label_000077</x:v>
       </x:c>
       <x:c r="E81" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F81" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2769</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10142</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -7732,16 +8167,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C82" s="14" t="str">
-        <x:v>2771</x:v>
+        <x:v>10144</x:v>
       </x:c>
       <x:c r="D82" s="14" t="str">
-        <x:v>label_000065</x:v>
+        <x:v>label_000080</x:v>
       </x:c>
       <x:c r="E82" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F82" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2771</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10144</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -7752,16 +8187,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C83" s="14" t="str">
-        <x:v>2776</x:v>
+        <x:v>10151</x:v>
       </x:c>
       <x:c r="D83" s="14" t="str">
-        <x:v>label_000068</x:v>
+        <x:v>label_000078</x:v>
       </x:c>
       <x:c r="E83" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F83" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/2776</x:v>
+        <x:v>https://ideapocket.com/works/list/label/10151</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -7772,16 +8207,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C84" s="14" t="str">
-        <x:v>85265</x:v>
+        <x:v>12442</x:v>
       </x:c>
       <x:c r="D84" s="14" t="str">
-        <x:v>label_000075</x:v>
+        <x:v>label_000069</x:v>
       </x:c>
       <x:c r="E84" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F84" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/85265</x:v>
+        <x:v>https://ideapocket.com/works/list/label/12442</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -7792,16 +8227,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C85" s="14" t="str">
-        <x:v>9483</x:v>
+        <x:v>12835</x:v>
       </x:c>
       <x:c r="D85" s="14" t="str">
-        <x:v>label_000074</x:v>
+        <x:v>label_000071</x:v>
       </x:c>
       <x:c r="E85" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F85" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/9483</x:v>
+        <x:v>https://ideapocket.com/works/list/label/12835</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -7812,16 +8247,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C86" s="14" t="str">
-        <x:v>9790</x:v>
+        <x:v>85265</x:v>
       </x:c>
       <x:c r="D86" s="14" t="str">
-        <x:v>label_000067</x:v>
+        <x:v>label_000075</x:v>
       </x:c>
       <x:c r="E86" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F86" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/label/9790</x:v>
+        <x:v>https://ideapocket.com/works/list/label/85265</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -7832,16 +8267,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C87" s="14" t="str">
-        <x:v>1011</x:v>
+        <x:v>863</x:v>
       </x:c>
       <x:c r="D87" s="14" t="str">
-        <x:v>series_000004</x:v>
+        <x:v>series_000003</x:v>
       </x:c>
       <x:c r="E87" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F87" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/series/1011</x:v>
+        <x:v>https://ideapocket.com/works/list/series/863</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -7852,16 +8287,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C88" s="14" t="str">
-        <x:v>863</x:v>
+        <x:v>939</x:v>
       </x:c>
       <x:c r="D88" s="14" t="str">
-        <x:v>series_000003</x:v>
+        <x:v>series_000104</x:v>
       </x:c>
       <x:c r="E88" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F88" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/series/863</x:v>
+        <x:v>https://ideapocket.com/works/list/series/939</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -7872,116 +8307,116 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C89" s="14" t="str">
-        <x:v>939</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="D89" s="14" t="str">
-        <x:v>series_000104</x:v>
+        <x:v>series_000110</x:v>
       </x:c>
       <x:c r="E89" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F89" s="14" t="str">
-        <x:v>https://ideapocket.com/works/list/series/939</x:v>
+        <x:v>https://ideapocket.com/works/list/series/940</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.series</x:v>
       </x:c>
       <x:c r="B90" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C90" s="14" t="str">
-        <x:v>10077</x:v>
+        <x:v>941</x:v>
       </x:c>
       <x:c r="D90" s="14" t="str">
-        <x:v>label_000035</x:v>
+        <x:v>series_000111</x:v>
       </x:c>
       <x:c r="E90" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F90" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10077</x:v>
+        <x:v>https://ideapocket.com/works/list/series/941</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.series</x:v>
       </x:c>
       <x:c r="B91" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C91" s="14" t="str">
-        <x:v>10119</x:v>
+        <x:v>942</x:v>
       </x:c>
       <x:c r="D91" s="14" t="str">
-        <x:v>label_000031</x:v>
+        <x:v>series_000112</x:v>
       </x:c>
       <x:c r="E91" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F91" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10119</x:v>
+        <x:v>https://ideapocket.com/works/list/series/942</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.series</x:v>
       </x:c>
       <x:c r="B92" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C92" s="14" t="str">
-        <x:v>10130</x:v>
+        <x:v>943</x:v>
       </x:c>
       <x:c r="D92" s="14" t="str">
-        <x:v>label_000028</x:v>
+        <x:v>series_000113</x:v>
       </x:c>
       <x:c r="E92" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F92" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10130</x:v>
+        <x:v>https://ideapocket.com/works/list/series/943</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.series</x:v>
       </x:c>
       <x:c r="B93" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C93" s="14" t="str">
-        <x:v>10142</x:v>
+        <x:v>944</x:v>
       </x:c>
       <x:c r="D93" s="14" t="str">
-        <x:v>label_000034</x:v>
+        <x:v>series_000114</x:v>
       </x:c>
       <x:c r="E93" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F93" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10142</x:v>
+        <x:v>https://ideapocket.com/works/list/series/944</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="14" t="str">
-        <x:v>madonna.label</x:v>
+        <x:v>ideapocket.series</x:v>
       </x:c>
       <x:c r="B94" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C94" s="14" t="str">
-        <x:v>10151</x:v>
+        <x:v>1011</x:v>
       </x:c>
       <x:c r="D94" s="14" t="str">
-        <x:v>label_000036</x:v>
+        <x:v>series_000004</x:v>
       </x:c>
       <x:c r="E94" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F94" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10151</x:v>
+        <x:v>https://ideapocket.com/works/list/series/1011</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -7992,16 +8427,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C95" s="14" t="str">
-        <x:v>10159</x:v>
+        <x:v>3125</x:v>
       </x:c>
       <x:c r="D95" s="14" t="str">
-        <x:v>label_000030</x:v>
+        <x:v>label_000037</x:v>
       </x:c>
       <x:c r="E95" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F95" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/10159</x:v>
+        <x:v>https://madonna-av.com/works/list/label/3125</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -8012,16 +8447,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C96" s="14" t="str">
-        <x:v>12490</x:v>
+        <x:v>3669</x:v>
       </x:c>
       <x:c r="D96" s="14" t="str">
-        <x:v>label_000021</x:v>
+        <x:v>label_000020</x:v>
       </x:c>
       <x:c r="E96" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F96" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/12490</x:v>
+        <x:v>https://madonna-av.com/works/list/label/3669</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -8032,16 +8467,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C97" s="14" t="str">
-        <x:v>12502</x:v>
+        <x:v>7354</x:v>
       </x:c>
       <x:c r="D97" s="14" t="str">
-        <x:v>label_000027</x:v>
+        <x:v>label_000024</x:v>
       </x:c>
       <x:c r="E97" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F97" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/12502</x:v>
+        <x:v>https://madonna-av.com/works/list/label/7354</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -8052,16 +8487,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C98" s="14" t="str">
-        <x:v>12603</x:v>
+        <x:v>7993</x:v>
       </x:c>
       <x:c r="D98" s="14" t="str">
-        <x:v>label_000026</x:v>
+        <x:v>label_000029</x:v>
       </x:c>
       <x:c r="E98" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F98" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/12603</x:v>
+        <x:v>https://madonna-av.com/works/list/label/7993</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -8072,16 +8507,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C99" s="14" t="str">
-        <x:v>3125</x:v>
+        <x:v>9387</x:v>
       </x:c>
       <x:c r="D99" s="14" t="str">
-        <x:v>label_000037</x:v>
+        <x:v>label_000022</x:v>
       </x:c>
       <x:c r="E99" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F99" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/3125</x:v>
+        <x:v>https://madonna-av.com/works/list/label/9387</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -8092,16 +8527,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C100" s="14" t="str">
-        <x:v>3669</x:v>
+        <x:v>9419</x:v>
       </x:c>
       <x:c r="D100" s="14" t="str">
-        <x:v>label_000020</x:v>
+        <x:v>label_000025</x:v>
       </x:c>
       <x:c r="E100" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F100" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/3669</x:v>
+        <x:v>https://madonna-av.com/works/list/label/9419</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -8112,16 +8547,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C101" s="14" t="str">
-        <x:v>7354</x:v>
+        <x:v>9483</x:v>
       </x:c>
       <x:c r="D101" s="14" t="str">
-        <x:v>label_000024</x:v>
+        <x:v>label_000033</x:v>
       </x:c>
       <x:c r="E101" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F101" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/7354</x:v>
+        <x:v>https://madonna-av.com/works/list/label/9483</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -8132,16 +8567,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C102" s="14" t="str">
-        <x:v>7993</x:v>
+        <x:v>9789</x:v>
       </x:c>
       <x:c r="D102" s="14" t="str">
-        <x:v>label_000029</x:v>
+        <x:v>label_000023</x:v>
       </x:c>
       <x:c r="E102" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F102" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/7993</x:v>
+        <x:v>https://madonna-av.com/works/list/label/9789</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -8152,16 +8587,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C103" s="14" t="str">
-        <x:v>85265</x:v>
+        <x:v>10077</x:v>
       </x:c>
       <x:c r="D103" s="14" t="str">
-        <x:v>label_000032</x:v>
+        <x:v>label_000035</x:v>
       </x:c>
       <x:c r="E103" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F103" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/85265</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10077</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -8172,16 +8607,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C104" s="14" t="str">
-        <x:v>9387</x:v>
+        <x:v>10119</x:v>
       </x:c>
       <x:c r="D104" s="14" t="str">
-        <x:v>label_000022</x:v>
+        <x:v>label_000031</x:v>
       </x:c>
       <x:c r="E104" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F104" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/9387</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10119</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -8192,16 +8627,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C105" s="14" t="str">
-        <x:v>9419</x:v>
+        <x:v>10130</x:v>
       </x:c>
       <x:c r="D105" s="14" t="str">
-        <x:v>label_000025</x:v>
+        <x:v>label_000028</x:v>
       </x:c>
       <x:c r="E105" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F105" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/9419</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10130</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -8212,16 +8647,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C106" s="14" t="str">
-        <x:v>9483</x:v>
+        <x:v>10142</x:v>
       </x:c>
       <x:c r="D106" s="14" t="str">
-        <x:v>label_000033</x:v>
+        <x:v>label_000034</x:v>
       </x:c>
       <x:c r="E106" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F106" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/9483</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10142</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -8232,116 +8667,116 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C107" s="14" t="str">
-        <x:v>9789</x:v>
+        <x:v>10151</x:v>
       </x:c>
       <x:c r="D107" s="14" t="str">
-        <x:v>label_000023</x:v>
+        <x:v>label_000036</x:v>
       </x:c>
       <x:c r="E107" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F107" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/label/9789</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10151</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B108" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C108" s="14" t="str">
-        <x:v>1546</x:v>
+        <x:v>10159</x:v>
       </x:c>
       <x:c r="D108" s="14" t="str">
-        <x:v>series_000053</x:v>
+        <x:v>label_000030</x:v>
       </x:c>
       <x:c r="E108" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F108" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1546</x:v>
+        <x:v>https://madonna-av.com/works/list/label/10159</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B109" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C109" s="14" t="str">
-        <x:v>1547</x:v>
+        <x:v>12490</x:v>
       </x:c>
       <x:c r="D109" s="14" t="str">
-        <x:v>series_000054</x:v>
+        <x:v>label_000021</x:v>
       </x:c>
       <x:c r="E109" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F109" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1547</x:v>
+        <x:v>https://madonna-av.com/works/list/label/12490</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B110" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C110" s="14" t="str">
-        <x:v>1548</x:v>
+        <x:v>12502</x:v>
       </x:c>
       <x:c r="D110" s="14" t="str">
-        <x:v>series_000055</x:v>
+        <x:v>label_000027</x:v>
       </x:c>
       <x:c r="E110" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F110" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1548</x:v>
+        <x:v>https://madonna-av.com/works/list/label/12502</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B111" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C111" s="14" t="str">
-        <x:v>1549</x:v>
+        <x:v>12603</x:v>
       </x:c>
       <x:c r="D111" s="14" t="str">
-        <x:v>series_000027</x:v>
+        <x:v>label_000026</x:v>
       </x:c>
       <x:c r="E111" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F111" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1549</x:v>
+        <x:v>https://madonna-av.com/works/list/label/12603</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>madonna.label</x:v>
       </x:c>
       <x:c r="B112" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C112" s="14" t="str">
-        <x:v>1550</x:v>
+        <x:v>85265</x:v>
       </x:c>
       <x:c r="D112" s="14" t="str">
-        <x:v>series_000028</x:v>
+        <x:v>label_000032</x:v>
       </x:c>
       <x:c r="E112" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F112" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1550</x:v>
+        <x:v>https://madonna-av.com/works/list/label/85265</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -8352,16 +8787,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C113" s="14" t="str">
-        <x:v>1551</x:v>
+        <x:v>1546</x:v>
       </x:c>
       <x:c r="D113" s="14" t="str">
-        <x:v>series_000029</x:v>
+        <x:v>series_000053</x:v>
       </x:c>
       <x:c r="E113" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F113" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1551</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1546</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -8372,16 +8807,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C114" s="14" t="str">
-        <x:v>1552</x:v>
+        <x:v>1547</x:v>
       </x:c>
       <x:c r="D114" s="14" t="str">
-        <x:v>series_000030</x:v>
+        <x:v>series_000054</x:v>
       </x:c>
       <x:c r="E114" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F114" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1552</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1547</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -8392,16 +8827,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C115" s="14" t="str">
-        <x:v>1553</x:v>
+        <x:v>1548</x:v>
       </x:c>
       <x:c r="D115" s="14" t="str">
-        <x:v>series_000031</x:v>
+        <x:v>series_000055</x:v>
       </x:c>
       <x:c r="E115" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F115" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1553</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1548</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -8412,16 +8847,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C116" s="14" t="str">
-        <x:v>1554</x:v>
+        <x:v>1549</x:v>
       </x:c>
       <x:c r="D116" s="14" t="str">
-        <x:v>series_000032</x:v>
+        <x:v>series_000027</x:v>
       </x:c>
       <x:c r="E116" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F116" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1554</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1549</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -8432,16 +8867,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C117" s="14" t="str">
-        <x:v>1555</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D117" s="14" t="str">
-        <x:v>series_000033</x:v>
+        <x:v>series_000028</x:v>
       </x:c>
       <x:c r="E117" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F117" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1555</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1550</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -8452,16 +8887,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C118" s="14" t="str">
-        <x:v>1556</x:v>
+        <x:v>1551</x:v>
       </x:c>
       <x:c r="D118" s="14" t="str">
-        <x:v>series_000034</x:v>
+        <x:v>series_000029</x:v>
       </x:c>
       <x:c r="E118" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F118" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1556</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1551</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -8472,16 +8907,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C119" s="14" t="str">
-        <x:v>1557</x:v>
+        <x:v>1552</x:v>
       </x:c>
       <x:c r="D119" s="14" t="str">
-        <x:v>series_000035</x:v>
+        <x:v>series_000030</x:v>
       </x:c>
       <x:c r="E119" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F119" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1557</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1552</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -8492,16 +8927,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C120" s="14" t="str">
-        <x:v>1558</x:v>
+        <x:v>1553</x:v>
       </x:c>
       <x:c r="D120" s="14" t="str">
-        <x:v>series_000036</x:v>
+        <x:v>series_000031</x:v>
       </x:c>
       <x:c r="E120" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F120" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1558</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1553</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
@@ -8512,16 +8947,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C121" s="14" t="str">
-        <x:v>1559</x:v>
+        <x:v>1554</x:v>
       </x:c>
       <x:c r="D121" s="14" t="str">
-        <x:v>series_000056</x:v>
+        <x:v>series_000032</x:v>
       </x:c>
       <x:c r="E121" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F121" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1559</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1554</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
@@ -8532,16 +8967,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C122" s="14" t="str">
-        <x:v>1560</x:v>
+        <x:v>1555</x:v>
       </x:c>
       <x:c r="D122" s="14" t="str">
-        <x:v>series_000057</x:v>
+        <x:v>series_000033</x:v>
       </x:c>
       <x:c r="E122" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F122" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1560</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1555</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -8552,16 +8987,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C123" s="14" t="str">
-        <x:v>1561</x:v>
+        <x:v>1556</x:v>
       </x:c>
       <x:c r="D123" s="14" t="str">
-        <x:v>series_000058</x:v>
+        <x:v>series_000034</x:v>
       </x:c>
       <x:c r="E123" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F123" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1561</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1556</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
@@ -8572,16 +9007,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C124" s="14" t="str">
-        <x:v>1562</x:v>
+        <x:v>1557</x:v>
       </x:c>
       <x:c r="D124" s="14" t="str">
-        <x:v>series_000059</x:v>
+        <x:v>series_000035</x:v>
       </x:c>
       <x:c r="E124" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F124" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1562</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1557</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
@@ -8592,16 +9027,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C125" s="14" t="str">
-        <x:v>1563</x:v>
+        <x:v>1558</x:v>
       </x:c>
       <x:c r="D125" s="14" t="str">
-        <x:v>series_000060</x:v>
+        <x:v>series_000036</x:v>
       </x:c>
       <x:c r="E125" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F125" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1563</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1558</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -8612,16 +9047,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C126" s="14" t="str">
-        <x:v>1564</x:v>
+        <x:v>1559</x:v>
       </x:c>
       <x:c r="D126" s="14" t="str">
-        <x:v>series_000061</x:v>
+        <x:v>series_000056</x:v>
       </x:c>
       <x:c r="E126" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F126" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1564</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1559</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
@@ -8632,16 +9067,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C127" s="14" t="str">
-        <x:v>1565</x:v>
+        <x:v>1560</x:v>
       </x:c>
       <x:c r="D127" s="14" t="str">
-        <x:v>series_000081</x:v>
+        <x:v>series_000057</x:v>
       </x:c>
       <x:c r="E127" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F127" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1565</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1560</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
@@ -8652,16 +9087,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C128" s="14" t="str">
-        <x:v>1566</x:v>
+        <x:v>1561</x:v>
       </x:c>
       <x:c r="D128" s="14" t="str">
-        <x:v>series_000082</x:v>
+        <x:v>series_000058</x:v>
       </x:c>
       <x:c r="E128" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F128" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1566</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1561</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
@@ -8672,16 +9107,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C129" s="14" t="str">
-        <x:v>1570</x:v>
+        <x:v>1562</x:v>
       </x:c>
       <x:c r="D129" s="14" t="str">
-        <x:v>series_000083</x:v>
+        <x:v>series_000059</x:v>
       </x:c>
       <x:c r="E129" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F129" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1570</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1562</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
@@ -8692,16 +9127,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C130" s="14" t="str">
-        <x:v>1571</x:v>
+        <x:v>1563</x:v>
       </x:c>
       <x:c r="D130" s="14" t="str">
-        <x:v>series_000084</x:v>
+        <x:v>series_000060</x:v>
       </x:c>
       <x:c r="E130" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F130" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1571</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1563</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
@@ -8712,16 +9147,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C131" s="14" t="str">
-        <x:v>1572</x:v>
+        <x:v>1564</x:v>
       </x:c>
       <x:c r="D131" s="14" t="str">
-        <x:v>series_000085</x:v>
+        <x:v>series_000061</x:v>
       </x:c>
       <x:c r="E131" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F131" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1572</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1564</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
@@ -8732,16 +9167,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C132" s="14" t="str">
-        <x:v>1573</x:v>
+        <x:v>1565</x:v>
       </x:c>
       <x:c r="D132" s="14" t="str">
-        <x:v>series_000086</x:v>
+        <x:v>series_000081</x:v>
       </x:c>
       <x:c r="E132" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F132" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1573</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1565</x:v>
       </x:c>
     </x:row>
     <x:row r="133">
@@ -8752,16 +9187,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C133" s="14" t="str">
-        <x:v>1574</x:v>
+        <x:v>1566</x:v>
       </x:c>
       <x:c r="D133" s="14" t="str">
-        <x:v>series_000087</x:v>
+        <x:v>series_000082</x:v>
       </x:c>
       <x:c r="E133" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F133" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1574</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1566</x:v>
       </x:c>
     </x:row>
     <x:row r="134">
@@ -8772,16 +9207,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C134" s="14" t="str">
-        <x:v>1579</x:v>
+        <x:v>1570</x:v>
       </x:c>
       <x:c r="D134" s="14" t="str">
-        <x:v>series_000088</x:v>
+        <x:v>series_000083</x:v>
       </x:c>
       <x:c r="E134" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F134" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1579</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1570</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
@@ -8792,16 +9227,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C135" s="14" t="str">
-        <x:v>1581</x:v>
+        <x:v>1571</x:v>
       </x:c>
       <x:c r="D135" s="14" t="str">
-        <x:v>series_000089</x:v>
+        <x:v>series_000084</x:v>
       </x:c>
       <x:c r="E135" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F135" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1581</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1571</x:v>
       </x:c>
     </x:row>
     <x:row r="136">
@@ -8812,16 +9247,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C136" s="14" t="str">
-        <x:v>1585</x:v>
+        <x:v>1572</x:v>
       </x:c>
       <x:c r="D136" s="14" t="str">
-        <x:v>series_000090</x:v>
+        <x:v>series_000085</x:v>
       </x:c>
       <x:c r="E136" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F136" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1585</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1572</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
@@ -8832,16 +9267,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C137" s="14" t="str">
-        <x:v>1586</x:v>
+        <x:v>1573</x:v>
       </x:c>
       <x:c r="D137" s="14" t="str">
-        <x:v>series_000091</x:v>
+        <x:v>series_000086</x:v>
       </x:c>
       <x:c r="E137" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F137" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1586</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1573</x:v>
       </x:c>
     </x:row>
     <x:row r="138">
@@ -8852,16 +9287,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C138" s="14" t="str">
-        <x:v>1587</x:v>
+        <x:v>1574</x:v>
       </x:c>
       <x:c r="D138" s="14" t="str">
-        <x:v>series_000092</x:v>
+        <x:v>series_000087</x:v>
       </x:c>
       <x:c r="E138" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F138" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1587</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1574</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
@@ -8872,16 +9307,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C139" s="14" t="str">
-        <x:v>1588</x:v>
+        <x:v>1579</x:v>
       </x:c>
       <x:c r="D139" s="14" t="str">
-        <x:v>series_000093</x:v>
+        <x:v>series_000088</x:v>
       </x:c>
       <x:c r="E139" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F139" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1588</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1579</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -8892,16 +9327,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C140" s="14" t="str">
-        <x:v>1589</x:v>
+        <x:v>1581</x:v>
       </x:c>
       <x:c r="D140" s="14" t="str">
-        <x:v>series_000094</x:v>
+        <x:v>series_000089</x:v>
       </x:c>
       <x:c r="E140" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F140" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1589</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1581</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
@@ -8912,16 +9347,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C141" s="14" t="str">
-        <x:v>1590</x:v>
+        <x:v>1585</x:v>
       </x:c>
       <x:c r="D141" s="14" t="str">
-        <x:v>series_000095</x:v>
+        <x:v>series_000090</x:v>
       </x:c>
       <x:c r="E141" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F141" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1590</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1585</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
@@ -8932,16 +9367,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C142" s="14" t="str">
-        <x:v>1591</x:v>
+        <x:v>1586</x:v>
       </x:c>
       <x:c r="D142" s="14" t="str">
-        <x:v>series_000096</x:v>
+        <x:v>series_000091</x:v>
       </x:c>
       <x:c r="E142" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F142" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1591</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1586</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
@@ -8952,16 +9387,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C143" s="14" t="str">
-        <x:v>1592</x:v>
+        <x:v>1587</x:v>
       </x:c>
       <x:c r="D143" s="14" t="str">
-        <x:v>series_000097</x:v>
+        <x:v>series_000092</x:v>
       </x:c>
       <x:c r="E143" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F143" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1592</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1587</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -8972,16 +9407,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C144" s="14" t="str">
-        <x:v>1593</x:v>
+        <x:v>1588</x:v>
       </x:c>
       <x:c r="D144" s="14" t="str">
-        <x:v>series_000098</x:v>
+        <x:v>series_000093</x:v>
       </x:c>
       <x:c r="E144" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F144" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1593</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1588</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -8992,16 +9427,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C145" s="14" t="str">
-        <x:v>1594</x:v>
+        <x:v>1589</x:v>
       </x:c>
       <x:c r="D145" s="14" t="str">
-        <x:v>series_000099</x:v>
+        <x:v>series_000094</x:v>
       </x:c>
       <x:c r="E145" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F145" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1594</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1589</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
@@ -9012,16 +9447,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C146" s="14" t="str">
-        <x:v>1595</x:v>
+        <x:v>1590</x:v>
       </x:c>
       <x:c r="D146" s="14" t="str">
-        <x:v>series_000100</x:v>
+        <x:v>series_000095</x:v>
       </x:c>
       <x:c r="E146" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F146" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1595</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1590</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
@@ -9032,16 +9467,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C147" s="14" t="str">
-        <x:v>1749</x:v>
+        <x:v>1591</x:v>
       </x:c>
       <x:c r="D147" s="14" t="str">
-        <x:v>series_000017</x:v>
+        <x:v>series_000096</x:v>
       </x:c>
       <x:c r="E147" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F147" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1749</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1591</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
@@ -9052,16 +9487,16 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C148" s="14" t="str">
-        <x:v>1846</x:v>
+        <x:v>1592</x:v>
       </x:c>
       <x:c r="D148" s="14" t="str">
-        <x:v>series_000015</x:v>
+        <x:v>series_000097</x:v>
       </x:c>
       <x:c r="E148" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F148" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1846</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1592</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
@@ -9072,116 +9507,116 @@
         <x:v>series</x:v>
       </x:c>
       <x:c r="C149" s="14" t="str">
-        <x:v>1891</x:v>
+        <x:v>1593</x:v>
       </x:c>
       <x:c r="D149" s="14" t="str">
-        <x:v>series_000016</x:v>
+        <x:v>series_000098</x:v>
       </x:c>
       <x:c r="E149" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F149" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1891</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1593</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B150" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C150" s="14" t="str">
-        <x:v>10077</x:v>
+        <x:v>1594</x:v>
       </x:c>
       <x:c r="D150" s="14" t="str">
-        <x:v>label_000063</x:v>
+        <x:v>series_000099</x:v>
       </x:c>
       <x:c r="E150" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F150" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10077</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1594</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B151" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C151" s="14" t="str">
-        <x:v>10106</x:v>
+        <x:v>1595</x:v>
       </x:c>
       <x:c r="D151" s="14" t="str">
-        <x:v>label_000053</x:v>
+        <x:v>series_000100</x:v>
       </x:c>
       <x:c r="E151" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F151" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10106</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1595</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B152" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C152" s="14" t="str">
-        <x:v>10107</x:v>
+        <x:v>1749</x:v>
       </x:c>
       <x:c r="D152" s="14" t="str">
-        <x:v>label_000046</x:v>
+        <x:v>series_000017</x:v>
       </x:c>
       <x:c r="E152" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F152" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10107</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1749</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B153" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C153" s="14" t="str">
-        <x:v>10131</x:v>
+        <x:v>1846</x:v>
       </x:c>
       <x:c r="D153" s="14" t="str">
-        <x:v>label_000047</x:v>
+        <x:v>series_000015</x:v>
       </x:c>
       <x:c r="E153" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F153" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10131</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1846</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="14" t="str">
-        <x:v>moodyz.label</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="B154" s="14" t="str">
-        <x:v>label</x:v>
+        <x:v>series</x:v>
       </x:c>
       <x:c r="C154" s="14" t="str">
-        <x:v>10142</x:v>
+        <x:v>1891</x:v>
       </x:c>
       <x:c r="D154" s="14" t="str">
-        <x:v>label_000060</x:v>
+        <x:v>series_000016</x:v>
       </x:c>
       <x:c r="E154" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F154" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10142</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1891</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
@@ -9192,16 +9627,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C155" s="14" t="str">
-        <x:v>10144</x:v>
+        <x:v>5046</x:v>
       </x:c>
       <x:c r="D155" s="14" t="str">
-        <x:v>label_000061</x:v>
+        <x:v>label_000039</x:v>
       </x:c>
       <x:c r="E155" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F155" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10144</x:v>
+        <x:v>https://moodyz.com/works/list/label/5046</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
@@ -9212,16 +9647,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C156" s="14" t="str">
-        <x:v>10151</x:v>
+        <x:v>5047</x:v>
       </x:c>
       <x:c r="D156" s="14" t="str">
-        <x:v>label_000062</x:v>
+        <x:v>label_000038</x:v>
       </x:c>
       <x:c r="E156" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F156" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10151</x:v>
+        <x:v>https://moodyz.com/works/list/label/5047</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
@@ -9232,16 +9667,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C157" s="14" t="str">
-        <x:v>10157</x:v>
+        <x:v>5048</x:v>
       </x:c>
       <x:c r="D157" s="14" t="str">
-        <x:v>label_000058</x:v>
+        <x:v>label_000001</x:v>
       </x:c>
       <x:c r="E157" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F157" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10157</x:v>
+        <x:v>https://moodyz.com/works/list/label/5048</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
@@ -9252,16 +9687,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C158" s="14" t="str">
-        <x:v>10172</x:v>
+        <x:v>5049</x:v>
       </x:c>
       <x:c r="D158" s="14" t="str">
-        <x:v>label_000064</x:v>
+        <x:v>label_000045</x:v>
       </x:c>
       <x:c r="E158" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F158" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10172</x:v>
+        <x:v>https://moodyz.com/works/list/label/5049</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
@@ -9272,16 +9707,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C159" s="14" t="str">
-        <x:v>10174</x:v>
+        <x:v>5090</x:v>
       </x:c>
       <x:c r="D159" s="14" t="str">
-        <x:v>label_000050</x:v>
+        <x:v>label_000044</x:v>
       </x:c>
       <x:c r="E159" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F159" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/10174</x:v>
+        <x:v>https://moodyz.com/works/list/label/5090</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
@@ -9292,16 +9727,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C160" s="14" t="str">
-        <x:v>11471</x:v>
+        <x:v>5409</x:v>
       </x:c>
       <x:c r="D160" s="14" t="str">
-        <x:v>label_000057</x:v>
+        <x:v>label_000049</x:v>
       </x:c>
       <x:c r="E160" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F160" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/11471</x:v>
+        <x:v>https://moodyz.com/works/list/label/5409</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
@@ -9312,16 +9747,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C161" s="14" t="str">
-        <x:v>12798</x:v>
+        <x:v>6879</x:v>
       </x:c>
       <x:c r="D161" s="14" t="str">
-        <x:v>label_000002</x:v>
+        <x:v>label_000040</x:v>
       </x:c>
       <x:c r="E161" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F161" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/12798</x:v>
+        <x:v>https://moodyz.com/works/list/label/6879</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
@@ -9332,16 +9767,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C162" s="14" t="str">
-        <x:v>5046</x:v>
+        <x:v>8916</x:v>
       </x:c>
       <x:c r="D162" s="14" t="str">
-        <x:v>label_000039</x:v>
+        <x:v>label_000051</x:v>
       </x:c>
       <x:c r="E162" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F162" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5046</x:v>
+        <x:v>https://moodyz.com/works/list/label/8916</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
@@ -9352,16 +9787,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C163" s="14" t="str">
-        <x:v>5047</x:v>
+        <x:v>8917</x:v>
       </x:c>
       <x:c r="D163" s="14" t="str">
-        <x:v>label_000038</x:v>
+        <x:v>label_000055</x:v>
       </x:c>
       <x:c r="E163" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F163" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5047</x:v>
+        <x:v>https://moodyz.com/works/list/label/8917</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
@@ -9372,16 +9807,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C164" s="14" t="str">
-        <x:v>5048</x:v>
+        <x:v>9288</x:v>
       </x:c>
       <x:c r="D164" s="14" t="str">
-        <x:v>label_000001</x:v>
+        <x:v>label_000054</x:v>
       </x:c>
       <x:c r="E164" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F164" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5048</x:v>
+        <x:v>https://moodyz.com/works/list/label/9288</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
@@ -9392,16 +9827,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C165" s="14" t="str">
-        <x:v>5049</x:v>
+        <x:v>9308</x:v>
       </x:c>
       <x:c r="D165" s="14" t="str">
-        <x:v>label_000045</x:v>
+        <x:v>label_000043</x:v>
       </x:c>
       <x:c r="E165" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F165" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5049</x:v>
+        <x:v>https://moodyz.com/works/list/label/9308</x:v>
       </x:c>
     </x:row>
     <x:row r="166">
@@ -9412,16 +9847,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C166" s="14" t="str">
-        <x:v>5090</x:v>
+        <x:v>9397</x:v>
       </x:c>
       <x:c r="D166" s="14" t="str">
-        <x:v>label_000044</x:v>
+        <x:v>label_000052</x:v>
       </x:c>
       <x:c r="E166" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F166" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5090</x:v>
+        <x:v>https://moodyz.com/works/list/label/9397</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
@@ -9432,16 +9867,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C167" s="14" t="str">
-        <x:v>5409</x:v>
+        <x:v>9458</x:v>
       </x:c>
       <x:c r="D167" s="14" t="str">
-        <x:v>label_000049</x:v>
+        <x:v>label_000048</x:v>
       </x:c>
       <x:c r="E167" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F167" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/5409</x:v>
+        <x:v>https://moodyz.com/works/list/label/9458</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
@@ -9452,16 +9887,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C168" s="14" t="str">
-        <x:v>6879</x:v>
+        <x:v>9483</x:v>
       </x:c>
       <x:c r="D168" s="14" t="str">
-        <x:v>label_000040</x:v>
+        <x:v>label_000059</x:v>
       </x:c>
       <x:c r="E168" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F168" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/6879</x:v>
+        <x:v>https://moodyz.com/works/list/label/9483</x:v>
       </x:c>
     </x:row>
     <x:row r="169">
@@ -9472,16 +9907,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C169" s="14" t="str">
-        <x:v>85265</x:v>
+        <x:v>9732</x:v>
       </x:c>
       <x:c r="D169" s="14" t="str">
-        <x:v>label_000056</x:v>
+        <x:v>label_000042</x:v>
       </x:c>
       <x:c r="E169" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F169" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/85265</x:v>
+        <x:v>https://moodyz.com/works/list/label/9732</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
@@ -9492,16 +9927,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C170" s="14" t="str">
-        <x:v>8916</x:v>
+        <x:v>9782</x:v>
       </x:c>
       <x:c r="D170" s="14" t="str">
-        <x:v>label_000051</x:v>
+        <x:v>label_000041</x:v>
       </x:c>
       <x:c r="E170" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F170" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/8916</x:v>
+        <x:v>https://moodyz.com/works/list/label/9782</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
@@ -9512,16 +9947,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C171" s="14" t="str">
-        <x:v>8917</x:v>
+        <x:v>10077</x:v>
       </x:c>
       <x:c r="D171" s="14" t="str">
-        <x:v>label_000055</x:v>
+        <x:v>label_000063</x:v>
       </x:c>
       <x:c r="E171" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F171" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/8917</x:v>
+        <x:v>https://moodyz.com/works/list/label/10077</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -9532,16 +9967,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C172" s="14" t="str">
-        <x:v>9288</x:v>
+        <x:v>10106</x:v>
       </x:c>
       <x:c r="D172" s="14" t="str">
-        <x:v>label_000054</x:v>
+        <x:v>label_000053</x:v>
       </x:c>
       <x:c r="E172" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F172" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9288</x:v>
+        <x:v>https://moodyz.com/works/list/label/10106</x:v>
       </x:c>
     </x:row>
     <x:row r="173">
@@ -9552,16 +9987,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C173" s="14" t="str">
-        <x:v>9308</x:v>
+        <x:v>10107</x:v>
       </x:c>
       <x:c r="D173" s="14" t="str">
-        <x:v>label_000043</x:v>
+        <x:v>label_000046</x:v>
       </x:c>
       <x:c r="E173" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F173" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9308</x:v>
+        <x:v>https://moodyz.com/works/list/label/10107</x:v>
       </x:c>
     </x:row>
     <x:row r="174">
@@ -9572,16 +10007,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C174" s="14" t="str">
-        <x:v>9397</x:v>
+        <x:v>10131</x:v>
       </x:c>
       <x:c r="D174" s="14" t="str">
-        <x:v>label_000052</x:v>
+        <x:v>label_000047</x:v>
       </x:c>
       <x:c r="E174" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F174" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9397</x:v>
+        <x:v>https://moodyz.com/works/list/label/10131</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -9592,16 +10027,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C175" s="14" t="str">
-        <x:v>9458</x:v>
+        <x:v>10142</x:v>
       </x:c>
       <x:c r="D175" s="14" t="str">
-        <x:v>label_000048</x:v>
+        <x:v>label_000060</x:v>
       </x:c>
       <x:c r="E175" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F175" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9458</x:v>
+        <x:v>https://moodyz.com/works/list/label/10142</x:v>
       </x:c>
     </x:row>
     <x:row r="176">
@@ -9612,16 +10047,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C176" s="14" t="str">
-        <x:v>9483</x:v>
+        <x:v>10144</x:v>
       </x:c>
       <x:c r="D176" s="14" t="str">
-        <x:v>label_000059</x:v>
+        <x:v>label_000061</x:v>
       </x:c>
       <x:c r="E176" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F176" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9483</x:v>
+        <x:v>https://moodyz.com/works/list/label/10144</x:v>
       </x:c>
     </x:row>
     <x:row r="177">
@@ -9632,16 +10067,16 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C177" s="14" t="str">
-        <x:v>9732</x:v>
+        <x:v>10151</x:v>
       </x:c>
       <x:c r="D177" s="14" t="str">
-        <x:v>label_000042</x:v>
+        <x:v>label_000062</x:v>
       </x:c>
       <x:c r="E177" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F177" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9732</x:v>
+        <x:v>https://moodyz.com/works/list/label/10151</x:v>
       </x:c>
     </x:row>
     <x:row r="178">
@@ -9652,176 +10087,476 @@
         <x:v>label</x:v>
       </x:c>
       <x:c r="C178" s="14" t="str">
-        <x:v>9782</x:v>
+        <x:v>10157</x:v>
       </x:c>
       <x:c r="D178" s="14" t="str">
-        <x:v>label_000041</x:v>
+        <x:v>label_000058</x:v>
       </x:c>
       <x:c r="E178" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F178" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/label/9782</x:v>
+        <x:v>https://moodyz.com/works/list/label/10157</x:v>
       </x:c>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="14" t="str">
-        <x:v>moodyz.series</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B179" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C179" s="14" t="str">
-        <x:v>3489</x:v>
+        <x:v>10172</x:v>
       </x:c>
       <x:c r="D179" s="14" t="str">
-        <x:v>series_000101</x:v>
+        <x:v>label_000064</x:v>
       </x:c>
       <x:c r="E179" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F179" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/series/3489</x:v>
+        <x:v>https://moodyz.com/works/list/label/10172</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="14" t="str">
-        <x:v>moodyz.series</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B180" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C180" s="14" t="str">
-        <x:v>3519</x:v>
+        <x:v>10174</x:v>
       </x:c>
       <x:c r="D180" s="14" t="str">
-        <x:v>series_000102</x:v>
+        <x:v>label_000050</x:v>
       </x:c>
       <x:c r="E180" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F180" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/series/3519</x:v>
+        <x:v>https://moodyz.com/works/list/label/10174</x:v>
       </x:c>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="14" t="str">
-        <x:v>moodyz.series</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B181" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C181" s="14" t="str">
-        <x:v>3562</x:v>
+        <x:v>11471</x:v>
       </x:c>
       <x:c r="D181" s="14" t="str">
-        <x:v>series_000103</x:v>
+        <x:v>label_000057</x:v>
       </x:c>
       <x:c r="E181" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F181" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/series/3562</x:v>
+        <x:v>https://moodyz.com/works/list/label/11471</x:v>
       </x:c>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="14" t="str">
-        <x:v>moodyz.series</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B182" s="14" t="str">
-        <x:v>series</x:v>
+        <x:v>label</x:v>
       </x:c>
       <x:c r="C182" s="14" t="str">
-        <x:v>5427</x:v>
+        <x:v>12798</x:v>
       </x:c>
       <x:c r="D182" s="14" t="str">
-        <x:v>series_000002</x:v>
+        <x:v>label_000002</x:v>
       </x:c>
       <x:c r="E182" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F182" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/series/5427</x:v>
+        <x:v>https://moodyz.com/works/list/label/12798</x:v>
       </x:c>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="14" t="str">
-        <x:v>s1.label</x:v>
+        <x:v>moodyz.label</x:v>
       </x:c>
       <x:c r="B183" s="14" t="str">
         <x:v>label</x:v>
       </x:c>
       <x:c r="C183" s="14" t="str">
-        <x:v>4355</x:v>
+        <x:v>85265</x:v>
       </x:c>
       <x:c r="D183" s="14" t="str">
-        <x:v>label_000081</x:v>
+        <x:v>label_000056</x:v>
       </x:c>
       <x:c r="E183" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F183" s="14" t="str">
-        <x:v>https://s1s1s1.com/works/list/label/4355</x:v>
+        <x:v>https://moodyz.com/works/list/label/85265</x:v>
       </x:c>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="14" t="str">
-        <x:v>s1.series</x:v>
+        <x:v>moodyz.series</x:v>
       </x:c>
       <x:c r="B184" s="14" t="str">
         <x:v>series</x:v>
       </x:c>
       <x:c r="C184" s="14" t="str">
-        <x:v>414</x:v>
+        <x:v>3489</x:v>
       </x:c>
       <x:c r="D184" s="14" t="str">
-        <x:v>series_000001</x:v>
+        <x:v>series_000101</x:v>
       </x:c>
       <x:c r="E184" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F184" s="14" t="str">
-        <x:v>https://s1s1s1.com/works/list/series/414</x:v>
+        <x:v>https://moodyz.com/works/list/series/3489</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="14" t="str">
-        <x:v>s1.series</x:v>
+        <x:v>moodyz.series</x:v>
       </x:c>
       <x:c r="B185" s="14" t="str">
         <x:v>series</x:v>
       </x:c>
       <x:c r="C185" s="14" t="str">
-        <x:v>422</x:v>
+        <x:v>3519</x:v>
       </x:c>
       <x:c r="D185" s="14" t="str">
-        <x:v>series_000005</x:v>
+        <x:v>series_000102</x:v>
       </x:c>
       <x:c r="E185" s="14" t="str">
         <x:v>approved</x:v>
       </x:c>
       <x:c r="F185" s="14" t="str">
-        <x:v>https://s1s1s1.com/works/list/series/422</x:v>
+        <x:v>https://moodyz.com/works/list/series/3519</x:v>
       </x:c>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="14" t="str">
-        <x:v>s1.series</x:v>
+        <x:v>moodyz.series</x:v>
       </x:c>
       <x:c r="B186" s="14" t="str">
         <x:v>series</x:v>
       </x:c>
       <x:c r="C186" s="14" t="str">
+        <x:v>3562</x:v>
+      </x:c>
+      <x:c r="D186" s="14" t="str">
+        <x:v>series_000103</x:v>
+      </x:c>
+      <x:c r="E186" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F186" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3562</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" s="14" t="str">
+        <x:v>moodyz.series</x:v>
+      </x:c>
+      <x:c r="B187" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C187" s="14" t="str">
+        <x:v>3563</x:v>
+      </x:c>
+      <x:c r="D187" s="14" t="str">
+        <x:v>series_000105</x:v>
+      </x:c>
+      <x:c r="E187" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F187" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3563</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" s="14" t="str">
+        <x:v>moodyz.series</x:v>
+      </x:c>
+      <x:c r="B188" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C188" s="14" t="str">
+        <x:v>3564</x:v>
+      </x:c>
+      <x:c r="D188" s="14" t="str">
+        <x:v>series_000106</x:v>
+      </x:c>
+      <x:c r="E188" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F188" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3564</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" s="14" t="str">
+        <x:v>moodyz.series</x:v>
+      </x:c>
+      <x:c r="B189" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C189" s="14" t="str">
+        <x:v>3565</x:v>
+      </x:c>
+      <x:c r="D189" s="14" t="str">
+        <x:v>series_000107</x:v>
+      </x:c>
+      <x:c r="E189" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F189" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3565</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" s="14" t="str">
+        <x:v>moodyz.series</x:v>
+      </x:c>
+      <x:c r="B190" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C190" s="14" t="str">
+        <x:v>3566</x:v>
+      </x:c>
+      <x:c r="D190" s="14" t="str">
+        <x:v>series_000108</x:v>
+      </x:c>
+      <x:c r="E190" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F190" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3566</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191" s="14" t="str">
+        <x:v>moodyz.series</x:v>
+      </x:c>
+      <x:c r="B191" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C191" s="14" t="str">
+        <x:v>3567</x:v>
+      </x:c>
+      <x:c r="D191" s="14" t="str">
+        <x:v>series_000109</x:v>
+      </x:c>
+      <x:c r="E191" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F191" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3567</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" s="14" t="str">
+        <x:v>moodyz.series</x:v>
+      </x:c>
+      <x:c r="B192" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C192" s="14" t="str">
+        <x:v>5427</x:v>
+      </x:c>
+      <x:c r="D192" s="14" t="str">
+        <x:v>series_000002</x:v>
+      </x:c>
+      <x:c r="E192" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F192" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/5427</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" s="14" t="str">
+        <x:v>s1.label</x:v>
+      </x:c>
+      <x:c r="B193" s="14" t="str">
+        <x:v>label</x:v>
+      </x:c>
+      <x:c r="C193" s="14" t="str">
+        <x:v>4355</x:v>
+      </x:c>
+      <x:c r="D193" s="14" t="str">
+        <x:v>label_000081</x:v>
+      </x:c>
+      <x:c r="E193" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F193" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/label/4355</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="B194" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C194" s="14" t="str">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="D194" s="14" t="str">
+        <x:v>series_000001</x:v>
+      </x:c>
+      <x:c r="E194" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F194" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/414</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="B195" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C195" s="14" t="str">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="D195" s="14" t="str">
+        <x:v>series_000005</x:v>
+      </x:c>
+      <x:c r="E195" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F195" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/422</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="B196" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C196" s="14" t="str">
         <x:v>570</x:v>
       </x:c>
-      <x:c r="D186" s="14" t="str">
+      <x:c r="D196" s="14" t="str">
         <x:v>series_000006</x:v>
       </x:c>
-      <x:c r="E186" s="14" t="str">
-        <x:v>approved</x:v>
-      </x:c>
-      <x:c r="F186" s="14" t="str">
+      <x:c r="E196" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F196" s="14" t="str">
         <x:v>https://s1s1s1.com/works/list/series/570</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="B197" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C197" s="14" t="str">
+        <x:v>571</x:v>
+      </x:c>
+      <x:c r="D197" s="14" t="str">
+        <x:v>series_000115</x:v>
+      </x:c>
+      <x:c r="E197" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F197" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/571</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="B198" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C198" s="14" t="str">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="D198" s="14" t="str">
+        <x:v>series_000116</x:v>
+      </x:c>
+      <x:c r="E198" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F198" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/572</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="B199" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C199" s="14" t="str">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="D199" s="14" t="str">
+        <x:v>series_000117</x:v>
+      </x:c>
+      <x:c r="E199" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F199" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/573</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="B200" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C200" s="14" t="str">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="D200" s="14" t="str">
+        <x:v>series_000118</x:v>
+      </x:c>
+      <x:c r="E200" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F200" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/574</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201">
+      <x:c r="A201" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="B201" s="14" t="str">
+        <x:v>series</x:v>
+      </x:c>
+      <x:c r="C201" s="14" t="str">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="D201" s="14" t="str">
+        <x:v>series_000119</x:v>
+      </x:c>
+      <x:c r="E201" s="14" t="str">
+        <x:v>approved</x:v>
+      </x:c>
+      <x:c r="F201" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/575</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9836,12 +10571,12 @@
     <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="46" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="44" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="60" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="80" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="62" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="82" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -11210,28 +11945,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B48" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>ideapocket.series</x:v>
       </x:c>
       <x:c r="C48" s="14" t="str">
-        <x:v>1546</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="D48" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+        <x:v>ideapocket-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="E48" s="14" t="str">
-        <x:v>series_000053</x:v>
+        <x:v>series_000110</x:v>
       </x:c>
       <x:c r="F48" s="14" t="str">
-        <x:v>もう一つの熟バス</x:v>
+        <x:v>究極のパンストフェチエロティックス</x:v>
       </x:c>
       <x:c r="G48" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000001</x:v>
       </x:c>
       <x:c r="H48" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1546</x:v>
+        <x:v>https://ideapocket.com/works/list/series/940</x:v>
       </x:c>
       <x:c r="I48" s="14" t="str">
-        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 0.4.9 Coverage Balance Batch Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -11239,28 +11974,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B49" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>ideapocket.series</x:v>
       </x:c>
       <x:c r="C49" s="14" t="str">
-        <x:v>1547</x:v>
+        <x:v>941</x:v>
       </x:c>
       <x:c r="D49" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+        <x:v>ideapocket-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="E49" s="14" t="str">
-        <x:v>series_000054</x:v>
+        <x:v>series_000111</x:v>
       </x:c>
       <x:c r="F49" s="14" t="str">
-        <x:v>母さんとしたい!</x:v>
+        <x:v>キミがイクまで腰振るのをやめない!</x:v>
       </x:c>
       <x:c r="G49" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000001</x:v>
       </x:c>
       <x:c r="H49" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1547</x:v>
+        <x:v>https://ideapocket.com/works/list/series/941</x:v>
       </x:c>
       <x:c r="I49" s="14" t="str">
-        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 0.4.9 Coverage Balance Batch Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -11268,28 +12003,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B50" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>ideapocket.series</x:v>
       </x:c>
       <x:c r="C50" s="14" t="str">
-        <x:v>1548</x:v>
+        <x:v>942</x:v>
       </x:c>
       <x:c r="D50" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+        <x:v>ideapocket-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="E50" s="14" t="str">
-        <x:v>series_000055</x:v>
+        <x:v>series_000112</x:v>
       </x:c>
       <x:c r="F50" s="14" t="str">
-        <x:v>義父に犯されて・・・ 美嫁いぢり</x:v>
+        <x:v>汗だくSEX</x:v>
       </x:c>
       <x:c r="G50" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000001</x:v>
       </x:c>
       <x:c r="H50" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1548</x:v>
+        <x:v>https://ideapocket.com/works/list/series/942</x:v>
       </x:c>
       <x:c r="I50" s="14" t="str">
-        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 0.4.9 Coverage Balance Batch Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -11297,28 +12032,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B51" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>ideapocket.series</x:v>
       </x:c>
       <x:c r="C51" s="14" t="str">
-        <x:v>1549</x:v>
+        <x:v>943</x:v>
       </x:c>
       <x:c r="D51" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+        <x:v>ideapocket-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="E51" s="14" t="str">
-        <x:v>series_000027</x:v>
+        <x:v>series_000113</x:v>
       </x:c>
       <x:c r="F51" s="14" t="str">
-        <x:v>となりの奥さん</x:v>
+        <x:v>女子高生痴漢電車</x:v>
       </x:c>
       <x:c r="G51" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000001</x:v>
       </x:c>
       <x:c r="H51" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1549</x:v>
+        <x:v>https://ideapocket.com/works/list/series/943</x:v>
       </x:c>
       <x:c r="I51" s="14" t="str">
-        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 0.4.9 Coverage Balance Batch Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -11326,28 +12061,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B52" s="14" t="str">
-        <x:v>madonna.series</x:v>
+        <x:v>ideapocket.series</x:v>
       </x:c>
       <x:c r="C52" s="14" t="str">
-        <x:v>1550</x:v>
+        <x:v>944</x:v>
       </x:c>
       <x:c r="D52" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+        <x:v>ideapocket-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="E52" s="14" t="str">
-        <x:v>series_000028</x:v>
+        <x:v>series_000114</x:v>
       </x:c>
       <x:c r="F52" s="14" t="str">
-        <x:v>美熟女と黒人</x:v>
+        <x:v>CLUBBER BITCHIZM</x:v>
       </x:c>
       <x:c r="G52" s="14" t="str">
-        <x:v>maker_000005</x:v>
+        <x:v>maker_000001</x:v>
       </x:c>
       <x:c r="H52" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1550</x:v>
+        <x:v>https://ideapocket.com/works/list/series/944</x:v>
       </x:c>
       <x:c r="I52" s="14" t="str">
-        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 0.4.9 Coverage Balance Batch Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -11358,25 +12093,25 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C53" s="14" t="str">
-        <x:v>1551</x:v>
+        <x:v>1546</x:v>
       </x:c>
       <x:c r="D53" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+        <x:v>madonna-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="E53" s="14" t="str">
-        <x:v>series_000029</x:v>
+        <x:v>series_000053</x:v>
       </x:c>
       <x:c r="F53" s="14" t="str">
-        <x:v>愛する夫の目の前で・・・</x:v>
+        <x:v>もう一つの熟バス</x:v>
       </x:c>
       <x:c r="G53" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H53" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1551</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1546</x:v>
       </x:c>
       <x:c r="I53" s="14" t="str">
-        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -11387,25 +12122,25 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C54" s="14" t="str">
-        <x:v>1552</x:v>
+        <x:v>1547</x:v>
       </x:c>
       <x:c r="D54" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+        <x:v>madonna-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="E54" s="14" t="str">
-        <x:v>series_000030</x:v>
+        <x:v>series_000054</x:v>
       </x:c>
       <x:c r="F54" s="14" t="str">
-        <x:v>特選 友達の母</x:v>
+        <x:v>母さんとしたい!</x:v>
       </x:c>
       <x:c r="G54" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H54" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1552</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1547</x:v>
       </x:c>
       <x:c r="I54" s="14" t="str">
-        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -11416,25 +12151,25 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C55" s="14" t="str">
-        <x:v>1553</x:v>
+        <x:v>1548</x:v>
       </x:c>
       <x:c r="D55" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-001</x:v>
+        <x:v>madonna-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="E55" s="14" t="str">
-        <x:v>series_000031</x:v>
+        <x:v>series_000055</x:v>
       </x:c>
       <x:c r="F55" s="14" t="str">
-        <x:v>僕のおばさん</x:v>
+        <x:v>義父に犯されて・・・ 美嫁いぢり</x:v>
       </x:c>
       <x:c r="G55" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H55" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1553</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1548</x:v>
       </x:c>
       <x:c r="I55" s="14" t="str">
-        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -11445,22 +12180,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C56" s="14" t="str">
-        <x:v>1554</x:v>
+        <x:v>1549</x:v>
       </x:c>
       <x:c r="D56" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E56" s="14" t="str">
-        <x:v>series_000032</x:v>
+        <x:v>series_000027</x:v>
       </x:c>
       <x:c r="F56" s="14" t="str">
-        <x:v>素人人妻ナンパ総集編4時間</x:v>
+        <x:v>となりの奥さん</x:v>
       </x:c>
       <x:c r="G56" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H56" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1554</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1549</x:v>
       </x:c>
       <x:c r="I56" s="14" t="str">
         <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11474,22 +12209,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C57" s="14" t="str">
-        <x:v>1555</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D57" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E57" s="14" t="str">
-        <x:v>series_000033</x:v>
+        <x:v>series_000028</x:v>
       </x:c>
       <x:c r="F57" s="14" t="str">
-        <x:v>五十路熟女18人4時間</x:v>
+        <x:v>美熟女と黒人</x:v>
       </x:c>
       <x:c r="G57" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H57" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1555</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1550</x:v>
       </x:c>
       <x:c r="I57" s="14" t="str">
         <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11503,22 +12238,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C58" s="14" t="str">
-        <x:v>1556</x:v>
+        <x:v>1551</x:v>
       </x:c>
       <x:c r="D58" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E58" s="14" t="str">
-        <x:v>series_000034</x:v>
+        <x:v>series_000029</x:v>
       </x:c>
       <x:c r="F58" s="14" t="str">
-        <x:v>団地妻20人4時間</x:v>
+        <x:v>愛する夫の目の前で・・・</x:v>
       </x:c>
       <x:c r="G58" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H58" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1556</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1551</x:v>
       </x:c>
       <x:c r="I58" s="14" t="str">
         <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11532,22 +12267,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C59" s="14" t="str">
-        <x:v>1557</x:v>
+        <x:v>1552</x:v>
       </x:c>
       <x:c r="D59" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E59" s="14" t="str">
-        <x:v>series_000035</x:v>
+        <x:v>series_000030</x:v>
       </x:c>
       <x:c r="F59" s="14" t="str">
-        <x:v>犯された熟女たち総集編4時間</x:v>
+        <x:v>特選 友達の母</x:v>
       </x:c>
       <x:c r="G59" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H59" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1557</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1552</x:v>
       </x:c>
       <x:c r="I59" s="14" t="str">
         <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11561,22 +12296,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C60" s="14" t="str">
-        <x:v>1558</x:v>
+        <x:v>1553</x:v>
       </x:c>
       <x:c r="D60" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E60" s="14" t="str">
-        <x:v>series_000036</x:v>
+        <x:v>series_000031</x:v>
       </x:c>
       <x:c r="F60" s="14" t="str">
-        <x:v>妖艶おんな愛戯</x:v>
+        <x:v>僕のおばさん</x:v>
       </x:c>
       <x:c r="G60" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H60" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1558</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1553</x:v>
       </x:c>
       <x:c r="I60" s="14" t="str">
         <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11590,25 +12325,25 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C61" s="14" t="str">
-        <x:v>1559</x:v>
+        <x:v>1554</x:v>
       </x:c>
       <x:c r="D61" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E61" s="14" t="str">
-        <x:v>series_000056</x:v>
+        <x:v>series_000032</x:v>
       </x:c>
       <x:c r="F61" s="14" t="str">
-        <x:v>五十路の性</x:v>
+        <x:v>素人人妻ナンパ総集編4時間</x:v>
       </x:c>
       <x:c r="G61" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H61" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1559</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1554</x:v>
       </x:c>
       <x:c r="I61" s="14" t="str">
-        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -11619,25 +12354,25 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C62" s="14" t="str">
-        <x:v>1560</x:v>
+        <x:v>1555</x:v>
       </x:c>
       <x:c r="D62" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E62" s="14" t="str">
-        <x:v>series_000057</x:v>
+        <x:v>series_000033</x:v>
       </x:c>
       <x:c r="F62" s="14" t="str">
-        <x:v>新・素人人妻ナンパ</x:v>
+        <x:v>五十路熟女18人4時間</x:v>
       </x:c>
       <x:c r="G62" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H62" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1560</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1555</x:v>
       </x:c>
       <x:c r="I62" s="14" t="str">
-        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -11648,25 +12383,25 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C63" s="14" t="str">
-        <x:v>1561</x:v>
+        <x:v>1556</x:v>
       </x:c>
       <x:c r="D63" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E63" s="14" t="str">
-        <x:v>series_000058</x:v>
+        <x:v>series_000034</x:v>
       </x:c>
       <x:c r="F63" s="14" t="str">
-        <x:v>こちらマドンナ独身寮・ただいま満室</x:v>
+        <x:v>団地妻20人4時間</x:v>
       </x:c>
       <x:c r="G63" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H63" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1561</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1556</x:v>
       </x:c>
       <x:c r="I63" s="14" t="str">
-        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -11677,25 +12412,25 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C64" s="14" t="str">
-        <x:v>1562</x:v>
+        <x:v>1557</x:v>
       </x:c>
       <x:c r="D64" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E64" s="14" t="str">
-        <x:v>series_000059</x:v>
+        <x:v>series_000035</x:v>
       </x:c>
       <x:c r="F64" s="14" t="str">
-        <x:v>3D作品</x:v>
+        <x:v>犯された熟女たち総集編4時間</x:v>
       </x:c>
       <x:c r="G64" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H64" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1562</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1557</x:v>
       </x:c>
       <x:c r="I64" s="14" t="str">
-        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -11706,25 +12441,25 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C65" s="14" t="str">
-        <x:v>1563</x:v>
+        <x:v>1558</x:v>
       </x:c>
       <x:c r="D65" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+        <x:v>madonna-series-2026-09-04-partial-001</x:v>
       </x:c>
       <x:c r="E65" s="14" t="str">
-        <x:v>series_000060</x:v>
+        <x:v>series_000036</x:v>
       </x:c>
       <x:c r="F65" s="14" t="str">
-        <x:v>密着セックス</x:v>
+        <x:v>妖艶おんな愛戯</x:v>
       </x:c>
       <x:c r="G65" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H65" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1563</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1558</x:v>
       </x:c>
       <x:c r="I65" s="14" t="str">
-        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -11735,22 +12470,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C66" s="14" t="str">
-        <x:v>1564</x:v>
+        <x:v>1559</x:v>
       </x:c>
       <x:c r="D66" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="E66" s="14" t="str">
-        <x:v>series_000061</x:v>
+        <x:v>series_000056</x:v>
       </x:c>
       <x:c r="F66" s="14" t="str">
-        <x:v>交換夫婦NTR</x:v>
+        <x:v>五十路の性</x:v>
       </x:c>
       <x:c r="G66" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H66" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1564</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1559</x:v>
       </x:c>
       <x:c r="I66" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11764,25 +12499,25 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C67" s="14" t="str">
-        <x:v>1565</x:v>
+        <x:v>1560</x:v>
       </x:c>
       <x:c r="D67" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+        <x:v>madonna-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="E67" s="14" t="str">
-        <x:v>series_000081</x:v>
+        <x:v>series_000057</x:v>
       </x:c>
       <x:c r="F67" s="14" t="str">
-        <x:v>出張先のビジネスホテルでずっと憧れていた女上司と</x:v>
+        <x:v>新・素人人妻ナンパ</x:v>
       </x:c>
       <x:c r="G67" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H67" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1565</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1560</x:v>
       </x:c>
       <x:c r="I67" s="14" t="str">
-        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -11793,25 +12528,25 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C68" s="14" t="str">
-        <x:v>1566</x:v>
+        <x:v>1561</x:v>
       </x:c>
       <x:c r="D68" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+        <x:v>madonna-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="E68" s="14" t="str">
-        <x:v>series_000082</x:v>
+        <x:v>series_000058</x:v>
       </x:c>
       <x:c r="F68" s="14" t="str">
-        <x:v>人妻秘書、汗と接吻に満ちた社長室中出し性交</x:v>
+        <x:v>こちらマドンナ独身寮・ただいま満室</x:v>
       </x:c>
       <x:c r="G68" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H68" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1566</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1561</x:v>
       </x:c>
       <x:c r="I68" s="14" t="str">
-        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -11822,25 +12557,25 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C69" s="14" t="str">
-        <x:v>1570</x:v>
+        <x:v>1562</x:v>
       </x:c>
       <x:c r="D69" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+        <x:v>madonna-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="E69" s="14" t="str">
-        <x:v>series_000083</x:v>
+        <x:v>series_000059</x:v>
       </x:c>
       <x:c r="F69" s="14" t="str">
-        <x:v>働くおばさん!</x:v>
+        <x:v>3D作品</x:v>
       </x:c>
       <x:c r="G69" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H69" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1570</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1562</x:v>
       </x:c>
       <x:c r="I69" s="14" t="str">
-        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -11851,25 +12586,25 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C70" s="14" t="str">
-        <x:v>1571</x:v>
+        <x:v>1563</x:v>
       </x:c>
       <x:c r="D70" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+        <x:v>madonna-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="E70" s="14" t="str">
-        <x:v>series_000084</x:v>
+        <x:v>series_000060</x:v>
       </x:c>
       <x:c r="F70" s="14" t="str">
-        <x:v>四十路の性</x:v>
+        <x:v>密着セックス</x:v>
       </x:c>
       <x:c r="G70" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H70" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1571</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1563</x:v>
       </x:c>
       <x:c r="I70" s="14" t="str">
-        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -11880,25 +12615,25 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C71" s="14" t="str">
-        <x:v>1572</x:v>
+        <x:v>1564</x:v>
       </x:c>
       <x:c r="D71" s="14" t="str">
-        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+        <x:v>madonna-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="E71" s="14" t="str">
-        <x:v>series_000085</x:v>
+        <x:v>series_000061</x:v>
       </x:c>
       <x:c r="F71" s="14" t="str">
-        <x:v>最高の筆おろし!</x:v>
+        <x:v>交換夫婦NTR</x:v>
       </x:c>
       <x:c r="G71" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H71" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1572</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1564</x:v>
       </x:c>
       <x:c r="I71" s="14" t="str">
-        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch B Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -11909,22 +12644,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C72" s="14" t="str">
-        <x:v>1573</x:v>
+        <x:v>1565</x:v>
       </x:c>
       <x:c r="D72" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E72" s="14" t="str">
-        <x:v>series_000086</x:v>
+        <x:v>series_000081</x:v>
       </x:c>
       <x:c r="F72" s="14" t="str">
-        <x:v>ハメ狂い淫乱熟女</x:v>
+        <x:v>出張先のビジネスホテルでずっと憧れていた女上司と</x:v>
       </x:c>
       <x:c r="G72" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H72" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1573</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1565</x:v>
       </x:c>
       <x:c r="I72" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11938,22 +12673,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C73" s="14" t="str">
-        <x:v>1574</x:v>
+        <x:v>1566</x:v>
       </x:c>
       <x:c r="D73" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E73" s="14" t="str">
-        <x:v>series_000087</x:v>
+        <x:v>series_000082</x:v>
       </x:c>
       <x:c r="F73" s="14" t="str">
-        <x:v>犯されたセールスレディ</x:v>
+        <x:v>人妻秘書、汗と接吻に満ちた社長室中出し性交</x:v>
       </x:c>
       <x:c r="G73" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H73" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1574</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1566</x:v>
       </x:c>
       <x:c r="I73" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11967,22 +12702,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C74" s="14" t="str">
-        <x:v>1579</x:v>
+        <x:v>1570</x:v>
       </x:c>
       <x:c r="D74" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E74" s="14" t="str">
-        <x:v>series_000088</x:v>
+        <x:v>series_000083</x:v>
       </x:c>
       <x:c r="F74" s="14" t="str">
-        <x:v>娘のカレシにイカされた母</x:v>
+        <x:v>働くおばさん!</x:v>
       </x:c>
       <x:c r="G74" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H74" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1579</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1570</x:v>
       </x:c>
       <x:c r="I74" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -11996,22 +12731,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C75" s="14" t="str">
-        <x:v>1581</x:v>
+        <x:v>1571</x:v>
       </x:c>
       <x:c r="D75" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E75" s="14" t="str">
-        <x:v>series_000089</x:v>
+        <x:v>series_000084</x:v>
       </x:c>
       <x:c r="F75" s="14" t="str">
-        <x:v>昼下がりのふしだら奥さん</x:v>
+        <x:v>四十路の性</x:v>
       </x:c>
       <x:c r="G75" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H75" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1581</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1571</x:v>
       </x:c>
       <x:c r="I75" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -12025,22 +12760,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C76" s="14" t="str">
-        <x:v>1585</x:v>
+        <x:v>1572</x:v>
       </x:c>
       <x:c r="D76" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E76" s="14" t="str">
-        <x:v>series_000090</x:v>
+        <x:v>series_000085</x:v>
       </x:c>
       <x:c r="F76" s="14" t="str">
-        <x:v>豊潤麗し競泳水着</x:v>
+        <x:v>最高の筆おろし!</x:v>
       </x:c>
       <x:c r="G76" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H76" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1585</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1572</x:v>
       </x:c>
       <x:c r="I76" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -12054,22 +12789,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C77" s="14" t="str">
-        <x:v>1586</x:v>
+        <x:v>1573</x:v>
       </x:c>
       <x:c r="D77" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E77" s="14" t="str">
-        <x:v>series_000091</x:v>
+        <x:v>series_000086</x:v>
       </x:c>
       <x:c r="F77" s="14" t="str">
-        <x:v>悶絶美熟女の卑猥な日常</x:v>
+        <x:v>ハメ狂い淫乱熟女</x:v>
       </x:c>
       <x:c r="G77" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H77" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1586</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1573</x:v>
       </x:c>
       <x:c r="I77" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -12083,22 +12818,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C78" s="14" t="str">
-        <x:v>1587</x:v>
+        <x:v>1574</x:v>
       </x:c>
       <x:c r="D78" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E78" s="14" t="str">
-        <x:v>series_000092</x:v>
+        <x:v>series_000087</x:v>
       </x:c>
       <x:c r="F78" s="14" t="str">
-        <x:v>MADAM QUEEN × DANCING FUCK</x:v>
+        <x:v>犯されたセールスレディ</x:v>
       </x:c>
       <x:c r="G78" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H78" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1587</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1574</x:v>
       </x:c>
       <x:c r="I78" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -12112,22 +12847,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C79" s="14" t="str">
-        <x:v>1588</x:v>
+        <x:v>1579</x:v>
       </x:c>
       <x:c r="D79" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E79" s="14" t="str">
-        <x:v>series_000093</x:v>
+        <x:v>series_000088</x:v>
       </x:c>
       <x:c r="F79" s="14" t="str">
-        <x:v>濡れ透け婦人の甘い疼き</x:v>
+        <x:v>娘のカレシにイカされた母</x:v>
       </x:c>
       <x:c r="G79" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H79" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1588</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1579</x:v>
       </x:c>
       <x:c r="I79" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -12141,22 +12876,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C80" s="14" t="str">
-        <x:v>1589</x:v>
+        <x:v>1581</x:v>
       </x:c>
       <x:c r="D80" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E80" s="14" t="str">
-        <x:v>series_000094</x:v>
+        <x:v>series_000089</x:v>
       </x:c>
       <x:c r="F80" s="14" t="str">
-        <x:v>溢れだす美熟女の泉</x:v>
+        <x:v>昼下がりのふしだら奥さん</x:v>
       </x:c>
       <x:c r="G80" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H80" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1589</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1581</x:v>
       </x:c>
       <x:c r="I80" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -12170,22 +12905,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C81" s="14" t="str">
-        <x:v>1590</x:v>
+        <x:v>1585</x:v>
       </x:c>
       <x:c r="D81" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E81" s="14" t="str">
-        <x:v>series_000095</x:v>
+        <x:v>series_000090</x:v>
       </x:c>
       <x:c r="F81" s="14" t="str">
-        <x:v>匂いたつパンストの誘惑</x:v>
+        <x:v>豊潤麗し競泳水着</x:v>
       </x:c>
       <x:c r="G81" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H81" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1590</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1585</x:v>
       </x:c>
       <x:c r="I81" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -12199,22 +12934,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C82" s="14" t="str">
-        <x:v>1591</x:v>
+        <x:v>1586</x:v>
       </x:c>
       <x:c r="D82" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E82" s="14" t="str">
-        <x:v>series_000096</x:v>
+        <x:v>series_000091</x:v>
       </x:c>
       <x:c r="F82" s="14" t="str">
-        <x:v>ムッチリ美熟女ハミ出し水着</x:v>
+        <x:v>悶絶美熟女の卑猥な日常</x:v>
       </x:c>
       <x:c r="G82" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H82" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1591</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1586</x:v>
       </x:c>
       <x:c r="I82" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -12228,22 +12963,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C83" s="14" t="str">
-        <x:v>1592</x:v>
+        <x:v>1587</x:v>
       </x:c>
       <x:c r="D83" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E83" s="14" t="str">
-        <x:v>series_000097</x:v>
+        <x:v>series_000092</x:v>
       </x:c>
       <x:c r="F83" s="14" t="str">
-        <x:v>巨尻誘惑</x:v>
+        <x:v>MADAM QUEEN × DANCING FUCK</x:v>
       </x:c>
       <x:c r="G83" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H83" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1592</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1587</x:v>
       </x:c>
       <x:c r="I83" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -12257,22 +12992,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C84" s="14" t="str">
-        <x:v>1593</x:v>
+        <x:v>1588</x:v>
       </x:c>
       <x:c r="D84" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E84" s="14" t="str">
-        <x:v>series_000098</x:v>
+        <x:v>series_000093</x:v>
       </x:c>
       <x:c r="F84" s="14" t="str">
-        <x:v>堕ちた万引き妻</x:v>
+        <x:v>濡れ透け婦人の甘い疼き</x:v>
       </x:c>
       <x:c r="G84" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H84" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1593</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1588</x:v>
       </x:c>
       <x:c r="I84" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -12286,22 +13021,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C85" s="14" t="str">
-        <x:v>1594</x:v>
+        <x:v>1589</x:v>
       </x:c>
       <x:c r="D85" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E85" s="14" t="str">
-        <x:v>series_000099</x:v>
+        <x:v>series_000094</x:v>
       </x:c>
       <x:c r="F85" s="14" t="str">
-        <x:v>義母の舌と接吻</x:v>
+        <x:v>溢れだす美熟女の泉</x:v>
       </x:c>
       <x:c r="G85" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H85" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1594</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1589</x:v>
       </x:c>
       <x:c r="I85" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -12315,22 +13050,22 @@
         <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C86" s="14" t="str">
-        <x:v>1595</x:v>
+        <x:v>1590</x:v>
       </x:c>
       <x:c r="D86" s="14" t="str">
         <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E86" s="14" t="str">
-        <x:v>series_000100</x:v>
+        <x:v>series_000095</x:v>
       </x:c>
       <x:c r="F86" s="14" t="str">
-        <x:v>狙われたパート妻</x:v>
+        <x:v>匂いたつパンストの誘惑</x:v>
       </x:c>
       <x:c r="G86" s="14" t="str">
         <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H86" s="14" t="str">
-        <x:v>https://madonna-av.com/works/list/series/1595</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1590</x:v>
       </x:c>
       <x:c r="I86" s="14" t="str">
         <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
@@ -12341,28 +13076,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B87" s="14" t="str">
-        <x:v>moodyz.series</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C87" s="14" t="str">
-        <x:v>3489</x:v>
+        <x:v>1591</x:v>
       </x:c>
       <x:c r="D87" s="14" t="str">
-        <x:v>moodyz-series-2026-09-04-partial-001</x:v>
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E87" s="14" t="str">
-        <x:v>series_000101</x:v>
+        <x:v>series_000096</x:v>
       </x:c>
       <x:c r="F87" s="14" t="str">
-        <x:v>聖水くらぶ</x:v>
+        <x:v>ムッチリ美熟女ハミ出し水着</x:v>
       </x:c>
       <x:c r="G87" s="14" t="str">
-        <x:v>maker_000002</x:v>
+        <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H87" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/series/3489</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1591</x:v>
       </x:c>
       <x:c r="I87" s="14" t="str">
-        <x:v>官方 Series 详情页与 0.4.8 跨 Provider partial Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -12370,28 +13105,28 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B88" s="14" t="str">
-        <x:v>moodyz.series</x:v>
+        <x:v>madonna.series</x:v>
       </x:c>
       <x:c r="C88" s="14" t="str">
-        <x:v>3519</x:v>
+        <x:v>1592</x:v>
       </x:c>
       <x:c r="D88" s="14" t="str">
-        <x:v>moodyz-series-2026-09-04-partial-001</x:v>
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
       </x:c>
       <x:c r="E88" s="14" t="str">
-        <x:v>series_000102</x:v>
+        <x:v>series_000097</x:v>
       </x:c>
       <x:c r="F88" s="14" t="str">
-        <x:v>W CAST</x:v>
+        <x:v>巨尻誘惑</x:v>
       </x:c>
       <x:c r="G88" s="14" t="str">
-        <x:v>maker_000002</x:v>
+        <x:v>maker_000005</x:v>
       </x:c>
       <x:c r="H88" s="14" t="str">
-        <x:v>https://moodyz.com/works/list/series/3519</x:v>
+        <x:v>https://madonna-av.com/works/list/series/1592</x:v>
       </x:c>
       <x:c r="I88" s="14" t="str">
-        <x:v>官方 Series 详情页与 0.4.8 跨 Provider partial Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -12399,28 +13134,463 @@
         <x:v>publish</x:v>
       </x:c>
       <x:c r="B89" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C89" s="14" t="str">
+        <x:v>1593</x:v>
+      </x:c>
+      <x:c r="D89" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E89" s="14" t="str">
+        <x:v>series_000098</x:v>
+      </x:c>
+      <x:c r="F89" s="14" t="str">
+        <x:v>堕ちた万引き妻</x:v>
+      </x:c>
+      <x:c r="G89" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H89" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1593</x:v>
+      </x:c>
+      <x:c r="I89" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B90" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C90" s="14" t="str">
+        <x:v>1594</x:v>
+      </x:c>
+      <x:c r="D90" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E90" s="14" t="str">
+        <x:v>series_000099</x:v>
+      </x:c>
+      <x:c r="F90" s="14" t="str">
+        <x:v>義母の舌と接吻</x:v>
+      </x:c>
+      <x:c r="G90" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H90" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1594</x:v>
+      </x:c>
+      <x:c r="I90" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B91" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="C91" s="14" t="str">
+        <x:v>1595</x:v>
+      </x:c>
+      <x:c r="D91" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="E91" s="14" t="str">
+        <x:v>series_000100</x:v>
+      </x:c>
+      <x:c r="F91" s="14" t="str">
+        <x:v>狙われたパート妻</x:v>
+      </x:c>
+      <x:c r="G91" s="14" t="str">
+        <x:v>maker_000005</x:v>
+      </x:c>
+      <x:c r="H91" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1595</x:v>
+      </x:c>
+      <x:c r="I91" s="14" t="str">
+        <x:v>官方 Series 详情页与 Batch C Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B92" s="14" t="str">
         <x:v>moodyz.series</x:v>
       </x:c>
-      <x:c r="C89" s="14" t="str">
+      <x:c r="C92" s="14" t="str">
+        <x:v>3489</x:v>
+      </x:c>
+      <x:c r="D92" s="14" t="str">
+        <x:v>moodyz-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E92" s="14" t="str">
+        <x:v>series_000101</x:v>
+      </x:c>
+      <x:c r="F92" s="14" t="str">
+        <x:v>聖水くらぶ</x:v>
+      </x:c>
+      <x:c r="G92" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H92" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3489</x:v>
+      </x:c>
+      <x:c r="I92" s="14" t="str">
+        <x:v>官方 Series 详情页与 0.4.8 跨 Provider partial Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B93" s="14" t="str">
+        <x:v>moodyz.series</x:v>
+      </x:c>
+      <x:c r="C93" s="14" t="str">
+        <x:v>3519</x:v>
+      </x:c>
+      <x:c r="D93" s="14" t="str">
+        <x:v>moodyz-series-2026-09-04-partial-001</x:v>
+      </x:c>
+      <x:c r="E93" s="14" t="str">
+        <x:v>series_000102</x:v>
+      </x:c>
+      <x:c r="F93" s="14" t="str">
+        <x:v>W CAST</x:v>
+      </x:c>
+      <x:c r="G93" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H93" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3519</x:v>
+      </x:c>
+      <x:c r="I93" s="14" t="str">
+        <x:v>官方 Series 详情页与 0.4.8 跨 Provider partial Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B94" s="14" t="str">
+        <x:v>moodyz.series</x:v>
+      </x:c>
+      <x:c r="C94" s="14" t="str">
         <x:v>3562</x:v>
       </x:c>
-      <x:c r="D89" s="14" t="str">
+      <x:c r="D94" s="14" t="str">
         <x:v>moodyz-series-2026-09-04-partial-001</x:v>
       </x:c>
-      <x:c r="E89" s="14" t="str">
+      <x:c r="E94" s="14" t="str">
         <x:v>series_000103</x:v>
       </x:c>
-      <x:c r="F89" s="14" t="str">
+      <x:c r="F94" s="14" t="str">
         <x:v>聖水痴女ハーレム</x:v>
       </x:c>
-      <x:c r="G89" s="14" t="str">
+      <x:c r="G94" s="14" t="str">
         <x:v>maker_000002</x:v>
       </x:c>
-      <x:c r="H89" s="14" t="str">
+      <x:c r="H94" s="14" t="str">
         <x:v>https://moodyz.com/works/list/series/3562</x:v>
       </x:c>
-      <x:c r="I89" s="14" t="str">
+      <x:c r="I94" s="14" t="str">
         <x:v>官方 Series 详情页与 0.4.8 跨 Provider partial Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B95" s="14" t="str">
+        <x:v>moodyz.series</x:v>
+      </x:c>
+      <x:c r="C95" s="14" t="str">
+        <x:v>3563</x:v>
+      </x:c>
+      <x:c r="D95" s="14" t="str">
+        <x:v>moodyz-series-2026-09-04-partial-002</x:v>
+      </x:c>
+      <x:c r="E95" s="14" t="str">
+        <x:v>series_000105</x:v>
+      </x:c>
+      <x:c r="F95" s="14" t="str">
+        <x:v>おねだりバックピストン</x:v>
+      </x:c>
+      <x:c r="G95" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H95" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3563</x:v>
+      </x:c>
+      <x:c r="I95" s="14" t="str">
+        <x:v>官方 Series 详情页与 0.4.9 Coverage Balance Batch Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B96" s="14" t="str">
+        <x:v>moodyz.series</x:v>
+      </x:c>
+      <x:c r="C96" s="14" t="str">
+        <x:v>3564</x:v>
+      </x:c>
+      <x:c r="D96" s="14" t="str">
+        <x:v>moodyz-series-2026-09-04-partial-002</x:v>
+      </x:c>
+      <x:c r="E96" s="14" t="str">
+        <x:v>series_000106</x:v>
+      </x:c>
+      <x:c r="F96" s="14" t="str">
+        <x:v>産後処女を義父に奪われ一度イッたら痙攣アクメが止まらなくなる妻</x:v>
+      </x:c>
+      <x:c r="G96" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H96" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3564</x:v>
+      </x:c>
+      <x:c r="I96" s="14" t="str">
+        <x:v>官方 Series 详情页与 0.4.9 Coverage Balance Batch Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B97" s="14" t="str">
+        <x:v>moodyz.series</x:v>
+      </x:c>
+      <x:c r="C97" s="14" t="str">
+        <x:v>3565</x:v>
+      </x:c>
+      <x:c r="D97" s="14" t="str">
+        <x:v>moodyz-series-2026-09-04-partial-002</x:v>
+      </x:c>
+      <x:c r="E97" s="14" t="str">
+        <x:v>series_000107</x:v>
+      </x:c>
+      <x:c r="F97" s="14" t="str">
+        <x:v>捜査官を辞めて妻になったのに…</x:v>
+      </x:c>
+      <x:c r="G97" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H97" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3565</x:v>
+      </x:c>
+      <x:c r="I97" s="14" t="str">
+        <x:v>官方 Series 详情页与 0.4.9 Coverage Balance Batch Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B98" s="14" t="str">
+        <x:v>moodyz.series</x:v>
+      </x:c>
+      <x:c r="C98" s="14" t="str">
+        <x:v>3566</x:v>
+      </x:c>
+      <x:c r="D98" s="14" t="str">
+        <x:v>moodyz-series-2026-09-04-partial-002</x:v>
+      </x:c>
+      <x:c r="E98" s="14" t="str">
+        <x:v>series_000108</x:v>
+      </x:c>
+      <x:c r="F98" s="14" t="str">
+        <x:v>おれに初めてセフレができたので彼女とはできないド変態プレイを</x:v>
+      </x:c>
+      <x:c r="G98" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H98" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3566</x:v>
+      </x:c>
+      <x:c r="I98" s="14" t="str">
+        <x:v>官方 Series 详情页与 0.4.9 Coverage Balance Batch Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B99" s="14" t="str">
+        <x:v>moodyz.series</x:v>
+      </x:c>
+      <x:c r="C99" s="14" t="str">
+        <x:v>3567</x:v>
+      </x:c>
+      <x:c r="D99" s="14" t="str">
+        <x:v>moodyz-series-2026-09-04-partial-002</x:v>
+      </x:c>
+      <x:c r="E99" s="14" t="str">
+        <x:v>series_000109</x:v>
+      </x:c>
+      <x:c r="F99" s="14" t="str">
+        <x:v>突然の大雨で帰宅難民になった彼女の妹と朝まで…</x:v>
+      </x:c>
+      <x:c r="G99" s="14" t="str">
+        <x:v>maker_000002</x:v>
+      </x:c>
+      <x:c r="H99" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3567</x:v>
+      </x:c>
+      <x:c r="I99" s="14" t="str">
+        <x:v>官方 Series 详情页与 0.4.9 Coverage Balance Batch Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B100" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="C100" s="14" t="str">
+        <x:v>571</x:v>
+      </x:c>
+      <x:c r="D100" s="14" t="str">
+        <x:v>s1-series-2026-09-04-partial-002</x:v>
+      </x:c>
+      <x:c r="E100" s="14" t="str">
+        <x:v>series_000115</x:v>
+      </x:c>
+      <x:c r="F100" s="14" t="str">
+        <x:v>ブラックディックファック</x:v>
+      </x:c>
+      <x:c r="G100" s="14" t="str">
+        <x:v>maker_000003</x:v>
+      </x:c>
+      <x:c r="H100" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/571</x:v>
+      </x:c>
+      <x:c r="I100" s="14" t="str">
+        <x:v>官方 Series 详情页与 0.4.9 Coverage Balance Batch Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B101" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="C101" s="14" t="str">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="D101" s="14" t="str">
+        <x:v>s1-series-2026-09-04-partial-002</x:v>
+      </x:c>
+      <x:c r="E101" s="14" t="str">
+        <x:v>series_000116</x:v>
+      </x:c>
+      <x:c r="F101" s="14" t="str">
+        <x:v>爆乳インストラクター</x:v>
+      </x:c>
+      <x:c r="G101" s="14" t="str">
+        <x:v>maker_000003</x:v>
+      </x:c>
+      <x:c r="H101" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/572</x:v>
+      </x:c>
+      <x:c r="I101" s="14" t="str">
+        <x:v>官方 Series 详情页与 0.4.9 Coverage Balance Batch Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B102" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="C102" s="14" t="str">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="D102" s="14" t="str">
+        <x:v>s1-series-2026-09-04-partial-002</x:v>
+      </x:c>
+      <x:c r="E102" s="14" t="str">
+        <x:v>series_000117</x:v>
+      </x:c>
+      <x:c r="F102" s="14" t="str">
+        <x:v>おっぱい離れできないボク</x:v>
+      </x:c>
+      <x:c r="G102" s="14" t="str">
+        <x:v>maker_000003</x:v>
+      </x:c>
+      <x:c r="H102" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/573</x:v>
+      </x:c>
+      <x:c r="I102" s="14" t="str">
+        <x:v>官方 Series 详情页与 0.4.9 Coverage Balance Batch Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B103" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="C103" s="14" t="str">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="D103" s="14" t="str">
+        <x:v>s1-series-2026-09-04-partial-002</x:v>
+      </x:c>
+      <x:c r="E103" s="14" t="str">
+        <x:v>series_000118</x:v>
+      </x:c>
+      <x:c r="F103" s="14" t="str">
+        <x:v>挿れッパ!!</x:v>
+      </x:c>
+      <x:c r="G103" s="14" t="str">
+        <x:v>maker_000003</x:v>
+      </x:c>
+      <x:c r="H103" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/574</x:v>
+      </x:c>
+      <x:c r="I103" s="14" t="str">
+        <x:v>官方 Series 详情页与 0.4.9 Coverage Balance Batch Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="14" t="str">
+        <x:v>publish</x:v>
+      </x:c>
+      <x:c r="B104" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="C104" s="14" t="str">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="D104" s="14" t="str">
+        <x:v>s1-series-2026-09-04-partial-002</x:v>
+      </x:c>
+      <x:c r="E104" s="14" t="str">
+        <x:v>series_000119</x:v>
+      </x:c>
+      <x:c r="F104" s="14" t="str">
+        <x:v>わたし、犯されにゆきます。</x:v>
+      </x:c>
+      <x:c r="G104" s="14" t="str">
+        <x:v>maker_000003</x:v>
+      </x:c>
+      <x:c r="H104" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/575</x:v>
+      </x:c>
+      <x:c r="I104" s="14" t="str">
+        <x:v>官方 Series 详情页与 0.4.9 Coverage Balance Batch Snapshot 的 Provider 外部 ID、日文名称和 Maker 归属一致；允许正式发布。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -12432,7 +13602,7 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="46" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="48" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
@@ -12482,7 +13652,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="14" t="str">
-        <x:v>ideapocket-series-2026-09-04-partial-001</x:v>
+        <x:v>ideapocket-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="B3" s="14" t="str">
         <x:v>ideapocket.series</x:v>
@@ -12494,7 +13664,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="E3" s="14" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F3" s="14" t="str">
         <x:v>no</x:v>
@@ -12522,7 +13692,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14" t="str">
-        <x:v>moodyz-series-2026-09-04-partial-001</x:v>
+        <x:v>moodyz-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
         <x:v>moodyz.series</x:v>
@@ -12534,7 +13704,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="E5" s="14" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F5" s="14" t="str">
         <x:v>no</x:v>
@@ -12542,7 +13712,7 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="14" t="str">
-        <x:v>s1-series-2026-09-04-partial-001</x:v>
+        <x:v>s1-series-2026-09-04-partial-002</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
         <x:v>s1.series</x:v>
@@ -12554,7 +13724,7 @@
         <x:v>2026-09-04</x:v>
       </x:c>
       <x:c r="E6" s="14" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F6" s="14" t="str">
         <x:v>no</x:v>
@@ -12573,9 +13743,9 @@
     <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="44" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="60" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="62" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">

--- a/exports/xlsx/organization-series-registry.xlsx
+++ b/exports/xlsx/organization-series-registry.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organizations" sheetId="1" r:id="Rb8bf91c6e1f74728"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series" sheetId="2" r:id="Rdd212fd0f1f04008"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Index Providers" sheetId="3" r:id="Re2de6957731347a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Registry" sheetId="4" r:id="R29063f2eff024c79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External ID Mapping" sheetId="5" r:id="R18161e3a313f49ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Candidate Reviews" sheetId="6" r:id="R1c7ff3dd77894792"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Latest Snapshots" sheetId="7" r:id="R719ec3c7f17f411a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Index Candidates" sheetId="8" r:id="Rf76d7fbd1b3b4f80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organizations" sheetId="1" r:id="Rccec6024515f40a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series" sheetId="2" r:id="Rd58b3781fcfa4954"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Index Providers" sheetId="3" r:id="Re1dde76516f642c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Registry" sheetId="4" r:id="R927e31a615af4e57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External ID Mapping" sheetId="5" r:id="Rd168c275fcdd4d26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Candidate Reviews" sheetId="6" r:id="R0ca10ac4518f4d9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Latest Snapshots" sheetId="7" r:id="Re79d4fa177504a03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Index Candidates" sheetId="8" r:id="R6ae3d52bf3334a8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series Index Progress" sheetId="9" r:id="Rfe7423f22ecb4e1c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6399,8 +6400,8 @@
     <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="90" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="94" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="92" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="96" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -10576,7 +10577,7 @@
     <x:col min="6" max="6" width="44" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="62" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="82" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="84" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -13608,6 +13609,12 @@
     <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="48" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -13629,6 +13636,24 @@
       <x:c r="F1" s="6" t="str">
         <x:v>Complete</x:v>
       </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>Window</x:v>
+      </x:c>
+      <x:c r="H1" s="6" t="str">
+        <x:v>Order Basis</x:v>
+      </x:c>
+      <x:c r="I1" s="6" t="str">
+        <x:v>Start ID</x:v>
+      </x:c>
+      <x:c r="J1" s="6" t="str">
+        <x:v>End ID</x:v>
+      </x:c>
+      <x:c r="K1" s="6" t="str">
+        <x:v>Resume After</x:v>
+      </x:c>
+      <x:c r="L1" s="6" t="str">
+        <x:v>Continues From</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="14" t="str">
@@ -13649,6 +13674,24 @@
       <x:c r="F2" s="14" t="str">
         <x:v>no</x:v>
       </x:c>
+      <x:c r="G2" s="14" t="str">
+        <x:v>segment</x:v>
+      </x:c>
+      <x:c r="H2" s="14" t="str">
+        <x:v>manual-review-order</x:v>
+      </x:c>
+      <x:c r="I2" s="14" t="str">
+        <x:v>2287</x:v>
+      </x:c>
+      <x:c r="J2" s="14" t="str">
+        <x:v>2312</x:v>
+      </x:c>
+      <x:c r="K2" s="14" t="str">
+        <x:v>2312</x:v>
+      </x:c>
+      <x:c r="L2" s="14" t="str">
+        <x:v>attackers-series-2026-09-04-partial-002</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="14" t="str">
@@ -13669,6 +13712,24 @@
       <x:c r="F3" s="14" t="str">
         <x:v>no</x:v>
       </x:c>
+      <x:c r="G3" s="14" t="str">
+        <x:v>segment</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="str">
+        <x:v>manual-review-order</x:v>
+      </x:c>
+      <x:c r="I3" s="14" t="str">
+        <x:v>940</x:v>
+      </x:c>
+      <x:c r="J3" s="14" t="str">
+        <x:v>944</x:v>
+      </x:c>
+      <x:c r="K3" s="14" t="str">
+        <x:v>944</x:v>
+      </x:c>
+      <x:c r="L3" s="14" t="str">
+        <x:v>ideapocket-series-2026-09-04-partial-001</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="14" t="str">
@@ -13689,6 +13750,24 @@
       <x:c r="F4" s="14" t="str">
         <x:v>no</x:v>
       </x:c>
+      <x:c r="G4" s="14" t="str">
+        <x:v>segment</x:v>
+      </x:c>
+      <x:c r="H4" s="14" t="str">
+        <x:v>manual-review-order</x:v>
+      </x:c>
+      <x:c r="I4" s="14" t="str">
+        <x:v>1565</x:v>
+      </x:c>
+      <x:c r="J4" s="14" t="str">
+        <x:v>1595</x:v>
+      </x:c>
+      <x:c r="K4" s="14" t="str">
+        <x:v>1595</x:v>
+      </x:c>
+      <x:c r="L4" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-002</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14" t="str">
@@ -13709,6 +13788,24 @@
       <x:c r="F5" s="14" t="str">
         <x:v>no</x:v>
       </x:c>
+      <x:c r="G5" s="14" t="str">
+        <x:v>segment</x:v>
+      </x:c>
+      <x:c r="H5" s="14" t="str">
+        <x:v>manual-review-order</x:v>
+      </x:c>
+      <x:c r="I5" s="14" t="str">
+        <x:v>3563</x:v>
+      </x:c>
+      <x:c r="J5" s="14" t="str">
+        <x:v>3567</x:v>
+      </x:c>
+      <x:c r="K5" s="14" t="str">
+        <x:v>3567</x:v>
+      </x:c>
+      <x:c r="L5" s="14" t="str">
+        <x:v>moodyz-series-2026-09-04-partial-001</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="14" t="str">
@@ -13728,6 +13825,24 @@
       </x:c>
       <x:c r="F6" s="14" t="str">
         <x:v>no</x:v>
+      </x:c>
+      <x:c r="G6" s="14" t="str">
+        <x:v>segment</x:v>
+      </x:c>
+      <x:c r="H6" s="14" t="str">
+        <x:v>manual-review-order</x:v>
+      </x:c>
+      <x:c r="I6" s="14" t="str">
+        <x:v>571</x:v>
+      </x:c>
+      <x:c r="J6" s="14" t="str">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="str">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="L6" s="14" t="str">
+        <x:v>s1-series-2026-09-04-partial-001</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -13774,4 +13889,350 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="10" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="10" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="10" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="48" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="14" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="60" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="14" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="14" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="6" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="B1" s="6" t="str">
+        <x:v>Maker</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="str">
+        <x:v>Snapshots</x:v>
+      </x:c>
+      <x:c r="D1" s="6" t="str">
+        <x:v>Entries</x:v>
+      </x:c>
+      <x:c r="E1" s="6" t="str">
+        <x:v>Unique IDs</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="str">
+        <x:v>Approved</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="str">
+        <x:v>Publish</x:v>
+      </x:c>
+      <x:c r="H1" s="6" t="str">
+        <x:v>Hold</x:v>
+      </x:c>
+      <x:c r="I1" s="6" t="str">
+        <x:v>Reject</x:v>
+      </x:c>
+      <x:c r="J1" s="6" t="str">
+        <x:v>Latest Snapshot</x:v>
+      </x:c>
+      <x:c r="K1" s="6" t="str">
+        <x:v>Window</x:v>
+      </x:c>
+      <x:c r="L1" s="6" t="str">
+        <x:v>Start ID</x:v>
+      </x:c>
+      <x:c r="M1" s="6" t="str">
+        <x:v>End ID</x:v>
+      </x:c>
+      <x:c r="N1" s="6" t="str">
+        <x:v>Resume After</x:v>
+      </x:c>
+      <x:c r="O1" s="6" t="str">
+        <x:v>Resume URL</x:v>
+      </x:c>
+      <x:c r="P1" s="6" t="str">
+        <x:v>Chain Depth</x:v>
+      </x:c>
+      <x:c r="Q1" s="6" t="str">
+        <x:v>Complete</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="14" t="str">
+        <x:v>attackers.series</x:v>
+      </x:c>
+      <x:c r="B2" s="14" t="str">
+        <x:v>ATTACKERS</x:v>
+      </x:c>
+      <x:c r="C2" s="14" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D2" s="14" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E2" s="14" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F2" s="14" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G2" s="14" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H2" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I2" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J2" s="14" t="str">
+        <x:v>attackers-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="K2" s="14" t="str">
+        <x:v>segment</x:v>
+      </x:c>
+      <x:c r="L2" s="14" t="str">
+        <x:v>2287</x:v>
+      </x:c>
+      <x:c r="M2" s="14" t="str">
+        <x:v>2312</x:v>
+      </x:c>
+      <x:c r="N2" s="14" t="str">
+        <x:v>2312</x:v>
+      </x:c>
+      <x:c r="O2" s="14" t="str">
+        <x:v>https://attackers.net/works/list/series/2312</x:v>
+      </x:c>
+      <x:c r="P2" s="14" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q2" s="14" t="str">
+        <x:v>no</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="14" t="str">
+        <x:v>ideapocket.series</x:v>
+      </x:c>
+      <x:c r="B3" s="14" t="str">
+        <x:v>アイデアポケット</x:v>
+      </x:c>
+      <x:c r="C3" s="14" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F3" s="14" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G3" s="14" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I3" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J3" s="14" t="str">
+        <x:v>ideapocket-series-2026-09-04-partial-002</x:v>
+      </x:c>
+      <x:c r="K3" s="14" t="str">
+        <x:v>segment</x:v>
+      </x:c>
+      <x:c r="L3" s="14" t="str">
+        <x:v>940</x:v>
+      </x:c>
+      <x:c r="M3" s="14" t="str">
+        <x:v>944</x:v>
+      </x:c>
+      <x:c r="N3" s="14" t="str">
+        <x:v>944</x:v>
+      </x:c>
+      <x:c r="O3" s="14" t="str">
+        <x:v>https://ideapocket.com/works/list/series/944</x:v>
+      </x:c>
+      <x:c r="P3" s="14" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q3" s="14" t="str">
+        <x:v>no</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="14" t="str">
+        <x:v>madonna.series</x:v>
+      </x:c>
+      <x:c r="B4" s="14" t="str">
+        <x:v>マドンナ</x:v>
+      </x:c>
+      <x:c r="C4" s="14" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D4" s="14" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E4" s="14" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F4" s="14" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G4" s="14" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I4" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J4" s="14" t="str">
+        <x:v>madonna-series-2026-09-04-partial-003</x:v>
+      </x:c>
+      <x:c r="K4" s="14" t="str">
+        <x:v>segment</x:v>
+      </x:c>
+      <x:c r="L4" s="14" t="str">
+        <x:v>1565</x:v>
+      </x:c>
+      <x:c r="M4" s="14" t="str">
+        <x:v>1595</x:v>
+      </x:c>
+      <x:c r="N4" s="14" t="str">
+        <x:v>1595</x:v>
+      </x:c>
+      <x:c r="O4" s="14" t="str">
+        <x:v>https://madonna-av.com/works/list/series/1595</x:v>
+      </x:c>
+      <x:c r="P4" s="14" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q4" s="14" t="str">
+        <x:v>no</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="14" t="str">
+        <x:v>moodyz.series</x:v>
+      </x:c>
+      <x:c r="B5" s="14" t="str">
+        <x:v>MOODYZ</x:v>
+      </x:c>
+      <x:c r="C5" s="14" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D5" s="14" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E5" s="14" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F5" s="14" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G5" s="14" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I5" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J5" s="14" t="str">
+        <x:v>moodyz-series-2026-09-04-partial-002</x:v>
+      </x:c>
+      <x:c r="K5" s="14" t="str">
+        <x:v>segment</x:v>
+      </x:c>
+      <x:c r="L5" s="14" t="str">
+        <x:v>3563</x:v>
+      </x:c>
+      <x:c r="M5" s="14" t="str">
+        <x:v>3567</x:v>
+      </x:c>
+      <x:c r="N5" s="14" t="str">
+        <x:v>3567</x:v>
+      </x:c>
+      <x:c r="O5" s="14" t="str">
+        <x:v>https://moodyz.com/works/list/series/3567</x:v>
+      </x:c>
+      <x:c r="P5" s="14" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q5" s="14" t="str">
+        <x:v>no</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="14" t="str">
+        <x:v>s1.series</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="str">
+        <x:v>エスワン</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E6" s="14" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F6" s="14" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G6" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I6" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J6" s="14" t="str">
+        <x:v>s1-series-2026-09-04-partial-002</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="str">
+        <x:v>segment</x:v>
+      </x:c>
+      <x:c r="L6" s="14" t="str">
+        <x:v>571</x:v>
+      </x:c>
+      <x:c r="M6" s="14" t="str">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="N6" s="14" t="str">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="O6" s="14" t="str">
+        <x:v>https://s1s1s1.com/works/list/series/575</x:v>
+      </x:c>
+      <x:c r="P6" s="14" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q6" s="14" t="str">
+        <x:v>no</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>